--- a/docs/downloads/2026-10-14/bursa-report-2026-10-14.xlsx
+++ b/docs/downloads/2026-10-14/bursa-report-2026-10-14.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-14" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-14'!$A$1:$M$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-14'!$A$1:$M$65</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -69,7 +69,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -84,6 +84,7 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -449,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -542,40 +543,31 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0138</t>
+          <t>0477</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ZETRIX</t>
+          <t>EcoSys (Malaysia) Berhad</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.065</v>
+        <v>0.75</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>6853800</v>
-      </c>
-      <c r="G2" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="H2" t="n">
-        <v>21.76</v>
-      </c>
+        <v>103903000</v>
+      </c>
+      <c r="G2" s="5" t="n"/>
       <c r="I2" s="6" t="inlineStr">
         <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="n">
-        <v>0.147</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>0.36</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="n"/>
+      <c r="K2" s="2" t="n"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" s="7" t="inlineStr"/>
     </row>
@@ -587,28 +579,28 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>0138</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>JAKS</t>
+          <t>ZETRIX</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>0</v>
+        <v>0.06</v>
+      </c>
+      <c r="E3" s="8" t="n">
+        <v>-0.07690000000000001</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>6435300</v>
+        <v>25343000</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="H3" t="n">
-        <v>45.73</v>
+        <v>21.31</v>
       </c>
       <c r="I3" s="6" t="inlineStr">
         <is>
@@ -616,10 +608,10 @@
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.164</v>
+        <v>0.147</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.136</v>
+        <v>0.36</v>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" s="7" t="inlineStr"/>
@@ -632,45 +624,2776 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.33</v>
+        <v>0.145</v>
       </c>
       <c r="E4" s="8" t="n">
-        <v>-0.0294</v>
+        <v>-0.0333</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>1983700</v>
+        <v>13989500</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.03</v>
+        <v>0.2</v>
       </c>
       <c r="H4" t="n">
-        <v>66.68000000000001</v>
-      </c>
-      <c r="I4" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.8</v>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.293</v>
+        <v>0.164</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.251</v>
+        <v>0.136</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" s="7" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>6963</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>VS</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>8885600</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H5" t="n">
+        <v>71.22</v>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>0.251</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" s="7" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>7113</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>TOPGLOV</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="E6" s="8" t="n">
+        <v>-0.0058</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>8493800</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H6" t="n">
+        <v>61.65</v>
+      </c>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>0.797</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>0.721</v>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" s="7" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>7020</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ASTEEL</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>7687500</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H7" t="n">
+        <v>60.79</v>
+      </c>
+      <c r="I7" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" s="7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>4456</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>DNEX</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>0.465</v>
+      </c>
+      <c r="E8" s="8" t="n">
+        <v>-0.0211</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>7409200</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H8" t="n">
+        <v>43.23</v>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>0.489</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>0.482</v>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" s="7" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>7079</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>TWL</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>7401500</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="H9" t="n">
+        <v>51.85</v>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" s="7" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>7215</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NIHSIN</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>5464800</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H10" t="n">
+        <v>70.36</v>
+      </c>
+      <c r="I10" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>0.366</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>0.256</v>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" s="7" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>5184</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CYPARK</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="E11" s="8" t="n">
+        <v>-0.1429</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>5072800</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="H11" t="n">
+        <v>41.14</v>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>0.766</v>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" s="7" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>7192</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>GIIB</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="E12" s="8" t="n">
+        <v>-0.008</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>4984400</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H12" t="n">
+        <v>66.34999999999999</v>
+      </c>
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>0.592</v>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>0.516</v>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" s="7" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>0270</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NATGATE</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>4317500</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H13" t="n">
+        <v>62.88</v>
+      </c>
+      <c r="I13" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>1.899</v>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>1.697</v>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" s="7" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>0457</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>PENTECH</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="E14" s="8" t="n">
+        <v>-0.0417</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>4154300</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="H14" t="n">
+        <v>51.1</v>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" s="7" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>0473</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>EVOCOM</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>4101600</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="n"/>
+      <c r="K15" s="2" t="n"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" s="7" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0215</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>SLVEST</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="E16" s="8" t="n">
+        <v>-0.0707</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>3597000</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="H16" t="n">
+        <v>47.45</v>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>3.983</v>
+      </c>
+      <c r="K16" s="2" t="n">
+        <v>3.505</v>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" s="7" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>3182</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>GENTING</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="E17" s="8" t="n">
+        <v>-0.0069</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>3052500</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H17" t="n">
+        <v>19.18</v>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="K17" s="2" t="n">
+        <v>1.985</v>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" s="7" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0024</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>JAG</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="E18" s="10" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>2642000</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="H18" t="n">
+        <v>61.86</v>
+      </c>
+      <c r="I18" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="K18" s="2" t="n">
+        <v>0.369</v>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" s="7" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>5336</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>CKI</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="E19" s="10" t="n">
+        <v>0.0137</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>2625500</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="H19" t="n">
+        <v>51.33</v>
+      </c>
+      <c r="I19" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="K19" s="2" t="n">
+        <v>0.387</v>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" s="7" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>5243</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>VELESTO</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="E20" s="10" t="n">
+        <v>0.0233</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>2538200</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H20" t="n">
+        <v>44.76</v>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="n">
+        <v>0.223</v>
+      </c>
+      <c r="K20" s="2" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" s="7" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>7106</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>SUPERMX</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="E21" s="8" t="n">
+        <v>-0.0115</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>2358800</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H21" t="n">
+        <v>57.59</v>
+      </c>
+      <c r="I21" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="n">
+        <v>0.414</v>
+      </c>
+      <c r="K21" s="2" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" s="7" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>0258</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>AGMO</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="E22" s="10" t="n">
+        <v>0.0351</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>2268800</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="H22" t="n">
+        <v>56</v>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="K22" s="2" t="n">
+        <v>0.301</v>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" s="7" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>0340</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NORTHERN</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="E23" s="8" t="n">
+        <v>-0.1102</v>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>2226800</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H23" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="n">
+        <v>1.099</v>
+      </c>
+      <c r="K23" s="2" t="n">
+        <v>0.859</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" s="7" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>0476</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>SLG</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>2131800</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I24" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="n"/>
+      <c r="K24" s="2" t="n"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" s="7" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>0223</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>SAMAIDEN</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="E25" s="8" t="n">
+        <v>-0.1042</v>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>2098100</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="H25" t="n">
+        <v>54.54</v>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="n">
+        <v>2.758</v>
+      </c>
+      <c r="K25" s="2" t="n">
+        <v>2.131</v>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" s="7" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>0318</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>ELRIDGE</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="E26" s="10" t="n">
+        <v>0.0054</v>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>2032800</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="H26" t="n">
+        <v>61.09</v>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="n">
+        <v>0.911</v>
+      </c>
+      <c r="K26" s="2" t="n">
+        <v>0.869</v>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" s="7" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>5168</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>HARTA</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>1867800</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H27" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="n">
+        <v>1.067</v>
+      </c>
+      <c r="K27" s="2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" s="7" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>0455</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>BUSCAP</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="E28" s="8" t="n">
+        <v>-0.0151</v>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>1783800</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="H28" t="n">
+        <v>80.73999999999999</v>
+      </c>
+      <c r="I28" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="n">
+        <v>0.744</v>
+      </c>
+      <c r="K28" s="2" t="n">
+        <v>0.522</v>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" s="7" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>5238</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>AAGB</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>0.445</v>
+      </c>
+      <c r="E29" s="8" t="n">
+        <v>-0.0111</v>
+      </c>
+      <c r="F29" s="4" t="n">
+        <v>1777200</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H29" t="n">
+        <v>23.61</v>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="n">
+        <v>0.524</v>
+      </c>
+      <c r="K29" s="2" t="n">
+        <v>0.713</v>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" s="7" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>0166</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>INARI</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="E30" s="8" t="n">
+        <v>-0.0148</v>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>1690300</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H30" t="n">
+        <v>53.02</v>
+      </c>
+      <c r="I30" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="n">
+        <v>2.655</v>
+      </c>
+      <c r="K30" s="2" t="n">
+        <v>2.532</v>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" s="7" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>5151</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>HEXTAR</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="4" t="n">
+        <v>1590100</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H31" t="n">
+        <v>50.46</v>
+      </c>
+      <c r="I31" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="n">
+        <v>0.774</v>
+      </c>
+      <c r="K31" s="2" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" s="7" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>5296</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>MRDIY</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E32" s="8" t="n">
+        <v>-0.0083</v>
+      </c>
+      <c r="F32" s="4" t="n">
+        <v>1551000</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H32" t="n">
+        <v>37.03</v>
+      </c>
+      <c r="I32" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="n">
+        <v>1.246</v>
+      </c>
+      <c r="K32" s="2" t="n">
+        <v>1.342</v>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" s="7" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>0339</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>CBHB</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="E33" s="8" t="n">
+        <v>-0.019</v>
+      </c>
+      <c r="F33" s="4" t="n">
+        <v>1332800</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H33" t="n">
+        <v>47.74</v>
+      </c>
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="n">
+        <v>1.068</v>
+      </c>
+      <c r="K33" s="2" t="n">
+        <v>0.9409999999999999</v>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" s="7" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>5161</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>JCY</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="4" t="n">
+        <v>1331900</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H34" t="n">
+        <v>52.1</v>
+      </c>
+      <c r="I34" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="K34" s="2" t="n">
+        <v>0.532</v>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" s="7" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>7121</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="4" t="n">
+        <v>1324900</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H35" t="n">
+        <v>58.27</v>
+      </c>
+      <c r="I35" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="n">
+        <v>0.8129999999999999</v>
+      </c>
+      <c r="K35" s="2" t="n">
+        <v>0.8080000000000001</v>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" s="7" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>0292</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>JTGROUP</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E36" s="8" t="n">
+        <v>-0.0385</v>
+      </c>
+      <c r="F36" s="4" t="n">
+        <v>1313800</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H36" t="n">
+        <v>54.24</v>
+      </c>
+      <c r="I36" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="n">
+        <v>1.256</v>
+      </c>
+      <c r="K36" s="2" t="n">
+        <v>1.041</v>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" s="7" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>4324</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>HENGYUAN</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="E37" s="10" t="n">
+        <v>0.0303</v>
+      </c>
+      <c r="F37" s="4" t="n">
+        <v>1246500</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H37" t="n">
+        <v>56.79</v>
+      </c>
+      <c r="I37" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="n">
+        <v>3.609</v>
+      </c>
+      <c r="K37" s="2" t="n">
+        <v>2.872</v>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" s="7" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>0196</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>QES</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="E38" s="8" t="n">
+        <v>-0.0167</v>
+      </c>
+      <c r="F38" s="4" t="n">
+        <v>1206200</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H38" t="n">
+        <v>49.07</v>
+      </c>
+      <c r="I38" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="n">
+        <v>0.599</v>
+      </c>
+      <c r="K38" s="2" t="n">
+        <v>0.584</v>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" s="7" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>0208</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>GREATEC</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="E39" s="8" t="n">
+        <v>-0.0116</v>
+      </c>
+      <c r="F39" s="4" t="n">
+        <v>1131000</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H39" t="n">
+        <v>45.19</v>
+      </c>
+      <c r="I39" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="n">
+        <v>2.626</v>
+      </c>
+      <c r="K39" s="2" t="n">
+        <v>2.596</v>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" s="7" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>0272</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>TTVHB</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="E40" s="8" t="n">
+        <v>-0.0204</v>
+      </c>
+      <c r="F40" s="4" t="n">
+        <v>1121500</v>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="H40" t="n">
+        <v>45.88</v>
+      </c>
+      <c r="I40" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K40" s="2" t="n">
+        <v>0.255</v>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" s="7" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>5311</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>CEB</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="E41" s="8" t="n">
+        <v>-0.0455</v>
+      </c>
+      <c r="F41" s="4" t="n">
+        <v>1109200</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H41" t="n">
+        <v>64.22</v>
+      </c>
+      <c r="I41" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="n">
+        <v>0.299</v>
+      </c>
+      <c r="K41" s="2" t="n">
+        <v>0.278</v>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" s="7" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>0376</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>IAB</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="E42" s="8" t="n">
+        <v>-0.0169</v>
+      </c>
+      <c r="F42" s="4" t="n">
+        <v>1049000</v>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="H42" t="n">
+        <v>39.49</v>
+      </c>
+      <c r="I42" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="K42" s="2" t="n">
+        <v>1.308</v>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" s="7" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>0275</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>OPPSTAR</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>0.665</v>
+      </c>
+      <c r="E43" s="8" t="n">
+        <v>-0.0075</v>
+      </c>
+      <c r="F43" s="4" t="n">
+        <v>1025800</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H43" t="n">
+        <v>45.49</v>
+      </c>
+      <c r="I43" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="K43" s="2" t="n">
+        <v>0.6860000000000001</v>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" s="7" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>5932</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>BPURI</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>0.215</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="4" t="n">
+        <v>1010900</v>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="H44" t="n">
+        <v>38.87</v>
+      </c>
+      <c r="I44" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="n">
+        <v>0.225</v>
+      </c>
+      <c r="K44" s="2" t="n">
+        <v>0.233</v>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" s="7" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>0262</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>SUNVIEW</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="E45" s="8" t="n">
+        <v>-0.03700000000000001</v>
+      </c>
+      <c r="F45" s="4" t="n">
+        <v>1008100</v>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H45" t="n">
+        <v>51.36</v>
+      </c>
+      <c r="I45" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="n">
+        <v>0.388</v>
+      </c>
+      <c r="K45" s="2" t="n">
+        <v>0.377</v>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" s="7" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>5327</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>MEGAFB</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" s="4" t="n">
+        <v>978700</v>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="H46" t="n">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I46" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="n">
+        <v>2.732</v>
+      </c>
+      <c r="K46" s="2" t="n">
+        <v>2.357</v>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" s="7" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>1295</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>PBBANK</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="E47" s="10" t="n">
+        <v>0.0128</v>
+      </c>
+      <c r="F47" s="4" t="n">
+        <v>977700</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H47" t="n">
+        <v>51.32</v>
+      </c>
+      <c r="I47" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="n">
+        <v>4.719</v>
+      </c>
+      <c r="K47" s="2" t="n">
+        <v>4.871</v>
+      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" s="7" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>0248</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>YEWLEE</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" s="4" t="n">
+        <v>973800</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H48" t="n">
+        <v>54.39</v>
+      </c>
+      <c r="I48" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="n">
+        <v>0.614</v>
+      </c>
+      <c r="K48" s="2" t="n">
+        <v>0.613</v>
+      </c>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" s="7" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>0372</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>CHEEDING</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="E49" s="8" t="n">
+        <v>-0.0172</v>
+      </c>
+      <c r="F49" s="4" t="n">
+        <v>945000</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H49" t="n">
+        <v>40.78</v>
+      </c>
+      <c r="I49" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="n">
+        <v>0.606</v>
+      </c>
+      <c r="K49" s="2" t="n">
+        <v>0.606</v>
+      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" s="7" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>0083</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>NOTION</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="E50" s="8" t="n">
+        <v>-0.0153</v>
+      </c>
+      <c r="F50" s="4" t="n">
+        <v>879800</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H50" t="n">
+        <v>47.44</v>
+      </c>
+      <c r="I50" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="n">
+        <v>0.669</v>
+      </c>
+      <c r="K50" s="2" t="n">
+        <v>0.616</v>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" s="7" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>0236</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>RAMSSOL</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="E51" s="8" t="n">
+        <v>-0.0064</v>
+      </c>
+      <c r="F51" s="4" t="n">
+        <v>828100</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H51" t="n">
+        <v>49.19</v>
+      </c>
+      <c r="I51" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="n">
+        <v>0.779</v>
+      </c>
+      <c r="K51" s="2" t="n">
+        <v>0.773</v>
+      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" s="7" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>CIMB</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>7.62</v>
+      </c>
+      <c r="E52" s="10" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="F52" s="4" t="n">
+        <v>824800</v>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H52" t="n">
+        <v>49.68</v>
+      </c>
+      <c r="I52" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="K52" s="2" t="n">
+        <v>7.719</v>
+      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" s="7" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>0233</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>PEKAT</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="E53" s="8" t="n">
+        <v>-0.0859</v>
+      </c>
+      <c r="F53" s="4" t="n">
+        <v>744400</v>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H53" t="n">
+        <v>54.56</v>
+      </c>
+      <c r="I53" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="n">
+        <v>2.668</v>
+      </c>
+      <c r="K53" s="2" t="n">
+        <v>2.205</v>
+      </c>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" s="7" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>1155</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>MAYBANK</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="E54" s="10" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="F54" s="4" t="n">
+        <v>721700</v>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H54" t="n">
+        <v>45.88</v>
+      </c>
+      <c r="I54" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="n">
+        <v>10.008</v>
+      </c>
+      <c r="K54" s="2" t="n">
+        <v>10.178</v>
+      </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" s="7" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>1015</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>AMBANK</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v>6.48</v>
+      </c>
+      <c r="E55" s="10" t="n">
+        <v>0.0335</v>
+      </c>
+      <c r="F55" s="4" t="n">
+        <v>721000</v>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H55" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="I55" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="n">
+        <v>6.432</v>
+      </c>
+      <c r="K55" s="2" t="n">
+        <v>6.806</v>
+      </c>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" s="7" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>0296</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>HEGROUP</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E56" s="8" t="n">
+        <v>-0.0566</v>
+      </c>
+      <c r="F56" s="4" t="n">
+        <v>714900</v>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H56" t="n">
+        <v>46.1</v>
+      </c>
+      <c r="I56" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="n">
+        <v>1.055</v>
+      </c>
+      <c r="K56" s="2" t="n">
+        <v>0.919</v>
+      </c>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" s="7" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>5398</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>GAMUDA</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="E57" s="8" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="F57" s="4" t="n">
+        <v>702000</v>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H57" t="n">
+        <v>52.47</v>
+      </c>
+      <c r="I57" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="n">
+        <v>4.935</v>
+      </c>
+      <c r="K57" s="2" t="n">
+        <v>4.698</v>
+      </c>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" s="7" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>0453</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>EIPOWER</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E58" s="8" t="n">
+        <v>-0.0217</v>
+      </c>
+      <c r="F58" s="4" t="n">
+        <v>693400</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H58" t="n">
+        <v>45.33</v>
+      </c>
+      <c r="I58" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="n">
+        <v>0.949</v>
+      </c>
+      <c r="K58" s="2" t="n">
+        <v>0.836</v>
+      </c>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" s="7" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>7579</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>AWC</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="E59" s="8" t="n">
+        <v>-0.0217</v>
+      </c>
+      <c r="F59" s="4" t="n">
+        <v>689300</v>
+      </c>
+      <c r="G59" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H59" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="I59" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="K59" s="2" t="n">
+        <v>0.543</v>
+      </c>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" s="7" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>5199</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>HIBISCS</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="E60" s="10" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="F60" s="4" t="n">
+        <v>684900</v>
+      </c>
+      <c r="G60" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H60" t="n">
+        <v>56.63</v>
+      </c>
+      <c r="I60" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="n">
+        <v>2.195</v>
+      </c>
+      <c r="K60" s="2" t="n">
+        <v>2.144</v>
+      </c>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" s="7" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>0390</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>ISF</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="E61" s="8" t="n">
+        <v>-0.0061</v>
+      </c>
+      <c r="F61" s="4" t="n">
+        <v>629400</v>
+      </c>
+      <c r="G61" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H61" t="n">
+        <v>50.94</v>
+      </c>
+      <c r="I61" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="n">
+        <v>0.827</v>
+      </c>
+      <c r="K61" s="2" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" s="7" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>4715</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>GENM</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="E62" s="10" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="F62" s="4" t="n">
+        <v>591700</v>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H62" t="n">
+        <v>23.74</v>
+      </c>
+      <c r="I62" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="n">
+        <v>1.441</v>
+      </c>
+      <c r="K62" s="2" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" s="7" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>5555</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>SUNMED</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" s="4" t="n">
+        <v>563000</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H63" t="n">
+        <v>55.72</v>
+      </c>
+      <c r="I63" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="n">
+        <v>2.112</v>
+      </c>
+      <c r="K63" s="2" t="n">
+        <v>2.094</v>
+      </c>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" s="7" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>0112</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>MIKROMB</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="E64" s="8" t="n">
+        <v>-0.0234</v>
+      </c>
+      <c r="F64" s="4" t="n">
+        <v>552500</v>
+      </c>
+      <c r="G64" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H64" t="n">
+        <v>46.09</v>
+      </c>
+      <c r="I64" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="n">
+        <v>0.637</v>
+      </c>
+      <c r="K64" s="2" t="n">
+        <v>0.617</v>
+      </c>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" s="7" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>0271</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>WELLS</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="E65" s="8" t="n">
+        <v>-0.0275</v>
+      </c>
+      <c r="F65" s="4" t="n">
+        <v>500200</v>
+      </c>
+      <c r="G65" s="5" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H65" t="n">
+        <v>32.04</v>
+      </c>
+      <c r="I65" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="n">
+        <v>0.573</v>
+      </c>
+      <c r="K65" s="2" t="n">
+        <v>0.616</v>
+      </c>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M4"/>
+  <autoFilter ref="A1:M65"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-14/bursa-report-2026-10-14.xlsx
+++ b/docs/downloads/2026-10-14/bursa-report-2026-10-14.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-14" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-14'!$A$1:$M$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-14'!$A$1:$M$122</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M99"/>
+  <dimension ref="A1:M122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -566,19 +566,19 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.0315</v>
+        <v>0.0225</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>1509900</v>
+        <v>1689100</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>0.37</v>
+        <v>0.42</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>58.75</v>
+        <v>57.36</v>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>2.198</v>
+        <v>2.196</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>2.145</v>
+        <v>2.144</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
@@ -598,7 +598,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>现价2.29高于50日均线2.145，RSI 58.75未超买，SAR转多信号技术面尚属可靠。</t>
+          <t>现价RM2.27高于50日均线RM2.144，RSI 57.36处中性偏多区间，未超买，SAR转多信号技术面尚属可靠。</t>
         </is>
       </c>
     </row>
@@ -619,13 +619,13 @@
         </is>
       </c>
       <c r="D3" s="9" t="n">
-        <v>0.75</v>
+        <v>0.775</v>
       </c>
       <c r="E3" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>114673800</v>
+        <v>124097500</v>
       </c>
       <c r="G3" s="12" t="n"/>
       <c r="I3" s="13" t="inlineStr">
@@ -646,28 +646,28 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>0138</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>JAKS</t>
+          <t>ZETRIX</t>
         </is>
       </c>
       <c r="D4" s="9" t="n">
-        <v>0.145</v>
+        <v>0.06</v>
       </c>
       <c r="E4" s="15" t="n">
-        <v>-0.0333</v>
+        <v>-0.07690000000000001</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>51805000</v>
+        <v>116608300</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>0.74</v>
+        <v>0.26</v>
       </c>
       <c r="H4" t="n">
-        <v>43.8</v>
+        <v>21.31</v>
       </c>
       <c r="I4" s="13" t="inlineStr">
         <is>
@@ -675,10 +675,10 @@
         </is>
       </c>
       <c r="J4" s="9" t="n">
-        <v>0.164</v>
+        <v>0.147</v>
       </c>
       <c r="K4" s="9" t="n">
-        <v>0.136</v>
+        <v>0.36</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" s="14" t="inlineStr"/>
@@ -691,28 +691,28 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0138</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ZETRIX</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D5" s="9" t="n">
-        <v>0.065</v>
-      </c>
-      <c r="E5" s="10" t="n">
-        <v>0</v>
+        <v>0.145</v>
+      </c>
+      <c r="E5" s="15" t="n">
+        <v>-0.0333</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>42594300</v>
+        <v>53229600</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>0.1</v>
+        <v>0.76</v>
       </c>
       <c r="H5" t="n">
-        <v>21.76</v>
+        <v>43.8</v>
       </c>
       <c r="I5" s="13" t="inlineStr">
         <is>
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="J5" s="9" t="n">
-        <v>0.147</v>
+        <v>0.164</v>
       </c>
       <c r="K5" s="9" t="n">
-        <v>0.36</v>
+        <v>0.136</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" s="14" t="inlineStr"/>
@@ -736,28 +736,28 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D6" s="9" t="n">
-        <v>0.87</v>
+        <v>0.405</v>
       </c>
       <c r="E6" s="16" t="n">
-        <v>0.0175</v>
+        <v>0.0385</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>20063500</v>
+        <v>26592400</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>0.31</v>
+        <v>0.72</v>
       </c>
       <c r="H6" t="n">
-        <v>64.34</v>
+        <v>73.73999999999999</v>
       </c>
       <c r="I6" s="17" t="inlineStr">
         <is>
@@ -765,10 +765,10 @@
         </is>
       </c>
       <c r="J6" s="9" t="n">
-        <v>0.799</v>
+        <v>0.367</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>0.721</v>
+        <v>0.256</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="14" t="inlineStr"/>
@@ -781,28 +781,28 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.335</v>
-      </c>
-      <c r="E7" s="15" t="n">
-        <v>-0.0147</v>
+        <v>0.87</v>
+      </c>
+      <c r="E7" s="16" t="n">
+        <v>0.0175</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>14552200</v>
+        <v>22816300</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>0.2</v>
+        <v>0.35</v>
       </c>
       <c r="H7" t="n">
-        <v>68.87</v>
+        <v>64.34</v>
       </c>
       <c r="I7" s="17" t="inlineStr">
         <is>
@@ -810,10 +810,10 @@
         </is>
       </c>
       <c r="J7" s="9" t="n">
-        <v>0.293</v>
+        <v>0.799</v>
       </c>
       <c r="K7" s="9" t="n">
-        <v>0.251</v>
+        <v>0.721</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="14" t="inlineStr"/>
@@ -826,39 +826,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>0.475</v>
-      </c>
-      <c r="E8" s="10" t="n">
-        <v>0</v>
+        <v>0.335</v>
+      </c>
+      <c r="E8" s="15" t="n">
+        <v>-0.0147</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>11885600</v>
+        <v>18021200</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>0.34</v>
+        <v>0.25</v>
       </c>
       <c r="H8" t="n">
-        <v>46.03</v>
-      </c>
-      <c r="I8" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>68.87</v>
+      </c>
+      <c r="I8" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J8" s="9" t="n">
-        <v>0.49</v>
+        <v>0.293</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>0.482</v>
+        <v>0.251</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="14" t="inlineStr"/>
@@ -886,10 +886,10 @@
         <v>0.1</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>11423100</v>
+        <v>13045800</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>4.16</v>
+        <v>4.76</v>
       </c>
       <c r="H9" t="n">
         <v>60.79</v>
@@ -916,28 +916,28 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>1.43</v>
+        <v>0.47</v>
       </c>
       <c r="E10" s="15" t="n">
-        <v>-0.0069</v>
+        <v>-0.0105</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>8747700</v>
+        <v>12329000</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>0.96</v>
+        <v>0.35</v>
       </c>
       <c r="H10" t="n">
-        <v>19.18</v>
+        <v>44.59</v>
       </c>
       <c r="I10" s="13" t="inlineStr">
         <is>
@@ -945,10 +945,10 @@
         </is>
       </c>
       <c r="J10" s="9" t="n">
-        <v>1.78</v>
+        <v>0.489</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>1.985</v>
+        <v>0.482</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="14" t="inlineStr"/>
@@ -961,28 +961,28 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="E11" s="16" t="n">
-        <v>0.0194</v>
+        <v>0.62</v>
+      </c>
+      <c r="E11" s="15" t="n">
+        <v>-0.008</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>8120800</v>
+        <v>11045900</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>0.27</v>
+        <v>0.44</v>
       </c>
       <c r="H11" t="n">
-        <v>64.45999999999999</v>
+        <v>66.34999999999999</v>
       </c>
       <c r="I11" s="17" t="inlineStr">
         <is>
@@ -990,10 +990,10 @@
         </is>
       </c>
       <c r="J11" s="9" t="n">
-        <v>1.903</v>
+        <v>0.592</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>1.698</v>
+        <v>0.516</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="14" t="inlineStr"/>
@@ -1006,39 +1006,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="E12" s="15" t="n">
-        <v>-0.008</v>
+        <v>1.44</v>
+      </c>
+      <c r="E12" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>7704400</v>
+        <v>10468900</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>0.3</v>
+        <v>1.15</v>
       </c>
       <c r="H12" t="n">
-        <v>66.34999999999999</v>
-      </c>
-      <c r="I12" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>19.46</v>
+      </c>
+      <c r="I12" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J12" s="9" t="n">
-        <v>0.592</v>
+        <v>1.781</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>0.516</v>
+        <v>1.985</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="14" t="inlineStr"/>
@@ -1051,39 +1051,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="E13" s="10" t="n">
-        <v>0</v>
+        <v>3.9</v>
+      </c>
+      <c r="E13" s="15" t="n">
+        <v>-0.0488</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>7550300</v>
+        <v>9529900</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>0.2</v>
+        <v>1.08</v>
       </c>
       <c r="H13" t="n">
-        <v>70.36</v>
-      </c>
-      <c r="I13" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.3</v>
+      </c>
+      <c r="I13" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J13" s="9" t="n">
-        <v>0.366</v>
+        <v>3.991</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>0.256</v>
+        <v>3.507</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="14" t="inlineStr"/>
@@ -1096,39 +1096,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>7079</t>
+          <t>0095</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>TWL</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="E14" s="16" t="n">
-        <v>0.25</v>
+        <v>0.155</v>
+      </c>
+      <c r="E14" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>7414200</v>
+        <v>9080000</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>0.42</v>
+        <v>0.27</v>
       </c>
       <c r="H14" t="n">
-        <v>51.85</v>
-      </c>
-      <c r="I14" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.61</v>
+      </c>
+      <c r="I14" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J14" s="9" t="n">
-        <v>0.024</v>
+        <v>0.155</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>0.025</v>
+        <v>0.157</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="14" t="inlineStr"/>
@@ -1141,39 +1141,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="E15" s="15" t="n">
-        <v>-0.118</v>
+        <v>2.08</v>
+      </c>
+      <c r="E15" s="16" t="n">
+        <v>0.0097</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>7241600</v>
+        <v>8932700</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>0.51</v>
+        <v>0.29</v>
       </c>
       <c r="H15" t="n">
-        <v>43.31</v>
-      </c>
-      <c r="I15" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.69</v>
+      </c>
+      <c r="I15" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J15" s="9" t="n">
-        <v>0.768</v>
+        <v>1.901</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>0.72</v>
+        <v>1.697</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="14" t="inlineStr"/>
@@ -1186,28 +1186,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>3.87</v>
+        <v>0.73</v>
       </c>
       <c r="E16" s="15" t="n">
-        <v>-0.0561</v>
+        <v>-0.09320000000000001</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>5806200</v>
+        <v>8586700</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>0.66</v>
+        <v>0.6</v>
       </c>
       <c r="H16" t="n">
-        <v>49.31</v>
+        <v>45.71</v>
       </c>
       <c r="I16" s="13" t="inlineStr">
         <is>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="J16" s="9" t="n">
-        <v>3.988</v>
+        <v>0.77</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>3.507</v>
+        <v>0.72</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="14" t="inlineStr"/>
@@ -1231,28 +1231,28 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>7079</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>TWL</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="E17" s="15" t="n">
-        <v>-0.0278</v>
+        <v>0.025</v>
+      </c>
+      <c r="E17" s="16" t="n">
+        <v>0.25</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>5373300</v>
+        <v>7414600</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>0.63</v>
+        <v>0.42</v>
       </c>
       <c r="H17" t="n">
-        <v>53.1</v>
+        <v>51.85</v>
       </c>
       <c r="I17" s="13" t="inlineStr">
         <is>
@@ -1260,10 +1260,10 @@
         </is>
       </c>
       <c r="J17" s="9" t="n">
-        <v>0.348</v>
+        <v>0.024</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>0.33</v>
+        <v>0.025</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="14" t="inlineStr"/>
@@ -1276,33 +1276,40 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0473</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>EVOCOM</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E18" s="10" t="n">
-        <v>0</v>
+        <v>0.375</v>
+      </c>
+      <c r="E18" s="16" t="n">
+        <v>0.0135</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>4767200</v>
+        <v>6325400</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="I18" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J18" s="9" t="n"/>
-      <c r="K18" s="9" t="n"/>
+        <v>0.89</v>
+      </c>
+      <c r="H18" t="n">
+        <v>57.68</v>
+      </c>
+      <c r="I18" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J18" s="9" t="n">
+        <v>0.369</v>
+      </c>
+      <c r="K18" s="9" t="n">
+        <v>0.369</v>
+      </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="14" t="inlineStr"/>
     </row>
@@ -1314,28 +1321,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>0.375</v>
+        <v>0.445</v>
       </c>
       <c r="E19" s="16" t="n">
-        <v>0.0135</v>
+        <v>0.023</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>4298600</v>
+        <v>5984400</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>0.61</v>
+        <v>0.29</v>
       </c>
       <c r="H19" t="n">
-        <v>57.68</v>
+        <v>61.25</v>
       </c>
       <c r="I19" s="17" t="inlineStr">
         <is>
@@ -1343,10 +1350,10 @@
         </is>
       </c>
       <c r="J19" s="9" t="n">
-        <v>0.369</v>
+        <v>0.416</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>0.369</v>
+        <v>0.357</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="14" t="inlineStr"/>
@@ -1359,39 +1366,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>0.445</v>
-      </c>
-      <c r="E20" s="16" t="n">
-        <v>0.023</v>
+        <v>0.355</v>
+      </c>
+      <c r="E20" s="15" t="n">
+        <v>-0.0139</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>4199700</v>
+        <v>5784000</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>0.21</v>
+        <v>0.68</v>
       </c>
       <c r="H20" t="n">
-        <v>61.25</v>
-      </c>
-      <c r="I20" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>55.26</v>
+      </c>
+      <c r="I20" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J20" s="9" t="n">
-        <v>0.416</v>
+        <v>0.349</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>0.357</v>
+        <v>0.33</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="14" t="inlineStr"/>
@@ -1404,33 +1411,40 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0476</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>SLG</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>0.25</v>
+        <v>0.18</v>
       </c>
       <c r="E21" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>4188800</v>
+        <v>5432300</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="I21" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J21" s="9" t="n"/>
-      <c r="K21" s="9" t="n"/>
+        <v>0.23</v>
+      </c>
+      <c r="H21" t="n">
+        <v>42.98</v>
+      </c>
+      <c r="I21" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J21" s="9" t="n">
+        <v>0.193</v>
+      </c>
+      <c r="K21" s="9" t="n">
+        <v>0.185</v>
+      </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="14" t="inlineStr"/>
     </row>
@@ -1442,39 +1456,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="E22" s="15" t="n">
-        <v>-0.08470000000000001</v>
+        <v>0.775</v>
+      </c>
+      <c r="E22" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>3973000</v>
+        <v>5013500</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>0.51</v>
+        <v>0.33</v>
       </c>
       <c r="H22" t="n">
-        <v>52.17</v>
-      </c>
-      <c r="I22" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.46</v>
+      </c>
+      <c r="I22" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J22" s="9" t="n">
-        <v>1.102</v>
+        <v>0.774</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>0.86</v>
+        <v>0.775</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="14" t="inlineStr"/>
@@ -1487,40 +1501,33 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>0473</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>EVOCOM</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>0.945</v>
-      </c>
-      <c r="E23" s="16" t="n">
-        <v>0.0161</v>
+        <v>0.1</v>
+      </c>
+      <c r="E23" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>3624300</v>
+        <v>4901400</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="H23" t="n">
-        <v>63.48</v>
+        <v>0.35</v>
       </c>
       <c r="I23" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J23" s="9" t="n">
-        <v>0.912</v>
-      </c>
-      <c r="K23" s="9" t="n">
-        <v>0.869</v>
-      </c>
+      <c r="J23" s="9" t="n"/>
+      <c r="K23" s="9" t="n"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="14" t="inlineStr"/>
     </row>
@@ -1532,40 +1539,33 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>0476</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>SLG</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="E24" s="15" t="n">
-        <v>-0.0037</v>
+        <v>0.25</v>
+      </c>
+      <c r="E24" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>3226500</v>
+        <v>4374500</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="H24" t="n">
-        <v>55.14</v>
+        <v>0.15</v>
       </c>
       <c r="I24" s="17" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J24" s="9" t="n">
-        <v>2.658</v>
-      </c>
-      <c r="K24" s="9" t="n">
-        <v>2.533</v>
-      </c>
+      <c r="J24" s="9" t="n"/>
+      <c r="K24" s="9" t="n"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="14" t="inlineStr"/>
     </row>
@@ -1577,39 +1577,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="E25" s="16" t="n">
-        <v>0.0172</v>
+        <v>0.41</v>
+      </c>
+      <c r="E25" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>3160900</v>
+        <v>4330900</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>0.16</v>
+        <v>2.62</v>
       </c>
       <c r="H25" t="n">
-        <v>53.84</v>
-      </c>
-      <c r="I25" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.24</v>
+      </c>
+      <c r="I25" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J25" s="9" t="n">
-        <v>0.584</v>
+        <v>0.419</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>0.532</v>
+        <v>0.437</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="14" t="inlineStr"/>
@@ -1622,39 +1622,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="E26" s="15" t="n">
-        <v>-0.07490000000000001</v>
+        <v>7.66</v>
+      </c>
+      <c r="E26" s="16" t="n">
+        <v>0.0213</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>3106500</v>
+        <v>4293000</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>0.71</v>
+        <v>0.29</v>
       </c>
       <c r="H26" t="n">
-        <v>58.08</v>
-      </c>
-      <c r="I26" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.2</v>
+      </c>
+      <c r="I26" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J26" s="9" t="n">
-        <v>2.767</v>
+        <v>7.603</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>2.133</v>
+        <v>7.72</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="14" t="inlineStr"/>
@@ -1667,39 +1667,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>0.175</v>
+        <v>2.68</v>
       </c>
       <c r="E27" s="15" t="n">
-        <v>-0.0278</v>
+        <v>-0.0111</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>3005200</v>
+        <v>4216700</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>0.13</v>
+        <v>0.23</v>
       </c>
       <c r="H27" t="n">
-        <v>40.7</v>
-      </c>
-      <c r="I27" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.71</v>
+      </c>
+      <c r="I27" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J27" s="9" t="n">
-        <v>0.192</v>
+        <v>2.656</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>0.185</v>
+        <v>2.533</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="14" t="inlineStr"/>
@@ -1712,39 +1712,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>0340</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>NORTHERN</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E28" s="10" t="n">
-        <v>0</v>
+        <v>1.09</v>
+      </c>
+      <c r="E28" s="15" t="n">
+        <v>-0.07629999999999999</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>2885100</v>
+        <v>4188700</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0.19</v>
+        <v>0.53</v>
       </c>
       <c r="H28" t="n">
-        <v>50.46</v>
-      </c>
-      <c r="I28" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.9</v>
+      </c>
+      <c r="I28" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J28" s="9" t="n">
-        <v>0.774</v>
+        <v>1.103</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>0.775</v>
+        <v>0.86</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="14" t="inlineStr"/>
@@ -1757,39 +1757,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>0223</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>SAMAIDEN</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>7.65</v>
-      </c>
-      <c r="E29" s="16" t="n">
-        <v>0.02</v>
+        <v>2.82</v>
+      </c>
+      <c r="E29" s="15" t="n">
+        <v>-0.0814</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>2837500</v>
+        <v>4018200</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0.19</v>
+        <v>0.92</v>
       </c>
       <c r="H29" t="n">
-        <v>50.83</v>
-      </c>
-      <c r="I29" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>57.25</v>
+      </c>
+      <c r="I29" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J29" s="9" t="n">
-        <v>7.602</v>
+        <v>2.765</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>7.72</v>
+        <v>2.132</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="14" t="inlineStr"/>
@@ -1802,39 +1802,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>VELESTO</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>0.225</v>
+        <v>0.585</v>
       </c>
       <c r="E30" s="16" t="n">
-        <v>0.04650000000000001</v>
+        <v>0.0086</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>2715200</v>
+        <v>3798600</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>0.13</v>
+        <v>0.19</v>
       </c>
       <c r="H30" t="n">
-        <v>48.41</v>
-      </c>
-      <c r="I30" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.99</v>
+      </c>
+      <c r="I30" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J30" s="9" t="n">
-        <v>0.224</v>
+        <v>0.583</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>0.24</v>
+        <v>0.532</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="14" t="inlineStr"/>
@@ -1847,39 +1847,39 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>5336</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CKI</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>0.37</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E31" s="16" t="n">
-        <v>0.0137</v>
+        <v>0.0108</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>2678600</v>
+        <v>3672900</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>1.74</v>
+        <v>0.67</v>
       </c>
       <c r="H31" t="n">
-        <v>51.33</v>
-      </c>
-      <c r="I31" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>62.32</v>
+      </c>
+      <c r="I31" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J31" s="9" t="n">
-        <v>0.364</v>
+        <v>0.912</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>0.387</v>
+        <v>0.869</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="14" t="inlineStr"/>
@@ -1892,39 +1892,39 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0258</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>AGMO</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="E32" s="16" t="n">
-        <v>0.0175</v>
+        <v>0.315</v>
+      </c>
+      <c r="E32" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>2641600</v>
+        <v>3627000</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>3.52</v>
+        <v>0.19</v>
       </c>
       <c r="H32" t="n">
-        <v>53.95</v>
-      </c>
-      <c r="I32" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.97</v>
+      </c>
+      <c r="I32" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J32" s="9" t="n">
-        <v>0.28</v>
+        <v>0.308</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>0.301</v>
+        <v>0.298</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="14" t="inlineStr"/>
@@ -1937,28 +1937,28 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="E33" s="16" t="n">
-        <v>0.009399999999999999</v>
+        <v>1.91</v>
+      </c>
+      <c r="E33" s="15" t="n">
+        <v>-0.0052</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>2486200</v>
+        <v>3591200</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>0.25</v>
+        <v>0.61</v>
       </c>
       <c r="H33" t="n">
-        <v>50.92</v>
+        <v>45.84</v>
       </c>
       <c r="I33" s="13" t="inlineStr">
         <is>
@@ -1966,10 +1966,10 @@
         </is>
       </c>
       <c r="J33" s="9" t="n">
-        <v>1.068</v>
+        <v>1.924</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>1.04</v>
+        <v>1.953</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="14" t="inlineStr"/>
@@ -1982,39 +1982,39 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>0.445</v>
+        <v>0.32</v>
       </c>
       <c r="E34" s="15" t="n">
-        <v>-0.0111</v>
+        <v>-0.0303</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>2474500</v>
+        <v>3417200</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>0.06</v>
+        <v>0.47</v>
       </c>
       <c r="H34" t="n">
-        <v>23.61</v>
-      </c>
-      <c r="I34" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>68.45</v>
+      </c>
+      <c r="I34" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J34" s="9" t="n">
-        <v>0.524</v>
+        <v>0.299</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>0.713</v>
+        <v>0.278</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="14" t="inlineStr"/>
@@ -2027,39 +2027,39 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>0258</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>AGMO</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="E35" s="10" t="n">
-        <v>0</v>
+        <v>0.295</v>
+      </c>
+      <c r="E35" s="16" t="n">
+        <v>0.0351</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>2392100</v>
+        <v>3181300</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0.14</v>
+        <v>4.24</v>
       </c>
       <c r="H35" t="n">
-        <v>58.27</v>
-      </c>
-      <c r="I35" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>56</v>
+      </c>
+      <c r="I35" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J35" s="9" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.28</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.301</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="14" t="inlineStr"/>
@@ -2072,28 +2072,28 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="E36" s="15" t="n">
-        <v>-0.0303</v>
+        <v>0.82</v>
+      </c>
+      <c r="E36" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>2220600</v>
+        <v>2892800</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>0.31</v>
+        <v>0.17</v>
       </c>
       <c r="H36" t="n">
-        <v>68.45</v>
+        <v>58.27</v>
       </c>
       <c r="I36" s="17" t="inlineStr">
         <is>
@@ -2101,10 +2101,10 @@
         </is>
       </c>
       <c r="J36" s="9" t="n">
-        <v>0.299</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>0.278</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="14" t="inlineStr"/>
@@ -2117,28 +2117,28 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>7243</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>MAGMA</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="E37" s="10" t="n">
-        <v>0</v>
+        <v>0.285</v>
+      </c>
+      <c r="E37" s="16" t="n">
+        <v>0.0556</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>2115300</v>
+        <v>2884700</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>1.28</v>
+        <v>4.18</v>
       </c>
       <c r="H37" t="n">
-        <v>39.24</v>
+        <v>53.17</v>
       </c>
       <c r="I37" s="13" t="inlineStr">
         <is>
@@ -2146,10 +2146,10 @@
         </is>
       </c>
       <c r="J37" s="9" t="n">
-        <v>0.419</v>
+        <v>0.281</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>0.437</v>
+        <v>0.285</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="14" t="inlineStr"/>
@@ -2162,28 +2162,28 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>4.79</v>
-      </c>
-      <c r="E38" s="16" t="n">
-        <v>0.0191</v>
+        <v>0.405</v>
+      </c>
+      <c r="E38" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>2064500</v>
+        <v>2834100</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>0.12</v>
+        <v>0.23</v>
       </c>
       <c r="H38" t="n">
-        <v>53.81</v>
+        <v>56.05</v>
       </c>
       <c r="I38" s="17" t="inlineStr">
         <is>
@@ -2191,10 +2191,10 @@
         </is>
       </c>
       <c r="J38" s="9" t="n">
-        <v>4.722</v>
+        <v>0.39</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>4.871</v>
+        <v>0.377</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="14" t="inlineStr"/>
@@ -2207,39 +2207,39 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>5336</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>CKI</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>0.66</v>
+        <v>0.37</v>
       </c>
       <c r="E39" s="16" t="n">
-        <v>0.0076</v>
+        <v>0.0137</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>2025300</v>
+        <v>2833700</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>0.23</v>
+        <v>1.84</v>
       </c>
       <c r="H39" t="n">
-        <v>50.26</v>
-      </c>
-      <c r="I39" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.33</v>
+      </c>
+      <c r="I39" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J39" s="9" t="n">
-        <v>0.67</v>
+        <v>0.364</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>0.617</v>
+        <v>0.387</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="14" t="inlineStr"/>
@@ -2252,39 +2252,39 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>VELESTO</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="E40" s="15" t="n">
-        <v>-0.005</v>
+        <v>0.225</v>
+      </c>
+      <c r="E40" s="16" t="n">
+        <v>0.04650000000000001</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>1957300</v>
+        <v>2827400</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="H40" t="n">
-        <v>82.36</v>
-      </c>
-      <c r="I40" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.41</v>
+      </c>
+      <c r="I40" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J40" s="9" t="n">
-        <v>0.745</v>
+        <v>0.224</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>0.522</v>
+        <v>0.24</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="14" t="inlineStr"/>
@@ -2297,28 +2297,28 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="E41" s="10" t="n">
-        <v>0</v>
+        <v>4.92</v>
+      </c>
+      <c r="E41" s="15" t="n">
+        <v>-0.0061</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>1906200</v>
+        <v>2744600</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>0.23</v>
+        <v>0.11</v>
       </c>
       <c r="H41" t="n">
-        <v>50.62</v>
+        <v>51.92</v>
       </c>
       <c r="I41" s="13" t="inlineStr">
         <is>
@@ -2326,10 +2326,10 @@
         </is>
       </c>
       <c r="J41" s="9" t="n">
-        <v>1.07</v>
+        <v>4.934</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>0.9409999999999999</v>
+        <v>4.698</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="14" t="inlineStr"/>
@@ -2342,39 +2342,39 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>0.67</v>
+        <v>2.14</v>
       </c>
       <c r="E42" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>1870000</v>
+        <v>2703400</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>0.21</v>
+        <v>0.13</v>
       </c>
       <c r="H42" t="n">
-        <v>46.36</v>
-      </c>
-      <c r="I42" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.72</v>
+      </c>
+      <c r="I42" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J42" s="9" t="n">
-        <v>0.6899999999999999</v>
+        <v>2.112</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>0.6860000000000001</v>
+        <v>2.094</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="14" t="inlineStr"/>
@@ -2387,28 +2387,28 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="E43" s="15" t="n">
-        <v>-0.0083</v>
+        <v>1.07</v>
+      </c>
+      <c r="E43" s="16" t="n">
+        <v>0.009399999999999999</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>1863200</v>
+        <v>2669200</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>0.23</v>
+        <v>0.27</v>
       </c>
       <c r="H43" t="n">
-        <v>37.03</v>
+        <v>50.92</v>
       </c>
       <c r="I43" s="13" t="inlineStr">
         <is>
@@ -2416,10 +2416,10 @@
         </is>
       </c>
       <c r="J43" s="9" t="n">
-        <v>1.246</v>
+        <v>1.068</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>1.342</v>
+        <v>1.04</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="14" t="inlineStr"/>
@@ -2432,39 +2432,39 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D44" s="9" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="E44" s="15" t="n">
-        <v>-0.0233</v>
+        <v>4.79</v>
+      </c>
+      <c r="E44" s="16" t="n">
+        <v>0.0191</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>1833400</v>
+        <v>2644700</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.15</v>
       </c>
       <c r="H44" t="n">
-        <v>28.68</v>
-      </c>
-      <c r="I44" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.81</v>
+      </c>
+      <c r="I44" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J44" s="9" t="n">
-        <v>0.24</v>
+        <v>4.722</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>0.295</v>
+        <v>4.871</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="14" t="inlineStr"/>
@@ -2477,28 +2477,28 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>1.25</v>
+        <v>0.445</v>
       </c>
       <c r="E45" s="15" t="n">
-        <v>-0.0385</v>
+        <v>-0.0111</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>1821800</v>
+        <v>2630600</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H45" t="n">
-        <v>54.24</v>
+        <v>23.61</v>
       </c>
       <c r="I45" s="13" t="inlineStr">
         <is>
@@ -2506,10 +2506,10 @@
         </is>
       </c>
       <c r="J45" s="9" t="n">
-        <v>1.256</v>
+        <v>0.524</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>1.041</v>
+        <v>0.713</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="14" t="inlineStr"/>
@@ -2522,28 +2522,28 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>3.71</v>
+        <v>0.68</v>
       </c>
       <c r="E46" s="16" t="n">
-        <v>0.022</v>
+        <v>0.0149</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>1819100</v>
+        <v>2607800</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0.19</v>
+        <v>0.29</v>
       </c>
       <c r="H46" t="n">
-        <v>56.15</v>
+        <v>48.33</v>
       </c>
       <c r="I46" s="13" t="inlineStr">
         <is>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="J46" s="9" t="n">
-        <v>3.606</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>2.871</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="14" t="inlineStr"/>
@@ -2567,28 +2567,28 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>1.9</v>
+        <v>0.31</v>
       </c>
       <c r="E47" s="15" t="n">
-        <v>-0.0104</v>
+        <v>-0.0159</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>1806800</v>
+        <v>2570300</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>0.31</v>
+        <v>0.51</v>
       </c>
       <c r="H47" t="n">
-        <v>44.29</v>
+        <v>24.94</v>
       </c>
       <c r="I47" s="13" t="inlineStr">
         <is>
@@ -2596,10 +2596,10 @@
         </is>
       </c>
       <c r="J47" s="9" t="n">
-        <v>1.923</v>
+        <v>0.35</v>
       </c>
       <c r="K47" s="9" t="n">
-        <v>1.953</v>
+        <v>0.379</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="14" t="inlineStr"/>
@@ -2612,39 +2612,39 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D48" s="9" t="n">
-        <v>1.26</v>
+        <v>1.03</v>
       </c>
       <c r="E48" s="16" t="n">
-        <v>0.008</v>
+        <v>0.0352</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>1732300</v>
+        <v>2517900</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>0.17</v>
+        <v>0.71</v>
       </c>
       <c r="H48" t="n">
-        <v>41.98</v>
-      </c>
-      <c r="I48" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>84.3</v>
+      </c>
+      <c r="I48" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J48" s="9" t="n">
-        <v>1.31</v>
+        <v>0.749</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>1.311</v>
+        <v>0.523</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="14" t="inlineStr"/>
@@ -2657,28 +2657,28 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0471</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>PIONEER</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="E49" s="16" t="n">
-        <v>0.0476</v>
+        <v>0.865</v>
+      </c>
+      <c r="E49" s="15" t="n">
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>1682900</v>
+        <v>2513500</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>0.18</v>
+        <v>0.13</v>
       </c>
       <c r="H49" t="n">
-        <v>58.79</v>
+        <v>46.29</v>
       </c>
       <c r="I49" s="17" t="inlineStr">
         <is>
@@ -2686,9 +2686,11 @@
         </is>
       </c>
       <c r="J49" s="9" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="K49" s="9" t="n"/>
+        <v>0.868</v>
+      </c>
+      <c r="K49" s="9" t="n">
+        <v>0.869</v>
+      </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="14" t="inlineStr"/>
     </row>
@@ -2700,39 +2702,39 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D50" s="9" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="E50" s="10" t="n">
-        <v>0</v>
+        <v>2.1</v>
+      </c>
+      <c r="E50" s="16" t="n">
+        <v>0.009599999999999999</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>1625600</v>
+        <v>2436300</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="H50" t="n">
-        <v>54.39</v>
-      </c>
-      <c r="I50" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.77</v>
+      </c>
+      <c r="I50" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J50" s="9" t="n">
-        <v>0.614</v>
+        <v>2.192</v>
       </c>
       <c r="K50" s="9" t="n">
-        <v>0.613</v>
+        <v>2.225</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="14" t="inlineStr"/>
@@ -2745,39 +2747,39 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0272</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>TTVHB</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>0.245</v>
+        <v>0.62</v>
       </c>
       <c r="E51" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>1583500</v>
+        <v>2431400</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>0.68</v>
+        <v>0.23</v>
       </c>
       <c r="H51" t="n">
-        <v>47.66</v>
-      </c>
-      <c r="I51" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.39</v>
+      </c>
+      <c r="I51" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J51" s="9" t="n">
-        <v>0.25</v>
+        <v>0.614</v>
       </c>
       <c r="K51" s="9" t="n">
-        <v>0.255</v>
+        <v>0.613</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="14" t="inlineStr"/>
@@ -2790,28 +2792,28 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D52" s="9" t="n">
-        <v>0.605</v>
+        <v>1.26</v>
       </c>
       <c r="E52" s="16" t="n">
-        <v>0.0083</v>
+        <v>0.008</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>1557100</v>
+        <v>2399200</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>0.37</v>
+        <v>0.62</v>
       </c>
       <c r="H52" t="n">
-        <v>52.64</v>
+        <v>23.74</v>
       </c>
       <c r="I52" s="13" t="inlineStr">
         <is>
@@ -2819,10 +2821,10 @@
         </is>
       </c>
       <c r="J52" s="9" t="n">
-        <v>0.6</v>
+        <v>1.441</v>
       </c>
       <c r="K52" s="9" t="n">
-        <v>0.585</v>
+        <v>1.59</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="14" t="inlineStr"/>
@@ -2835,39 +2837,39 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>WCT</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D53" s="9" t="n">
-        <v>0.315</v>
+        <v>2.99</v>
       </c>
       <c r="E53" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>1544900</v>
+        <v>2397600</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>0.31</v>
+        <v>0.76</v>
       </c>
       <c r="H53" t="n">
-        <v>26.24</v>
-      </c>
-      <c r="I53" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I53" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J53" s="9" t="n">
-        <v>0.351</v>
+        <v>2.732</v>
       </c>
       <c r="K53" s="9" t="n">
-        <v>0.379</v>
+        <v>2.357</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="14" t="inlineStr"/>
@@ -2880,39 +2882,39 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D54" s="9" t="n">
-        <v>0.315</v>
-      </c>
-      <c r="E54" s="10" t="n">
-        <v>0</v>
+        <v>0.66</v>
+      </c>
+      <c r="E54" s="16" t="n">
+        <v>0.0076</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>1510000</v>
+        <v>2254400</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>0.08</v>
+        <v>0.26</v>
       </c>
       <c r="H54" t="n">
-        <v>61.97</v>
-      </c>
-      <c r="I54" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.26</v>
+      </c>
+      <c r="I54" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J54" s="9" t="n">
-        <v>0.308</v>
+        <v>0.67</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>0.298</v>
+        <v>0.617</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="14" t="inlineStr"/>
@@ -2925,28 +2927,28 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>0.5</v>
+        <v>0.215</v>
       </c>
       <c r="E55" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>1508800</v>
+        <v>2220700</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>0.18</v>
+        <v>0.08</v>
       </c>
       <c r="H55" t="n">
-        <v>43.41</v>
+        <v>30.12</v>
       </c>
       <c r="I55" s="13" t="inlineStr">
         <is>
@@ -2954,10 +2956,10 @@
         </is>
       </c>
       <c r="J55" s="9" t="n">
-        <v>0.517</v>
+        <v>0.241</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>0.529</v>
+        <v>0.295</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="14" t="inlineStr"/>
@@ -2970,39 +2972,39 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>7243</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>MAGMA</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D56" s="9" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="E56" s="16" t="n">
-        <v>0.03700000000000001</v>
+        <v>0.805</v>
+      </c>
+      <c r="E56" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>1454000</v>
+        <v>2163300</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>2.11</v>
+        <v>0.36</v>
       </c>
       <c r="H56" t="n">
-        <v>47.72</v>
-      </c>
-      <c r="I56" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.90000000000001</v>
+      </c>
+      <c r="I56" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J56" s="9" t="n">
-        <v>0.28</v>
+        <v>0.791</v>
       </c>
       <c r="K56" s="9" t="n">
-        <v>0.285</v>
+        <v>0.768</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="14" t="inlineStr"/>
@@ -3015,39 +3017,39 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>2.99</v>
+        <v>1.05</v>
       </c>
       <c r="E57" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>1453100</v>
+        <v>2159800</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>0.46</v>
+        <v>0.26</v>
       </c>
       <c r="H57" t="n">
-        <v>79.09999999999999</v>
-      </c>
-      <c r="I57" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.62</v>
+      </c>
+      <c r="I57" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J57" s="9" t="n">
-        <v>2.732</v>
+        <v>1.07</v>
       </c>
       <c r="K57" s="9" t="n">
-        <v>2.357</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="14" t="inlineStr"/>
@@ -3060,28 +3062,28 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D58" s="9" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="E58" s="16" t="n">
-        <v>0.008</v>
+        <v>0.0083</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>1418900</v>
+        <v>2096900</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>0.37</v>
+        <v>0.26</v>
       </c>
       <c r="H58" t="n">
-        <v>23.74</v>
+        <v>40.63</v>
       </c>
       <c r="I58" s="13" t="inlineStr">
         <is>
@@ -3089,10 +3091,10 @@
         </is>
       </c>
       <c r="J58" s="9" t="n">
-        <v>1.441</v>
+        <v>1.248</v>
       </c>
       <c r="K58" s="9" t="n">
-        <v>1.59</v>
+        <v>1.343</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="14" t="inlineStr"/>
@@ -3105,28 +3107,28 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="E59" s="10" t="n">
-        <v>0</v>
+        <v>3.73</v>
+      </c>
+      <c r="E59" s="16" t="n">
+        <v>0.0275</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>1363900</v>
+        <v>2082300</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="H59" t="n">
-        <v>47.15</v>
+        <v>56.58</v>
       </c>
       <c r="I59" s="13" t="inlineStr">
         <is>
@@ -3134,10 +3136,10 @@
         </is>
       </c>
       <c r="J59" s="9" t="n">
-        <v>2.628</v>
+        <v>3.608</v>
       </c>
       <c r="K59" s="9" t="n">
-        <v>2.597</v>
+        <v>2.871</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="14" t="inlineStr"/>
@@ -3150,28 +3152,28 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="E60" s="16" t="n">
-        <v>0.0048</v>
+        <v>1.24</v>
+      </c>
+      <c r="E60" s="15" t="n">
+        <v>-0.0462</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>1358800</v>
+        <v>2071000</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>0.09</v>
+        <v>0.63</v>
       </c>
       <c r="H60" t="n">
-        <v>38.63</v>
+        <v>53.25</v>
       </c>
       <c r="I60" s="13" t="inlineStr">
         <is>
@@ -3179,10 +3181,10 @@
         </is>
       </c>
       <c r="J60" s="9" t="n">
-        <v>2.191</v>
+        <v>1.255</v>
       </c>
       <c r="K60" s="9" t="n">
-        <v>2.225</v>
+        <v>1.041</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="14" t="inlineStr"/>
@@ -3195,39 +3197,39 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>0.39</v>
+        <v>0.47</v>
       </c>
       <c r="E61" s="15" t="n">
-        <v>-0.03700000000000001</v>
+        <v>-0.0105</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>1342200</v>
+        <v>2058000</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>0.11</v>
+        <v>0.3</v>
       </c>
       <c r="H61" t="n">
-        <v>51.36</v>
-      </c>
-      <c r="I61" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>22.01</v>
+      </c>
+      <c r="I61" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J61" s="9" t="n">
-        <v>0.388</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="K61" s="9" t="n">
-        <v>0.377</v>
+        <v>0.629</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="14" t="inlineStr"/>
@@ -3240,28 +3242,28 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0233</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>PEKAT</t>
+          <t>AMBANK</t>
         </is>
       </c>
       <c r="D62" s="9" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="E62" s="15" t="n">
-        <v>-0.0653</v>
+        <v>6.47</v>
+      </c>
+      <c r="E62" s="16" t="n">
+        <v>0.0319</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>1311800</v>
+        <v>2032500</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="H62" t="n">
-        <v>57.9</v>
+        <v>48.82</v>
       </c>
       <c r="I62" s="13" t="inlineStr">
         <is>
@@ -3269,10 +3271,10 @@
         </is>
       </c>
       <c r="J62" s="9" t="n">
-        <v>2.674</v>
+        <v>6.431</v>
       </c>
       <c r="K62" s="9" t="n">
-        <v>2.207</v>
+        <v>6.805</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="14" t="inlineStr"/>
@@ -3285,28 +3287,28 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>0471</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>PIONEER</t>
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>0.425</v>
+        <v>0.33</v>
       </c>
       <c r="E63" s="16" t="n">
-        <v>0.0119</v>
+        <v>0.0476</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>1302800</v>
+        <v>1984300</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>0.19</v>
+        <v>0.22</v>
       </c>
       <c r="H63" t="n">
-        <v>50.96</v>
+        <v>58.79</v>
       </c>
       <c r="I63" s="17" t="inlineStr">
         <is>
@@ -3314,11 +3316,9 @@
         </is>
       </c>
       <c r="J63" s="9" t="n">
-        <v>0.427</v>
-      </c>
-      <c r="K63" s="9" t="n">
-        <v>0.415</v>
-      </c>
+        <v>0.305</v>
+      </c>
+      <c r="K63" s="9" t="n"/>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="14" t="inlineStr"/>
     </row>
@@ -3330,28 +3330,28 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D64" s="9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="E64" s="15" t="n">
-        <v>-0.0283</v>
+        <v>9.98</v>
+      </c>
+      <c r="E64" s="16" t="n">
+        <v>0.002</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>1239700</v>
+        <v>1976000</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>0.27</v>
+        <v>0.15</v>
       </c>
       <c r="H64" t="n">
-        <v>50.19</v>
+        <v>45.15</v>
       </c>
       <c r="I64" s="13" t="inlineStr">
         <is>
@@ -3359,10 +3359,10 @@
         </is>
       </c>
       <c r="J64" s="9" t="n">
-        <v>1.058</v>
+        <v>10.007</v>
       </c>
       <c r="K64" s="9" t="n">
-        <v>0.919</v>
+        <v>10.178</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="14" t="inlineStr"/>
@@ -3375,28 +3375,28 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>4.94</v>
-      </c>
-      <c r="E65" s="15" t="n">
-        <v>-0.002</v>
+        <v>0.5</v>
+      </c>
+      <c r="E65" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>1214300</v>
+        <v>1873900</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>0.05</v>
+        <v>0.22</v>
       </c>
       <c r="H65" t="n">
-        <v>53.02</v>
+        <v>43.41</v>
       </c>
       <c r="I65" s="13" t="inlineStr">
         <is>
@@ -3404,10 +3404,10 @@
         </is>
       </c>
       <c r="J65" s="9" t="n">
-        <v>4.936</v>
+        <v>0.517</v>
       </c>
       <c r="K65" s="9" t="n">
-        <v>4.698</v>
+        <v>0.529</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="14" t="inlineStr"/>
@@ -3420,28 +3420,28 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0376</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>IAB</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D66" s="9" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="E66" s="15" t="n">
-        <v>-0.0169</v>
+        <v>1.26</v>
+      </c>
+      <c r="E66" s="16" t="n">
+        <v>0.008</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>1213800</v>
+        <v>1818900</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>0.54</v>
+        <v>0.18</v>
       </c>
       <c r="H66" t="n">
-        <v>39.49</v>
+        <v>41.98</v>
       </c>
       <c r="I66" s="13" t="inlineStr">
         <is>
@@ -3449,10 +3449,10 @@
         </is>
       </c>
       <c r="J66" s="9" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="K66" s="9" t="n">
-        <v>1.308</v>
+        <v>1.311</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="14" t="inlineStr"/>
@@ -3465,28 +3465,28 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D67" s="9" t="n">
-        <v>0.475</v>
-      </c>
-      <c r="E67" s="10" t="n">
-        <v>0</v>
+        <v>0.61</v>
+      </c>
+      <c r="E67" s="16" t="n">
+        <v>0.0167</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>1173500</v>
+        <v>1806000</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>0.17</v>
+        <v>0.43</v>
       </c>
       <c r="H67" t="n">
-        <v>22.56</v>
+        <v>53.75</v>
       </c>
       <c r="I67" s="13" t="inlineStr">
         <is>
@@ -3494,10 +3494,10 @@
         </is>
       </c>
       <c r="J67" s="9" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.601</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>0.629</v>
+        <v>0.585</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="14" t="inlineStr"/>
@@ -3510,28 +3510,28 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0104</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>GENETEC</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D68" s="9" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="E68" s="16" t="n">
-        <v>0.0164</v>
+        <v>2.77</v>
+      </c>
+      <c r="E68" s="15" t="n">
+        <v>-0.0177</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>1105500</v>
+        <v>1805200</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>0.18</v>
+        <v>0.13</v>
       </c>
       <c r="H68" t="n">
-        <v>43.28</v>
+        <v>49.37</v>
       </c>
       <c r="I68" s="13" t="inlineStr">
         <is>
@@ -3539,10 +3539,10 @@
         </is>
       </c>
       <c r="J68" s="9" t="n">
-        <v>0.322</v>
+        <v>2.795</v>
       </c>
       <c r="K68" s="9" t="n">
-        <v>0.338</v>
+        <v>2.721</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="14" t="inlineStr"/>
@@ -3555,28 +3555,28 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>0233</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>PEKAT</t>
         </is>
       </c>
       <c r="D69" s="9" t="n">
-        <v>9.99</v>
-      </c>
-      <c r="E69" s="16" t="n">
-        <v>0.003</v>
+        <v>2.67</v>
+      </c>
+      <c r="E69" s="15" t="n">
+        <v>-0.0825</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>1104500</v>
+        <v>1647600</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>0.08</v>
+        <v>0.51</v>
       </c>
       <c r="H69" t="n">
-        <v>45.88</v>
+        <v>55.09</v>
       </c>
       <c r="I69" s="13" t="inlineStr">
         <is>
@@ -3584,10 +3584,10 @@
         </is>
       </c>
       <c r="J69" s="9" t="n">
-        <v>10.008</v>
+        <v>2.669</v>
       </c>
       <c r="K69" s="9" t="n">
-        <v>10.178</v>
+        <v>2.206</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="14" t="inlineStr"/>
@@ -3600,28 +3600,28 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>0272</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>TTVHB</t>
         </is>
       </c>
       <c r="D70" s="9" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="E70" s="15" t="n">
-        <v>-0.0109</v>
+        <v>0.25</v>
+      </c>
+      <c r="E70" s="16" t="n">
+        <v>0.0204</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>1081600</v>
+        <v>1585800</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>0.13</v>
+        <v>0.68</v>
       </c>
       <c r="H70" t="n">
-        <v>46.74</v>
+        <v>49.61</v>
       </c>
       <c r="I70" s="13" t="inlineStr">
         <is>
@@ -3629,10 +3629,10 @@
         </is>
       </c>
       <c r="J70" s="9" t="n">
-        <v>0.95</v>
+        <v>0.251</v>
       </c>
       <c r="K70" s="9" t="n">
-        <v>0.837</v>
+        <v>0.255</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="14" t="inlineStr"/>
@@ -3645,39 +3645,39 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>0296</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>HEGROUP</t>
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="E71" s="10" t="n">
-        <v>0</v>
+        <v>1.02</v>
+      </c>
+      <c r="E71" s="15" t="n">
+        <v>-0.0377</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>1060000</v>
+        <v>1486500</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>0.05</v>
+        <v>0.32</v>
       </c>
       <c r="H71" t="n">
-        <v>55.72</v>
-      </c>
-      <c r="I71" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.75</v>
+      </c>
+      <c r="I71" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J71" s="9" t="n">
-        <v>2.112</v>
+        <v>1.057</v>
       </c>
       <c r="K71" s="9" t="n">
-        <v>2.094</v>
+        <v>0.919</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="14" t="inlineStr"/>
@@ -3690,39 +3690,39 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D72" s="9" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E72" s="15" t="n">
-        <v>-0.0064</v>
+        <v>0.425</v>
+      </c>
+      <c r="E72" s="16" t="n">
+        <v>0.0119</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>1056800</v>
+        <v>1461500</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>0.13</v>
+        <v>0.21</v>
       </c>
       <c r="H72" t="n">
-        <v>49.19</v>
-      </c>
-      <c r="I72" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.96</v>
+      </c>
+      <c r="I72" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J72" s="9" t="n">
-        <v>0.779</v>
+        <v>0.427</v>
       </c>
       <c r="K72" s="9" t="n">
-        <v>0.773</v>
+        <v>0.415</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="14" t="inlineStr"/>
@@ -3735,28 +3735,28 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>5932</t>
+          <t>0376</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>BPURI</t>
+          <t>IAB</t>
         </is>
       </c>
       <c r="D73" s="9" t="n">
-        <v>0.215</v>
-      </c>
-      <c r="E73" s="10" t="n">
-        <v>0</v>
+        <v>1.17</v>
+      </c>
+      <c r="E73" s="15" t="n">
+        <v>-0.008500000000000001</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>1055800</v>
+        <v>1443500</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>2.34</v>
+        <v>0.64</v>
       </c>
       <c r="H73" t="n">
-        <v>38.87</v>
+        <v>40.26</v>
       </c>
       <c r="I73" s="13" t="inlineStr">
         <is>
@@ -3764,10 +3764,10 @@
         </is>
       </c>
       <c r="J73" s="9" t="n">
-        <v>0.225</v>
+        <v>1.251</v>
       </c>
       <c r="K73" s="9" t="n">
-        <v>0.233</v>
+        <v>1.309</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="14" t="inlineStr"/>
@@ -3780,28 +3780,28 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D74" s="9" t="n">
-        <v>0.365</v>
-      </c>
-      <c r="E74" s="10" t="n">
-        <v>0</v>
+        <v>2.57</v>
+      </c>
+      <c r="E74" s="15" t="n">
+        <v>-0.0039</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>1050600</v>
+        <v>1415900</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>0.11</v>
+        <v>0.23</v>
       </c>
       <c r="H74" t="n">
-        <v>57.29</v>
+        <v>46.48</v>
       </c>
       <c r="I74" s="13" t="inlineStr">
         <is>
@@ -3809,10 +3809,10 @@
         </is>
       </c>
       <c r="J74" s="9" t="n">
-        <v>0.357</v>
+        <v>2.627</v>
       </c>
       <c r="K74" s="9" t="n">
-        <v>0.325</v>
+        <v>2.597</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="14" t="inlineStr"/>
@@ -3825,39 +3825,39 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D75" s="9" t="n">
-        <v>0.805</v>
-      </c>
-      <c r="E75" s="10" t="n">
-        <v>0</v>
+        <v>0.91</v>
+      </c>
+      <c r="E75" s="15" t="n">
+        <v>-0.0109</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>1030000</v>
+        <v>1390700</v>
       </c>
       <c r="G75" s="12" t="n">
         <v>0.17</v>
       </c>
       <c r="H75" t="n">
-        <v>66.90000000000001</v>
-      </c>
-      <c r="I75" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.74</v>
+      </c>
+      <c r="I75" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J75" s="9" t="n">
-        <v>0.791</v>
+        <v>0.95</v>
       </c>
       <c r="K75" s="9" t="n">
-        <v>0.768</v>
+        <v>0.837</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="14" t="inlineStr"/>
@@ -3870,28 +3870,28 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0372</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>CHEEDING</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D76" s="9" t="n">
-        <v>0.57</v>
+        <v>5.47</v>
       </c>
       <c r="E76" s="15" t="n">
-        <v>-0.0172</v>
+        <v>-0.005500000000000001</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>1001100</v>
+        <v>1289800</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>0.25</v>
+        <v>0.09</v>
       </c>
       <c r="H76" t="n">
-        <v>40.78</v>
+        <v>45.57</v>
       </c>
       <c r="I76" s="13" t="inlineStr">
         <is>
@@ -3899,10 +3899,10 @@
         </is>
       </c>
       <c r="J76" s="9" t="n">
-        <v>0.606</v>
+        <v>5.605</v>
       </c>
       <c r="K76" s="9" t="n">
-        <v>0.606</v>
+        <v>5.388</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="14" t="inlineStr"/>
@@ -3915,28 +3915,28 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>AMBANK</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D77" s="9" t="n">
-        <v>6.43</v>
-      </c>
-      <c r="E77" s="16" t="n">
-        <v>0.0255</v>
+        <v>0.775</v>
+      </c>
+      <c r="E77" s="15" t="n">
+        <v>-0.0064</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>962900</v>
+        <v>1243800</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="H77" t="n">
-        <v>46.82</v>
+        <v>49.19</v>
       </c>
       <c r="I77" s="13" t="inlineStr">
         <is>
@@ -3944,10 +3944,10 @@
         </is>
       </c>
       <c r="J77" s="9" t="n">
-        <v>6.427</v>
+        <v>0.779</v>
       </c>
       <c r="K77" s="9" t="n">
-        <v>6.805</v>
+        <v>0.773</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="14" t="inlineStr"/>
@@ -3960,39 +3960,39 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>0372</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>CHEEDING</t>
         </is>
       </c>
       <c r="D78" s="9" t="n">
-        <v>0.825</v>
-      </c>
-      <c r="E78" s="10" t="n">
-        <v>0</v>
+        <v>0.575</v>
+      </c>
+      <c r="E78" s="15" t="n">
+        <v>-0.0086</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>894300</v>
+        <v>1242900</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>0.24</v>
+        <v>0.31</v>
       </c>
       <c r="H78" t="n">
-        <v>51.87</v>
-      </c>
-      <c r="I78" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.75</v>
+      </c>
+      <c r="I78" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J78" s="9" t="n">
-        <v>0.828</v>
+        <v>0.606</v>
       </c>
       <c r="K78" s="9" t="n">
-        <v>0.77</v>
+        <v>0.606</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="14" t="inlineStr"/>
@@ -4005,39 +4005,39 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D79" s="9" t="n">
-        <v>0.645</v>
+        <v>1.61</v>
       </c>
       <c r="E79" s="16" t="n">
-        <v>0.0238</v>
+        <v>0.0126</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>874500</v>
+        <v>1208300</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="H79" t="n">
-        <v>66.98999999999999</v>
-      </c>
-      <c r="I79" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.72</v>
+      </c>
+      <c r="I79" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J79" s="9" t="n">
-        <v>0.554</v>
+        <v>1.613</v>
       </c>
       <c r="K79" s="9" t="n">
-        <v>0.458</v>
+        <v>1.709</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="14" t="inlineStr"/>
@@ -4050,39 +4050,39 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D80" s="9" t="n">
-        <v>4.37</v>
+        <v>0.645</v>
       </c>
       <c r="E80" s="16" t="n">
-        <v>0.0116</v>
+        <v>0.0238</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>859600</v>
+        <v>1206400</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>0.13</v>
+        <v>0.23</v>
       </c>
       <c r="H80" t="n">
-        <v>49.26</v>
-      </c>
-      <c r="I80" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>66.98999999999999</v>
+      </c>
+      <c r="I80" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J80" s="9" t="n">
-        <v>4.359</v>
+        <v>0.554</v>
       </c>
       <c r="K80" s="9" t="n">
-        <v>4.441</v>
+        <v>0.458</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="14" t="inlineStr"/>
@@ -4095,39 +4095,39 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>AWC</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D81" s="9" t="n">
-        <v>0.675</v>
-      </c>
-      <c r="E81" s="15" t="n">
-        <v>-0.0217</v>
+        <v>7.35</v>
+      </c>
+      <c r="E81" s="16" t="n">
+        <v>0.0068</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>859500</v>
+        <v>1179600</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>0.37</v>
+        <v>0.12</v>
       </c>
       <c r="H81" t="n">
-        <v>62.4</v>
-      </c>
-      <c r="I81" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.49</v>
+      </c>
+      <c r="I81" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J81" s="9" t="n">
-        <v>0.635</v>
+        <v>7.522</v>
       </c>
       <c r="K81" s="9" t="n">
-        <v>0.543</v>
+        <v>8.026999999999999</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="14" t="inlineStr"/>
@@ -4140,28 +4140,28 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0291</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>CHB</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D82" s="9" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="E82" s="15" t="n">
-        <v>-0.039</v>
+        <v>0.305</v>
+      </c>
+      <c r="E82" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>779100</v>
+        <v>1166400</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>0.5</v>
+        <v>0.19</v>
       </c>
       <c r="H82" t="n">
-        <v>65.63</v>
+        <v>40.49</v>
       </c>
       <c r="I82" s="13" t="inlineStr">
         <is>
@@ -4169,10 +4169,10 @@
         </is>
       </c>
       <c r="J82" s="9" t="n">
-        <v>2.54</v>
+        <v>0.321</v>
       </c>
       <c r="K82" s="9" t="n">
-        <v>2.213</v>
+        <v>0.338</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="14" t="inlineStr"/>
@@ -4185,28 +4185,28 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>0468</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>UNIPAC</t>
         </is>
       </c>
       <c r="D83" s="9" t="n">
-        <v>7.36</v>
-      </c>
-      <c r="E83" s="16" t="n">
-        <v>0.008199999999999999</v>
+        <v>0.23</v>
+      </c>
+      <c r="E83" s="15" t="n">
+        <v>-0.0213</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>749900</v>
+        <v>1090700</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="H83" t="n">
-        <v>36.12</v>
+        <v>24.97</v>
       </c>
       <c r="I83" s="13" t="inlineStr">
         <is>
@@ -4214,11 +4214,9 @@
         </is>
       </c>
       <c r="J83" s="9" t="n">
-        <v>7.523</v>
-      </c>
-      <c r="K83" s="9" t="n">
-        <v>8.028</v>
-      </c>
+        <v>0.257</v>
+      </c>
+      <c r="K83" s="9" t="n"/>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="14" t="inlineStr"/>
     </row>
@@ -4230,28 +4228,28 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D84" s="9" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="E84" s="15" t="n">
-        <v>-0.008100000000000001</v>
+        <v>0.535</v>
+      </c>
+      <c r="E84" s="16" t="n">
+        <v>0.009399999999999999</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>705000</v>
+        <v>1076200</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H84" t="n">
-        <v>49.6</v>
+        <v>55.88</v>
       </c>
       <c r="I84" s="13" t="inlineStr">
         <is>
@@ -4259,10 +4257,10 @@
         </is>
       </c>
       <c r="J84" s="9" t="n">
-        <v>2.459</v>
+        <v>0.519</v>
       </c>
       <c r="K84" s="9" t="n">
-        <v>2.368</v>
+        <v>0.45</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="14" t="inlineStr"/>
@@ -4275,39 +4273,39 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>AWC</t>
         </is>
       </c>
       <c r="D85" s="9" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E85" s="16" t="n">
-        <v>0.0063</v>
+        <v>0.6850000000000001</v>
+      </c>
+      <c r="E85" s="15" t="n">
+        <v>-0.0072</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>682300</v>
+        <v>1073700</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>0.11</v>
+        <v>0.46</v>
       </c>
       <c r="H85" t="n">
-        <v>62.86</v>
-      </c>
-      <c r="I85" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.98999999999999</v>
+      </c>
+      <c r="I85" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J85" s="9" t="n">
-        <v>0.764</v>
+        <v>0.636</v>
       </c>
       <c r="K85" s="9" t="n">
-        <v>0.676</v>
+        <v>0.543</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="14" t="inlineStr"/>
@@ -4320,28 +4318,28 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D86" s="9" t="n">
-        <v>7.38</v>
+        <v>0.835</v>
       </c>
       <c r="E86" s="16" t="n">
-        <v>0.0179</v>
+        <v>0.0121</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>665200</v>
+        <v>1067500</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>0.09</v>
+        <v>0.28</v>
       </c>
       <c r="H86" t="n">
-        <v>46.49</v>
+        <v>53.55</v>
       </c>
       <c r="I86" s="17" t="inlineStr">
         <is>
@@ -4349,10 +4347,10 @@
         </is>
       </c>
       <c r="J86" s="9" t="n">
-        <v>7.38</v>
+        <v>0.829</v>
       </c>
       <c r="K86" s="9" t="n">
-        <v>7.687</v>
+        <v>0.771</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="14" t="inlineStr"/>
@@ -4365,39 +4363,39 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D87" s="9" t="n">
-        <v>0.54</v>
+        <v>4.35</v>
       </c>
       <c r="E87" s="16" t="n">
-        <v>0.0189</v>
+        <v>0.0069</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>661700</v>
+        <v>1062800</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>0.04</v>
+        <v>0.16</v>
       </c>
       <c r="H87" t="n">
-        <v>56.68</v>
-      </c>
-      <c r="I87" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.43</v>
+      </c>
+      <c r="I87" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J87" s="9" t="n">
-        <v>0.52</v>
+        <v>4.357</v>
       </c>
       <c r="K87" s="9" t="n">
-        <v>0.45</v>
+        <v>4.441</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="14" t="inlineStr"/>
@@ -4410,28 +4408,28 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>5932</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>MALAKOF</t>
+          <t>BPURI</t>
         </is>
       </c>
       <c r="D88" s="9" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="E88" s="15" t="n">
-        <v>-0.006500000000000001</v>
+        <v>0.215</v>
+      </c>
+      <c r="E88" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>648200</v>
+        <v>1055800</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>0.15</v>
+        <v>2.34</v>
       </c>
       <c r="H88" t="n">
-        <v>43.67</v>
+        <v>38.87</v>
       </c>
       <c r="I88" s="13" t="inlineStr">
         <is>
@@ -4439,10 +4437,10 @@
         </is>
       </c>
       <c r="J88" s="9" t="n">
-        <v>0.787</v>
+        <v>0.225</v>
       </c>
       <c r="K88" s="9" t="n">
-        <v>0.804</v>
+        <v>0.233</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="14" t="inlineStr"/>
@@ -4455,28 +4453,28 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D89" s="9" t="n">
-        <v>0.745</v>
-      </c>
-      <c r="E89" s="16" t="n">
-        <v>0.0068</v>
+        <v>0.36</v>
+      </c>
+      <c r="E89" s="15" t="n">
+        <v>-0.0137</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>641400</v>
+        <v>1053900</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>0.29</v>
+        <v>0.11</v>
       </c>
       <c r="H89" t="n">
-        <v>55.71</v>
+        <v>54.85</v>
       </c>
       <c r="I89" s="13" t="inlineStr">
         <is>
@@ -4484,10 +4482,10 @@
         </is>
       </c>
       <c r="J89" s="9" t="n">
-        <v>0.724</v>
+        <v>0.356</v>
       </c>
       <c r="K89" s="9" t="n">
-        <v>0.699</v>
+        <v>0.325</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="14" t="inlineStr"/>
@@ -4500,39 +4498,39 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0271</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>WELLS</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D90" s="9" t="n">
-        <v>0.535</v>
+        <v>2.44</v>
       </c>
       <c r="E90" s="15" t="n">
-        <v>-0.0183</v>
+        <v>-0.008100000000000001</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>607700</v>
+        <v>1040700</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>0.55</v>
+        <v>0.08</v>
       </c>
       <c r="H90" t="n">
-        <v>33.07</v>
-      </c>
-      <c r="I90" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.6</v>
+      </c>
+      <c r="I90" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J90" s="9" t="n">
-        <v>0.573</v>
+        <v>2.459</v>
       </c>
       <c r="K90" s="9" t="n">
-        <v>0.616</v>
+        <v>2.368</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="14" t="inlineStr"/>
@@ -4545,39 +4543,39 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>7943</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>GREENTEC</t>
         </is>
       </c>
       <c r="D91" s="9" t="n">
-        <v>0.755</v>
-      </c>
-      <c r="E91" s="10" t="n">
-        <v>0</v>
+        <v>0.29</v>
+      </c>
+      <c r="E91" s="15" t="n">
+        <v>-0.0333</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>594500</v>
+        <v>1007000</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>0.08</v>
+        <v>0.92</v>
       </c>
       <c r="H91" t="n">
-        <v>55.72</v>
-      </c>
-      <c r="I91" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.97</v>
+      </c>
+      <c r="I91" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J91" s="9" t="n">
-        <v>0.743</v>
+        <v>0.257</v>
       </c>
       <c r="K91" s="9" t="n">
-        <v>0.665</v>
+        <v>0.211</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="14" t="inlineStr"/>
@@ -4590,39 +4588,39 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D92" s="9" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E92" s="15" t="n">
-        <v>-0.005699999999999999</v>
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="E92" s="16" t="n">
+        <v>0.0217</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>584500</v>
+        <v>993100</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>0.03</v>
+        <v>0.71</v>
       </c>
       <c r="H92" t="n">
-        <v>46.29</v>
-      </c>
-      <c r="I92" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>55.19</v>
+      </c>
+      <c r="I92" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J92" s="9" t="n">
-        <v>0.868</v>
+        <v>0.925</v>
       </c>
       <c r="K92" s="9" t="n">
-        <v>0.869</v>
+        <v>0.863</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="14" t="inlineStr"/>
@@ -4635,39 +4633,39 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D93" s="9" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="E93" s="16" t="n">
-        <v>0.0092</v>
+        <v>0.0063</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>580800</v>
+        <v>975200</v>
       </c>
       <c r="G93" s="12" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="H93" t="n">
-        <v>59.17</v>
-      </c>
-      <c r="I93" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>62.86</v>
+      </c>
+      <c r="I93" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J93" s="9" t="n">
-        <v>1.045</v>
+        <v>0.764</v>
       </c>
       <c r="K93" s="9" t="n">
-        <v>0.888</v>
+        <v>0.676</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="14" t="inlineStr"/>
@@ -4680,39 +4678,39 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>5337</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>TENAGA</t>
+          <t>ECOSHOP</t>
         </is>
       </c>
       <c r="D94" s="9" t="n">
-        <v>12.96</v>
+        <v>1.43</v>
       </c>
       <c r="E94" s="15" t="n">
-        <v>-0.0061</v>
+        <v>-0.0069</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>576500</v>
+        <v>972300</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>0.06</v>
+        <v>0.23</v>
       </c>
       <c r="H94" t="n">
-        <v>43.28</v>
-      </c>
-      <c r="I94" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.99</v>
+      </c>
+      <c r="I94" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J94" s="9" t="n">
-        <v>13.023</v>
+        <v>1.453</v>
       </c>
       <c r="K94" s="9" t="n">
-        <v>13.492</v>
+        <v>1.467</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="14" t="inlineStr"/>
@@ -4725,28 +4723,28 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D95" s="9" t="n">
-        <v>1.18</v>
+        <v>0.595</v>
       </c>
       <c r="E95" s="16" t="n">
-        <v>0.0172</v>
+        <v>0.0259</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>574000</v>
+        <v>969400</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.19</v>
       </c>
       <c r="H95" t="n">
-        <v>53.23</v>
+        <v>64.37</v>
       </c>
       <c r="I95" s="13" t="inlineStr">
         <is>
@@ -4754,10 +4752,10 @@
         </is>
       </c>
       <c r="J95" s="9" t="n">
-        <v>1.162</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="K95" s="9" t="n">
-        <v>1.127</v>
+        <v>0.506</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="14" t="inlineStr"/>
@@ -4770,28 +4768,28 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>0291</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>CHB</t>
         </is>
       </c>
       <c r="D96" s="9" t="n">
-        <v>0.625</v>
+        <v>2.73</v>
       </c>
       <c r="E96" s="15" t="n">
-        <v>-0.0234</v>
+        <v>-0.0319</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>552500</v>
+        <v>968500</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>0.21</v>
+        <v>0.63</v>
       </c>
       <c r="H96" t="n">
-        <v>46.09</v>
+        <v>67.19</v>
       </c>
       <c r="I96" s="13" t="inlineStr">
         <is>
@@ -4799,10 +4797,10 @@
         </is>
       </c>
       <c r="J96" s="9" t="n">
-        <v>0.637</v>
+        <v>2.542</v>
       </c>
       <c r="K96" s="9" t="n">
-        <v>0.617</v>
+        <v>2.213</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="14" t="inlineStr"/>
@@ -4815,39 +4813,39 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D97" s="9" t="n">
-        <v>1.71</v>
+        <v>7.38</v>
       </c>
       <c r="E97" s="16" t="n">
-        <v>0.0059</v>
+        <v>0.0179</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>544100</v>
+        <v>945600</v>
       </c>
       <c r="G97" s="12" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="H97" t="n">
-        <v>43.69</v>
-      </c>
-      <c r="I97" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.49</v>
+      </c>
+      <c r="I97" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J97" s="9" t="n">
-        <v>1.747</v>
+        <v>7.38</v>
       </c>
       <c r="K97" s="9" t="n">
-        <v>1.774</v>
+        <v>7.687</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="14" t="inlineStr"/>
@@ -4860,28 +4858,28 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D98" s="9" t="n">
-        <v>0.915</v>
-      </c>
-      <c r="E98" s="15" t="n">
-        <v>-0.0054</v>
+        <v>0.755</v>
+      </c>
+      <c r="E98" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>533600</v>
+        <v>907500</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>0.38</v>
+        <v>0.13</v>
       </c>
       <c r="H98" t="n">
-        <v>50.82</v>
+        <v>55.72</v>
       </c>
       <c r="I98" s="13" t="inlineStr">
         <is>
@@ -4889,10 +4887,10 @@
         </is>
       </c>
       <c r="J98" s="9" t="n">
-        <v>0.923</v>
+        <v>0.743</v>
       </c>
       <c r="K98" s="9" t="n">
-        <v>0.863</v>
+        <v>0.665</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="14" t="inlineStr"/>
@@ -4905,45 +4903,1080 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D99" s="9" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="E99" s="15" t="n">
-        <v>-0.0142</v>
+        <v>1.22</v>
+      </c>
+      <c r="E99" s="16" t="n">
+        <v>0.0167</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>533200</v>
+        <v>899000</v>
       </c>
       <c r="G99" s="12" t="n">
-        <v>0.04</v>
+        <v>0.16</v>
       </c>
       <c r="H99" t="n">
-        <v>50.17</v>
-      </c>
-      <c r="I99" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.43</v>
+      </c>
+      <c r="I99" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J99" s="9" t="n">
-        <v>2.796</v>
+        <v>1.171</v>
       </c>
       <c r="K99" s="9" t="n">
-        <v>2.721</v>
+        <v>1.176</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="14" t="inlineStr"/>
     </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>5878</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>KPJ</t>
+        </is>
+      </c>
+      <c r="D100" s="9" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="E100" s="16" t="n">
+        <v>0.0244</v>
+      </c>
+      <c r="F100" s="11" t="n">
+        <v>826000</v>
+      </c>
+      <c r="G100" s="12" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H100" t="n">
+        <v>42.82</v>
+      </c>
+      <c r="I100" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J100" s="9" t="n">
+        <v>2.572</v>
+      </c>
+      <c r="K100" s="9" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" s="14" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>0146</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>JFTECH</t>
+        </is>
+      </c>
+      <c r="D101" s="9" t="n">
+        <v>0.745</v>
+      </c>
+      <c r="E101" s="16" t="n">
+        <v>0.0068</v>
+      </c>
+      <c r="F101" s="11" t="n">
+        <v>772000</v>
+      </c>
+      <c r="G101" s="12" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H101" t="n">
+        <v>55.71</v>
+      </c>
+      <c r="I101" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J101" s="9" t="n">
+        <v>0.724</v>
+      </c>
+      <c r="K101" s="9" t="n">
+        <v>0.699</v>
+      </c>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" s="14" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>5347</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>TENAGA</t>
+        </is>
+      </c>
+      <c r="D102" s="9" t="n">
+        <v>12.96</v>
+      </c>
+      <c r="E102" s="15" t="n">
+        <v>-0.0061</v>
+      </c>
+      <c r="F102" s="11" t="n">
+        <v>719200</v>
+      </c>
+      <c r="G102" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H102" t="n">
+        <v>43.28</v>
+      </c>
+      <c r="I102" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J102" s="9" t="n">
+        <v>13.023</v>
+      </c>
+      <c r="K102" s="9" t="n">
+        <v>13.492</v>
+      </c>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" s="14" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>5286</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="D103" s="9" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="E103" s="16" t="n">
+        <v>0.0077</v>
+      </c>
+      <c r="F103" s="11" t="n">
+        <v>713900</v>
+      </c>
+      <c r="G103" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H103" t="n">
+        <v>59.27</v>
+      </c>
+      <c r="I103" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J103" s="9" t="n">
+        <v>6.056</v>
+      </c>
+      <c r="K103" s="9" t="n">
+        <v>5.856</v>
+      </c>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" s="14" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>5264</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>MALAKOF</t>
+        </is>
+      </c>
+      <c r="D104" s="9" t="n">
+        <v>0.765</v>
+      </c>
+      <c r="E104" s="15" t="n">
+        <v>-0.0129</v>
+      </c>
+      <c r="F104" s="11" t="n">
+        <v>707300</v>
+      </c>
+      <c r="G104" s="12" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H104" t="n">
+        <v>42.45</v>
+      </c>
+      <c r="I104" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J104" s="9" t="n">
+        <v>0.787</v>
+      </c>
+      <c r="K104" s="9" t="n">
+        <v>0.804</v>
+      </c>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" s="14" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>7498</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>RALCO</t>
+        </is>
+      </c>
+      <c r="D105" s="9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="E105" s="16" t="n">
+        <v>0.009899999999999999</v>
+      </c>
+      <c r="F105" s="11" t="n">
+        <v>703200</v>
+      </c>
+      <c r="G105" s="12" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="H105" t="n">
+        <v>59.02</v>
+      </c>
+      <c r="I105" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J105" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K105" s="9" t="n">
+        <v>0.982</v>
+      </c>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" s="14" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>5356</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>STRATUS</t>
+        </is>
+      </c>
+      <c r="D106" s="9" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="E106" s="16" t="n">
+        <v>0.0074</v>
+      </c>
+      <c r="F106" s="11" t="n">
+        <v>691100</v>
+      </c>
+      <c r="G106" s="12" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H106" t="n">
+        <v>40.24</v>
+      </c>
+      <c r="I106" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J106" s="9" t="n">
+        <v>2.908</v>
+      </c>
+      <c r="K106" s="9" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" s="14" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>5302</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>ATECH</t>
+        </is>
+      </c>
+      <c r="D107" s="9" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="E107" s="16" t="n">
+        <v>0.0128</v>
+      </c>
+      <c r="F107" s="11" t="n">
+        <v>659100</v>
+      </c>
+      <c r="G107" s="12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H107" t="n">
+        <v>54.81</v>
+      </c>
+      <c r="I107" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J107" s="9" t="n">
+        <v>0.776</v>
+      </c>
+      <c r="K107" s="9" t="n">
+        <v>0.765</v>
+      </c>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" s="14" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>0167</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>MCLEAN</t>
+        </is>
+      </c>
+      <c r="D108" s="9" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="E108" s="16" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="F108" s="11" t="n">
+        <v>657600</v>
+      </c>
+      <c r="G108" s="12" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H108" t="n">
+        <v>42.33</v>
+      </c>
+      <c r="I108" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J108" s="9" t="n">
+        <v>0.747</v>
+      </c>
+      <c r="K108" s="9" t="n">
+        <v>0.748</v>
+      </c>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" s="14" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>0246</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>CNERGEN</t>
+        </is>
+      </c>
+      <c r="D109" s="9" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="E109" s="15" t="n">
+        <v>-0.0183</v>
+      </c>
+      <c r="F109" s="11" t="n">
+        <v>648100</v>
+      </c>
+      <c r="G109" s="12" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H109" t="n">
+        <v>56.22</v>
+      </c>
+      <c r="I109" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J109" s="9" t="n">
+        <v>1.042</v>
+      </c>
+      <c r="K109" s="9" t="n">
+        <v>0.887</v>
+      </c>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" s="14" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>7153</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>KOSSAN</t>
+        </is>
+      </c>
+      <c r="D110" s="9" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="E110" s="16" t="n">
+        <v>0.0086</v>
+      </c>
+      <c r="F110" s="11" t="n">
+        <v>648100</v>
+      </c>
+      <c r="G110" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H110" t="n">
+        <v>52.01</v>
+      </c>
+      <c r="I110" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J110" s="9" t="n">
+        <v>1.162</v>
+      </c>
+      <c r="K110" s="9" t="n">
+        <v>1.127</v>
+      </c>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" s="14" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>0271</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>WELLS</t>
+        </is>
+      </c>
+      <c r="D111" s="9" t="n">
+        <v>0.535</v>
+      </c>
+      <c r="E111" s="15" t="n">
+        <v>-0.0183</v>
+      </c>
+      <c r="F111" s="11" t="n">
+        <v>607700</v>
+      </c>
+      <c r="G111" s="12" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="H111" t="n">
+        <v>33.07</v>
+      </c>
+      <c r="I111" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J111" s="9" t="n">
+        <v>0.573</v>
+      </c>
+      <c r="K111" s="9" t="n">
+        <v>0.616</v>
+      </c>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" s="14" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>8907</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="D112" s="9" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="E112" s="16" t="n">
+        <v>0.0059</v>
+      </c>
+      <c r="F112" s="11" t="n">
+        <v>604100</v>
+      </c>
+      <c r="G112" s="12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H112" t="n">
+        <v>43.69</v>
+      </c>
+      <c r="I112" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J112" s="9" t="n">
+        <v>1.747</v>
+      </c>
+      <c r="K112" s="9" t="n">
+        <v>1.774</v>
+      </c>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" s="14" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>0277</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>CLOUDPT</t>
+        </is>
+      </c>
+      <c r="D113" s="9" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="E113" s="16" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F113" s="11" t="n">
+        <v>594200</v>
+      </c>
+      <c r="G113" s="12" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H113" t="n">
+        <v>55.44</v>
+      </c>
+      <c r="I113" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J113" s="9" t="n">
+        <v>0.495</v>
+      </c>
+      <c r="K113" s="9" t="n">
+        <v>0.483</v>
+      </c>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" s="14" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>5292</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>UWC</t>
+        </is>
+      </c>
+      <c r="D114" s="9" t="n">
+        <v>7.63</v>
+      </c>
+      <c r="E114" s="15" t="n">
+        <v>-0.0026</v>
+      </c>
+      <c r="F114" s="11" t="n">
+        <v>591700</v>
+      </c>
+      <c r="G114" s="12" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H114" t="n">
+        <v>60.95</v>
+      </c>
+      <c r="I114" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J114" s="9" t="n">
+        <v>7.372</v>
+      </c>
+      <c r="K114" s="9" t="n">
+        <v>6.846</v>
+      </c>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" s="14" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>5223</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>MENTIGA</t>
+        </is>
+      </c>
+      <c r="D115" s="9" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E115" s="16" t="n">
+        <v>0.3793</v>
+      </c>
+      <c r="F115" s="11" t="n">
+        <v>578400</v>
+      </c>
+      <c r="G115" s="12" t="n">
+        <v>26.17</v>
+      </c>
+      <c r="H115" t="n">
+        <v>74.09</v>
+      </c>
+      <c r="I115" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J115" s="9" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="K115" s="9" t="n">
+        <v>0.642</v>
+      </c>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" s="14" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>0368</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>OXB</t>
+        </is>
+      </c>
+      <c r="D116" s="9" t="n">
+        <v>0.515</v>
+      </c>
+      <c r="E116" s="15" t="n">
+        <v>-0.009599999999999999</v>
+      </c>
+      <c r="F116" s="11" t="n">
+        <v>565200</v>
+      </c>
+      <c r="G116" s="12" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H116" t="n">
+        <v>59.96</v>
+      </c>
+      <c r="I116" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J116" s="9" t="n">
+        <v>0.489</v>
+      </c>
+      <c r="K116" s="9" t="n">
+        <v>0.459</v>
+      </c>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" s="14" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>5357</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>SKYECHIP</t>
+        </is>
+      </c>
+      <c r="D117" s="9" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="E117" s="16" t="n">
+        <v>0.0072</v>
+      </c>
+      <c r="F117" s="11" t="n">
+        <v>555600</v>
+      </c>
+      <c r="G117" s="12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H117" t="n">
+        <v>35.93</v>
+      </c>
+      <c r="I117" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J117" s="9" t="n">
+        <v>2.933</v>
+      </c>
+      <c r="K117" s="9" t="n">
+        <v>3.026</v>
+      </c>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" s="14" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>0112</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>MIKROMB</t>
+        </is>
+      </c>
+      <c r="D118" s="9" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="E118" s="15" t="n">
+        <v>-0.0234</v>
+      </c>
+      <c r="F118" s="11" t="n">
+        <v>552500</v>
+      </c>
+      <c r="G118" s="12" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H118" t="n">
+        <v>46.09</v>
+      </c>
+      <c r="I118" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J118" s="9" t="n">
+        <v>0.637</v>
+      </c>
+      <c r="K118" s="9" t="n">
+        <v>0.617</v>
+      </c>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" s="14" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>7233</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>DUFU</t>
+        </is>
+      </c>
+      <c r="D119" s="9" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="E119" s="16" t="n">
+        <v>0.0227</v>
+      </c>
+      <c r="F119" s="11" t="n">
+        <v>549100</v>
+      </c>
+      <c r="G119" s="12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H119" t="n">
+        <v>58.18</v>
+      </c>
+      <c r="I119" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J119" s="9" t="n">
+        <v>3.036</v>
+      </c>
+      <c r="K119" s="9" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" s="14" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>0245</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>MNHLDG</t>
+        </is>
+      </c>
+      <c r="D120" s="9" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="E120" s="15" t="n">
+        <v>-0.0102</v>
+      </c>
+      <c r="F120" s="11" t="n">
+        <v>541400</v>
+      </c>
+      <c r="G120" s="12" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H120" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="I120" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J120" s="9" t="n">
+        <v>3.875</v>
+      </c>
+      <c r="K120" s="9" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" s="14" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>5249</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>IOIPG</t>
+        </is>
+      </c>
+      <c r="D121" s="9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="E121" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F121" s="11" t="n">
+        <v>528300</v>
+      </c>
+      <c r="G121" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H121" t="n">
+        <v>33.44</v>
+      </c>
+      <c r="I121" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J121" s="9" t="n">
+        <v>3.425</v>
+      </c>
+      <c r="K121" s="9" t="n">
+        <v>3.632</v>
+      </c>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" s="14" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>0338</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>KOPI</t>
+        </is>
+      </c>
+      <c r="D122" s="9" t="n">
+        <v>0.895</v>
+      </c>
+      <c r="E122" s="15" t="n">
+        <v>-0.011</v>
+      </c>
+      <c r="F122" s="11" t="n">
+        <v>516500</v>
+      </c>
+      <c r="G122" s="12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H122" t="n">
+        <v>41.46</v>
+      </c>
+      <c r="I122" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J122" s="9" t="n">
+        <v>0.909</v>
+      </c>
+      <c r="K122" s="9" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M99"/>
+  <autoFilter ref="A1:M122"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-14/bursa-report-2026-10-14.xlsx
+++ b/docs/downloads/2026-10-14/bursa-report-2026-10-14.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-14" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-14'!$A$1:$M$122</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-14'!$A$1:$M$145</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M122"/>
+  <dimension ref="A1:M145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -566,19 +566,19 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.0225</v>
+        <v>0.036</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>1689100</v>
+        <v>1993900</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>0.42</v>
+        <v>0.49</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>57.36</v>
+        <v>59.41</v>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>2.196</v>
+        <v>2.199</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>2.144</v>
+        <v>2.145</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
@@ -598,7 +598,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>现价RM2.27高于50日均线RM2.144，RSI 57.36处中性偏多区间，未超买，SAR转多信号技术面尚属可靠。</t>
+          <t>SAR转多，现价2.3高于50日均线2.145，RSI 59.41未超买，信号偏可靠。</t>
         </is>
       </c>
     </row>
@@ -619,13 +619,13 @@
         </is>
       </c>
       <c r="D3" s="9" t="n">
-        <v>0.775</v>
+        <v>0.77</v>
       </c>
       <c r="E3" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>124097500</v>
+        <v>129678800</v>
       </c>
       <c r="G3" s="12" t="n"/>
       <c r="I3" s="13" t="inlineStr">
@@ -655,19 +655,19 @@
         </is>
       </c>
       <c r="D4" s="9" t="n">
-        <v>0.06</v>
+        <v>0.055</v>
       </c>
       <c r="E4" s="15" t="n">
-        <v>-0.07690000000000001</v>
+        <v>-0.1538</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>116608300</v>
+        <v>128480300</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>0.26</v>
+        <v>0.29</v>
       </c>
       <c r="H4" t="n">
-        <v>21.31</v>
+        <v>20.87</v>
       </c>
       <c r="I4" s="13" t="inlineStr">
         <is>
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="J4" s="9" t="n">
-        <v>0.147</v>
+        <v>0.146</v>
       </c>
       <c r="K4" s="9" t="n">
         <v>0.36</v>
@@ -706,10 +706,10 @@
         <v>-0.0333</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>53229600</v>
+        <v>58661300</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>0.76</v>
+        <v>0.84</v>
       </c>
       <c r="H5" t="n">
         <v>43.8</v>
@@ -745,19 +745,19 @@
         </is>
       </c>
       <c r="D6" s="9" t="n">
-        <v>0.405</v>
+        <v>0.41</v>
       </c>
       <c r="E6" s="16" t="n">
-        <v>0.0385</v>
+        <v>0.0513</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>26592400</v>
+        <v>35750000</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>0.72</v>
+        <v>0.96</v>
       </c>
       <c r="H6" t="n">
-        <v>73.73999999999999</v>
+        <v>74.70999999999999</v>
       </c>
       <c r="I6" s="17" t="inlineStr">
         <is>
@@ -765,7 +765,7 @@
         </is>
       </c>
       <c r="J6" s="9" t="n">
-        <v>0.367</v>
+        <v>0.368</v>
       </c>
       <c r="K6" s="9" t="n">
         <v>0.256</v>
@@ -790,19 +790,19 @@
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.87</v>
+        <v>0.875</v>
       </c>
       <c r="E7" s="16" t="n">
-        <v>0.0175</v>
+        <v>0.0234</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>22816300</v>
+        <v>30701800</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>0.35</v>
+        <v>0.47</v>
       </c>
       <c r="H7" t="n">
-        <v>64.34</v>
+        <v>64.88</v>
       </c>
       <c r="I7" s="17" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="J7" s="9" t="n">
-        <v>0.799</v>
+        <v>0.8</v>
       </c>
       <c r="K7" s="9" t="n">
         <v>0.721</v>
@@ -841,10 +841,10 @@
         <v>-0.0147</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>18021200</v>
+        <v>24636500</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>0.25</v>
+        <v>0.34</v>
       </c>
       <c r="H8" t="n">
         <v>68.87</v>
@@ -871,28 +871,28 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>7020</t>
+          <t>0095</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ASTEEL</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="E9" s="16" t="n">
-        <v>0.1</v>
+        <v>0.155</v>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>13045800</v>
+        <v>17460000</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>4.76</v>
+        <v>0.52</v>
       </c>
       <c r="H9" t="n">
-        <v>60.79</v>
+        <v>48.61</v>
       </c>
       <c r="I9" s="17" t="inlineStr">
         <is>
@@ -900,10 +900,10 @@
         </is>
       </c>
       <c r="J9" s="9" t="n">
-        <v>0.097</v>
+        <v>0.155</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.157</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="14" t="inlineStr"/>
@@ -916,39 +916,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>7020</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>ASTEEL</t>
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="E10" s="15" t="n">
-        <v>-0.0105</v>
+        <v>0.105</v>
+      </c>
+      <c r="E10" s="16" t="n">
+        <v>0.05</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>12329000</v>
+        <v>14954500</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>0.35</v>
+        <v>5.45</v>
       </c>
       <c r="H10" t="n">
-        <v>44.59</v>
-      </c>
-      <c r="I10" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.96</v>
+      </c>
+      <c r="I10" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J10" s="9" t="n">
-        <v>0.489</v>
+        <v>0.097</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>0.482</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="14" t="inlineStr"/>
@@ -961,39 +961,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="E11" s="15" t="n">
-        <v>-0.008</v>
+        <v>1.44</v>
+      </c>
+      <c r="E11" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>11045900</v>
+        <v>13037900</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>0.44</v>
+        <v>1.43</v>
       </c>
       <c r="H11" t="n">
-        <v>66.34999999999999</v>
-      </c>
-      <c r="I11" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>19.46</v>
+      </c>
+      <c r="I11" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J11" s="9" t="n">
-        <v>0.592</v>
+        <v>1.781</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>0.516</v>
+        <v>1.985</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="14" t="inlineStr"/>
@@ -1006,28 +1006,28 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>1.44</v>
+        <v>0.475</v>
       </c>
       <c r="E12" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>10468900</v>
+        <v>12471300</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>1.15</v>
+        <v>0.35</v>
       </c>
       <c r="H12" t="n">
-        <v>19.46</v>
+        <v>46.03</v>
       </c>
       <c r="I12" s="13" t="inlineStr">
         <is>
@@ -1035,10 +1035,10 @@
         </is>
       </c>
       <c r="J12" s="9" t="n">
-        <v>1.781</v>
+        <v>0.49</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>1.985</v>
+        <v>0.482</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="14" t="inlineStr"/>
@@ -1051,39 +1051,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>3.9</v>
+        <v>0.62</v>
       </c>
       <c r="E13" s="15" t="n">
-        <v>-0.0488</v>
+        <v>-0.008</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>9529900</v>
+        <v>11695000</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>1.08</v>
+        <v>0.46</v>
       </c>
       <c r="H13" t="n">
-        <v>50.3</v>
-      </c>
-      <c r="I13" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.34999999999999</v>
+      </c>
+      <c r="I13" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J13" s="9" t="n">
-        <v>3.991</v>
+        <v>0.592</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>3.507</v>
+        <v>0.516</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="14" t="inlineStr"/>
@@ -1096,39 +1096,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0095</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MAG</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="E14" s="10" t="n">
-        <v>0</v>
+        <v>3.84</v>
+      </c>
+      <c r="E14" s="15" t="n">
+        <v>-0.0634</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>9080000</v>
+        <v>10746700</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>0.27</v>
+        <v>1.21</v>
       </c>
       <c r="H14" t="n">
-        <v>48.61</v>
-      </c>
-      <c r="I14" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.36</v>
+      </c>
+      <c r="I14" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J14" s="9" t="n">
-        <v>0.155</v>
+        <v>3.985</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>0.157</v>
+        <v>3.506</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="14" t="inlineStr"/>
@@ -1141,39 +1141,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="E15" s="16" t="n">
-        <v>0.0097</v>
+        <v>0.73</v>
+      </c>
+      <c r="E15" s="15" t="n">
+        <v>-0.09320000000000001</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>8932700</v>
+        <v>10443200</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>0.29</v>
+        <v>0.73</v>
       </c>
       <c r="H15" t="n">
-        <v>63.69</v>
-      </c>
-      <c r="I15" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.71</v>
+      </c>
+      <c r="I15" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J15" s="9" t="n">
-        <v>1.901</v>
+        <v>0.77</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>1.697</v>
+        <v>0.72</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="14" t="inlineStr"/>
@@ -1186,39 +1186,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="E16" s="15" t="n">
-        <v>-0.09320000000000001</v>
+        <v>2.07</v>
+      </c>
+      <c r="E16" s="16" t="n">
+        <v>0.0049</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>8586700</v>
+        <v>9459400</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>0.6</v>
+        <v>0.31</v>
       </c>
       <c r="H16" t="n">
-        <v>45.71</v>
-      </c>
-      <c r="I16" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.29</v>
+      </c>
+      <c r="I16" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J16" s="9" t="n">
-        <v>0.77</v>
+        <v>1.9</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>0.72</v>
+        <v>1.697</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="14" t="inlineStr"/>
@@ -1231,39 +1231,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>7079</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>TWL</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>0.025</v>
+        <v>0.445</v>
       </c>
       <c r="E17" s="16" t="n">
-        <v>0.25</v>
+        <v>0.023</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>7414600</v>
+        <v>8185500</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="H17" t="n">
-        <v>51.85</v>
-      </c>
-      <c r="I17" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.25</v>
+      </c>
+      <c r="I17" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J17" s="9" t="n">
-        <v>0.024</v>
+        <v>0.416</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>0.025</v>
+        <v>0.357</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="14" t="inlineStr"/>
@@ -1276,39 +1276,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>7079</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>TWL</t>
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>0.375</v>
+        <v>0.025</v>
       </c>
       <c r="E18" s="16" t="n">
-        <v>0.0135</v>
+        <v>0.25</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>6325400</v>
+        <v>7414600</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>0.89</v>
+        <v>0.42</v>
       </c>
       <c r="H18" t="n">
-        <v>57.68</v>
-      </c>
-      <c r="I18" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.85</v>
+      </c>
+      <c r="I18" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J18" s="9" t="n">
-        <v>0.369</v>
+        <v>0.024</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>0.369</v>
+        <v>0.025</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="14" t="inlineStr"/>
@@ -1321,28 +1321,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>0.445</v>
+        <v>0.38</v>
       </c>
       <c r="E19" s="16" t="n">
-        <v>0.023</v>
+        <v>0.027</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>5984400</v>
+        <v>6896800</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>0.29</v>
+        <v>0.98</v>
       </c>
       <c r="H19" t="n">
-        <v>61.25</v>
+        <v>61.86</v>
       </c>
       <c r="I19" s="17" t="inlineStr">
         <is>
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="J19" s="9" t="n">
-        <v>0.416</v>
+        <v>0.37</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>0.357</v>
+        <v>0.369</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="14" t="inlineStr"/>
@@ -1366,39 +1366,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>0.355</v>
-      </c>
-      <c r="E20" s="15" t="n">
-        <v>-0.0139</v>
+        <v>0.775</v>
+      </c>
+      <c r="E20" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>5784000</v>
+        <v>6262400</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>0.68</v>
+        <v>0.41</v>
       </c>
       <c r="H20" t="n">
-        <v>55.26</v>
-      </c>
-      <c r="I20" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.46</v>
+      </c>
+      <c r="I20" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J20" s="9" t="n">
-        <v>0.349</v>
+        <v>0.774</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>0.33</v>
+        <v>0.775</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="14" t="inlineStr"/>
@@ -1411,39 +1411,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>0.18</v>
+        <v>0.315</v>
       </c>
       <c r="E21" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>5432300</v>
+        <v>6144000</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>0.23</v>
+        <v>0.32</v>
       </c>
       <c r="H21" t="n">
-        <v>42.98</v>
-      </c>
-      <c r="I21" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.97</v>
+      </c>
+      <c r="I21" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J21" s="9" t="n">
-        <v>0.193</v>
+        <v>0.308</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>0.185</v>
+        <v>0.298</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="14" t="inlineStr"/>
@@ -1456,39 +1456,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E22" s="10" t="n">
-        <v>0</v>
+        <v>0.35</v>
+      </c>
+      <c r="E22" s="15" t="n">
+        <v>-0.0278</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>5013500</v>
+        <v>5867700</v>
       </c>
       <c r="G22" s="12" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="H22" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="I22" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J22" s="9" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="K22" s="9" t="n">
         <v>0.33</v>
-      </c>
-      <c r="H22" t="n">
-        <v>50.46</v>
-      </c>
-      <c r="I22" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J22" s="9" t="n">
-        <v>0.774</v>
-      </c>
-      <c r="K22" s="9" t="n">
-        <v>0.775</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="14" t="inlineStr"/>
@@ -1501,33 +1501,40 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0473</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>EVOCOM</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="E23" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>4901400</v>
+        <v>5463600</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>0.35</v>
+        <v>0.23</v>
+      </c>
+      <c r="H23" t="n">
+        <v>42.98</v>
       </c>
       <c r="I23" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J23" s="9" t="n"/>
-      <c r="K23" s="9" t="n"/>
+      <c r="J23" s="9" t="n">
+        <v>0.193</v>
+      </c>
+      <c r="K23" s="9" t="n">
+        <v>0.185</v>
+      </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="14" t="inlineStr"/>
     </row>
@@ -1539,33 +1546,40 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0476</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>SLG</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E24" s="10" t="n">
-        <v>0</v>
+        <v>7.65</v>
+      </c>
+      <c r="E24" s="16" t="n">
+        <v>0.02</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>4374500</v>
+        <v>5203200</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>0.15</v>
+        <v>0.35</v>
+      </c>
+      <c r="H24" t="n">
+        <v>50.83</v>
       </c>
       <c r="I24" s="17" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J24" s="9" t="n"/>
-      <c r="K24" s="9" t="n"/>
+      <c r="J24" s="9" t="n">
+        <v>7.602</v>
+      </c>
+      <c r="K24" s="9" t="n">
+        <v>7.72</v>
+      </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="14" t="inlineStr"/>
     </row>
@@ -1577,40 +1591,33 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>0473</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>EVOCOM</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>0.41</v>
+        <v>0.1</v>
       </c>
       <c r="E25" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>4330900</v>
+        <v>4970000</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="H25" t="n">
-        <v>39.24</v>
+        <v>0.35</v>
       </c>
       <c r="I25" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J25" s="9" t="n">
-        <v>0.419</v>
-      </c>
-      <c r="K25" s="9" t="n">
-        <v>0.437</v>
-      </c>
+      <c r="J25" s="9" t="n"/>
+      <c r="K25" s="9" t="n"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="14" t="inlineStr"/>
     </row>
@@ -1622,28 +1629,28 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>7.66</v>
-      </c>
-      <c r="E26" s="16" t="n">
-        <v>0.0213</v>
+        <v>2.68</v>
+      </c>
+      <c r="E26" s="15" t="n">
+        <v>-0.0111</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>4293000</v>
+        <v>4693100</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>0.29</v>
+        <v>0.26</v>
       </c>
       <c r="H26" t="n">
-        <v>51.2</v>
+        <v>53.71</v>
       </c>
       <c r="I26" s="17" t="inlineStr">
         <is>
@@ -1651,10 +1658,10 @@
         </is>
       </c>
       <c r="J26" s="9" t="n">
-        <v>7.603</v>
+        <v>2.656</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>7.72</v>
+        <v>2.533</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="14" t="inlineStr"/>
@@ -1667,28 +1674,28 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>7195</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>BNASTRA</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="E27" s="15" t="n">
-        <v>-0.0111</v>
+        <v>2.7</v>
+      </c>
+      <c r="E27" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>4216700</v>
+        <v>4625600</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>0.23</v>
+        <v>4.25</v>
       </c>
       <c r="H27" t="n">
-        <v>53.71</v>
+        <v>82.43000000000001</v>
       </c>
       <c r="I27" s="17" t="inlineStr">
         <is>
@@ -1696,10 +1703,10 @@
         </is>
       </c>
       <c r="J27" s="9" t="n">
-        <v>2.656</v>
+        <v>2.539</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>2.533</v>
+        <v>2.386</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="14" t="inlineStr"/>
@@ -1712,40 +1719,33 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>0476</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>SLG</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>1.09</v>
+        <v>0.245</v>
       </c>
       <c r="E28" s="15" t="n">
-        <v>-0.07629999999999999</v>
+        <v>-0.02</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>4188700</v>
+        <v>4623400</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="H28" t="n">
-        <v>52.9</v>
-      </c>
-      <c r="I28" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J28" s="9" t="n">
-        <v>1.103</v>
-      </c>
-      <c r="K28" s="9" t="n">
-        <v>0.86</v>
-      </c>
+        <v>0.16</v>
+      </c>
+      <c r="I28" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J28" s="9" t="n"/>
+      <c r="K28" s="9" t="n"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="14" t="inlineStr"/>
     </row>
@@ -1757,39 +1757,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="E29" s="15" t="n">
-        <v>-0.0814</v>
+        <v>0.405</v>
+      </c>
+      <c r="E29" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>4018200</v>
+        <v>4521900</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0.92</v>
+        <v>0.36</v>
       </c>
       <c r="H29" t="n">
-        <v>57.25</v>
-      </c>
-      <c r="I29" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.05</v>
+      </c>
+      <c r="I29" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J29" s="9" t="n">
-        <v>2.765</v>
+        <v>0.39</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>2.132</v>
+        <v>0.377</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="14" t="inlineStr"/>
@@ -1802,39 +1802,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>0.585</v>
+        <v>1.09</v>
       </c>
       <c r="E30" s="16" t="n">
-        <v>0.0086</v>
+        <v>0.0283</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>3798600</v>
+        <v>4503700</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>0.19</v>
+        <v>0.46</v>
       </c>
       <c r="H30" t="n">
-        <v>52.99</v>
-      </c>
-      <c r="I30" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.79</v>
+      </c>
+      <c r="I30" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J30" s="9" t="n">
-        <v>0.583</v>
+        <v>1.07</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>0.532</v>
+        <v>1.04</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="14" t="inlineStr"/>
@@ -1847,28 +1847,28 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>0223</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>SAMAIDEN</t>
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="E31" s="16" t="n">
-        <v>0.0108</v>
+        <v>2.83</v>
+      </c>
+      <c r="E31" s="15" t="n">
+        <v>-0.07820000000000001</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>3672900</v>
+        <v>4500700</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>0.67</v>
+        <v>1.03</v>
       </c>
       <c r="H31" t="n">
-        <v>62.32</v>
+        <v>57.66</v>
       </c>
       <c r="I31" s="13" t="inlineStr">
         <is>
@@ -1876,10 +1876,10 @@
         </is>
       </c>
       <c r="J31" s="9" t="n">
-        <v>0.912</v>
+        <v>2.766</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>0.869</v>
+        <v>2.132</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="14" t="inlineStr"/>
@@ -1892,28 +1892,28 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>0.315</v>
+        <v>0.62</v>
       </c>
       <c r="E32" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>3627000</v>
+        <v>4485400</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>0.19</v>
+        <v>0.42</v>
       </c>
       <c r="H32" t="n">
-        <v>61.97</v>
+        <v>54.39</v>
       </c>
       <c r="I32" s="17" t="inlineStr">
         <is>
@@ -1921,10 +1921,10 @@
         </is>
       </c>
       <c r="J32" s="9" t="n">
-        <v>0.308</v>
+        <v>0.614</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>0.298</v>
+        <v>0.613</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="14" t="inlineStr"/>
@@ -1937,39 +1937,39 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="E33" s="15" t="n">
-        <v>-0.0052</v>
+        <v>0.585</v>
+      </c>
+      <c r="E33" s="16" t="n">
+        <v>0.0086</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>3591200</v>
+        <v>4473700</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>0.61</v>
+        <v>0.23</v>
       </c>
       <c r="H33" t="n">
-        <v>45.84</v>
-      </c>
-      <c r="I33" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.99</v>
+      </c>
+      <c r="I33" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J33" s="9" t="n">
-        <v>1.924</v>
+        <v>0.583</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>1.953</v>
+        <v>0.532</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="14" t="inlineStr"/>
@@ -1982,39 +1982,39 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="E34" s="15" t="n">
-        <v>-0.0303</v>
+        <v>0.41</v>
+      </c>
+      <c r="E34" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>3417200</v>
+        <v>4330900</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>0.47</v>
+        <v>2.62</v>
       </c>
       <c r="H34" t="n">
-        <v>68.45</v>
-      </c>
-      <c r="I34" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.24</v>
+      </c>
+      <c r="I34" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J34" s="9" t="n">
-        <v>0.299</v>
+        <v>0.419</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>0.278</v>
+        <v>0.437</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="14" t="inlineStr"/>
@@ -2027,28 +2027,28 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0258</t>
+          <t>0340</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>AGMO</t>
+          <t>NORTHERN</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E35" s="16" t="n">
-        <v>0.0351</v>
+        <v>1.1</v>
+      </c>
+      <c r="E35" s="15" t="n">
+        <v>-0.0678</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>3181300</v>
+        <v>4297400</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>4.24</v>
+        <v>0.55</v>
       </c>
       <c r="H35" t="n">
-        <v>56</v>
+        <v>53.65</v>
       </c>
       <c r="I35" s="13" t="inlineStr">
         <is>
@@ -2056,10 +2056,10 @@
         </is>
       </c>
       <c r="J35" s="9" t="n">
-        <v>0.28</v>
+        <v>1.103</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>0.301</v>
+        <v>0.86</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="14" t="inlineStr"/>
@@ -2072,39 +2072,39 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>0.82</v>
+        <v>0.295</v>
       </c>
       <c r="E36" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>2892800</v>
+        <v>4294000</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>0.17</v>
+        <v>1.51</v>
       </c>
       <c r="H36" t="n">
-        <v>58.27</v>
-      </c>
-      <c r="I36" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.15</v>
+      </c>
+      <c r="I36" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J36" s="9" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.295</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.296</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="14" t="inlineStr"/>
@@ -2117,28 +2117,28 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>7243</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>MAGMA</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>0.285</v>
-      </c>
-      <c r="E37" s="16" t="n">
-        <v>0.0556</v>
+        <v>1.25</v>
+      </c>
+      <c r="E37" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>2884700</v>
+        <v>4172900</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>4.18</v>
+        <v>0.42</v>
       </c>
       <c r="H37" t="n">
-        <v>53.17</v>
+        <v>40.29</v>
       </c>
       <c r="I37" s="13" t="inlineStr">
         <is>
@@ -2146,10 +2146,10 @@
         </is>
       </c>
       <c r="J37" s="9" t="n">
-        <v>0.281</v>
+        <v>1.309</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>0.285</v>
+        <v>1.311</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="14" t="inlineStr"/>
@@ -2162,28 +2162,28 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>0.405</v>
+        <v>0.82</v>
       </c>
       <c r="E38" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>2834100</v>
+        <v>4169800</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>0.23</v>
+        <v>0.25</v>
       </c>
       <c r="H38" t="n">
-        <v>56.05</v>
+        <v>58.27</v>
       </c>
       <c r="I38" s="17" t="inlineStr">
         <is>
@@ -2191,10 +2191,10 @@
         </is>
       </c>
       <c r="J38" s="9" t="n">
-        <v>0.39</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>0.377</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="14" t="inlineStr"/>
@@ -2207,39 +2207,39 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>5336</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CKI</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="E39" s="16" t="n">
-        <v>0.0137</v>
+        <v>0.39</v>
+      </c>
+      <c r="E39" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>2833700</v>
+        <v>4093800</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>1.84</v>
+        <v>0.38</v>
       </c>
       <c r="H39" t="n">
-        <v>51.33</v>
-      </c>
-      <c r="I39" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.84</v>
+      </c>
+      <c r="I39" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J39" s="9" t="n">
-        <v>0.364</v>
+        <v>0.399</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>0.387</v>
+        <v>0.408</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="14" t="inlineStr"/>
@@ -2252,28 +2252,28 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>VELESTO</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="E40" s="16" t="n">
-        <v>0.04650000000000001</v>
+        <v>4.9</v>
+      </c>
+      <c r="E40" s="15" t="n">
+        <v>-0.0101</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>2827400</v>
+        <v>3918100</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>0.13</v>
+        <v>0.15</v>
       </c>
       <c r="H40" t="n">
-        <v>48.41</v>
+        <v>50.88</v>
       </c>
       <c r="I40" s="13" t="inlineStr">
         <is>
@@ -2281,10 +2281,10 @@
         </is>
       </c>
       <c r="J40" s="9" t="n">
-        <v>0.224</v>
+        <v>4.932</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>0.24</v>
+        <v>4.698</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="14" t="inlineStr"/>
@@ -2297,28 +2297,28 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>4.92</v>
-      </c>
-      <c r="E41" s="15" t="n">
-        <v>-0.0061</v>
+        <v>1.92</v>
+      </c>
+      <c r="E41" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>2744600</v>
+        <v>3848600</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>0.11</v>
+        <v>0.65</v>
       </c>
       <c r="H41" t="n">
-        <v>51.92</v>
+        <v>47.51</v>
       </c>
       <c r="I41" s="13" t="inlineStr">
         <is>
@@ -2326,10 +2326,10 @@
         </is>
       </c>
       <c r="J41" s="9" t="n">
-        <v>4.934</v>
+        <v>1.925</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>4.698</v>
+        <v>1.953</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="14" t="inlineStr"/>
@@ -2342,39 +2342,39 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="E42" s="10" t="n">
-        <v>0</v>
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="E42" s="16" t="n">
+        <v>0.0108</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>2703400</v>
+        <v>3847300</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>0.13</v>
+        <v>0.7</v>
       </c>
       <c r="H42" t="n">
-        <v>55.72</v>
-      </c>
-      <c r="I42" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>62.32</v>
+      </c>
+      <c r="I42" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J42" s="9" t="n">
-        <v>2.112</v>
+        <v>0.912</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>2.094</v>
+        <v>0.869</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="14" t="inlineStr"/>
@@ -2387,39 +2387,39 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="E43" s="16" t="n">
-        <v>0.009399999999999999</v>
+        <v>2.12</v>
+      </c>
+      <c r="E43" s="15" t="n">
+        <v>-0.009300000000000001</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>2669200</v>
+        <v>3694600</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>0.27</v>
+        <v>0.18</v>
       </c>
       <c r="H43" t="n">
-        <v>50.92</v>
-      </c>
-      <c r="I43" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.35</v>
+      </c>
+      <c r="I43" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J43" s="9" t="n">
-        <v>1.068</v>
+        <v>2.11</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>1.04</v>
+        <v>2.094</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="14" t="inlineStr"/>
@@ -2432,28 +2432,28 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D44" s="9" t="n">
-        <v>4.79</v>
-      </c>
-      <c r="E44" s="16" t="n">
-        <v>0.0191</v>
+        <v>0.865</v>
+      </c>
+      <c r="E44" s="15" t="n">
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>2644700</v>
+        <v>3583300</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0.15</v>
+        <v>0.18</v>
       </c>
       <c r="H44" t="n">
-        <v>53.81</v>
+        <v>46.29</v>
       </c>
       <c r="I44" s="17" t="inlineStr">
         <is>
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="J44" s="9" t="n">
-        <v>4.722</v>
+        <v>0.868</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>4.871</v>
+        <v>0.869</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="14" t="inlineStr"/>
@@ -2477,39 +2477,39 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>0.445</v>
+        <v>0.32</v>
       </c>
       <c r="E45" s="15" t="n">
-        <v>-0.0111</v>
+        <v>-0.0303</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>2630600</v>
+        <v>3535600</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.49</v>
       </c>
       <c r="H45" t="n">
-        <v>23.61</v>
-      </c>
-      <c r="I45" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>68.45</v>
+      </c>
+      <c r="I45" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J45" s="9" t="n">
-        <v>0.524</v>
+        <v>0.299</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>0.713</v>
+        <v>0.278</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="14" t="inlineStr"/>
@@ -2522,28 +2522,28 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>0258</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>AGMO</t>
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>0.68</v>
+        <v>0.29</v>
       </c>
       <c r="E46" s="16" t="n">
-        <v>0.0149</v>
+        <v>0.0175</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>2607800</v>
+        <v>3399700</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0.29</v>
+        <v>4.53</v>
       </c>
       <c r="H46" t="n">
-        <v>48.33</v>
+        <v>53.95</v>
       </c>
       <c r="I46" s="13" t="inlineStr">
         <is>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="J46" s="9" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.28</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.301</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="14" t="inlineStr"/>
@@ -2567,28 +2567,28 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>WCT</t>
+          <t>IOICORP</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>0.31</v>
+        <v>4.55</v>
       </c>
       <c r="E47" s="15" t="n">
-        <v>-0.0159</v>
+        <v>-0.0022</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>2570300</v>
+        <v>3372300</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>0.51</v>
+        <v>0.35</v>
       </c>
       <c r="H47" t="n">
-        <v>24.94</v>
+        <v>39.27</v>
       </c>
       <c r="I47" s="13" t="inlineStr">
         <is>
@@ -2596,10 +2596,10 @@
         </is>
       </c>
       <c r="J47" s="9" t="n">
-        <v>0.35</v>
+        <v>4.644</v>
       </c>
       <c r="K47" s="9" t="n">
-        <v>0.379</v>
+        <v>4.63</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="14" t="inlineStr"/>
@@ -2612,39 +2612,39 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D48" s="9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="E48" s="16" t="n">
-        <v>0.0352</v>
+        <v>0.45</v>
+      </c>
+      <c r="E48" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>2517900</v>
+        <v>3220800</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>0.71</v>
+        <v>0.08</v>
       </c>
       <c r="H48" t="n">
-        <v>84.3</v>
-      </c>
-      <c r="I48" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>24.11</v>
+      </c>
+      <c r="I48" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J48" s="9" t="n">
-        <v>0.749</v>
+        <v>0.524</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>0.523</v>
+        <v>0.713</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="14" t="inlineStr"/>
@@ -2657,28 +2657,28 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E49" s="15" t="n">
-        <v>-0.005699999999999999</v>
+        <v>4.79</v>
+      </c>
+      <c r="E49" s="16" t="n">
+        <v>0.0191</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>2513500</v>
+        <v>3091900</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>0.13</v>
+        <v>0.18</v>
       </c>
       <c r="H49" t="n">
-        <v>46.29</v>
+        <v>53.81</v>
       </c>
       <c r="I49" s="17" t="inlineStr">
         <is>
@@ -2686,10 +2686,10 @@
         </is>
       </c>
       <c r="J49" s="9" t="n">
-        <v>0.868</v>
+        <v>4.722</v>
       </c>
       <c r="K49" s="9" t="n">
-        <v>0.869</v>
+        <v>4.871</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="14" t="inlineStr"/>
@@ -2702,28 +2702,28 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D50" s="9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="E50" s="16" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.315</v>
+      </c>
+      <c r="E50" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>2436300</v>
+        <v>2906800</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>0.16</v>
+        <v>0.58</v>
       </c>
       <c r="H50" t="n">
-        <v>39.77</v>
+        <v>26.24</v>
       </c>
       <c r="I50" s="13" t="inlineStr">
         <is>
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="J50" s="9" t="n">
-        <v>2.192</v>
+        <v>0.351</v>
       </c>
       <c r="K50" s="9" t="n">
-        <v>2.225</v>
+        <v>0.379</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="14" t="inlineStr"/>
@@ -2747,39 +2747,39 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="E51" s="10" t="n">
-        <v>0</v>
+        <v>0.47</v>
+      </c>
+      <c r="E51" s="15" t="n">
+        <v>-0.0105</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>2431400</v>
+        <v>2900300</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>0.23</v>
+        <v>0.42</v>
       </c>
       <c r="H51" t="n">
-        <v>54.39</v>
-      </c>
-      <c r="I51" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>22.01</v>
+      </c>
+      <c r="I51" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J51" s="9" t="n">
-        <v>0.614</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="K51" s="9" t="n">
-        <v>0.613</v>
+        <v>0.629</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="14" t="inlineStr"/>
@@ -2792,28 +2792,28 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>7243</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>MAGMA</t>
         </is>
       </c>
       <c r="D52" s="9" t="n">
-        <v>1.26</v>
+        <v>0.285</v>
       </c>
       <c r="E52" s="16" t="n">
-        <v>0.008</v>
+        <v>0.0556</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>2399200</v>
+        <v>2884700</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>0.62</v>
+        <v>4.18</v>
       </c>
       <c r="H52" t="n">
-        <v>23.74</v>
+        <v>53.17</v>
       </c>
       <c r="I52" s="13" t="inlineStr">
         <is>
@@ -2821,10 +2821,10 @@
         </is>
       </c>
       <c r="J52" s="9" t="n">
-        <v>1.441</v>
+        <v>0.281</v>
       </c>
       <c r="K52" s="9" t="n">
-        <v>1.59</v>
+        <v>0.285</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="14" t="inlineStr"/>
@@ -2837,39 +2837,39 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D53" s="9" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="E53" s="10" t="n">
-        <v>0</v>
+        <v>1.27</v>
+      </c>
+      <c r="E53" s="16" t="n">
+        <v>0.016</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>2397600</v>
+        <v>2857800</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>0.76</v>
+        <v>0.74</v>
       </c>
       <c r="H53" t="n">
-        <v>79.09999999999999</v>
-      </c>
-      <c r="I53" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>25.43</v>
+      </c>
+      <c r="I53" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J53" s="9" t="n">
-        <v>2.732</v>
+        <v>1.442</v>
       </c>
       <c r="K53" s="9" t="n">
-        <v>2.357</v>
+        <v>1.59</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="14" t="inlineStr"/>
@@ -2882,28 +2882,28 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D54" s="9" t="n">
-        <v>0.66</v>
+        <v>2.09</v>
       </c>
       <c r="E54" s="16" t="n">
-        <v>0.0076</v>
+        <v>0.0048</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>2254400</v>
+        <v>2854700</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>0.26</v>
+        <v>0.19</v>
       </c>
       <c r="H54" t="n">
-        <v>50.26</v>
+        <v>38.63</v>
       </c>
       <c r="I54" s="13" t="inlineStr">
         <is>
@@ -2911,10 +2911,10 @@
         </is>
       </c>
       <c r="J54" s="9" t="n">
-        <v>0.67</v>
+        <v>2.191</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>0.617</v>
+        <v>2.225</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="14" t="inlineStr"/>
@@ -2927,39 +2927,39 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>5336</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>CKI</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>0.215</v>
-      </c>
-      <c r="E55" s="10" t="n">
-        <v>0</v>
+        <v>0.37</v>
+      </c>
+      <c r="E55" s="16" t="n">
+        <v>0.0137</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>2220700</v>
+        <v>2835200</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>0.08</v>
+        <v>1.84</v>
       </c>
       <c r="H55" t="n">
-        <v>30.12</v>
-      </c>
-      <c r="I55" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.33</v>
+      </c>
+      <c r="I55" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J55" s="9" t="n">
-        <v>0.241</v>
+        <v>0.364</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>0.295</v>
+        <v>0.387</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="14" t="inlineStr"/>
@@ -2972,39 +2972,39 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>VELESTO</t>
         </is>
       </c>
       <c r="D56" s="9" t="n">
-        <v>0.805</v>
-      </c>
-      <c r="E56" s="10" t="n">
-        <v>0</v>
+        <v>0.225</v>
+      </c>
+      <c r="E56" s="16" t="n">
+        <v>0.04650000000000001</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>2163300</v>
+        <v>2834300</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>0.36</v>
+        <v>0.13</v>
       </c>
       <c r="H56" t="n">
-        <v>66.90000000000001</v>
-      </c>
-      <c r="I56" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.41</v>
+      </c>
+      <c r="I56" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J56" s="9" t="n">
-        <v>0.791</v>
+        <v>0.224</v>
       </c>
       <c r="K56" s="9" t="n">
-        <v>0.768</v>
+        <v>0.24</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="14" t="inlineStr"/>
@@ -3026,19 +3026,19 @@
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="E57" s="10" t="n">
-        <v>0</v>
+        <v>1.04</v>
+      </c>
+      <c r="E57" s="15" t="n">
+        <v>-0.0095</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>2159800</v>
+        <v>2719200</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>0.26</v>
+        <v>0.32</v>
       </c>
       <c r="H57" t="n">
-        <v>50.62</v>
+        <v>49.14</v>
       </c>
       <c r="I57" s="13" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
         </is>
       </c>
       <c r="J57" s="9" t="n">
-        <v>1.07</v>
+        <v>1.069</v>
       </c>
       <c r="K57" s="9" t="n">
         <v>0.9409999999999999</v>
@@ -3062,28 +3062,28 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D58" s="9" t="n">
-        <v>1.22</v>
+        <v>0.68</v>
       </c>
       <c r="E58" s="16" t="n">
-        <v>0.0083</v>
+        <v>0.0149</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>2096900</v>
+        <v>2661800</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>0.26</v>
+        <v>0.3</v>
       </c>
       <c r="H58" t="n">
-        <v>40.63</v>
+        <v>48.33</v>
       </c>
       <c r="I58" s="13" t="inlineStr">
         <is>
@@ -3091,10 +3091,10 @@
         </is>
       </c>
       <c r="J58" s="9" t="n">
-        <v>1.248</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="K58" s="9" t="n">
-        <v>1.343</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="14" t="inlineStr"/>
@@ -3107,39 +3107,39 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>3.73</v>
+        <v>1.03</v>
       </c>
       <c r="E59" s="16" t="n">
-        <v>0.0275</v>
+        <v>0.0352</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>2082300</v>
+        <v>2658200</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>0.21</v>
+        <v>0.75</v>
       </c>
       <c r="H59" t="n">
-        <v>56.58</v>
-      </c>
-      <c r="I59" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>84.3</v>
+      </c>
+      <c r="I59" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J59" s="9" t="n">
-        <v>3.608</v>
+        <v>0.749</v>
       </c>
       <c r="K59" s="9" t="n">
-        <v>2.871</v>
+        <v>0.523</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="14" t="inlineStr"/>
@@ -3152,28 +3152,28 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="E60" s="15" t="n">
-        <v>-0.0462</v>
+        <v>0.215</v>
+      </c>
+      <c r="E60" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>2071000</v>
+        <v>2641600</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>0.63</v>
+        <v>0.1</v>
       </c>
       <c r="H60" t="n">
-        <v>53.25</v>
+        <v>30.12</v>
       </c>
       <c r="I60" s="13" t="inlineStr">
         <is>
@@ -3181,10 +3181,10 @@
         </is>
       </c>
       <c r="J60" s="9" t="n">
-        <v>1.255</v>
+        <v>0.241</v>
       </c>
       <c r="K60" s="9" t="n">
-        <v>1.041</v>
+        <v>0.295</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="14" t="inlineStr"/>
@@ -3197,28 +3197,28 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>AMBANK</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="E61" s="15" t="n">
-        <v>-0.0105</v>
+        <v>6.45</v>
+      </c>
+      <c r="E61" s="16" t="n">
+        <v>0.0287</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>2058000</v>
+        <v>2604800</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>0.3</v>
+        <v>0.46</v>
       </c>
       <c r="H61" t="n">
-        <v>22.01</v>
+        <v>47.84</v>
       </c>
       <c r="I61" s="13" t="inlineStr">
         <is>
@@ -3226,10 +3226,10 @@
         </is>
       </c>
       <c r="J61" s="9" t="n">
-        <v>0.5620000000000001</v>
+        <v>6.429</v>
       </c>
       <c r="K61" s="9" t="n">
-        <v>0.629</v>
+        <v>6.805</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="14" t="inlineStr"/>
@@ -3242,39 +3242,39 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>AMBANK</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D62" s="9" t="n">
-        <v>6.47</v>
-      </c>
-      <c r="E62" s="16" t="n">
-        <v>0.0319</v>
+        <v>2.99</v>
+      </c>
+      <c r="E62" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>2032500</v>
+        <v>2591600</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>0.36</v>
+        <v>0.82</v>
       </c>
       <c r="H62" t="n">
-        <v>48.82</v>
-      </c>
-      <c r="I62" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I62" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J62" s="9" t="n">
-        <v>6.431</v>
+        <v>2.732</v>
       </c>
       <c r="K62" s="9" t="n">
-        <v>6.805</v>
+        <v>2.357</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="14" t="inlineStr"/>
@@ -3287,28 +3287,28 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0471</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>PIONEER</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="E63" s="16" t="n">
-        <v>0.0476</v>
+        <v>0.805</v>
+      </c>
+      <c r="E63" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>1984300</v>
+        <v>2590400</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>0.22</v>
+        <v>0.44</v>
       </c>
       <c r="H63" t="n">
-        <v>58.79</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="I63" s="17" t="inlineStr">
         <is>
@@ -3316,9 +3316,11 @@
         </is>
       </c>
       <c r="J63" s="9" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="K63" s="9" t="n"/>
+        <v>0.791</v>
+      </c>
+      <c r="K63" s="9" t="n">
+        <v>0.768</v>
+      </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="14" t="inlineStr"/>
     </row>
@@ -3339,19 +3341,19 @@
         </is>
       </c>
       <c r="D64" s="9" t="n">
-        <v>9.98</v>
+        <v>9.99</v>
       </c>
       <c r="E64" s="16" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>1976000</v>
+        <v>2488900</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="H64" t="n">
-        <v>45.15</v>
+        <v>45.88</v>
       </c>
       <c r="I64" s="13" t="inlineStr">
         <is>
@@ -3359,7 +3361,7 @@
         </is>
       </c>
       <c r="J64" s="9" t="n">
-        <v>10.007</v>
+        <v>10.008</v>
       </c>
       <c r="K64" s="9" t="n">
         <v>10.178</v>
@@ -3375,28 +3377,28 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E65" s="10" t="n">
-        <v>0</v>
+        <v>1.2</v>
+      </c>
+      <c r="E65" s="15" t="n">
+        <v>-0.0083</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>1873900</v>
+        <v>2411700</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="H65" t="n">
-        <v>43.41</v>
+        <v>37.03</v>
       </c>
       <c r="I65" s="13" t="inlineStr">
         <is>
@@ -3404,10 +3406,10 @@
         </is>
       </c>
       <c r="J65" s="9" t="n">
-        <v>0.517</v>
+        <v>1.246</v>
       </c>
       <c r="K65" s="9" t="n">
-        <v>0.529</v>
+        <v>1.342</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="14" t="inlineStr"/>
@@ -3420,28 +3422,28 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D66" s="9" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="E66" s="16" t="n">
-        <v>0.008</v>
+        <v>1.23</v>
+      </c>
+      <c r="E66" s="15" t="n">
+        <v>-0.0538</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>1818900</v>
+        <v>2349000</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>0.18</v>
+        <v>0.72</v>
       </c>
       <c r="H66" t="n">
-        <v>41.98</v>
+        <v>52.29</v>
       </c>
       <c r="I66" s="13" t="inlineStr">
         <is>
@@ -3449,10 +3451,10 @@
         </is>
       </c>
       <c r="J66" s="9" t="n">
-        <v>1.31</v>
+        <v>1.254</v>
       </c>
       <c r="K66" s="9" t="n">
-        <v>1.311</v>
+        <v>1.041</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="14" t="inlineStr"/>
@@ -3465,28 +3467,28 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D67" s="9" t="n">
-        <v>0.61</v>
+        <v>3.73</v>
       </c>
       <c r="E67" s="16" t="n">
-        <v>0.0167</v>
+        <v>0.0275</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>1806000</v>
+        <v>2312200</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>0.43</v>
+        <v>0.24</v>
       </c>
       <c r="H67" t="n">
-        <v>53.75</v>
+        <v>56.58</v>
       </c>
       <c r="I67" s="13" t="inlineStr">
         <is>
@@ -3494,10 +3496,10 @@
         </is>
       </c>
       <c r="J67" s="9" t="n">
-        <v>0.601</v>
+        <v>3.608</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>0.585</v>
+        <v>2.871</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="14" t="inlineStr"/>
@@ -3510,28 +3512,28 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D68" s="9" t="n">
-        <v>2.77</v>
+        <v>0.495</v>
       </c>
       <c r="E68" s="15" t="n">
-        <v>-0.0177</v>
+        <v>-0.01</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>1805200</v>
+        <v>2279100</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>0.13</v>
+        <v>0.27</v>
       </c>
       <c r="H68" t="n">
-        <v>49.37</v>
+        <v>42.01</v>
       </c>
       <c r="I68" s="13" t="inlineStr">
         <is>
@@ -3539,10 +3541,10 @@
         </is>
       </c>
       <c r="J68" s="9" t="n">
-        <v>2.795</v>
+        <v>0.517</v>
       </c>
       <c r="K68" s="9" t="n">
-        <v>2.721</v>
+        <v>0.529</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="14" t="inlineStr"/>
@@ -3555,28 +3557,28 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0233</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>PEKAT</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D69" s="9" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="E69" s="15" t="n">
-        <v>-0.0825</v>
+        <v>0.66</v>
+      </c>
+      <c r="E69" s="16" t="n">
+        <v>0.0076</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>1647600</v>
+        <v>2274400</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>0.51</v>
+        <v>0.26</v>
       </c>
       <c r="H69" t="n">
-        <v>55.09</v>
+        <v>50.26</v>
       </c>
       <c r="I69" s="13" t="inlineStr">
         <is>
@@ -3584,10 +3586,10 @@
         </is>
       </c>
       <c r="J69" s="9" t="n">
-        <v>2.669</v>
+        <v>0.67</v>
       </c>
       <c r="K69" s="9" t="n">
-        <v>2.206</v>
+        <v>0.617</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="14" t="inlineStr"/>
@@ -3600,40 +3602,38 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0272</t>
+          <t>0471</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>TTVHB</t>
+          <t>PIONEER</t>
         </is>
       </c>
       <c r="D70" s="9" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="E70" s="16" t="n">
+        <v>0.0476</v>
+      </c>
+      <c r="F70" s="11" t="n">
+        <v>2263100</v>
+      </c>
+      <c r="G70" s="12" t="n">
         <v>0.25</v>
       </c>
-      <c r="E70" s="16" t="n">
-        <v>0.0204</v>
-      </c>
-      <c r="F70" s="11" t="n">
-        <v>1585800</v>
-      </c>
-      <c r="G70" s="12" t="n">
-        <v>0.68</v>
-      </c>
       <c r="H70" t="n">
-        <v>49.61</v>
-      </c>
-      <c r="I70" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.79</v>
+      </c>
+      <c r="I70" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J70" s="9" t="n">
-        <v>0.251</v>
-      </c>
-      <c r="K70" s="9" t="n">
-        <v>0.255</v>
-      </c>
+        <v>0.305</v>
+      </c>
+      <c r="K70" s="9" t="n"/>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="14" t="inlineStr"/>
     </row>
@@ -3645,28 +3645,28 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="E71" s="15" t="n">
-        <v>-0.0377</v>
+        <v>0.6</v>
+      </c>
+      <c r="E71" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>1486500</v>
+        <v>2176600</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>0.32</v>
+        <v>0.52</v>
       </c>
       <c r="H71" t="n">
-        <v>48.75</v>
+        <v>51.48</v>
       </c>
       <c r="I71" s="13" t="inlineStr">
         <is>
@@ -3674,10 +3674,10 @@
         </is>
       </c>
       <c r="J71" s="9" t="n">
-        <v>1.057</v>
+        <v>0.6</v>
       </c>
       <c r="K71" s="9" t="n">
-        <v>0.919</v>
+        <v>0.585</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="14" t="inlineStr"/>
@@ -3690,39 +3690,39 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>0272</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>TTVHB</t>
         </is>
       </c>
       <c r="D72" s="9" t="n">
-        <v>0.425</v>
-      </c>
-      <c r="E72" s="16" t="n">
-        <v>0.0119</v>
+        <v>0.245</v>
+      </c>
+      <c r="E72" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>1461500</v>
+        <v>2051900</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>0.21</v>
+        <v>0.88</v>
       </c>
       <c r="H72" t="n">
-        <v>50.96</v>
-      </c>
-      <c r="I72" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.66</v>
+      </c>
+      <c r="I72" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J72" s="9" t="n">
-        <v>0.427</v>
+        <v>0.25</v>
       </c>
       <c r="K72" s="9" t="n">
-        <v>0.415</v>
+        <v>0.255</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="14" t="inlineStr"/>
@@ -3735,28 +3735,28 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0376</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>IAB</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D73" s="9" t="n">
-        <v>1.17</v>
+        <v>2.77</v>
       </c>
       <c r="E73" s="15" t="n">
-        <v>-0.008500000000000001</v>
+        <v>-0.0177</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>1443500</v>
+        <v>1977200</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>0.64</v>
+        <v>0.14</v>
       </c>
       <c r="H73" t="n">
-        <v>40.26</v>
+        <v>49.37</v>
       </c>
       <c r="I73" s="13" t="inlineStr">
         <is>
@@ -3764,10 +3764,10 @@
         </is>
       </c>
       <c r="J73" s="9" t="n">
-        <v>1.251</v>
+        <v>2.795</v>
       </c>
       <c r="K73" s="9" t="n">
-        <v>1.309</v>
+        <v>2.721</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="14" t="inlineStr"/>
@@ -3780,28 +3780,28 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>0296</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>HEGROUP</t>
         </is>
       </c>
       <c r="D74" s="9" t="n">
-        <v>2.57</v>
+        <v>1</v>
       </c>
       <c r="E74" s="15" t="n">
-        <v>-0.0039</v>
+        <v>-0.0566</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>1415900</v>
+        <v>1888700</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>0.23</v>
+        <v>0.41</v>
       </c>
       <c r="H74" t="n">
-        <v>46.48</v>
+        <v>46.1</v>
       </c>
       <c r="I74" s="13" t="inlineStr">
         <is>
@@ -3809,10 +3809,10 @@
         </is>
       </c>
       <c r="J74" s="9" t="n">
-        <v>2.627</v>
+        <v>1.055</v>
       </c>
       <c r="K74" s="9" t="n">
-        <v>2.597</v>
+        <v>0.919</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="14" t="inlineStr"/>
@@ -3825,28 +3825,28 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>0233</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>PEKAT</t>
         </is>
       </c>
       <c r="D75" s="9" t="n">
-        <v>0.91</v>
+        <v>2.69</v>
       </c>
       <c r="E75" s="15" t="n">
-        <v>-0.0109</v>
+        <v>-0.0756</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>1390700</v>
+        <v>1848500</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>0.17</v>
+        <v>0.57</v>
       </c>
       <c r="H75" t="n">
-        <v>46.74</v>
+        <v>56.18</v>
       </c>
       <c r="I75" s="13" t="inlineStr">
         <is>
@@ -3854,10 +3854,10 @@
         </is>
       </c>
       <c r="J75" s="9" t="n">
-        <v>0.95</v>
+        <v>2.671</v>
       </c>
       <c r="K75" s="9" t="n">
-        <v>0.837</v>
+        <v>2.206</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="14" t="inlineStr"/>
@@ -3870,28 +3870,28 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D76" s="9" t="n">
-        <v>5.47</v>
-      </c>
-      <c r="E76" s="15" t="n">
-        <v>-0.005500000000000001</v>
+        <v>1.19</v>
+      </c>
+      <c r="E76" s="16" t="n">
+        <v>0.0259</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>1289800</v>
+        <v>1762800</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>0.09</v>
+        <v>0.23</v>
       </c>
       <c r="H76" t="n">
-        <v>45.57</v>
+        <v>54.4</v>
       </c>
       <c r="I76" s="13" t="inlineStr">
         <is>
@@ -3899,10 +3899,10 @@
         </is>
       </c>
       <c r="J76" s="9" t="n">
-        <v>5.605</v>
+        <v>1.163</v>
       </c>
       <c r="K76" s="9" t="n">
-        <v>5.388</v>
+        <v>1.127</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="14" t="inlineStr"/>
@@ -3915,39 +3915,39 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>0388</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>SEMICO</t>
         </is>
       </c>
       <c r="D77" s="9" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E77" s="15" t="n">
-        <v>-0.0064</v>
+        <v>0.62</v>
+      </c>
+      <c r="E77" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>1243800</v>
+        <v>1675700</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>0.15</v>
+        <v>0.54</v>
       </c>
       <c r="H77" t="n">
-        <v>49.19</v>
-      </c>
-      <c r="I77" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.41</v>
+      </c>
+      <c r="I77" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J77" s="9" t="n">
-        <v>0.779</v>
+        <v>0.615</v>
       </c>
       <c r="K77" s="9" t="n">
-        <v>0.773</v>
+        <v>0.602</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="14" t="inlineStr"/>
@@ -3960,28 +3960,28 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0372</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>CHEEDING</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D78" s="9" t="n">
-        <v>0.575</v>
+        <v>0.775</v>
       </c>
       <c r="E78" s="15" t="n">
-        <v>-0.0086</v>
+        <v>-0.0064</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>1242900</v>
+        <v>1669800</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>0.31</v>
+        <v>0.2</v>
       </c>
       <c r="H78" t="n">
-        <v>41.75</v>
+        <v>49.19</v>
       </c>
       <c r="I78" s="13" t="inlineStr">
         <is>
@@ -3989,10 +3989,10 @@
         </is>
       </c>
       <c r="J78" s="9" t="n">
-        <v>0.606</v>
+        <v>0.779</v>
       </c>
       <c r="K78" s="9" t="n">
-        <v>0.606</v>
+        <v>0.773</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="14" t="inlineStr"/>
@@ -4005,39 +4005,39 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D79" s="9" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="E79" s="16" t="n">
-        <v>0.0126</v>
+        <v>0.905</v>
+      </c>
+      <c r="E79" s="15" t="n">
+        <v>-0.0163</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>1208300</v>
+        <v>1586200</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="H79" t="n">
-        <v>46.72</v>
-      </c>
-      <c r="I79" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.02</v>
+      </c>
+      <c r="I79" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J79" s="9" t="n">
-        <v>1.613</v>
+        <v>0.95</v>
       </c>
       <c r="K79" s="9" t="n">
-        <v>1.709</v>
+        <v>0.837</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="14" t="inlineStr"/>
@@ -4050,28 +4050,28 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D80" s="9" t="n">
-        <v>0.645</v>
-      </c>
-      <c r="E80" s="16" t="n">
-        <v>0.0238</v>
+        <v>5.46</v>
+      </c>
+      <c r="E80" s="15" t="n">
+        <v>-0.0073</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>1206400</v>
+        <v>1582500</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>0.23</v>
+        <v>0.11</v>
       </c>
       <c r="H80" t="n">
-        <v>66.98999999999999</v>
+        <v>45.19</v>
       </c>
       <c r="I80" s="13" t="inlineStr">
         <is>
@@ -4079,10 +4079,10 @@
         </is>
       </c>
       <c r="J80" s="9" t="n">
-        <v>0.554</v>
+        <v>5.604</v>
       </c>
       <c r="K80" s="9" t="n">
-        <v>0.458</v>
+        <v>5.388</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="14" t="inlineStr"/>
@@ -4095,28 +4095,28 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>0376</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>IAB</t>
         </is>
       </c>
       <c r="D81" s="9" t="n">
-        <v>7.35</v>
-      </c>
-      <c r="E81" s="16" t="n">
-        <v>0.0068</v>
+        <v>1.17</v>
+      </c>
+      <c r="E81" s="15" t="n">
+        <v>-0.008500000000000001</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>1179600</v>
+        <v>1572700</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>0.12</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H81" t="n">
-        <v>35.49</v>
+        <v>40.26</v>
       </c>
       <c r="I81" s="13" t="inlineStr">
         <is>
@@ -4124,10 +4124,10 @@
         </is>
       </c>
       <c r="J81" s="9" t="n">
-        <v>7.522</v>
+        <v>1.251</v>
       </c>
       <c r="K81" s="9" t="n">
-        <v>8.026999999999999</v>
+        <v>1.309</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="14" t="inlineStr"/>
@@ -4140,28 +4140,28 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0104</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>GENETEC</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D82" s="9" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="E82" s="10" t="n">
-        <v>0</v>
+        <v>2.56</v>
+      </c>
+      <c r="E82" s="15" t="n">
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>1166400</v>
+        <v>1483500</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>0.19</v>
+        <v>0.24</v>
       </c>
       <c r="H82" t="n">
-        <v>40.49</v>
+        <v>45.83</v>
       </c>
       <c r="I82" s="13" t="inlineStr">
         <is>
@@ -4169,10 +4169,10 @@
         </is>
       </c>
       <c r="J82" s="9" t="n">
-        <v>0.321</v>
+        <v>2.626</v>
       </c>
       <c r="K82" s="9" t="n">
-        <v>0.338</v>
+        <v>2.597</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="14" t="inlineStr"/>
@@ -4185,28 +4185,28 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0468</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>UNIPAC</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D83" s="9" t="n">
-        <v>0.23</v>
+        <v>2.43</v>
       </c>
       <c r="E83" s="15" t="n">
-        <v>-0.0213</v>
+        <v>-0.0122</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>1090700</v>
+        <v>1480900</v>
       </c>
       <c r="G83" s="12" t="n">
         <v>0.12</v>
       </c>
       <c r="H83" t="n">
-        <v>24.97</v>
+        <v>48.22</v>
       </c>
       <c r="I83" s="13" t="inlineStr">
         <is>
@@ -4214,9 +4214,11 @@
         </is>
       </c>
       <c r="J83" s="9" t="n">
-        <v>0.257</v>
-      </c>
-      <c r="K83" s="9" t="n"/>
+        <v>2.459</v>
+      </c>
+      <c r="K83" s="9" t="n">
+        <v>2.367</v>
+      </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="14" t="inlineStr"/>
     </row>
@@ -4228,39 +4230,39 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D84" s="9" t="n">
-        <v>0.535</v>
+        <v>7.38</v>
       </c>
       <c r="E84" s="16" t="n">
-        <v>0.009399999999999999</v>
+        <v>0.0179</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>1076200</v>
+        <v>1474200</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.19</v>
       </c>
       <c r="H84" t="n">
-        <v>55.88</v>
-      </c>
-      <c r="I84" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.49</v>
+      </c>
+      <c r="I84" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J84" s="9" t="n">
-        <v>0.519</v>
+        <v>7.38</v>
       </c>
       <c r="K84" s="9" t="n">
-        <v>0.45</v>
+        <v>7.687</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="14" t="inlineStr"/>
@@ -4273,28 +4275,28 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>AWC</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D85" s="9" t="n">
-        <v>0.6850000000000001</v>
-      </c>
-      <c r="E85" s="15" t="n">
-        <v>-0.0072</v>
+        <v>0.425</v>
+      </c>
+      <c r="E85" s="16" t="n">
+        <v>0.0119</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>1073700</v>
+        <v>1461500</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>0.46</v>
+        <v>0.21</v>
       </c>
       <c r="H85" t="n">
-        <v>64.98999999999999</v>
+        <v>50.96</v>
       </c>
       <c r="I85" s="17" t="inlineStr">
         <is>
@@ -4302,10 +4304,10 @@
         </is>
       </c>
       <c r="J85" s="9" t="n">
-        <v>0.636</v>
+        <v>0.427</v>
       </c>
       <c r="K85" s="9" t="n">
-        <v>0.543</v>
+        <v>0.415</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="14" t="inlineStr"/>
@@ -4318,28 +4320,28 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>0398</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>GDGROUP</t>
         </is>
       </c>
       <c r="D86" s="9" t="n">
-        <v>0.835</v>
-      </c>
-      <c r="E86" s="16" t="n">
-        <v>0.0121</v>
+        <v>0.38</v>
+      </c>
+      <c r="E86" s="15" t="n">
+        <v>-0.013</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>1067500</v>
+        <v>1454500</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>0.28</v>
+        <v>1.63</v>
       </c>
       <c r="H86" t="n">
-        <v>53.55</v>
+        <v>49.68</v>
       </c>
       <c r="I86" s="17" t="inlineStr">
         <is>
@@ -4347,10 +4349,10 @@
         </is>
       </c>
       <c r="J86" s="9" t="n">
-        <v>0.829</v>
+        <v>0.381</v>
       </c>
       <c r="K86" s="9" t="n">
-        <v>0.771</v>
+        <v>0.379</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="14" t="inlineStr"/>
@@ -4363,28 +4365,28 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D87" s="9" t="n">
-        <v>4.35</v>
+        <v>1.22</v>
       </c>
       <c r="E87" s="16" t="n">
-        <v>0.0069</v>
+        <v>0.0167</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>1062800</v>
+        <v>1453500</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>0.16</v>
+        <v>0.25</v>
       </c>
       <c r="H87" t="n">
-        <v>48.43</v>
+        <v>57.43</v>
       </c>
       <c r="I87" s="17" t="inlineStr">
         <is>
@@ -4392,10 +4394,10 @@
         </is>
       </c>
       <c r="J87" s="9" t="n">
-        <v>4.357</v>
+        <v>1.171</v>
       </c>
       <c r="K87" s="9" t="n">
-        <v>4.441</v>
+        <v>1.176</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="14" t="inlineStr"/>
@@ -4408,39 +4410,39 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>5932</t>
+          <t>5329</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>BPURI</t>
+          <t>AZAMJAYA</t>
         </is>
       </c>
       <c r="D88" s="9" t="n">
-        <v>0.215</v>
-      </c>
-      <c r="E88" s="10" t="n">
-        <v>0</v>
+        <v>0.99</v>
+      </c>
+      <c r="E88" s="16" t="n">
+        <v>0.0421</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>1055800</v>
+        <v>1445500</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>2.34</v>
+        <v>15.94</v>
       </c>
       <c r="H88" t="n">
-        <v>38.87</v>
-      </c>
-      <c r="I88" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.39</v>
+      </c>
+      <c r="I88" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J88" s="9" t="n">
-        <v>0.225</v>
+        <v>0.969</v>
       </c>
       <c r="K88" s="9" t="n">
-        <v>0.233</v>
+        <v>0.978</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="14" t="inlineStr"/>
@@ -4453,28 +4455,28 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D89" s="9" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="E89" s="15" t="n">
-        <v>-0.0137</v>
+        <v>0.635</v>
+      </c>
+      <c r="E89" s="16" t="n">
+        <v>0.007900000000000001</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>1053900</v>
+        <v>1430300</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>0.11</v>
+        <v>0.27</v>
       </c>
       <c r="H89" t="n">
-        <v>54.85</v>
+        <v>66.08</v>
       </c>
       <c r="I89" s="13" t="inlineStr">
         <is>
@@ -4482,10 +4484,10 @@
         </is>
       </c>
       <c r="J89" s="9" t="n">
-        <v>0.356</v>
+        <v>0.553</v>
       </c>
       <c r="K89" s="9" t="n">
-        <v>0.325</v>
+        <v>0.458</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="14" t="inlineStr"/>
@@ -4498,39 +4500,39 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D90" s="9" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="E90" s="15" t="n">
-        <v>-0.008100000000000001</v>
+        <v>1.61</v>
+      </c>
+      <c r="E90" s="16" t="n">
+        <v>0.0126</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>1040700</v>
+        <v>1426800</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>0.08</v>
+        <v>0.21</v>
       </c>
       <c r="H90" t="n">
-        <v>49.6</v>
-      </c>
-      <c r="I90" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.72</v>
+      </c>
+      <c r="I90" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J90" s="9" t="n">
-        <v>2.459</v>
+        <v>1.613</v>
       </c>
       <c r="K90" s="9" t="n">
-        <v>2.368</v>
+        <v>1.709</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="14" t="inlineStr"/>
@@ -4543,39 +4545,39 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>7943</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>GREENTEC</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D91" s="9" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="E91" s="15" t="n">
-        <v>-0.0333</v>
+        <v>7.36</v>
+      </c>
+      <c r="E91" s="16" t="n">
+        <v>0.008199999999999999</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>1007000</v>
+        <v>1353500</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>0.92</v>
+        <v>0.13</v>
       </c>
       <c r="H91" t="n">
-        <v>66.97</v>
-      </c>
-      <c r="I91" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.12</v>
+      </c>
+      <c r="I91" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J91" s="9" t="n">
-        <v>0.257</v>
+        <v>7.523</v>
       </c>
       <c r="K91" s="9" t="n">
-        <v>0.211</v>
+        <v>8.028</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="14" t="inlineStr"/>
@@ -4588,28 +4590,28 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D92" s="9" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="E92" s="16" t="n">
-        <v>0.0217</v>
+        <v>0.47</v>
+      </c>
+      <c r="E92" s="15" t="n">
+        <v>-0.0105</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>993100</v>
+        <v>1311700</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>0.71</v>
+        <v>0.17</v>
       </c>
       <c r="H92" t="n">
-        <v>55.19</v>
+        <v>28.83</v>
       </c>
       <c r="I92" s="13" t="inlineStr">
         <is>
@@ -4617,10 +4619,10 @@
         </is>
       </c>
       <c r="J92" s="9" t="n">
-        <v>0.925</v>
+        <v>0.511</v>
       </c>
       <c r="K92" s="9" t="n">
-        <v>0.863</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="14" t="inlineStr"/>
@@ -4633,39 +4635,39 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>7498</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>RALCO</t>
         </is>
       </c>
       <c r="D93" s="9" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E93" s="16" t="n">
-        <v>0.0063</v>
+        <v>1.01</v>
+      </c>
+      <c r="E93" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>975200</v>
+        <v>1301700</v>
       </c>
       <c r="G93" s="12" t="n">
-        <v>0.15</v>
+        <v>1.99</v>
       </c>
       <c r="H93" t="n">
-        <v>62.86</v>
-      </c>
-      <c r="I93" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.9</v>
+      </c>
+      <c r="I93" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J93" s="9" t="n">
-        <v>0.764</v>
+        <v>0.999</v>
       </c>
       <c r="K93" s="9" t="n">
-        <v>0.676</v>
+        <v>0.982</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="14" t="inlineStr"/>
@@ -4678,28 +4680,28 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>5337</t>
+          <t>0372</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>ECOSHOP</t>
+          <t>CHEEDING</t>
         </is>
       </c>
       <c r="D94" s="9" t="n">
-        <v>1.43</v>
+        <v>0.57</v>
       </c>
       <c r="E94" s="15" t="n">
-        <v>-0.0069</v>
+        <v>-0.0172</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>972300</v>
+        <v>1299000</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>0.23</v>
+        <v>0.33</v>
       </c>
       <c r="H94" t="n">
-        <v>40.99</v>
+        <v>40.78</v>
       </c>
       <c r="I94" s="13" t="inlineStr">
         <is>
@@ -4707,10 +4709,10 @@
         </is>
       </c>
       <c r="J94" s="9" t="n">
-        <v>1.453</v>
+        <v>0.606</v>
       </c>
       <c r="K94" s="9" t="n">
-        <v>1.467</v>
+        <v>0.606</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="14" t="inlineStr"/>
@@ -4723,28 +4725,28 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>KPJ</t>
         </is>
       </c>
       <c r="D95" s="9" t="n">
-        <v>0.595</v>
+        <v>2.52</v>
       </c>
       <c r="E95" s="16" t="n">
-        <v>0.0259</v>
+        <v>0.0244</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>969400</v>
+        <v>1291800</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>0.19</v>
+        <v>0.24</v>
       </c>
       <c r="H95" t="n">
-        <v>64.37</v>
+        <v>42.82</v>
       </c>
       <c r="I95" s="13" t="inlineStr">
         <is>
@@ -4752,10 +4754,10 @@
         </is>
       </c>
       <c r="J95" s="9" t="n">
-        <v>0.5590000000000001</v>
+        <v>2.572</v>
       </c>
       <c r="K95" s="9" t="n">
-        <v>0.506</v>
+        <v>2.75</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="14" t="inlineStr"/>
@@ -4768,39 +4770,39 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0291</t>
+          <t>0100</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>CHB</t>
+          <t>ESCERAM</t>
         </is>
       </c>
       <c r="D96" s="9" t="n">
-        <v>2.73</v>
+        <v>0.22</v>
       </c>
       <c r="E96" s="15" t="n">
-        <v>-0.0319</v>
+        <v>-0.0222</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>968500</v>
+        <v>1275500</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>0.63</v>
+        <v>0.74</v>
       </c>
       <c r="H96" t="n">
-        <v>67.19</v>
-      </c>
-      <c r="I96" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>69.75</v>
+      </c>
+      <c r="I96" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J96" s="9" t="n">
-        <v>2.542</v>
+        <v>0.193</v>
       </c>
       <c r="K96" s="9" t="n">
-        <v>2.213</v>
+        <v>0.186</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="14" t="inlineStr"/>
@@ -4813,28 +4815,28 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>0278</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>EDELTEQ</t>
         </is>
       </c>
       <c r="D97" s="9" t="n">
-        <v>7.38</v>
+        <v>0.42</v>
       </c>
       <c r="E97" s="16" t="n">
-        <v>0.0179</v>
+        <v>0.03700000000000001</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>945600</v>
+        <v>1213100</v>
       </c>
       <c r="G97" s="12" t="n">
-        <v>0.12</v>
+        <v>0.26</v>
       </c>
       <c r="H97" t="n">
-        <v>46.49</v>
+        <v>62.11</v>
       </c>
       <c r="I97" s="17" t="inlineStr">
         <is>
@@ -4842,10 +4844,10 @@
         </is>
       </c>
       <c r="J97" s="9" t="n">
-        <v>7.38</v>
+        <v>0.374</v>
       </c>
       <c r="K97" s="9" t="n">
-        <v>7.687</v>
+        <v>0.354</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="14" t="inlineStr"/>
@@ -4858,28 +4860,28 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>5337</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>ECOSHOP</t>
         </is>
       </c>
       <c r="D98" s="9" t="n">
-        <v>0.755</v>
-      </c>
-      <c r="E98" s="10" t="n">
-        <v>0</v>
+        <v>1.43</v>
+      </c>
+      <c r="E98" s="15" t="n">
+        <v>-0.0069</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>907500</v>
+        <v>1211900</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>0.13</v>
+        <v>0.28</v>
       </c>
       <c r="H98" t="n">
-        <v>55.72</v>
+        <v>40.99</v>
       </c>
       <c r="I98" s="13" t="inlineStr">
         <is>
@@ -4887,10 +4889,10 @@
         </is>
       </c>
       <c r="J98" s="9" t="n">
-        <v>0.743</v>
+        <v>1.453</v>
       </c>
       <c r="K98" s="9" t="n">
-        <v>0.665</v>
+        <v>1.467</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="14" t="inlineStr"/>
@@ -4903,28 +4905,28 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D99" s="9" t="n">
-        <v>1.22</v>
+        <v>4.37</v>
       </c>
       <c r="E99" s="16" t="n">
-        <v>0.0167</v>
+        <v>0.0116</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>899000</v>
+        <v>1204200</v>
       </c>
       <c r="G99" s="12" t="n">
-        <v>0.16</v>
+        <v>0.19</v>
       </c>
       <c r="H99" t="n">
-        <v>57.43</v>
+        <v>49.26</v>
       </c>
       <c r="I99" s="17" t="inlineStr">
         <is>
@@ -4932,10 +4934,10 @@
         </is>
       </c>
       <c r="J99" s="9" t="n">
-        <v>1.171</v>
+        <v>4.359</v>
       </c>
       <c r="K99" s="9" t="n">
-        <v>1.176</v>
+        <v>4.441</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="14" t="inlineStr"/>
@@ -4948,28 +4950,28 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>KPJ</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D100" s="9" t="n">
-        <v>2.52</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E100" s="16" t="n">
-        <v>0.0244</v>
+        <v>0.0217</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>826000</v>
+        <v>1202100</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>0.16</v>
+        <v>0.86</v>
       </c>
       <c r="H100" t="n">
-        <v>42.82</v>
+        <v>55.19</v>
       </c>
       <c r="I100" s="13" t="inlineStr">
         <is>
@@ -4977,10 +4979,10 @@
         </is>
       </c>
       <c r="J100" s="9" t="n">
-        <v>2.572</v>
+        <v>0.925</v>
       </c>
       <c r="K100" s="9" t="n">
-        <v>2.75</v>
+        <v>0.863</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="14" t="inlineStr"/>
@@ -4993,28 +4995,28 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D101" s="9" t="n">
-        <v>0.745</v>
+        <v>0.8</v>
       </c>
       <c r="E101" s="16" t="n">
-        <v>0.0068</v>
+        <v>0.0063</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>772000</v>
+        <v>1194900</v>
       </c>
       <c r="G101" s="12" t="n">
-        <v>0.35</v>
+        <v>0.19</v>
       </c>
       <c r="H101" t="n">
-        <v>55.71</v>
+        <v>62.86</v>
       </c>
       <c r="I101" s="13" t="inlineStr">
         <is>
@@ -5022,10 +5024,10 @@
         </is>
       </c>
       <c r="J101" s="9" t="n">
-        <v>0.724</v>
+        <v>0.764</v>
       </c>
       <c r="K101" s="9" t="n">
-        <v>0.699</v>
+        <v>0.676</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="14" t="inlineStr"/>
@@ -5038,39 +5040,39 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>TENAGA</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D102" s="9" t="n">
-        <v>12.96</v>
-      </c>
-      <c r="E102" s="15" t="n">
-        <v>-0.0061</v>
+        <v>0.305</v>
+      </c>
+      <c r="E102" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>719200</v>
+        <v>1176400</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>0.08</v>
+        <v>0.19</v>
       </c>
       <c r="H102" t="n">
-        <v>43.28</v>
-      </c>
-      <c r="I102" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.49</v>
+      </c>
+      <c r="I102" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J102" s="9" t="n">
-        <v>13.023</v>
+        <v>0.321</v>
       </c>
       <c r="K102" s="9" t="n">
-        <v>13.492</v>
+        <v>0.338</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="14" t="inlineStr"/>
@@ -5083,28 +5085,28 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>0056</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>NCT</t>
         </is>
       </c>
       <c r="D103" s="9" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="E103" s="16" t="n">
-        <v>0.0077</v>
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E103" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>713900</v>
+        <v>1173000</v>
       </c>
       <c r="G103" s="12" t="n">
-        <v>0.13</v>
+        <v>0.54</v>
       </c>
       <c r="H103" t="n">
-        <v>59.27</v>
+        <v>48.27</v>
       </c>
       <c r="I103" s="17" t="inlineStr">
         <is>
@@ -5112,10 +5114,10 @@
         </is>
       </c>
       <c r="J103" s="9" t="n">
-        <v>6.056</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="K103" s="9" t="n">
-        <v>5.856</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="14" t="inlineStr"/>
@@ -5128,39 +5130,39 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>MALAKOF</t>
+          <t>AWC</t>
         </is>
       </c>
       <c r="D104" s="9" t="n">
-        <v>0.765</v>
+        <v>0.68</v>
       </c>
       <c r="E104" s="15" t="n">
-        <v>-0.0129</v>
+        <v>-0.0145</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>707300</v>
+        <v>1123900</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>0.16</v>
+        <v>0.48</v>
       </c>
       <c r="H104" t="n">
-        <v>42.45</v>
-      </c>
-      <c r="I104" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.67</v>
+      </c>
+      <c r="I104" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J104" s="9" t="n">
-        <v>0.787</v>
+        <v>0.636</v>
       </c>
       <c r="K104" s="9" t="n">
-        <v>0.804</v>
+        <v>0.543</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="14" t="inlineStr"/>
@@ -5173,40 +5175,38 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>7498</t>
+          <t>0468</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>RALCO</t>
+          <t>UNIPAC</t>
         </is>
       </c>
       <c r="D105" s="9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="E105" s="16" t="n">
-        <v>0.009899999999999999</v>
+        <v>0.23</v>
+      </c>
+      <c r="E105" s="15" t="n">
+        <v>-0.0213</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>703200</v>
+        <v>1118800</v>
       </c>
       <c r="G105" s="12" t="n">
-        <v>1.07</v>
+        <v>0.12</v>
       </c>
       <c r="H105" t="n">
-        <v>59.02</v>
-      </c>
-      <c r="I105" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>24.97</v>
+      </c>
+      <c r="I105" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J105" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K105" s="9" t="n">
-        <v>0.982</v>
-      </c>
+        <v>0.257</v>
+      </c>
+      <c r="K105" s="9" t="n"/>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="14" t="inlineStr"/>
     </row>
@@ -5218,39 +5218,39 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D106" s="9" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="E106" s="16" t="n">
-        <v>0.0074</v>
+        <v>0.825</v>
+      </c>
+      <c r="E106" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>691100</v>
+        <v>1101200</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>0.14</v>
+        <v>0.29</v>
       </c>
       <c r="H106" t="n">
-        <v>40.24</v>
-      </c>
-      <c r="I106" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.87</v>
+      </c>
+      <c r="I106" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J106" s="9" t="n">
-        <v>2.908</v>
+        <v>0.828</v>
       </c>
       <c r="K106" s="9" t="n">
-        <v>2.86</v>
+        <v>0.77</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="14" t="inlineStr"/>
@@ -5263,39 +5263,39 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>ATECH</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D107" s="9" t="n">
-        <v>0.79</v>
+        <v>0.535</v>
       </c>
       <c r="E107" s="16" t="n">
-        <v>0.0128</v>
+        <v>0.009399999999999999</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>659100</v>
+        <v>1091700</v>
       </c>
       <c r="G107" s="12" t="n">
-        <v>0.3</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H107" t="n">
-        <v>54.81</v>
-      </c>
-      <c r="I107" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>55.88</v>
+      </c>
+      <c r="I107" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J107" s="9" t="n">
-        <v>0.776</v>
+        <v>0.519</v>
       </c>
       <c r="K107" s="9" t="n">
-        <v>0.765</v>
+        <v>0.45</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="14" t="inlineStr"/>
@@ -5308,28 +5308,28 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D108" s="9" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="E108" s="16" t="n">
-        <v>0.029</v>
+        <v>0.75</v>
+      </c>
+      <c r="E108" s="15" t="n">
+        <v>-0.0066</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>657600</v>
+        <v>1079000</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>0.21</v>
+        <v>0.15</v>
       </c>
       <c r="H108" t="n">
-        <v>42.33</v>
+        <v>54.72</v>
       </c>
       <c r="I108" s="13" t="inlineStr">
         <is>
@@ -5337,10 +5337,10 @@
         </is>
       </c>
       <c r="J108" s="9" t="n">
-        <v>0.747</v>
+        <v>0.743</v>
       </c>
       <c r="K108" s="9" t="n">
-        <v>0.748</v>
+        <v>0.665</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="14" t="inlineStr"/>
@@ -5353,39 +5353,39 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D109" s="9" t="n">
-        <v>1.07</v>
+        <v>0.36</v>
       </c>
       <c r="E109" s="15" t="n">
-        <v>-0.0183</v>
+        <v>-0.0137</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>648100</v>
+        <v>1063900</v>
       </c>
       <c r="G109" s="12" t="n">
-        <v>0.16</v>
+        <v>0.12</v>
       </c>
       <c r="H109" t="n">
-        <v>56.22</v>
-      </c>
-      <c r="I109" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>54.85</v>
+      </c>
+      <c r="I109" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J109" s="9" t="n">
-        <v>1.042</v>
+        <v>0.356</v>
       </c>
       <c r="K109" s="9" t="n">
-        <v>0.887</v>
+        <v>0.325</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="14" t="inlineStr"/>
@@ -5398,28 +5398,28 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>5932</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>BPURI</t>
         </is>
       </c>
       <c r="D110" s="9" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="E110" s="16" t="n">
-        <v>0.0086</v>
+        <v>0.215</v>
+      </c>
+      <c r="E110" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>648100</v>
+        <v>1055800</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>0.08</v>
+        <v>2.34</v>
       </c>
       <c r="H110" t="n">
-        <v>52.01</v>
+        <v>38.87</v>
       </c>
       <c r="I110" s="13" t="inlineStr">
         <is>
@@ -5427,10 +5427,10 @@
         </is>
       </c>
       <c r="J110" s="9" t="n">
-        <v>1.162</v>
+        <v>0.225</v>
       </c>
       <c r="K110" s="9" t="n">
-        <v>1.127</v>
+        <v>0.233</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="14" t="inlineStr"/>
@@ -5443,39 +5443,39 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>0271</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>WELLS</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D111" s="9" t="n">
-        <v>0.535</v>
-      </c>
-      <c r="E111" s="15" t="n">
-        <v>-0.0183</v>
+        <v>0.59</v>
+      </c>
+      <c r="E111" s="16" t="n">
+        <v>0.0172</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>607700</v>
+        <v>1036700</v>
       </c>
       <c r="G111" s="12" t="n">
-        <v>0.55</v>
+        <v>0.2</v>
       </c>
       <c r="H111" t="n">
-        <v>33.07</v>
-      </c>
-      <c r="I111" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>63.36</v>
+      </c>
+      <c r="I111" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J111" s="9" t="n">
-        <v>0.573</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="K111" s="9" t="n">
-        <v>0.616</v>
+        <v>0.506</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="14" t="inlineStr"/>
@@ -5488,28 +5488,28 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>0146</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>JFTECH</t>
         </is>
       </c>
       <c r="D112" s="9" t="n">
-        <v>1.71</v>
+        <v>0.745</v>
       </c>
       <c r="E112" s="16" t="n">
-        <v>0.0059</v>
+        <v>0.0068</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>604100</v>
+        <v>1031500</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>0.12</v>
+        <v>0.47</v>
       </c>
       <c r="H112" t="n">
-        <v>43.69</v>
+        <v>55.71</v>
       </c>
       <c r="I112" s="13" t="inlineStr">
         <is>
@@ -5517,10 +5517,10 @@
         </is>
       </c>
       <c r="J112" s="9" t="n">
-        <v>1.747</v>
+        <v>0.724</v>
       </c>
       <c r="K112" s="9" t="n">
-        <v>1.774</v>
+        <v>0.699</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="14" t="inlineStr"/>
@@ -5533,39 +5533,39 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>0277</t>
+          <t>7943</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>CLOUDPT</t>
+          <t>GREENTEC</t>
         </is>
       </c>
       <c r="D113" s="9" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="E113" s="16" t="n">
-        <v>0.01</v>
+        <v>0.29</v>
+      </c>
+      <c r="E113" s="15" t="n">
+        <v>-0.0333</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>594200</v>
+        <v>1007000</v>
       </c>
       <c r="G113" s="12" t="n">
-        <v>0.28</v>
+        <v>0.92</v>
       </c>
       <c r="H113" t="n">
-        <v>55.44</v>
-      </c>
-      <c r="I113" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.97</v>
+      </c>
+      <c r="I113" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J113" s="9" t="n">
-        <v>0.495</v>
+        <v>0.257</v>
       </c>
       <c r="K113" s="9" t="n">
-        <v>0.483</v>
+        <v>0.211</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="14" t="inlineStr"/>
@@ -5578,39 +5578,39 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>UWC</t>
+          <t>TENAGA</t>
         </is>
       </c>
       <c r="D114" s="9" t="n">
-        <v>7.63</v>
+        <v>13.02</v>
       </c>
       <c r="E114" s="15" t="n">
-        <v>-0.0026</v>
+        <v>-0.0015</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>591700</v>
+        <v>996300</v>
       </c>
       <c r="G114" s="12" t="n">
-        <v>0.14</v>
+        <v>0.11</v>
       </c>
       <c r="H114" t="n">
-        <v>60.95</v>
-      </c>
-      <c r="I114" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>45.65</v>
+      </c>
+      <c r="I114" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J114" s="9" t="n">
-        <v>7.372</v>
+        <v>13.029</v>
       </c>
       <c r="K114" s="9" t="n">
-        <v>6.846</v>
+        <v>13.493</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="14" t="inlineStr"/>
@@ -5623,39 +5623,39 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>5223</t>
+          <t>0291</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>MENTIGA</t>
+          <t>CHB</t>
         </is>
       </c>
       <c r="D115" s="9" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E115" s="16" t="n">
-        <v>0.3793</v>
+        <v>2.69</v>
+      </c>
+      <c r="E115" s="15" t="n">
+        <v>-0.0461</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>578400</v>
+        <v>996100</v>
       </c>
       <c r="G115" s="12" t="n">
-        <v>26.17</v>
+        <v>0.64</v>
       </c>
       <c r="H115" t="n">
-        <v>74.09</v>
-      </c>
-      <c r="I115" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>64.14</v>
+      </c>
+      <c r="I115" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J115" s="9" t="n">
-        <v>0.61</v>
+        <v>2.538</v>
       </c>
       <c r="K115" s="9" t="n">
-        <v>0.642</v>
+        <v>2.212</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="14" t="inlineStr"/>
@@ -5668,28 +5668,28 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>0245</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>MNHLDG</t>
         </is>
       </c>
       <c r="D116" s="9" t="n">
-        <v>0.515</v>
+        <v>3.84</v>
       </c>
       <c r="E116" s="15" t="n">
-        <v>-0.009599999999999999</v>
+        <v>-0.0179</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>565200</v>
+        <v>865600</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v>0.15</v>
+        <v>0.31</v>
       </c>
       <c r="H116" t="n">
-        <v>59.96</v>
+        <v>51.04</v>
       </c>
       <c r="I116" s="17" t="inlineStr">
         <is>
@@ -5697,10 +5697,10 @@
         </is>
       </c>
       <c r="J116" s="9" t="n">
-        <v>0.489</v>
+        <v>3.873</v>
       </c>
       <c r="K116" s="9" t="n">
-        <v>0.459</v>
+        <v>3.63</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="14" t="inlineStr"/>
@@ -5713,39 +5713,39 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D117" s="9" t="n">
-        <v>2.78</v>
+        <v>6.59</v>
       </c>
       <c r="E117" s="16" t="n">
-        <v>0.0072</v>
+        <v>0.0138</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>555600</v>
+        <v>854300</v>
       </c>
       <c r="G117" s="12" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="H117" t="n">
-        <v>35.93</v>
-      </c>
-      <c r="I117" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.75</v>
+      </c>
+      <c r="I117" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J117" s="9" t="n">
-        <v>2.933</v>
+        <v>6.06</v>
       </c>
       <c r="K117" s="9" t="n">
-        <v>3.026</v>
+        <v>5.857</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="14" t="inlineStr"/>
@@ -5758,39 +5758,39 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>0240</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>CORAZA</t>
         </is>
       </c>
       <c r="D118" s="9" t="n">
-        <v>0.625</v>
+        <v>1.28</v>
       </c>
       <c r="E118" s="15" t="n">
-        <v>-0.0234</v>
+        <v>-0.0154</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>552500</v>
+        <v>847300</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v>0.21</v>
+        <v>0.36</v>
       </c>
       <c r="H118" t="n">
-        <v>46.09</v>
-      </c>
-      <c r="I118" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.11</v>
+      </c>
+      <c r="I118" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J118" s="9" t="n">
-        <v>0.637</v>
+        <v>1.242</v>
       </c>
       <c r="K118" s="9" t="n">
-        <v>0.617</v>
+        <v>1.164</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="14" t="inlineStr"/>
@@ -5803,39 +5803,39 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>5302</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>DUFU</t>
+          <t>ATECH</t>
         </is>
       </c>
       <c r="D119" s="9" t="n">
-        <v>3.15</v>
+        <v>0.8</v>
       </c>
       <c r="E119" s="16" t="n">
-        <v>0.0227</v>
+        <v>0.0256</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>549100</v>
+        <v>831100</v>
       </c>
       <c r="G119" s="12" t="n">
-        <v>0.17</v>
+        <v>0.38</v>
       </c>
       <c r="H119" t="n">
-        <v>58.18</v>
-      </c>
-      <c r="I119" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.99</v>
+      </c>
+      <c r="I119" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J119" s="9" t="n">
-        <v>3.036</v>
+        <v>0.777</v>
       </c>
       <c r="K119" s="9" t="n">
-        <v>2.84</v>
+        <v>0.765</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="14" t="inlineStr"/>
@@ -5848,39 +5848,39 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>MALAKOF</t>
         </is>
       </c>
       <c r="D120" s="9" t="n">
-        <v>3.87</v>
+        <v>0.765</v>
       </c>
       <c r="E120" s="15" t="n">
-        <v>-0.0102</v>
+        <v>-0.0129</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>541400</v>
+        <v>828100</v>
       </c>
       <c r="G120" s="12" t="n">
         <v>0.19</v>
       </c>
       <c r="H120" t="n">
-        <v>52.8</v>
-      </c>
-      <c r="I120" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.45</v>
+      </c>
+      <c r="I120" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J120" s="9" t="n">
-        <v>3.875</v>
+        <v>0.787</v>
       </c>
       <c r="K120" s="9" t="n">
-        <v>3.63</v>
+        <v>0.804</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="14" t="inlineStr"/>
@@ -5893,39 +5893,39 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>IOIPG</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D121" s="9" t="n">
-        <v>3.3</v>
+        <v>1.09</v>
       </c>
       <c r="E121" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>528300</v>
+        <v>779300</v>
       </c>
       <c r="G121" s="12" t="n">
-        <v>0.08</v>
+        <v>0.19</v>
       </c>
       <c r="H121" t="n">
-        <v>33.44</v>
-      </c>
-      <c r="I121" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.39</v>
+      </c>
+      <c r="I121" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J121" s="9" t="n">
-        <v>3.425</v>
+        <v>1.044</v>
       </c>
       <c r="K121" s="9" t="n">
-        <v>3.632</v>
+        <v>0.887</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="14" t="inlineStr"/>
@@ -5938,28 +5938,28 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D122" s="9" t="n">
-        <v>0.895</v>
+        <v>1.69</v>
       </c>
       <c r="E122" s="15" t="n">
-        <v>-0.011</v>
+        <v>-0.0059</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>516500</v>
+        <v>763400</v>
       </c>
       <c r="G122" s="12" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="H122" t="n">
-        <v>41.46</v>
+        <v>40.93</v>
       </c>
       <c r="I122" s="13" t="inlineStr">
         <is>
@@ -5967,16 +5967,1051 @@
         </is>
       </c>
       <c r="J122" s="9" t="n">
-        <v>0.909</v>
+        <v>1.745</v>
       </c>
       <c r="K122" s="9" t="n">
-        <v>0.96</v>
+        <v>1.774</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="14" t="inlineStr"/>
     </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>2852</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>CMSB</t>
+        </is>
+      </c>
+      <c r="D123" s="9" t="n">
+        <v>0.885</v>
+      </c>
+      <c r="E123" s="15" t="n">
+        <v>-0.005600000000000001</v>
+      </c>
+      <c r="F123" s="11" t="n">
+        <v>762800</v>
+      </c>
+      <c r="G123" s="12" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="H123" t="n">
+        <v>22.89</v>
+      </c>
+      <c r="I123" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J123" s="9" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="K123" s="9" t="n">
+        <v>0.983</v>
+      </c>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" s="14" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>0167</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>MCLEAN</t>
+        </is>
+      </c>
+      <c r="D124" s="9" t="n">
+        <v>0.705</v>
+      </c>
+      <c r="E124" s="16" t="n">
+        <v>0.0217</v>
+      </c>
+      <c r="F124" s="11" t="n">
+        <v>735000</v>
+      </c>
+      <c r="G124" s="12" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H124" t="n">
+        <v>41.23</v>
+      </c>
+      <c r="I124" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J124" s="9" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="K124" s="9" t="n">
+        <v>0.747</v>
+      </c>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" s="14" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>5292</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>UWC</t>
+        </is>
+      </c>
+      <c r="D125" s="9" t="n">
+        <v>7.65</v>
+      </c>
+      <c r="E125" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F125" s="11" t="n">
+        <v>727400</v>
+      </c>
+      <c r="G125" s="12" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H125" t="n">
+        <v>61.58</v>
+      </c>
+      <c r="I125" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J125" s="9" t="n">
+        <v>7.374</v>
+      </c>
+      <c r="K125" s="9" t="n">
+        <v>6.846</v>
+      </c>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" s="14" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>5356</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>STRATUS</t>
+        </is>
+      </c>
+      <c r="D126" s="9" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="E126" s="16" t="n">
+        <v>0.0074</v>
+      </c>
+      <c r="F126" s="11" t="n">
+        <v>709400</v>
+      </c>
+      <c r="G126" s="12" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H126" t="n">
+        <v>40.24</v>
+      </c>
+      <c r="I126" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J126" s="9" t="n">
+        <v>2.908</v>
+      </c>
+      <c r="K126" s="9" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" s="14" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>5357</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>SKYECHIP</t>
+        </is>
+      </c>
+      <c r="D127" s="9" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="E127" s="16" t="n">
+        <v>0.0072</v>
+      </c>
+      <c r="F127" s="11" t="n">
+        <v>706000</v>
+      </c>
+      <c r="G127" s="12" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H127" t="n">
+        <v>35.93</v>
+      </c>
+      <c r="I127" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J127" s="9" t="n">
+        <v>2.933</v>
+      </c>
+      <c r="K127" s="9" t="n">
+        <v>3.026</v>
+      </c>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" s="14" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>0277</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>CLOUDPT</t>
+        </is>
+      </c>
+      <c r="D128" s="9" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="E128" s="16" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F128" s="11" t="n">
+        <v>689300</v>
+      </c>
+      <c r="G128" s="12" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="H128" t="n">
+        <v>55.44</v>
+      </c>
+      <c r="I128" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J128" s="9" t="n">
+        <v>0.495</v>
+      </c>
+      <c r="K128" s="9" t="n">
+        <v>0.483</v>
+      </c>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" s="14" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>5249</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>IOIPG</t>
+        </is>
+      </c>
+      <c r="D129" s="9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="E129" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F129" s="11" t="n">
+        <v>629000</v>
+      </c>
+      <c r="G129" s="12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H129" t="n">
+        <v>33.44</v>
+      </c>
+      <c r="I129" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J129" s="9" t="n">
+        <v>3.425</v>
+      </c>
+      <c r="K129" s="9" t="n">
+        <v>3.632</v>
+      </c>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" s="14" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>9792</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>SEG</t>
+        </is>
+      </c>
+      <c r="D130" s="9" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="E130" s="15" t="n">
+        <v>-0.007900000000000001</v>
+      </c>
+      <c r="F130" s="11" t="n">
+        <v>620000</v>
+      </c>
+      <c r="G130" s="12" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="H130" t="n">
+        <v>36.25</v>
+      </c>
+      <c r="I130" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J130" s="9" t="n">
+        <v>0.631</v>
+      </c>
+      <c r="K130" s="9" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" s="14" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>7233</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>DUFU</t>
+        </is>
+      </c>
+      <c r="D131" s="9" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="E131" s="16" t="n">
+        <v>0.0162</v>
+      </c>
+      <c r="F131" s="11" t="n">
+        <v>610300</v>
+      </c>
+      <c r="G131" s="12" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H131" t="n">
+        <v>57.42</v>
+      </c>
+      <c r="I131" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J131" s="9" t="n">
+        <v>3.034</v>
+      </c>
+      <c r="K131" s="9" t="n">
+        <v>2.839</v>
+      </c>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" s="14" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>5223</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>MENTIGA</t>
+        </is>
+      </c>
+      <c r="D132" s="9" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E132" s="16" t="n">
+        <v>0.3793</v>
+      </c>
+      <c r="F132" s="11" t="n">
+        <v>608500</v>
+      </c>
+      <c r="G132" s="12" t="n">
+        <v>27.53</v>
+      </c>
+      <c r="H132" t="n">
+        <v>74.09</v>
+      </c>
+      <c r="I132" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J132" s="9" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="K132" s="9" t="n">
+        <v>0.642</v>
+      </c>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" s="14" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>0271</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>WELLS</t>
+        </is>
+      </c>
+      <c r="D133" s="9" t="n">
+        <v>0.535</v>
+      </c>
+      <c r="E133" s="15" t="n">
+        <v>-0.0183</v>
+      </c>
+      <c r="F133" s="11" t="n">
+        <v>607700</v>
+      </c>
+      <c r="G133" s="12" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="H133" t="n">
+        <v>33.07</v>
+      </c>
+      <c r="I133" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J133" s="9" t="n">
+        <v>0.573</v>
+      </c>
+      <c r="K133" s="9" t="n">
+        <v>0.616</v>
+      </c>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" s="14" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>0097</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>VITROX</t>
+        </is>
+      </c>
+      <c r="D134" s="9" t="n">
+        <v>10.58</v>
+      </c>
+      <c r="E134" s="15" t="n">
+        <v>-0.0149</v>
+      </c>
+      <c r="F134" s="11" t="n">
+        <v>601200</v>
+      </c>
+      <c r="G134" s="12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H134" t="n">
+        <v>58.01</v>
+      </c>
+      <c r="I134" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J134" s="9" t="n">
+        <v>10.389</v>
+      </c>
+      <c r="K134" s="9" t="n">
+        <v>9.659000000000001</v>
+      </c>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" s="14" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>0368</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>OXB</t>
+        </is>
+      </c>
+      <c r="D135" s="9" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="E135" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F135" s="11" t="n">
+        <v>596500</v>
+      </c>
+      <c r="G135" s="12" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H135" t="n">
+        <v>61.55</v>
+      </c>
+      <c r="I135" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J135" s="9" t="n">
+        <v>0.489</v>
+      </c>
+      <c r="K135" s="9" t="n">
+        <v>0.459</v>
+      </c>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" s="14" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>0225</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>SCGBHD</t>
+        </is>
+      </c>
+      <c r="D136" s="9" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="E136" s="15" t="n">
+        <v>-0.006999999999999999</v>
+      </c>
+      <c r="F136" s="11" t="n">
+        <v>595100</v>
+      </c>
+      <c r="G136" s="12" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H136" t="n">
+        <v>56.6</v>
+      </c>
+      <c r="I136" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J136" s="9" t="n">
+        <v>2.799</v>
+      </c>
+      <c r="K136" s="9" t="n">
+        <v>2.636</v>
+      </c>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" s="14" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>0045</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>SSB8</t>
+        </is>
+      </c>
+      <c r="D137" s="9" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="E137" s="16" t="n">
+        <v>0.0156</v>
+      </c>
+      <c r="F137" s="11" t="n">
+        <v>584800</v>
+      </c>
+      <c r="G137" s="12" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H137" t="n">
+        <v>55.56</v>
+      </c>
+      <c r="I137" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J137" s="9" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="K137" s="9" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" s="14" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>9059</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>TSH</t>
+        </is>
+      </c>
+      <c r="D138" s="9" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="E138" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F138" s="11" t="n">
+        <v>557600</v>
+      </c>
+      <c r="G138" s="12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H138" t="n">
+        <v>30.53</v>
+      </c>
+      <c r="I138" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J138" s="9" t="n">
+        <v>1.261</v>
+      </c>
+      <c r="K138" s="9" t="n">
+        <v>1.309</v>
+      </c>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" s="14" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>0112</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>MIKROMB</t>
+        </is>
+      </c>
+      <c r="D139" s="9" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="E139" s="15" t="n">
+        <v>-0.0234</v>
+      </c>
+      <c r="F139" s="11" t="n">
+        <v>557500</v>
+      </c>
+      <c r="G139" s="12" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H139" t="n">
+        <v>46.09</v>
+      </c>
+      <c r="I139" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J139" s="9" t="n">
+        <v>0.637</v>
+      </c>
+      <c r="K139" s="9" t="n">
+        <v>0.617</v>
+      </c>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" s="14" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>7160</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>PENTA</t>
+        </is>
+      </c>
+      <c r="D140" s="9" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="E140" s="15" t="n">
+        <v>-0.0073</v>
+      </c>
+      <c r="F140" s="11" t="n">
+        <v>554800</v>
+      </c>
+      <c r="G140" s="12" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H140" t="n">
+        <v>50.32</v>
+      </c>
+      <c r="I140" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J140" s="9" t="n">
+        <v>5.506</v>
+      </c>
+      <c r="K140" s="9" t="n">
+        <v>5.386</v>
+      </c>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" s="14" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>0338</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>KOPI</t>
+        </is>
+      </c>
+      <c r="D141" s="9" t="n">
+        <v>0.895</v>
+      </c>
+      <c r="E141" s="15" t="n">
+        <v>-0.011</v>
+      </c>
+      <c r="F141" s="11" t="n">
+        <v>549700</v>
+      </c>
+      <c r="G141" s="12" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H141" t="n">
+        <v>41.46</v>
+      </c>
+      <c r="I141" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J141" s="9" t="n">
+        <v>0.909</v>
+      </c>
+      <c r="K141" s="9" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" s="14" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>8583</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>MAHSING</t>
+        </is>
+      </c>
+      <c r="D142" s="9" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="E142" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F142" s="11" t="n">
+        <v>545900</v>
+      </c>
+      <c r="G142" s="12" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H142" t="n">
+        <v>31.13</v>
+      </c>
+      <c r="I142" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J142" s="9" t="n">
+        <v>0.984</v>
+      </c>
+      <c r="K142" s="9" t="n">
+        <v>1.062</v>
+      </c>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" s="14" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>1171</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>MBSB</t>
+        </is>
+      </c>
+      <c r="D143" s="9" t="n">
+        <v>0.545</v>
+      </c>
+      <c r="E143" s="15" t="n">
+        <v>-0.0091</v>
+      </c>
+      <c r="F143" s="11" t="n">
+        <v>523800</v>
+      </c>
+      <c r="G143" s="12" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H143" t="n">
+        <v>43.84</v>
+      </c>
+      <c r="I143" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J143" s="9" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="K143" s="9" t="n">
+        <v>0.577</v>
+      </c>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" s="14" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>5258</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>BIMB</t>
+        </is>
+      </c>
+      <c r="D144" s="9" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="E144" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F144" s="11" t="n">
+        <v>518400</v>
+      </c>
+      <c r="G144" s="12" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="H144" t="n">
+        <v>37.42</v>
+      </c>
+      <c r="I144" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J144" s="9" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="K144" s="9" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" s="14" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>5916</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>MSC</t>
+        </is>
+      </c>
+      <c r="D145" s="9" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="E145" s="16" t="n">
+        <v>0.0184</v>
+      </c>
+      <c r="F145" s="11" t="n">
+        <v>500000</v>
+      </c>
+      <c r="G145" s="12" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="H145" t="n">
+        <v>46.45</v>
+      </c>
+      <c r="I145" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J145" s="9" t="n">
+        <v>1.671</v>
+      </c>
+      <c r="K145" s="9" t="n">
+        <v>1.798</v>
+      </c>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M122"/>
+  <autoFilter ref="A1:M145"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-14/bursa-report-2026-10-14.xlsx
+++ b/docs/downloads/2026-10-14/bursa-report-2026-10-14.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-14" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-14'!$A$1:$M$145</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-14'!$A$1:$M$160</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M145"/>
+  <dimension ref="A1:M160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -572,10 +572,10 @@
         <v>0.036</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>1993900</v>
+        <v>3545800</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>0.49</v>
+        <v>0.88</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>59.41</v>
@@ -619,13 +619,13 @@
         </is>
       </c>
       <c r="D3" s="9" t="n">
-        <v>0.77</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="E3" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>129678800</v>
+        <v>143529300</v>
       </c>
       <c r="G3" s="12" t="n"/>
       <c r="I3" s="13" t="inlineStr">
@@ -655,19 +655,19 @@
         </is>
       </c>
       <c r="D4" s="9" t="n">
-        <v>0.055</v>
+        <v>0.06</v>
       </c>
       <c r="E4" s="15" t="n">
-        <v>-0.1538</v>
+        <v>-0.07690000000000001</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>128480300</v>
+        <v>132888800</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="H4" t="n">
-        <v>20.87</v>
+        <v>21.31</v>
       </c>
       <c r="I4" s="13" t="inlineStr">
         <is>
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="J4" s="9" t="n">
-        <v>0.146</v>
+        <v>0.147</v>
       </c>
       <c r="K4" s="9" t="n">
         <v>0.36</v>
@@ -706,7 +706,7 @@
         <v>-0.0333</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>58661300</v>
+        <v>58919600</v>
       </c>
       <c r="G5" s="12" t="n">
         <v>0.84</v>
@@ -736,28 +736,28 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D6" s="9" t="n">
-        <v>0.41</v>
+        <v>0.87</v>
       </c>
       <c r="E6" s="16" t="n">
-        <v>0.0513</v>
+        <v>0.0175</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>35750000</v>
+        <v>38368000</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>0.96</v>
+        <v>0.59</v>
       </c>
       <c r="H6" t="n">
-        <v>74.70999999999999</v>
+        <v>64.34</v>
       </c>
       <c r="I6" s="17" t="inlineStr">
         <is>
@@ -765,10 +765,10 @@
         </is>
       </c>
       <c r="J6" s="9" t="n">
-        <v>0.368</v>
+        <v>0.799</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>0.256</v>
+        <v>0.721</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="14" t="inlineStr"/>
@@ -781,28 +781,28 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.875</v>
+        <v>0.41</v>
       </c>
       <c r="E7" s="16" t="n">
-        <v>0.0234</v>
+        <v>0.0513</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>30701800</v>
+        <v>36731000</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>0.47</v>
+        <v>0.99</v>
       </c>
       <c r="H7" t="n">
-        <v>64.88</v>
+        <v>74.70999999999999</v>
       </c>
       <c r="I7" s="17" t="inlineStr">
         <is>
@@ -810,10 +810,10 @@
         </is>
       </c>
       <c r="J7" s="9" t="n">
-        <v>0.8</v>
+        <v>0.368</v>
       </c>
       <c r="K7" s="9" t="n">
-        <v>0.721</v>
+        <v>0.256</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="14" t="inlineStr"/>
@@ -835,19 +835,19 @@
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>0.335</v>
-      </c>
-      <c r="E8" s="15" t="n">
-        <v>-0.0147</v>
+        <v>0.34</v>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>24636500</v>
+        <v>29482000</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>0.34</v>
+        <v>0.41</v>
       </c>
       <c r="H8" t="n">
-        <v>68.87</v>
+        <v>71.22</v>
       </c>
       <c r="I8" s="17" t="inlineStr">
         <is>
@@ -855,7 +855,7 @@
         </is>
       </c>
       <c r="J8" s="9" t="n">
-        <v>0.293</v>
+        <v>0.294</v>
       </c>
       <c r="K8" s="9" t="n">
         <v>0.251</v>
@@ -931,10 +931,10 @@
         <v>0.05</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>14954500</v>
+        <v>15697400</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>5.45</v>
+        <v>5.72</v>
       </c>
       <c r="H10" t="n">
         <v>57.96</v>
@@ -961,28 +961,28 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="E11" s="10" t="n">
-        <v>0</v>
+        <v>0.47</v>
+      </c>
+      <c r="E11" s="15" t="n">
+        <v>-0.0105</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>13037900</v>
+        <v>15449200</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>1.43</v>
+        <v>0.44</v>
       </c>
       <c r="H11" t="n">
-        <v>19.46</v>
+        <v>44.59</v>
       </c>
       <c r="I11" s="13" t="inlineStr">
         <is>
@@ -990,10 +990,10 @@
         </is>
       </c>
       <c r="J11" s="9" t="n">
-        <v>1.781</v>
+        <v>0.489</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>1.985</v>
+        <v>0.482</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="14" t="inlineStr"/>
@@ -1006,28 +1006,28 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>0.475</v>
-      </c>
-      <c r="E12" s="10" t="n">
-        <v>0</v>
+        <v>1.43</v>
+      </c>
+      <c r="E12" s="15" t="n">
+        <v>-0.0069</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>12471300</v>
+        <v>14074600</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>0.35</v>
+        <v>1.55</v>
       </c>
       <c r="H12" t="n">
-        <v>46.03</v>
+        <v>19.18</v>
       </c>
       <c r="I12" s="13" t="inlineStr">
         <is>
@@ -1035,10 +1035,10 @@
         </is>
       </c>
       <c r="J12" s="9" t="n">
-        <v>0.49</v>
+        <v>1.78</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>0.482</v>
+        <v>1.985</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="14" t="inlineStr"/>
@@ -1060,19 +1060,19 @@
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="E13" s="15" t="n">
-        <v>-0.008</v>
+        <v>0.625</v>
+      </c>
+      <c r="E13" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>11695000</v>
+        <v>12375500</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>0.46</v>
+        <v>0.49</v>
       </c>
       <c r="H13" t="n">
-        <v>66.34999999999999</v>
+        <v>68.89</v>
       </c>
       <c r="I13" s="17" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         </is>
       </c>
       <c r="J13" s="9" t="n">
-        <v>0.592</v>
+        <v>0.593</v>
       </c>
       <c r="K13" s="9" t="n">
         <v>0.516</v>
@@ -1105,19 +1105,19 @@
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>3.84</v>
+        <v>3.88</v>
       </c>
       <c r="E14" s="15" t="n">
-        <v>-0.0634</v>
+        <v>-0.0537</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>10746700</v>
+        <v>11905600</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>1.21</v>
+        <v>1.34</v>
       </c>
       <c r="H14" t="n">
-        <v>48.36</v>
+        <v>49.64</v>
       </c>
       <c r="I14" s="13" t="inlineStr">
         <is>
@@ -1125,10 +1125,10 @@
         </is>
       </c>
       <c r="J14" s="9" t="n">
-        <v>3.985</v>
+        <v>3.989</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>3.506</v>
+        <v>3.507</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="14" t="inlineStr"/>
@@ -1150,19 +1150,19 @@
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>0.73</v>
+        <v>0.725</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>-0.09320000000000001</v>
+        <v>-0.09939999999999999</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>10443200</v>
+        <v>10758600</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>0.73</v>
+        <v>0.76</v>
       </c>
       <c r="H15" t="n">
-        <v>45.71</v>
+        <v>45.09</v>
       </c>
       <c r="I15" s="13" t="inlineStr">
         <is>
@@ -1186,28 +1186,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="E16" s="16" t="n">
-        <v>0.0049</v>
+        <v>0.435</v>
+      </c>
+      <c r="E16" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>9459400</v>
+        <v>10237700</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>0.31</v>
+        <v>0.5</v>
       </c>
       <c r="H16" t="n">
-        <v>63.29</v>
+        <v>59.15</v>
       </c>
       <c r="I16" s="17" t="inlineStr">
         <is>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="J16" s="9" t="n">
-        <v>1.9</v>
+        <v>0.415</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>1.697</v>
+        <v>0.356</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="14" t="inlineStr"/>
@@ -1231,28 +1231,28 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>0.445</v>
+        <v>2.07</v>
       </c>
       <c r="E17" s="16" t="n">
-        <v>0.023</v>
+        <v>0.0049</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>8185500</v>
+        <v>9983300</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="H17" t="n">
-        <v>61.25</v>
+        <v>63.29</v>
       </c>
       <c r="I17" s="17" t="inlineStr">
         <is>
@@ -1260,10 +1260,10 @@
         </is>
       </c>
       <c r="J17" s="9" t="n">
-        <v>0.416</v>
+        <v>1.9</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>0.357</v>
+        <v>1.697</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="14" t="inlineStr"/>
@@ -1276,39 +1276,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>7079</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>TWL</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="E18" s="16" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
+      </c>
+      <c r="E18" s="15" t="n">
+        <v>-0.0159</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>7414600</v>
+        <v>8029100</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="H18" t="n">
-        <v>51.85</v>
-      </c>
-      <c r="I18" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55</v>
+      </c>
+      <c r="I18" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J18" s="9" t="n">
-        <v>0.024</v>
+        <v>0.308</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>0.025</v>
+        <v>0.298</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="14" t="inlineStr"/>
@@ -1321,28 +1321,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="E19" s="16" t="n">
-        <v>0.027</v>
+        <v>0.775</v>
+      </c>
+      <c r="E19" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>6896800</v>
+        <v>7470700</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>0.98</v>
+        <v>0.49</v>
       </c>
       <c r="H19" t="n">
-        <v>61.86</v>
+        <v>50.46</v>
       </c>
       <c r="I19" s="17" t="inlineStr">
         <is>
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="J19" s="9" t="n">
-        <v>0.37</v>
+        <v>0.774</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>0.369</v>
+        <v>0.775</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="14" t="inlineStr"/>
@@ -1366,39 +1366,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>7079</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>TWL</t>
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E20" s="10" t="n">
-        <v>0</v>
+        <v>0.025</v>
+      </c>
+      <c r="E20" s="16" t="n">
+        <v>0.25</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>6262400</v>
+        <v>7414600</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="H20" t="n">
-        <v>50.46</v>
-      </c>
-      <c r="I20" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.85</v>
+      </c>
+      <c r="I20" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J20" s="9" t="n">
-        <v>0.774</v>
+        <v>0.024</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>0.775</v>
+        <v>0.025</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="14" t="inlineStr"/>
@@ -1411,28 +1411,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>0.315</v>
-      </c>
-      <c r="E21" s="10" t="n">
-        <v>0</v>
+        <v>0.38</v>
+      </c>
+      <c r="E21" s="16" t="n">
+        <v>0.027</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>6144000</v>
+        <v>7202800</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>0.32</v>
+        <v>1.02</v>
       </c>
       <c r="H21" t="n">
-        <v>61.97</v>
+        <v>61.86</v>
       </c>
       <c r="I21" s="17" t="inlineStr">
         <is>
@@ -1440,10 +1440,10 @@
         </is>
       </c>
       <c r="J21" s="9" t="n">
-        <v>0.308</v>
+        <v>0.37</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>0.298</v>
+        <v>0.369</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="14" t="inlineStr"/>
@@ -1456,39 +1456,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="E22" s="15" t="n">
-        <v>-0.0278</v>
+        <v>7.61</v>
+      </c>
+      <c r="E22" s="16" t="n">
+        <v>0.0147</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>5867700</v>
+        <v>7098900</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.48</v>
       </c>
       <c r="H22" t="n">
-        <v>53.1</v>
-      </c>
-      <c r="I22" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.28</v>
+      </c>
+      <c r="I22" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J22" s="9" t="n">
-        <v>0.348</v>
+        <v>7.599</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>0.33</v>
+        <v>7.719</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="14" t="inlineStr"/>
@@ -1501,28 +1501,28 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>0.18</v>
+        <v>0.295</v>
       </c>
       <c r="E23" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>5463600</v>
+        <v>6462700</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>0.23</v>
+        <v>2.28</v>
       </c>
       <c r="H23" t="n">
-        <v>42.98</v>
+        <v>49.15</v>
       </c>
       <c r="I23" s="13" t="inlineStr">
         <is>
@@ -1530,10 +1530,10 @@
         </is>
       </c>
       <c r="J23" s="9" t="n">
-        <v>0.193</v>
+        <v>0.295</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>0.185</v>
+        <v>0.296</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="14" t="inlineStr"/>
@@ -1546,39 +1546,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>IOICORP</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>7.65</v>
-      </c>
-      <c r="E24" s="16" t="n">
-        <v>0.02</v>
+        <v>4.55</v>
+      </c>
+      <c r="E24" s="15" t="n">
+        <v>-0.0022</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>5203200</v>
+        <v>6406500</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>0.35</v>
+        <v>0.67</v>
       </c>
       <c r="H24" t="n">
-        <v>50.83</v>
-      </c>
-      <c r="I24" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.27</v>
+      </c>
+      <c r="I24" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J24" s="9" t="n">
-        <v>7.602</v>
+        <v>4.644</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>7.72</v>
+        <v>4.63</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="14" t="inlineStr"/>
@@ -1591,29 +1591,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0473</t>
+          <t>0476</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>EVOCOM</t>
+          <t>SLG</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
       <c r="E25" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>4970000</v>
+        <v>6368300</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="I25" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>0.21</v>
+      </c>
+      <c r="I25" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J25" s="9" t="n"/>
@@ -1629,28 +1629,28 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>0034</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>MMAG</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>2.68</v>
+        <v>0.02</v>
       </c>
       <c r="E26" s="15" t="n">
-        <v>-0.0111</v>
+        <v>-0.2</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>4693100</v>
+        <v>6236300</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>0.26</v>
+        <v>1.44</v>
       </c>
       <c r="H26" t="n">
-        <v>53.71</v>
+        <v>44.58</v>
       </c>
       <c r="I26" s="17" t="inlineStr">
         <is>
@@ -1658,10 +1658,10 @@
         </is>
       </c>
       <c r="J26" s="9" t="n">
-        <v>2.656</v>
+        <v>0.024</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>2.533</v>
+        <v>0.026</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="14" t="inlineStr"/>
@@ -1674,39 +1674,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>7195</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>BNASTRA</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="E27" s="10" t="n">
-        <v>0</v>
+        <v>0.355</v>
+      </c>
+      <c r="E27" s="15" t="n">
+        <v>-0.0139</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>4625600</v>
+        <v>5991200</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>4.25</v>
+        <v>0.7</v>
       </c>
       <c r="H27" t="n">
-        <v>82.43000000000001</v>
-      </c>
-      <c r="I27" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>55.26</v>
+      </c>
+      <c r="I27" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J27" s="9" t="n">
-        <v>2.539</v>
+        <v>0.349</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>2.386</v>
+        <v>0.33</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="14" t="inlineStr"/>
@@ -1719,33 +1719,40 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0476</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>SLG</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>0.245</v>
-      </c>
-      <c r="E28" s="15" t="n">
-        <v>-0.02</v>
+        <v>0.62</v>
+      </c>
+      <c r="E28" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>4623400</v>
+        <v>5929900</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0.16</v>
+        <v>0.55</v>
+      </c>
+      <c r="H28" t="n">
+        <v>54.39</v>
       </c>
       <c r="I28" s="17" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J28" s="9" t="n"/>
-      <c r="K28" s="9" t="n"/>
+      <c r="J28" s="9" t="n">
+        <v>0.614</v>
+      </c>
+      <c r="K28" s="9" t="n">
+        <v>0.613</v>
+      </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="14" t="inlineStr"/>
     </row>
@@ -1757,39 +1764,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>0.405</v>
-      </c>
-      <c r="E29" s="10" t="n">
-        <v>0</v>
+        <v>0.175</v>
+      </c>
+      <c r="E29" s="15" t="n">
+        <v>-0.0278</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>4521900</v>
+        <v>5796900</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0.36</v>
+        <v>0.25</v>
       </c>
       <c r="H29" t="n">
-        <v>56.05</v>
-      </c>
-      <c r="I29" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.7</v>
+      </c>
+      <c r="I29" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J29" s="9" t="n">
-        <v>0.39</v>
+        <v>0.192</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>0.377</v>
+        <v>0.185</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="14" t="inlineStr"/>
@@ -1802,39 +1809,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="E30" s="16" t="n">
-        <v>0.0283</v>
+        <v>0.4</v>
+      </c>
+      <c r="E30" s="15" t="n">
+        <v>-0.0123</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>4503700</v>
+        <v>5612600</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
       <c r="H30" t="n">
-        <v>53.79</v>
-      </c>
-      <c r="I30" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.4</v>
+      </c>
+      <c r="I30" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J30" s="9" t="n">
-        <v>1.07</v>
+        <v>0.389</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>1.04</v>
+        <v>0.377</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="14" t="inlineStr"/>
@@ -1847,28 +1854,28 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="E31" s="15" t="n">
-        <v>-0.07820000000000001</v>
+        <v>1.26</v>
+      </c>
+      <c r="E31" s="16" t="n">
+        <v>0.008</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>4500700</v>
+        <v>5491700</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>1.03</v>
+        <v>0.55</v>
       </c>
       <c r="H31" t="n">
-        <v>57.66</v>
+        <v>41.98</v>
       </c>
       <c r="I31" s="13" t="inlineStr">
         <is>
@@ -1876,10 +1883,10 @@
         </is>
       </c>
       <c r="J31" s="9" t="n">
-        <v>2.766</v>
+        <v>1.31</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>2.132</v>
+        <v>1.311</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="14" t="inlineStr"/>
@@ -1892,28 +1899,28 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="E32" s="10" t="n">
-        <v>0</v>
+        <v>2.69</v>
+      </c>
+      <c r="E32" s="15" t="n">
+        <v>-0.0074</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>4485400</v>
+        <v>5378300</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>0.42</v>
+        <v>0.3</v>
       </c>
       <c r="H32" t="n">
-        <v>54.39</v>
+        <v>54.42</v>
       </c>
       <c r="I32" s="17" t="inlineStr">
         <is>
@@ -1921,10 +1928,10 @@
         </is>
       </c>
       <c r="J32" s="9" t="n">
-        <v>0.614</v>
+        <v>2.657</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>0.613</v>
+        <v>2.533</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="14" t="inlineStr"/>
@@ -1937,28 +1944,28 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>0.585</v>
-      </c>
-      <c r="E33" s="16" t="n">
-        <v>0.0086</v>
+        <v>0.865</v>
+      </c>
+      <c r="E33" s="15" t="n">
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>4473700</v>
+        <v>5346800</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>0.23</v>
+        <v>0.27</v>
       </c>
       <c r="H33" t="n">
-        <v>52.99</v>
+        <v>46.29</v>
       </c>
       <c r="I33" s="17" t="inlineStr">
         <is>
@@ -1966,10 +1973,10 @@
         </is>
       </c>
       <c r="J33" s="9" t="n">
-        <v>0.583</v>
+        <v>0.868</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>0.532</v>
+        <v>0.869</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="14" t="inlineStr"/>
@@ -1982,39 +1989,39 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="E34" s="10" t="n">
-        <v>0</v>
+        <v>1.93</v>
+      </c>
+      <c r="E34" s="16" t="n">
+        <v>0.0052</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>4330900</v>
+        <v>5178100</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>2.62</v>
+        <v>0.88</v>
       </c>
       <c r="H34" t="n">
-        <v>39.24</v>
-      </c>
-      <c r="I34" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.36</v>
+      </c>
+      <c r="I34" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J34" s="9" t="n">
-        <v>0.419</v>
+        <v>1.926</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>0.437</v>
+        <v>1.954</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="14" t="inlineStr"/>
@@ -2027,28 +2034,28 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>0223</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>SAMAIDEN</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>1.1</v>
+        <v>2.81</v>
       </c>
       <c r="E35" s="15" t="n">
-        <v>-0.0678</v>
+        <v>-0.08470000000000001</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>4297400</v>
+        <v>5120400</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0.55</v>
+        <v>1.18</v>
       </c>
       <c r="H35" t="n">
-        <v>53.65</v>
+        <v>56.85</v>
       </c>
       <c r="I35" s="13" t="inlineStr">
         <is>
@@ -2056,10 +2063,10 @@
         </is>
       </c>
       <c r="J35" s="9" t="n">
-        <v>1.103</v>
+        <v>2.764</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>0.86</v>
+        <v>2.132</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="14" t="inlineStr"/>
@@ -2072,40 +2079,33 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>0473</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>AVANGAAD</t>
+          <t>EVOCOM</t>
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>0.295</v>
+        <v>0.1</v>
       </c>
       <c r="E36" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>4294000</v>
+        <v>4979600</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="H36" t="n">
-        <v>49.15</v>
+        <v>0.35</v>
       </c>
       <c r="I36" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J36" s="9" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="K36" s="9" t="n">
-        <v>0.296</v>
-      </c>
+      <c r="J36" s="9" t="n"/>
+      <c r="K36" s="9" t="n"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="14" t="inlineStr"/>
     </row>
@@ -2117,28 +2117,28 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="E37" s="10" t="n">
-        <v>0</v>
+        <v>1.07</v>
+      </c>
+      <c r="E37" s="16" t="n">
+        <v>0.009399999999999999</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>4172900</v>
+        <v>4960900</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0.42</v>
+        <v>0.5</v>
       </c>
       <c r="H37" t="n">
-        <v>40.29</v>
+        <v>50.92</v>
       </c>
       <c r="I37" s="13" t="inlineStr">
         <is>
@@ -2146,10 +2146,10 @@
         </is>
       </c>
       <c r="J37" s="9" t="n">
-        <v>1.309</v>
+        <v>1.068</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>1.311</v>
+        <v>1.04</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="14" t="inlineStr"/>
@@ -2177,10 +2177,10 @@
         <v>0</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>4169800</v>
+        <v>4856500</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>0.25</v>
+        <v>0.29</v>
       </c>
       <c r="H38" t="n">
         <v>58.27</v>
@@ -2207,28 +2207,28 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="E39" s="10" t="n">
-        <v>0</v>
+        <v>4.9</v>
+      </c>
+      <c r="E39" s="15" t="n">
+        <v>-0.0101</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>4093800</v>
+        <v>4846800</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>0.38</v>
+        <v>0.19</v>
       </c>
       <c r="H39" t="n">
-        <v>33.84</v>
+        <v>50.88</v>
       </c>
       <c r="I39" s="13" t="inlineStr">
         <is>
@@ -2236,10 +2236,10 @@
         </is>
       </c>
       <c r="J39" s="9" t="n">
-        <v>0.399</v>
+        <v>4.932</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>0.408</v>
+        <v>4.698</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="14" t="inlineStr"/>
@@ -2252,39 +2252,39 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>7195</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>BNASTRA</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="E40" s="15" t="n">
-        <v>-0.0101</v>
+        <v>2.71</v>
+      </c>
+      <c r="E40" s="16" t="n">
+        <v>0.0037</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>3918100</v>
+        <v>4652500</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>0.15</v>
+        <v>4.28</v>
       </c>
       <c r="H40" t="n">
-        <v>50.88</v>
-      </c>
-      <c r="I40" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>82.95</v>
+      </c>
+      <c r="I40" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J40" s="9" t="n">
-        <v>4.932</v>
+        <v>2.54</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>4.698</v>
+        <v>2.386</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="14" t="inlineStr"/>
@@ -2297,39 +2297,39 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="E41" s="10" t="n">
-        <v>0</v>
+        <v>0.585</v>
+      </c>
+      <c r="E41" s="16" t="n">
+        <v>0.0086</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>3848600</v>
+        <v>4619400</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>0.65</v>
+        <v>0.23</v>
       </c>
       <c r="H41" t="n">
-        <v>47.51</v>
-      </c>
-      <c r="I41" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.99</v>
+      </c>
+      <c r="I41" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J41" s="9" t="n">
-        <v>1.925</v>
+        <v>0.583</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>1.953</v>
+        <v>0.532</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="14" t="inlineStr"/>
@@ -2342,39 +2342,39 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.13</v>
       </c>
       <c r="E42" s="16" t="n">
-        <v>0.0108</v>
+        <v>0.1357</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>3847300</v>
+        <v>4545200</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>0.7</v>
+        <v>1.29</v>
       </c>
       <c r="H42" t="n">
-        <v>62.32</v>
-      </c>
-      <c r="I42" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>86.79000000000001</v>
+      </c>
+      <c r="I42" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J42" s="9" t="n">
-        <v>0.912</v>
+        <v>0.758</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>0.869</v>
+        <v>0.525</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="14" t="inlineStr"/>
@@ -2387,39 +2387,39 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>0340</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>NORTHERN</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>2.12</v>
+        <v>1.1</v>
       </c>
       <c r="E43" s="15" t="n">
-        <v>-0.009300000000000001</v>
+        <v>-0.0678</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>3694600</v>
+        <v>4428600</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>0.18</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H43" t="n">
-        <v>52.35</v>
-      </c>
-      <c r="I43" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.65</v>
+      </c>
+      <c r="I43" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J43" s="9" t="n">
-        <v>2.11</v>
+        <v>1.103</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>2.094</v>
+        <v>0.86</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="14" t="inlineStr"/>
@@ -2432,39 +2432,39 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D44" s="9" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E44" s="15" t="n">
-        <v>-0.005699999999999999</v>
+        <v>0.41</v>
+      </c>
+      <c r="E44" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>3583300</v>
+        <v>4330900</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0.18</v>
+        <v>2.62</v>
       </c>
       <c r="H44" t="n">
-        <v>46.29</v>
-      </c>
-      <c r="I44" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.24</v>
+      </c>
+      <c r="I44" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J44" s="9" t="n">
-        <v>0.868</v>
+        <v>0.419</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>0.869</v>
+        <v>0.437</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="14" t="inlineStr"/>
@@ -2477,39 +2477,39 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="E45" s="15" t="n">
-        <v>-0.0303</v>
+        <v>0.39</v>
+      </c>
+      <c r="E45" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>3535600</v>
+        <v>4099800</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>0.49</v>
+        <v>0.38</v>
       </c>
       <c r="H45" t="n">
-        <v>68.45</v>
-      </c>
-      <c r="I45" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.84</v>
+      </c>
+      <c r="I45" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J45" s="9" t="n">
-        <v>0.299</v>
+        <v>0.399</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>0.278</v>
+        <v>0.408</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="14" t="inlineStr"/>
@@ -2522,28 +2522,28 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0258</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>AGMO</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>0.29</v>
+        <v>3.75</v>
       </c>
       <c r="E46" s="16" t="n">
-        <v>0.0175</v>
+        <v>0.0331</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>3399700</v>
+        <v>4046900</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>4.53</v>
+        <v>0.42</v>
       </c>
       <c r="H46" t="n">
-        <v>53.95</v>
+        <v>57</v>
       </c>
       <c r="I46" s="13" t="inlineStr">
         <is>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="J46" s="9" t="n">
-        <v>0.28</v>
+        <v>3.61</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>0.301</v>
+        <v>2.872</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="14" t="inlineStr"/>
@@ -2567,39 +2567,39 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>IOICORP</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="E47" s="15" t="n">
-        <v>-0.0022</v>
+        <v>4.79</v>
+      </c>
+      <c r="E47" s="16" t="n">
+        <v>0.0191</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>3372300</v>
+        <v>4038400</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>0.35</v>
+        <v>0.24</v>
       </c>
       <c r="H47" t="n">
-        <v>39.27</v>
-      </c>
-      <c r="I47" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.81</v>
+      </c>
+      <c r="I47" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J47" s="9" t="n">
-        <v>4.644</v>
+        <v>4.722</v>
       </c>
       <c r="K47" s="9" t="n">
-        <v>4.63</v>
+        <v>4.871</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="14" t="inlineStr"/>
@@ -2612,28 +2612,28 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D48" s="9" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="E48" s="10" t="n">
-        <v>0</v>
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="E48" s="16" t="n">
+        <v>0.0108</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>3220800</v>
+        <v>4034200</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>0.08</v>
+        <v>0.73</v>
       </c>
       <c r="H48" t="n">
-        <v>24.11</v>
+        <v>62.32</v>
       </c>
       <c r="I48" s="13" t="inlineStr">
         <is>
@@ -2641,10 +2641,10 @@
         </is>
       </c>
       <c r="J48" s="9" t="n">
-        <v>0.524</v>
+        <v>0.912</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>0.713</v>
+        <v>0.869</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="14" t="inlineStr"/>
@@ -2657,28 +2657,28 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>4.79</v>
-      </c>
-      <c r="E49" s="16" t="n">
-        <v>0.0191</v>
+        <v>2.13</v>
+      </c>
+      <c r="E49" s="15" t="n">
+        <v>-0.004699999999999999</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>3091900</v>
+        <v>3955200</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
       <c r="H49" t="n">
-        <v>53.81</v>
+        <v>53.98</v>
       </c>
       <c r="I49" s="17" t="inlineStr">
         <is>
@@ -2686,10 +2686,10 @@
         </is>
       </c>
       <c r="J49" s="9" t="n">
-        <v>4.722</v>
+        <v>2.111</v>
       </c>
       <c r="K49" s="9" t="n">
-        <v>4.871</v>
+        <v>2.094</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="14" t="inlineStr"/>
@@ -2702,28 +2702,28 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>WCT</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D50" s="9" t="n">
-        <v>0.315</v>
-      </c>
-      <c r="E50" s="10" t="n">
-        <v>0</v>
+        <v>1.21</v>
+      </c>
+      <c r="E50" s="15" t="n">
+        <v>-0.0692</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>2906800</v>
+        <v>3945300</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>0.58</v>
+        <v>1.21</v>
       </c>
       <c r="H50" t="n">
-        <v>26.24</v>
+        <v>50.47</v>
       </c>
       <c r="I50" s="13" t="inlineStr">
         <is>
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="J50" s="9" t="n">
-        <v>0.351</v>
+        <v>1.252</v>
       </c>
       <c r="K50" s="9" t="n">
-        <v>0.379</v>
+        <v>1.04</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="14" t="inlineStr"/>
@@ -2747,28 +2747,28 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>AMBANK</t>
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="E51" s="15" t="n">
-        <v>-0.0105</v>
+        <v>6.45</v>
+      </c>
+      <c r="E51" s="16" t="n">
+        <v>0.0287</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>2900300</v>
+        <v>3681800</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>0.42</v>
+        <v>0.65</v>
       </c>
       <c r="H51" t="n">
-        <v>22.01</v>
+        <v>47.84</v>
       </c>
       <c r="I51" s="13" t="inlineStr">
         <is>
@@ -2776,10 +2776,10 @@
         </is>
       </c>
       <c r="J51" s="9" t="n">
-        <v>0.5620000000000001</v>
+        <v>6.429</v>
       </c>
       <c r="K51" s="9" t="n">
-        <v>0.629</v>
+        <v>6.805</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="14" t="inlineStr"/>
@@ -2792,28 +2792,28 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>7243</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>MAGMA</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D52" s="9" t="n">
-        <v>0.285</v>
+        <v>0.455</v>
       </c>
       <c r="E52" s="16" t="n">
-        <v>0.0556</v>
+        <v>0.0111</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>2884700</v>
+        <v>3595800</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>4.18</v>
+        <v>0.09</v>
       </c>
       <c r="H52" t="n">
-        <v>53.17</v>
+        <v>25.7</v>
       </c>
       <c r="I52" s="13" t="inlineStr">
         <is>
@@ -2821,10 +2821,10 @@
         </is>
       </c>
       <c r="J52" s="9" t="n">
-        <v>0.281</v>
+        <v>0.525</v>
       </c>
       <c r="K52" s="9" t="n">
-        <v>0.285</v>
+        <v>0.713</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="14" t="inlineStr"/>
@@ -2837,28 +2837,28 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D53" s="9" t="n">
-        <v>1.27</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="E53" s="16" t="n">
-        <v>0.016</v>
+        <v>0.001</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>2857800</v>
+        <v>3573500</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>0.74</v>
+        <v>0.27</v>
       </c>
       <c r="H53" t="n">
-        <v>25.43</v>
+        <v>44.4</v>
       </c>
       <c r="I53" s="13" t="inlineStr">
         <is>
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="J53" s="9" t="n">
-        <v>1.442</v>
+        <v>10.006</v>
       </c>
       <c r="K53" s="9" t="n">
-        <v>1.59</v>
+        <v>10.178</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="14" t="inlineStr"/>
@@ -2882,39 +2882,39 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D54" s="9" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="E54" s="16" t="n">
-        <v>0.0048</v>
+        <v>0.32</v>
+      </c>
+      <c r="E54" s="15" t="n">
+        <v>-0.0303</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>2854700</v>
+        <v>3555600</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>0.19</v>
+        <v>0.49</v>
       </c>
       <c r="H54" t="n">
-        <v>38.63</v>
-      </c>
-      <c r="I54" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>68.45</v>
+      </c>
+      <c r="I54" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J54" s="9" t="n">
-        <v>2.191</v>
+        <v>0.299</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>2.225</v>
+        <v>0.278</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="14" t="inlineStr"/>
@@ -2927,39 +2927,39 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>5336</t>
+          <t>0258</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>CKI</t>
+          <t>AGMO</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>0.37</v>
+        <v>0.29</v>
       </c>
       <c r="E55" s="16" t="n">
-        <v>0.0137</v>
+        <v>0.0175</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>2835200</v>
+        <v>3442500</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>1.84</v>
+        <v>4.58</v>
       </c>
       <c r="H55" t="n">
-        <v>51.33</v>
-      </c>
-      <c r="I55" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.95</v>
+      </c>
+      <c r="I55" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J55" s="9" t="n">
-        <v>0.364</v>
+        <v>0.28</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>0.387</v>
+        <v>0.301</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="14" t="inlineStr"/>
@@ -2972,28 +2972,28 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>VELESTO</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D56" s="9" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="E56" s="16" t="n">
-        <v>0.04650000000000001</v>
+        <v>0.215</v>
+      </c>
+      <c r="E56" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>2834300</v>
+        <v>3440000</v>
       </c>
       <c r="G56" s="12" t="n">
         <v>0.13</v>
       </c>
       <c r="H56" t="n">
-        <v>48.41</v>
+        <v>30.12</v>
       </c>
       <c r="I56" s="13" t="inlineStr">
         <is>
@@ -3001,10 +3001,10 @@
         </is>
       </c>
       <c r="J56" s="9" t="n">
-        <v>0.224</v>
+        <v>0.241</v>
       </c>
       <c r="K56" s="9" t="n">
-        <v>0.24</v>
+        <v>0.295</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="14" t="inlineStr"/>
@@ -3017,28 +3017,28 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>1.04</v>
+        <v>0.31</v>
       </c>
       <c r="E57" s="15" t="n">
-        <v>-0.0095</v>
+        <v>-0.0159</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>2719200</v>
+        <v>3391000</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>0.32</v>
+        <v>0.68</v>
       </c>
       <c r="H57" t="n">
-        <v>49.14</v>
+        <v>24.94</v>
       </c>
       <c r="I57" s="13" t="inlineStr">
         <is>
@@ -3046,10 +3046,10 @@
         </is>
       </c>
       <c r="J57" s="9" t="n">
-        <v>1.069</v>
+        <v>0.35</v>
       </c>
       <c r="K57" s="9" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.379</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="14" t="inlineStr"/>
@@ -3062,28 +3062,28 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D58" s="9" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="E58" s="16" t="n">
-        <v>0.0149</v>
+        <v>0.475</v>
+      </c>
+      <c r="E58" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>2661800</v>
+        <v>3347000</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>0.3</v>
+        <v>0.48</v>
       </c>
       <c r="H58" t="n">
-        <v>48.33</v>
+        <v>22.56</v>
       </c>
       <c r="I58" s="13" t="inlineStr">
         <is>
@@ -3091,10 +3091,10 @@
         </is>
       </c>
       <c r="J58" s="9" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="K58" s="9" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.629</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="14" t="inlineStr"/>
@@ -3107,39 +3107,39 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>VELESTO</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>1.03</v>
+        <v>0.225</v>
       </c>
       <c r="E59" s="16" t="n">
-        <v>0.0352</v>
+        <v>0.04650000000000001</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>2658200</v>
+        <v>3335000</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>0.75</v>
+        <v>0.16</v>
       </c>
       <c r="H59" t="n">
-        <v>84.3</v>
-      </c>
-      <c r="I59" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.41</v>
+      </c>
+      <c r="I59" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J59" s="9" t="n">
-        <v>0.749</v>
+        <v>0.224</v>
       </c>
       <c r="K59" s="9" t="n">
-        <v>0.523</v>
+        <v>0.24</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="14" t="inlineStr"/>
@@ -3152,28 +3152,28 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>0.215</v>
-      </c>
-      <c r="E60" s="10" t="n">
-        <v>0</v>
+        <v>2.09</v>
+      </c>
+      <c r="E60" s="16" t="n">
+        <v>0.0048</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>2641600</v>
+        <v>3230900</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>0.1</v>
+        <v>0.22</v>
       </c>
       <c r="H60" t="n">
-        <v>30.12</v>
+        <v>38.63</v>
       </c>
       <c r="I60" s="13" t="inlineStr">
         <is>
@@ -3181,10 +3181,10 @@
         </is>
       </c>
       <c r="J60" s="9" t="n">
-        <v>0.241</v>
+        <v>2.191</v>
       </c>
       <c r="K60" s="9" t="n">
-        <v>0.295</v>
+        <v>2.225</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="14" t="inlineStr"/>
@@ -3197,28 +3197,28 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>AMBANK</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>6.45</v>
-      </c>
-      <c r="E61" s="16" t="n">
-        <v>0.0287</v>
+        <v>0.495</v>
+      </c>
+      <c r="E61" s="15" t="n">
+        <v>-0.01</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>2604800</v>
+        <v>3203900</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>0.46</v>
+        <v>0.38</v>
       </c>
       <c r="H61" t="n">
-        <v>47.84</v>
+        <v>42.01</v>
       </c>
       <c r="I61" s="13" t="inlineStr">
         <is>
@@ -3226,10 +3226,10 @@
         </is>
       </c>
       <c r="J61" s="9" t="n">
-        <v>6.429</v>
+        <v>0.517</v>
       </c>
       <c r="K61" s="9" t="n">
-        <v>6.805</v>
+        <v>0.529</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="14" t="inlineStr"/>
@@ -3242,39 +3242,39 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D62" s="9" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="E62" s="10" t="n">
-        <v>0</v>
+        <v>1.27</v>
+      </c>
+      <c r="E62" s="16" t="n">
+        <v>0.016</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>2591600</v>
+        <v>2970200</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>0.82</v>
+        <v>0.77</v>
       </c>
       <c r="H62" t="n">
-        <v>79.09999999999999</v>
-      </c>
-      <c r="I62" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>25.43</v>
+      </c>
+      <c r="I62" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J62" s="9" t="n">
-        <v>2.732</v>
+        <v>1.442</v>
       </c>
       <c r="K62" s="9" t="n">
-        <v>2.357</v>
+        <v>1.59</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="14" t="inlineStr"/>
@@ -3287,39 +3287,39 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>0.805</v>
-      </c>
-      <c r="E63" s="10" t="n">
-        <v>0</v>
+        <v>1.2</v>
+      </c>
+      <c r="E63" s="15" t="n">
+        <v>-0.0083</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>2590400</v>
+        <v>2951200</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>0.44</v>
+        <v>0.37</v>
       </c>
       <c r="H63" t="n">
-        <v>66.90000000000001</v>
-      </c>
-      <c r="I63" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.03</v>
+      </c>
+      <c r="I63" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J63" s="9" t="n">
-        <v>0.791</v>
+        <v>1.246</v>
       </c>
       <c r="K63" s="9" t="n">
-        <v>0.768</v>
+        <v>1.342</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="14" t="inlineStr"/>
@@ -3332,39 +3332,39 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>5336</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>CKI</t>
         </is>
       </c>
       <c r="D64" s="9" t="n">
-        <v>9.99</v>
+        <v>0.37</v>
       </c>
       <c r="E64" s="16" t="n">
-        <v>0.003</v>
+        <v>0.0137</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>2488900</v>
+        <v>2950600</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>0.19</v>
+        <v>1.92</v>
       </c>
       <c r="H64" t="n">
-        <v>45.88</v>
-      </c>
-      <c r="I64" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.33</v>
+      </c>
+      <c r="I64" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J64" s="9" t="n">
-        <v>10.008</v>
+        <v>0.364</v>
       </c>
       <c r="K64" s="9" t="n">
-        <v>10.178</v>
+        <v>0.387</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="14" t="inlineStr"/>
@@ -3377,28 +3377,28 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="E65" s="15" t="n">
-        <v>-0.0083</v>
+        <v>1.18</v>
+      </c>
+      <c r="E65" s="16" t="n">
+        <v>0.0172</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>2411700</v>
+        <v>2942000</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>0.3</v>
+        <v>0.38</v>
       </c>
       <c r="H65" t="n">
-        <v>37.03</v>
+        <v>53.23</v>
       </c>
       <c r="I65" s="13" t="inlineStr">
         <is>
@@ -3406,10 +3406,10 @@
         </is>
       </c>
       <c r="J65" s="9" t="n">
-        <v>1.246</v>
+        <v>1.162</v>
       </c>
       <c r="K65" s="9" t="n">
-        <v>1.342</v>
+        <v>1.127</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="14" t="inlineStr"/>
@@ -3422,39 +3422,39 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D66" s="9" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="E66" s="15" t="n">
-        <v>-0.0538</v>
+        <v>0.805</v>
+      </c>
+      <c r="E66" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>2349000</v>
+        <v>2912100</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>0.72</v>
+        <v>0.49</v>
       </c>
       <c r="H66" t="n">
-        <v>52.29</v>
-      </c>
-      <c r="I66" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.90000000000001</v>
+      </c>
+      <c r="I66" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J66" s="9" t="n">
-        <v>1.254</v>
+        <v>0.791</v>
       </c>
       <c r="K66" s="9" t="n">
-        <v>1.041</v>
+        <v>0.768</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="14" t="inlineStr"/>
@@ -3467,28 +3467,28 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>7243</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>MAGMA</t>
         </is>
       </c>
       <c r="D67" s="9" t="n">
-        <v>3.73</v>
+        <v>0.285</v>
       </c>
       <c r="E67" s="16" t="n">
-        <v>0.0275</v>
+        <v>0.0556</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>2312200</v>
+        <v>2891000</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>0.24</v>
+        <v>4.19</v>
       </c>
       <c r="H67" t="n">
-        <v>56.58</v>
+        <v>53.17</v>
       </c>
       <c r="I67" s="13" t="inlineStr">
         <is>
@@ -3496,10 +3496,10 @@
         </is>
       </c>
       <c r="J67" s="9" t="n">
-        <v>3.608</v>
+        <v>0.281</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>2.871</v>
+        <v>0.285</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="14" t="inlineStr"/>
@@ -3512,28 +3512,28 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D68" s="9" t="n">
-        <v>0.495</v>
+        <v>1.04</v>
       </c>
       <c r="E68" s="15" t="n">
-        <v>-0.01</v>
+        <v>-0.0095</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>2279100</v>
+        <v>2802200</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="H68" t="n">
-        <v>42.01</v>
+        <v>49.14</v>
       </c>
       <c r="I68" s="13" t="inlineStr">
         <is>
@@ -3541,10 +3541,10 @@
         </is>
       </c>
       <c r="J68" s="9" t="n">
-        <v>0.517</v>
+        <v>1.069</v>
       </c>
       <c r="K68" s="9" t="n">
-        <v>0.529</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="14" t="inlineStr"/>
@@ -3557,28 +3557,28 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D69" s="9" t="n">
-        <v>0.66</v>
+        <v>0.675</v>
       </c>
       <c r="E69" s="16" t="n">
-        <v>0.0076</v>
+        <v>0.0075</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>2274400</v>
+        <v>2764900</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>0.26</v>
+        <v>0.31</v>
       </c>
       <c r="H69" t="n">
-        <v>50.26</v>
+        <v>47.36</v>
       </c>
       <c r="I69" s="13" t="inlineStr">
         <is>
@@ -3586,10 +3586,10 @@
         </is>
       </c>
       <c r="J69" s="9" t="n">
-        <v>0.67</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="K69" s="9" t="n">
-        <v>0.617</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="14" t="inlineStr"/>
@@ -3602,28 +3602,28 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0471</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>PIONEER</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D70" s="9" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="E70" s="16" t="n">
-        <v>0.0476</v>
+        <v>2.99</v>
+      </c>
+      <c r="E70" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>2263100</v>
+        <v>2698000</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>0.25</v>
+        <v>0.85</v>
       </c>
       <c r="H70" t="n">
-        <v>58.79</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="I70" s="17" t="inlineStr">
         <is>
@@ -3631,9 +3631,11 @@
         </is>
       </c>
       <c r="J70" s="9" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="K70" s="9" t="n"/>
+        <v>2.732</v>
+      </c>
+      <c r="K70" s="9" t="n">
+        <v>2.357</v>
+      </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="14" t="inlineStr"/>
     </row>
@@ -3645,28 +3647,28 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>0.6</v>
+        <v>0.655</v>
       </c>
       <c r="E71" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>2176600</v>
+        <v>2657600</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>0.52</v>
+        <v>0.3</v>
       </c>
       <c r="H71" t="n">
-        <v>51.48</v>
+        <v>49.29</v>
       </c>
       <c r="I71" s="13" t="inlineStr">
         <is>
@@ -3674,10 +3676,10 @@
         </is>
       </c>
       <c r="J71" s="9" t="n">
-        <v>0.6</v>
+        <v>0.669</v>
       </c>
       <c r="K71" s="9" t="n">
-        <v>0.585</v>
+        <v>0.617</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="14" t="inlineStr"/>
@@ -3690,39 +3692,39 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0272</t>
+          <t>0388</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>TTVHB</t>
+          <t>SEMICO</t>
         </is>
       </c>
       <c r="D72" s="9" t="n">
-        <v>0.245</v>
+        <v>0.62</v>
       </c>
       <c r="E72" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>2051900</v>
+        <v>2535000</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="H72" t="n">
-        <v>47.66</v>
-      </c>
-      <c r="I72" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.41</v>
+      </c>
+      <c r="I72" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J72" s="9" t="n">
-        <v>0.25</v>
+        <v>0.615</v>
       </c>
       <c r="K72" s="9" t="n">
-        <v>0.255</v>
+        <v>0.602</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="14" t="inlineStr"/>
@@ -3735,40 +3737,38 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>0471</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>PIONEER</t>
         </is>
       </c>
       <c r="D73" s="9" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="E73" s="15" t="n">
-        <v>-0.0177</v>
+        <v>0.33</v>
+      </c>
+      <c r="E73" s="16" t="n">
+        <v>0.0476</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>1977200</v>
+        <v>2409200</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>0.14</v>
+        <v>0.26</v>
       </c>
       <c r="H73" t="n">
-        <v>49.37</v>
-      </c>
-      <c r="I73" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.79</v>
+      </c>
+      <c r="I73" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J73" s="9" t="n">
-        <v>2.795</v>
-      </c>
-      <c r="K73" s="9" t="n">
-        <v>2.721</v>
-      </c>
+        <v>0.305</v>
+      </c>
+      <c r="K73" s="9" t="n"/>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="14" t="inlineStr"/>
     </row>
@@ -3780,28 +3780,28 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D74" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E74" s="15" t="n">
-        <v>-0.0566</v>
+        <v>0.605</v>
+      </c>
+      <c r="E74" s="16" t="n">
+        <v>0.0083</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>1888700</v>
+        <v>2387900</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>0.41</v>
+        <v>0.57</v>
       </c>
       <c r="H74" t="n">
-        <v>46.1</v>
+        <v>52.64</v>
       </c>
       <c r="I74" s="13" t="inlineStr">
         <is>
@@ -3809,10 +3809,10 @@
         </is>
       </c>
       <c r="J74" s="9" t="n">
-        <v>1.055</v>
+        <v>0.6</v>
       </c>
       <c r="K74" s="9" t="n">
-        <v>0.919</v>
+        <v>0.585</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="14" t="inlineStr"/>
@@ -3825,28 +3825,28 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0233</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>PEKAT</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D75" s="9" t="n">
-        <v>2.69</v>
+        <v>2.78</v>
       </c>
       <c r="E75" s="15" t="n">
-        <v>-0.0756</v>
+        <v>-0.0142</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>1848500</v>
+        <v>2379300</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>0.57</v>
+        <v>0.17</v>
       </c>
       <c r="H75" t="n">
-        <v>56.18</v>
+        <v>50.17</v>
       </c>
       <c r="I75" s="13" t="inlineStr">
         <is>
@@ -3854,10 +3854,10 @@
         </is>
       </c>
       <c r="J75" s="9" t="n">
-        <v>2.671</v>
+        <v>2.796</v>
       </c>
       <c r="K75" s="9" t="n">
-        <v>2.206</v>
+        <v>2.721</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="14" t="inlineStr"/>
@@ -3870,28 +3870,28 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D76" s="9" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="E76" s="16" t="n">
-        <v>0.0259</v>
+        <v>5.48</v>
+      </c>
+      <c r="E76" s="15" t="n">
+        <v>-0.0036</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>1762800</v>
+        <v>2266300</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>0.23</v>
+        <v>0.16</v>
       </c>
       <c r="H76" t="n">
-        <v>54.4</v>
+        <v>45.95</v>
       </c>
       <c r="I76" s="13" t="inlineStr">
         <is>
@@ -3899,10 +3899,10 @@
         </is>
       </c>
       <c r="J76" s="9" t="n">
-        <v>1.163</v>
+        <v>5.606</v>
       </c>
       <c r="K76" s="9" t="n">
-        <v>1.127</v>
+        <v>5.388</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="14" t="inlineStr"/>
@@ -3915,39 +3915,39 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0388</t>
+          <t>0296</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>SEMICO</t>
+          <t>HEGROUP</t>
         </is>
       </c>
       <c r="D77" s="9" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="E77" s="10" t="n">
-        <v>0</v>
+        <v>1.02</v>
+      </c>
+      <c r="E77" s="15" t="n">
+        <v>-0.0377</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>1675700</v>
+        <v>2110400</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>0.54</v>
+        <v>0.46</v>
       </c>
       <c r="H77" t="n">
-        <v>64.41</v>
-      </c>
-      <c r="I77" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.75</v>
+      </c>
+      <c r="I77" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J77" s="9" t="n">
-        <v>0.615</v>
+        <v>1.057</v>
       </c>
       <c r="K77" s="9" t="n">
-        <v>0.602</v>
+        <v>0.919</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="14" t="inlineStr"/>
@@ -3960,28 +3960,28 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>0272</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>TTVHB</t>
         </is>
       </c>
       <c r="D78" s="9" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E78" s="15" t="n">
-        <v>-0.0064</v>
+        <v>0.245</v>
+      </c>
+      <c r="E78" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>1669800</v>
+        <v>2083400</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>0.2</v>
+        <v>0.89</v>
       </c>
       <c r="H78" t="n">
-        <v>49.19</v>
+        <v>47.66</v>
       </c>
       <c r="I78" s="13" t="inlineStr">
         <is>
@@ -3989,10 +3989,10 @@
         </is>
       </c>
       <c r="J78" s="9" t="n">
-        <v>0.779</v>
+        <v>0.25</v>
       </c>
       <c r="K78" s="9" t="n">
-        <v>0.773</v>
+        <v>0.255</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="14" t="inlineStr"/>
@@ -4005,28 +4005,28 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>0233</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>PEKAT</t>
         </is>
       </c>
       <c r="D79" s="9" t="n">
-        <v>0.905</v>
+        <v>2.68</v>
       </c>
       <c r="E79" s="15" t="n">
-        <v>-0.0163</v>
+        <v>-0.079</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>1586200</v>
+        <v>2057700</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>0.19</v>
+        <v>0.63</v>
       </c>
       <c r="H79" t="n">
-        <v>46.02</v>
+        <v>55.63</v>
       </c>
       <c r="I79" s="13" t="inlineStr">
         <is>
@@ -4034,10 +4034,10 @@
         </is>
       </c>
       <c r="J79" s="9" t="n">
-        <v>0.95</v>
+        <v>2.67</v>
       </c>
       <c r="K79" s="9" t="n">
-        <v>0.837</v>
+        <v>2.206</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="14" t="inlineStr"/>
@@ -4050,39 +4050,39 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D80" s="9" t="n">
-        <v>5.46</v>
-      </c>
-      <c r="E80" s="15" t="n">
-        <v>-0.0073</v>
+        <v>7.34</v>
+      </c>
+      <c r="E80" s="16" t="n">
+        <v>0.0124</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>1582500</v>
+        <v>2009000</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>0.11</v>
+        <v>0.26</v>
       </c>
       <c r="H80" t="n">
-        <v>45.19</v>
-      </c>
-      <c r="I80" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>44.29</v>
+      </c>
+      <c r="I80" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J80" s="9" t="n">
-        <v>5.604</v>
+        <v>7.376</v>
       </c>
       <c r="K80" s="9" t="n">
-        <v>5.388</v>
+        <v>7.687</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="14" t="inlineStr"/>
@@ -4095,39 +4095,39 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0376</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>IAB</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D81" s="9" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="E81" s="15" t="n">
-        <v>-0.008500000000000001</v>
+        <v>1.62</v>
+      </c>
+      <c r="E81" s="16" t="n">
+        <v>0.0189</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>1572700</v>
+        <v>1964500</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.29</v>
       </c>
       <c r="H81" t="n">
-        <v>40.26</v>
-      </c>
-      <c r="I81" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.09</v>
+      </c>
+      <c r="I81" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J81" s="9" t="n">
-        <v>1.251</v>
+        <v>1.614</v>
       </c>
       <c r="K81" s="9" t="n">
-        <v>1.309</v>
+        <v>1.709</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="14" t="inlineStr"/>
@@ -4140,28 +4140,28 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>0470</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>BFIELD</t>
         </is>
       </c>
       <c r="D82" s="9" t="n">
-        <v>2.56</v>
+        <v>0.45</v>
       </c>
       <c r="E82" s="15" t="n">
-        <v>-0.007800000000000001</v>
+        <v>-0.011</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>1483500</v>
+        <v>1956800</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>0.24</v>
+        <v>0.18</v>
       </c>
       <c r="H82" t="n">
-        <v>45.83</v>
+        <v>30.03</v>
       </c>
       <c r="I82" s="13" t="inlineStr">
         <is>
@@ -4169,11 +4169,9 @@
         </is>
       </c>
       <c r="J82" s="9" t="n">
-        <v>2.626</v>
-      </c>
-      <c r="K82" s="9" t="n">
-        <v>2.597</v>
-      </c>
+        <v>0.472</v>
+      </c>
+      <c r="K82" s="9" t="n"/>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="14" t="inlineStr"/>
     </row>
@@ -4185,28 +4183,28 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D83" s="9" t="n">
-        <v>2.43</v>
+        <v>0.775</v>
       </c>
       <c r="E83" s="15" t="n">
-        <v>-0.0122</v>
+        <v>-0.0064</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>1480900</v>
+        <v>1826800</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="H83" t="n">
-        <v>48.22</v>
+        <v>49.19</v>
       </c>
       <c r="I83" s="13" t="inlineStr">
         <is>
@@ -4214,10 +4212,10 @@
         </is>
       </c>
       <c r="J83" s="9" t="n">
-        <v>2.459</v>
+        <v>0.779</v>
       </c>
       <c r="K83" s="9" t="n">
-        <v>2.367</v>
+        <v>0.773</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="14" t="inlineStr"/>
@@ -4230,39 +4228,39 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D84" s="9" t="n">
-        <v>7.38</v>
-      </c>
-      <c r="E84" s="16" t="n">
-        <v>0.0179</v>
+        <v>2.43</v>
+      </c>
+      <c r="E84" s="15" t="n">
+        <v>-0.0122</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>1474200</v>
+        <v>1757400</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>0.19</v>
+        <v>0.14</v>
       </c>
       <c r="H84" t="n">
-        <v>46.49</v>
-      </c>
-      <c r="I84" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.22</v>
+      </c>
+      <c r="I84" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J84" s="9" t="n">
-        <v>7.38</v>
+        <v>2.459</v>
       </c>
       <c r="K84" s="9" t="n">
-        <v>7.687</v>
+        <v>2.367</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="14" t="inlineStr"/>
@@ -4275,39 +4273,39 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D85" s="9" t="n">
-        <v>0.425</v>
+        <v>7.34</v>
       </c>
       <c r="E85" s="16" t="n">
-        <v>0.0119</v>
+        <v>0.005500000000000001</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>1461500</v>
+        <v>1719100</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>0.21</v>
+        <v>0.17</v>
       </c>
       <c r="H85" t="n">
-        <v>50.96</v>
-      </c>
-      <c r="I85" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.85</v>
+      </c>
+      <c r="I85" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J85" s="9" t="n">
-        <v>0.427</v>
+        <v>7.521</v>
       </c>
       <c r="K85" s="9" t="n">
-        <v>0.415</v>
+        <v>8.026999999999999</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="14" t="inlineStr"/>
@@ -4320,39 +4318,39 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0398</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>GDGROUP</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D86" s="9" t="n">
-        <v>0.38</v>
+        <v>0.905</v>
       </c>
       <c r="E86" s="15" t="n">
-        <v>-0.013</v>
+        <v>-0.0163</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>1454500</v>
+        <v>1679700</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>1.63</v>
+        <v>0.2</v>
       </c>
       <c r="H86" t="n">
-        <v>49.68</v>
-      </c>
-      <c r="I86" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.02</v>
+      </c>
+      <c r="I86" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J86" s="9" t="n">
-        <v>0.381</v>
+        <v>0.95</v>
       </c>
       <c r="K86" s="9" t="n">
-        <v>0.379</v>
+        <v>0.837</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="14" t="inlineStr"/>
@@ -4365,39 +4363,39 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>KPJ</t>
         </is>
       </c>
       <c r="D87" s="9" t="n">
-        <v>1.22</v>
+        <v>2.52</v>
       </c>
       <c r="E87" s="16" t="n">
-        <v>0.0167</v>
+        <v>0.0244</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>1453500</v>
+        <v>1662600</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="H87" t="n">
-        <v>57.43</v>
-      </c>
-      <c r="I87" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.82</v>
+      </c>
+      <c r="I87" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J87" s="9" t="n">
-        <v>1.171</v>
+        <v>2.572</v>
       </c>
       <c r="K87" s="9" t="n">
-        <v>1.176</v>
+        <v>2.75</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="14" t="inlineStr"/>
@@ -4410,39 +4408,39 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>5329</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>AZAMJAYA</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D88" s="9" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="E88" s="16" t="n">
-        <v>0.0421</v>
+        <v>0.475</v>
+      </c>
+      <c r="E88" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>1445500</v>
+        <v>1634300</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>15.94</v>
+        <v>0.21</v>
       </c>
       <c r="H88" t="n">
-        <v>54.39</v>
-      </c>
-      <c r="I88" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>29.95</v>
+      </c>
+      <c r="I88" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J88" s="9" t="n">
-        <v>0.969</v>
+        <v>0.511</v>
       </c>
       <c r="K88" s="9" t="n">
-        <v>0.978</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="14" t="inlineStr"/>
@@ -4455,28 +4453,28 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>0376</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>IAB</t>
         </is>
       </c>
       <c r="D89" s="9" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E89" s="16" t="n">
-        <v>0.007900000000000001</v>
+        <v>1.17</v>
+      </c>
+      <c r="E89" s="15" t="n">
+        <v>-0.008500000000000001</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>1430300</v>
+        <v>1626700</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>0.27</v>
+        <v>0.72</v>
       </c>
       <c r="H89" t="n">
-        <v>66.08</v>
+        <v>40.26</v>
       </c>
       <c r="I89" s="13" t="inlineStr">
         <is>
@@ -4484,10 +4482,10 @@
         </is>
       </c>
       <c r="J89" s="9" t="n">
-        <v>0.553</v>
+        <v>1.251</v>
       </c>
       <c r="K89" s="9" t="n">
-        <v>0.458</v>
+        <v>1.309</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="14" t="inlineStr"/>
@@ -4500,28 +4498,28 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D90" s="9" t="n">
-        <v>1.61</v>
+        <v>1.23</v>
       </c>
       <c r="E90" s="16" t="n">
-        <v>0.0126</v>
+        <v>0.025</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>1426800</v>
+        <v>1626600</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>0.21</v>
+        <v>0.28</v>
       </c>
       <c r="H90" t="n">
-        <v>46.72</v>
+        <v>58.53</v>
       </c>
       <c r="I90" s="17" t="inlineStr">
         <is>
@@ -4529,10 +4527,10 @@
         </is>
       </c>
       <c r="J90" s="9" t="n">
-        <v>1.613</v>
+        <v>1.172</v>
       </c>
       <c r="K90" s="9" t="n">
-        <v>1.709</v>
+        <v>1.176</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="14" t="inlineStr"/>
@@ -4545,39 +4543,39 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>0056</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>NCT</t>
         </is>
       </c>
       <c r="D91" s="9" t="n">
-        <v>7.36</v>
-      </c>
-      <c r="E91" s="16" t="n">
-        <v>0.008199999999999999</v>
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E91" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>1353500</v>
+        <v>1523700</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>0.13</v>
+        <v>0.7</v>
       </c>
       <c r="H91" t="n">
-        <v>36.12</v>
-      </c>
-      <c r="I91" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.27</v>
+      </c>
+      <c r="I91" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J91" s="9" t="n">
-        <v>7.523</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="K91" s="9" t="n">
-        <v>8.028</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="14" t="inlineStr"/>
@@ -4590,28 +4588,28 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D92" s="9" t="n">
-        <v>0.47</v>
+        <v>2.57</v>
       </c>
       <c r="E92" s="15" t="n">
-        <v>-0.0105</v>
+        <v>-0.0039</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>1311700</v>
+        <v>1513700</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>0.17</v>
+        <v>0.24</v>
       </c>
       <c r="H92" t="n">
-        <v>28.83</v>
+        <v>46.48</v>
       </c>
       <c r="I92" s="13" t="inlineStr">
         <is>
@@ -4619,10 +4617,10 @@
         </is>
       </c>
       <c r="J92" s="9" t="n">
-        <v>0.511</v>
+        <v>2.627</v>
       </c>
       <c r="K92" s="9" t="n">
-        <v>0.5649999999999999</v>
+        <v>2.597</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="14" t="inlineStr"/>
@@ -4635,28 +4633,28 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>7498</t>
+          <t>0278</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>RALCO</t>
+          <t>EDELTEQ</t>
         </is>
       </c>
       <c r="D93" s="9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="E93" s="10" t="n">
-        <v>0</v>
+        <v>0.42</v>
+      </c>
+      <c r="E93" s="16" t="n">
+        <v>0.03700000000000001</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>1301700</v>
+        <v>1504400</v>
       </c>
       <c r="G93" s="12" t="n">
-        <v>1.99</v>
+        <v>0.32</v>
       </c>
       <c r="H93" t="n">
-        <v>55.9</v>
+        <v>62.11</v>
       </c>
       <c r="I93" s="17" t="inlineStr">
         <is>
@@ -4664,10 +4662,10 @@
         </is>
       </c>
       <c r="J93" s="9" t="n">
-        <v>0.999</v>
+        <v>0.374</v>
       </c>
       <c r="K93" s="9" t="n">
-        <v>0.982</v>
+        <v>0.354</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="14" t="inlineStr"/>
@@ -4680,39 +4678,39 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0372</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>CHEEDING</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D94" s="9" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="E94" s="15" t="n">
-        <v>-0.0172</v>
+        <v>0.425</v>
+      </c>
+      <c r="E94" s="16" t="n">
+        <v>0.0119</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>1299000</v>
+        <v>1481500</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>0.33</v>
+        <v>0.22</v>
       </c>
       <c r="H94" t="n">
-        <v>40.78</v>
-      </c>
-      <c r="I94" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.96</v>
+      </c>
+      <c r="I94" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J94" s="9" t="n">
-        <v>0.606</v>
+        <v>0.427</v>
       </c>
       <c r="K94" s="9" t="n">
-        <v>0.606</v>
+        <v>0.415</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="14" t="inlineStr"/>
@@ -4725,28 +4723,28 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>KPJ</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D95" s="9" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="E95" s="16" t="n">
-        <v>0.0244</v>
+        <v>0.92</v>
+      </c>
+      <c r="E95" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>1291800</v>
+        <v>1481500</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>0.24</v>
+        <v>1.06</v>
       </c>
       <c r="H95" t="n">
-        <v>42.82</v>
+        <v>51.78</v>
       </c>
       <c r="I95" s="13" t="inlineStr">
         <is>
@@ -4754,10 +4752,10 @@
         </is>
       </c>
       <c r="J95" s="9" t="n">
-        <v>2.572</v>
+        <v>0.923</v>
       </c>
       <c r="K95" s="9" t="n">
-        <v>2.75</v>
+        <v>0.863</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="14" t="inlineStr"/>
@@ -4770,28 +4768,28 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0100</t>
+          <t>0398</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>ESCERAM</t>
+          <t>GDGROUP</t>
         </is>
       </c>
       <c r="D96" s="9" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="E96" s="15" t="n">
-        <v>-0.0222</v>
+        <v>0.385</v>
+      </c>
+      <c r="E96" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>1275500</v>
+        <v>1474500</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>0.74</v>
+        <v>1.65</v>
       </c>
       <c r="H96" t="n">
-        <v>69.75</v>
+        <v>57.12</v>
       </c>
       <c r="I96" s="17" t="inlineStr">
         <is>
@@ -4799,10 +4797,10 @@
         </is>
       </c>
       <c r="J96" s="9" t="n">
-        <v>0.193</v>
+        <v>0.381</v>
       </c>
       <c r="K96" s="9" t="n">
-        <v>0.186</v>
+        <v>0.379</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="14" t="inlineStr"/>
@@ -4815,39 +4813,39 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0278</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>EDELTEQ</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D97" s="9" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="E97" s="16" t="n">
-        <v>0.03700000000000001</v>
+        <v>0.63</v>
+      </c>
+      <c r="E97" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>1213100</v>
+        <v>1465300</v>
       </c>
       <c r="G97" s="12" t="n">
-        <v>0.26</v>
+        <v>0.28</v>
       </c>
       <c r="H97" t="n">
-        <v>62.11</v>
-      </c>
-      <c r="I97" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>65.61</v>
+      </c>
+      <c r="I97" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J97" s="9" t="n">
-        <v>0.374</v>
+        <v>0.553</v>
       </c>
       <c r="K97" s="9" t="n">
-        <v>0.354</v>
+        <v>0.458</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="14" t="inlineStr"/>
@@ -4860,39 +4858,39 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>5337</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>ECOSHOP</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D98" s="9" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="E98" s="15" t="n">
-        <v>-0.0069</v>
+        <v>4.34</v>
+      </c>
+      <c r="E98" s="16" t="n">
+        <v>0.0046</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>1211900</v>
+        <v>1463600</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>0.28</v>
+        <v>0.23</v>
       </c>
       <c r="H98" t="n">
-        <v>40.99</v>
-      </c>
-      <c r="I98" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.01</v>
+      </c>
+      <c r="I98" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J98" s="9" t="n">
-        <v>1.453</v>
+        <v>4.356</v>
       </c>
       <c r="K98" s="9" t="n">
-        <v>1.467</v>
+        <v>4.441</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="14" t="inlineStr"/>
@@ -4905,28 +4903,28 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>5329</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>AZAMJAYA</t>
         </is>
       </c>
       <c r="D99" s="9" t="n">
-        <v>4.37</v>
+        <v>0.99</v>
       </c>
       <c r="E99" s="16" t="n">
-        <v>0.0116</v>
+        <v>0.0421</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>1204200</v>
+        <v>1445500</v>
       </c>
       <c r="G99" s="12" t="n">
-        <v>0.19</v>
+        <v>15.94</v>
       </c>
       <c r="H99" t="n">
-        <v>49.26</v>
+        <v>54.39</v>
       </c>
       <c r="I99" s="17" t="inlineStr">
         <is>
@@ -4934,10 +4932,10 @@
         </is>
       </c>
       <c r="J99" s="9" t="n">
-        <v>4.359</v>
+        <v>0.969</v>
       </c>
       <c r="K99" s="9" t="n">
-        <v>4.441</v>
+        <v>0.978</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="14" t="inlineStr"/>
@@ -4950,28 +4948,28 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>5337</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>ECOSHOP</t>
         </is>
       </c>
       <c r="D100" s="9" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="E100" s="16" t="n">
-        <v>0.0217</v>
+        <v>1.43</v>
+      </c>
+      <c r="E100" s="15" t="n">
+        <v>-0.0069</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>1202100</v>
+        <v>1400000</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>0.86</v>
+        <v>0.33</v>
       </c>
       <c r="H100" t="n">
-        <v>55.19</v>
+        <v>40.99</v>
       </c>
       <c r="I100" s="13" t="inlineStr">
         <is>
@@ -4979,10 +4977,10 @@
         </is>
       </c>
       <c r="J100" s="9" t="n">
-        <v>0.925</v>
+        <v>1.453</v>
       </c>
       <c r="K100" s="9" t="n">
-        <v>0.863</v>
+        <v>1.467</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="14" t="inlineStr"/>
@@ -4995,28 +4993,28 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>0372</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>CHEEDING</t>
         </is>
       </c>
       <c r="D101" s="9" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E101" s="16" t="n">
-        <v>0.0063</v>
+        <v>0.57</v>
+      </c>
+      <c r="E101" s="15" t="n">
+        <v>-0.0172</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>1194900</v>
+        <v>1366000</v>
       </c>
       <c r="G101" s="12" t="n">
-        <v>0.19</v>
+        <v>0.34</v>
       </c>
       <c r="H101" t="n">
-        <v>62.86</v>
+        <v>40.78</v>
       </c>
       <c r="I101" s="13" t="inlineStr">
         <is>
@@ -5024,10 +5022,10 @@
         </is>
       </c>
       <c r="J101" s="9" t="n">
-        <v>0.764</v>
+        <v>0.606</v>
       </c>
       <c r="K101" s="9" t="n">
-        <v>0.676</v>
+        <v>0.606</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="14" t="inlineStr"/>
@@ -5040,39 +5038,39 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0104</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>GENETEC</t>
+          <t>TENAGA</t>
         </is>
       </c>
       <c r="D102" s="9" t="n">
-        <v>0.305</v>
+        <v>13.04</v>
       </c>
       <c r="E102" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>1176400</v>
+        <v>1346200</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>0.19</v>
+        <v>0.14</v>
       </c>
       <c r="H102" t="n">
-        <v>40.49</v>
-      </c>
-      <c r="I102" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.5</v>
+      </c>
+      <c r="I102" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J102" s="9" t="n">
-        <v>0.321</v>
+        <v>13.031</v>
       </c>
       <c r="K102" s="9" t="n">
-        <v>0.338</v>
+        <v>13.494</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="14" t="inlineStr"/>
@@ -5085,28 +5083,28 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0056</t>
+          <t>7498</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>NCT</t>
+          <t>RALCO</t>
         </is>
       </c>
       <c r="D103" s="9" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="E103" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>1173000</v>
+        <v>1301700</v>
       </c>
       <c r="G103" s="12" t="n">
-        <v>0.54</v>
+        <v>1.99</v>
       </c>
       <c r="H103" t="n">
-        <v>48.27</v>
+        <v>55.9</v>
       </c>
       <c r="I103" s="17" t="inlineStr">
         <is>
@@ -5114,10 +5112,10 @@
         </is>
       </c>
       <c r="J103" s="9" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.999</v>
       </c>
       <c r="K103" s="9" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.982</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="14" t="inlineStr"/>
@@ -5130,39 +5128,39 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>AWC</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D104" s="9" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="E104" s="15" t="n">
-        <v>-0.0145</v>
+        <v>0.535</v>
+      </c>
+      <c r="E104" s="16" t="n">
+        <v>0.009399999999999999</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>1123900</v>
+        <v>1286700</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>0.48</v>
+        <v>0.09</v>
       </c>
       <c r="H104" t="n">
-        <v>63.67</v>
-      </c>
-      <c r="I104" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>55.88</v>
+      </c>
+      <c r="I104" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J104" s="9" t="n">
-        <v>0.636</v>
+        <v>0.519</v>
       </c>
       <c r="K104" s="9" t="n">
-        <v>0.543</v>
+        <v>0.45</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="14" t="inlineStr"/>
@@ -5175,38 +5173,40 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>0468</t>
+          <t>0100</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>UNIPAC</t>
+          <t>ESCERAM</t>
         </is>
       </c>
       <c r="D105" s="9" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="E105" s="15" t="n">
-        <v>-0.0213</v>
+        <v>-0.0222</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>1118800</v>
+        <v>1283500</v>
       </c>
       <c r="G105" s="12" t="n">
-        <v>0.12</v>
+        <v>0.75</v>
       </c>
       <c r="H105" t="n">
-        <v>24.97</v>
-      </c>
-      <c r="I105" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>69.75</v>
+      </c>
+      <c r="I105" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J105" s="9" t="n">
-        <v>0.257</v>
-      </c>
-      <c r="K105" s="9" t="n"/>
+        <v>0.193</v>
+      </c>
+      <c r="K105" s="9" t="n">
+        <v>0.186</v>
+      </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="14" t="inlineStr"/>
     </row>
@@ -5218,39 +5218,39 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>0291</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>CHB</t>
         </is>
       </c>
       <c r="D106" s="9" t="n">
-        <v>0.825</v>
-      </c>
-      <c r="E106" s="10" t="n">
-        <v>0</v>
+        <v>2.65</v>
+      </c>
+      <c r="E106" s="15" t="n">
+        <v>-0.0603</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>1101200</v>
+        <v>1253700</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>0.29</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H106" t="n">
-        <v>51.87</v>
-      </c>
-      <c r="I106" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>61.35</v>
+      </c>
+      <c r="I106" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J106" s="9" t="n">
-        <v>0.828</v>
+        <v>2.534</v>
       </c>
       <c r="K106" s="9" t="n">
-        <v>0.77</v>
+        <v>2.212</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="14" t="inlineStr"/>
@@ -5263,39 +5263,39 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D107" s="9" t="n">
-        <v>0.535</v>
+        <v>6.68</v>
       </c>
       <c r="E107" s="16" t="n">
-        <v>0.009399999999999999</v>
+        <v>0.0277</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>1091700</v>
+        <v>1253100</v>
       </c>
       <c r="G107" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.23</v>
       </c>
       <c r="H107" t="n">
-        <v>55.88</v>
-      </c>
-      <c r="I107" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.8</v>
+      </c>
+      <c r="I107" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J107" s="9" t="n">
-        <v>0.519</v>
+        <v>6.068</v>
       </c>
       <c r="K107" s="9" t="n">
-        <v>0.45</v>
+        <v>5.859</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="14" t="inlineStr"/>
@@ -5323,10 +5323,10 @@
         <v>-0.0066</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>1079000</v>
+        <v>1249300</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>0.15</v>
+        <v>0.18</v>
       </c>
       <c r="H108" t="n">
         <v>54.72</v>
@@ -5353,28 +5353,28 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>0468</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>UNIPAC</t>
         </is>
       </c>
       <c r="D109" s="9" t="n">
-        <v>0.36</v>
+        <v>0.23</v>
       </c>
       <c r="E109" s="15" t="n">
-        <v>-0.0137</v>
+        <v>-0.0213</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>1063900</v>
+        <v>1246800</v>
       </c>
       <c r="G109" s="12" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="H109" t="n">
-        <v>54.85</v>
+        <v>24.97</v>
       </c>
       <c r="I109" s="13" t="inlineStr">
         <is>
@@ -5382,11 +5382,9 @@
         </is>
       </c>
       <c r="J109" s="9" t="n">
-        <v>0.356</v>
-      </c>
-      <c r="K109" s="9" t="n">
-        <v>0.325</v>
-      </c>
+        <v>0.257</v>
+      </c>
+      <c r="K109" s="9" t="n"/>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="14" t="inlineStr"/>
     </row>
@@ -5398,28 +5396,28 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>5932</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>BPURI</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D110" s="9" t="n">
-        <v>0.215</v>
+        <v>0.795</v>
       </c>
       <c r="E110" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>1055800</v>
+        <v>1232600</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>2.34</v>
+        <v>0.19</v>
       </c>
       <c r="H110" t="n">
-        <v>38.87</v>
+        <v>62.06</v>
       </c>
       <c r="I110" s="13" t="inlineStr">
         <is>
@@ -5427,10 +5425,10 @@
         </is>
       </c>
       <c r="J110" s="9" t="n">
-        <v>0.225</v>
+        <v>0.764</v>
       </c>
       <c r="K110" s="9" t="n">
-        <v>0.233</v>
+        <v>0.676</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="14" t="inlineStr"/>
@@ -5443,39 +5441,39 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D111" s="9" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="E111" s="16" t="n">
-        <v>0.0172</v>
+        <v>0.82</v>
+      </c>
+      <c r="E111" s="15" t="n">
+        <v>-0.0061</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>1036700</v>
+        <v>1204300</v>
       </c>
       <c r="G111" s="12" t="n">
-        <v>0.2</v>
+        <v>0.32</v>
       </c>
       <c r="H111" t="n">
-        <v>63.36</v>
-      </c>
-      <c r="I111" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.94</v>
+      </c>
+      <c r="I111" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J111" s="9" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.827</v>
       </c>
       <c r="K111" s="9" t="n">
-        <v>0.506</v>
+        <v>0.77</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="14" t="inlineStr"/>
@@ -5488,28 +5486,28 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D112" s="9" t="n">
-        <v>0.745</v>
+        <v>0.31</v>
       </c>
       <c r="E112" s="16" t="n">
-        <v>0.0068</v>
+        <v>0.0164</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>1031500</v>
+        <v>1190100</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>0.47</v>
+        <v>0.19</v>
       </c>
       <c r="H112" t="n">
-        <v>55.71</v>
+        <v>43.28</v>
       </c>
       <c r="I112" s="13" t="inlineStr">
         <is>
@@ -5517,10 +5515,10 @@
         </is>
       </c>
       <c r="J112" s="9" t="n">
-        <v>0.724</v>
+        <v>0.322</v>
       </c>
       <c r="K112" s="9" t="n">
-        <v>0.699</v>
+        <v>0.338</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="14" t="inlineStr"/>
@@ -5533,39 +5531,39 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>7943</t>
+          <t>5932</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>GREENTEC</t>
+          <t>BPURI</t>
         </is>
       </c>
       <c r="D113" s="9" t="n">
-        <v>0.29</v>
+        <v>0.21</v>
       </c>
       <c r="E113" s="15" t="n">
-        <v>-0.0333</v>
+        <v>-0.0233</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>1007000</v>
+        <v>1179600</v>
       </c>
       <c r="G113" s="12" t="n">
-        <v>0.92</v>
+        <v>2.62</v>
       </c>
       <c r="H113" t="n">
-        <v>66.97</v>
-      </c>
-      <c r="I113" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.94</v>
+      </c>
+      <c r="I113" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J113" s="9" t="n">
-        <v>0.257</v>
+        <v>0.225</v>
       </c>
       <c r="K113" s="9" t="n">
-        <v>0.211</v>
+        <v>0.233</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="14" t="inlineStr"/>
@@ -5578,39 +5576,39 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>TENAGA</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D114" s="9" t="n">
-        <v>13.02</v>
-      </c>
-      <c r="E114" s="15" t="n">
-        <v>-0.0015</v>
+        <v>0.595</v>
+      </c>
+      <c r="E114" s="16" t="n">
+        <v>0.0259</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>996300</v>
+        <v>1175200</v>
       </c>
       <c r="G114" s="12" t="n">
-        <v>0.11</v>
+        <v>0.23</v>
       </c>
       <c r="H114" t="n">
-        <v>45.65</v>
-      </c>
-      <c r="I114" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>64.37</v>
+      </c>
+      <c r="I114" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J114" s="9" t="n">
-        <v>13.029</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="K114" s="9" t="n">
-        <v>13.493</v>
+        <v>0.506</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="14" t="inlineStr"/>
@@ -5623,28 +5621,28 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>0291</t>
+          <t>5195</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>CHB</t>
+          <t>CENSOF</t>
         </is>
       </c>
       <c r="D115" s="9" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="E115" s="15" t="n">
-        <v>-0.0461</v>
+        <v>0.21</v>
+      </c>
+      <c r="E115" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>996100</v>
+        <v>1146600</v>
       </c>
       <c r="G115" s="12" t="n">
-        <v>0.64</v>
+        <v>0.52</v>
       </c>
       <c r="H115" t="n">
-        <v>64.14</v>
+        <v>46.19</v>
       </c>
       <c r="I115" s="13" t="inlineStr">
         <is>
@@ -5652,10 +5650,10 @@
         </is>
       </c>
       <c r="J115" s="9" t="n">
-        <v>2.538</v>
+        <v>0.218</v>
       </c>
       <c r="K115" s="9" t="n">
-        <v>2.212</v>
+        <v>0.208</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="14" t="inlineStr"/>
@@ -5668,28 +5666,28 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>AWC</t>
         </is>
       </c>
       <c r="D116" s="9" t="n">
-        <v>3.84</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="E116" s="15" t="n">
-        <v>-0.0179</v>
+        <v>-0.0072</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>865600</v>
+        <v>1144200</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v>0.31</v>
+        <v>0.49</v>
       </c>
       <c r="H116" t="n">
-        <v>51.04</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="I116" s="17" t="inlineStr">
         <is>
@@ -5697,10 +5695,10 @@
         </is>
       </c>
       <c r="J116" s="9" t="n">
-        <v>3.873</v>
+        <v>0.636</v>
       </c>
       <c r="K116" s="9" t="n">
-        <v>3.63</v>
+        <v>0.543</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="14" t="inlineStr"/>
@@ -5713,39 +5711,39 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>0146</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>JFTECH</t>
         </is>
       </c>
       <c r="D117" s="9" t="n">
-        <v>6.59</v>
-      </c>
-      <c r="E117" s="16" t="n">
-        <v>0.0138</v>
+        <v>0.74</v>
+      </c>
+      <c r="E117" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>854300</v>
+        <v>1121000</v>
       </c>
       <c r="G117" s="12" t="n">
-        <v>0.16</v>
+        <v>0.51</v>
       </c>
       <c r="H117" t="n">
-        <v>59.75</v>
-      </c>
-      <c r="I117" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>54.93</v>
+      </c>
+      <c r="I117" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J117" s="9" t="n">
-        <v>6.06</v>
+        <v>0.723</v>
       </c>
       <c r="K117" s="9" t="n">
-        <v>5.857</v>
+        <v>0.699</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="14" t="inlineStr"/>
@@ -5758,39 +5756,39 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D118" s="9" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="E118" s="15" t="n">
-        <v>-0.0154</v>
+        <v>0.365</v>
+      </c>
+      <c r="E118" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>847300</v>
+        <v>1117200</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v>0.36</v>
+        <v>0.12</v>
       </c>
       <c r="H118" t="n">
-        <v>57.11</v>
-      </c>
-      <c r="I118" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>57.29</v>
+      </c>
+      <c r="I118" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J118" s="9" t="n">
-        <v>1.242</v>
+        <v>0.357</v>
       </c>
       <c r="K118" s="9" t="n">
-        <v>1.164</v>
+        <v>0.325</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="14" t="inlineStr"/>
@@ -5803,39 +5801,39 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>ATECH</t>
+          <t>DATASONIC</t>
         </is>
       </c>
       <c r="D119" s="9" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E119" s="16" t="n">
-        <v>0.0256</v>
+        <v>0.295</v>
+      </c>
+      <c r="E119" s="15" t="n">
+        <v>-0.0167</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>831100</v>
+        <v>1081900</v>
       </c>
       <c r="G119" s="12" t="n">
-        <v>0.38</v>
+        <v>0.08</v>
       </c>
       <c r="H119" t="n">
-        <v>56.99</v>
-      </c>
-      <c r="I119" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.87</v>
+      </c>
+      <c r="I119" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J119" s="9" t="n">
-        <v>0.777</v>
+        <v>0.292</v>
       </c>
       <c r="K119" s="9" t="n">
-        <v>0.765</v>
+        <v>0.282</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="14" t="inlineStr"/>
@@ -5848,28 +5846,28 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>MALAKOF</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D120" s="9" t="n">
-        <v>0.765</v>
-      </c>
-      <c r="E120" s="15" t="n">
-        <v>-0.0129</v>
+        <v>0.27</v>
+      </c>
+      <c r="E120" s="16" t="n">
+        <v>0.0189</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>828100</v>
+        <v>1033400</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>0.19</v>
+        <v>0.13</v>
       </c>
       <c r="H120" t="n">
-        <v>42.45</v>
+        <v>34.49</v>
       </c>
       <c r="I120" s="13" t="inlineStr">
         <is>
@@ -5877,10 +5875,10 @@
         </is>
       </c>
       <c r="J120" s="9" t="n">
-        <v>0.787</v>
+        <v>0.284</v>
       </c>
       <c r="K120" s="9" t="n">
-        <v>0.804</v>
+        <v>0.305</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="14" t="inlineStr"/>
@@ -5893,39 +5891,39 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>0373</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>VERDANT</t>
         </is>
       </c>
       <c r="D121" s="9" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="E121" s="10" t="n">
-        <v>0</v>
+        <v>0.235</v>
+      </c>
+      <c r="E121" s="15" t="n">
+        <v>-0.0408</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>779300</v>
+        <v>1031000</v>
       </c>
       <c r="G121" s="12" t="n">
-        <v>0.19</v>
+        <v>0.21</v>
       </c>
       <c r="H121" t="n">
-        <v>58.39</v>
-      </c>
-      <c r="I121" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.82</v>
+      </c>
+      <c r="I121" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J121" s="9" t="n">
-        <v>1.044</v>
+        <v>0.249</v>
       </c>
       <c r="K121" s="9" t="n">
-        <v>0.887</v>
+        <v>0.222</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="14" t="inlineStr"/>
@@ -5938,39 +5936,39 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>7943</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>GREENTEC</t>
         </is>
       </c>
       <c r="D122" s="9" t="n">
-        <v>1.69</v>
+        <v>0.29</v>
       </c>
       <c r="E122" s="15" t="n">
-        <v>-0.0059</v>
+        <v>-0.0333</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>763400</v>
+        <v>1007000</v>
       </c>
       <c r="G122" s="12" t="n">
-        <v>0.16</v>
+        <v>0.92</v>
       </c>
       <c r="H122" t="n">
-        <v>40.93</v>
-      </c>
-      <c r="I122" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.97</v>
+      </c>
+      <c r="I122" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J122" s="9" t="n">
-        <v>1.745</v>
+        <v>0.257</v>
       </c>
       <c r="K122" s="9" t="n">
-        <v>1.774</v>
+        <v>0.211</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="14" t="inlineStr"/>
@@ -5983,28 +5981,28 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>MALAKOF</t>
         </is>
       </c>
       <c r="D123" s="9" t="n">
-        <v>0.885</v>
+        <v>0.765</v>
       </c>
       <c r="E123" s="15" t="n">
-        <v>-0.005600000000000001</v>
+        <v>-0.0129</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>762800</v>
+        <v>990900</v>
       </c>
       <c r="G123" s="12" t="n">
-        <v>0.31</v>
+        <v>0.23</v>
       </c>
       <c r="H123" t="n">
-        <v>22.89</v>
+        <v>42.45</v>
       </c>
       <c r="I123" s="13" t="inlineStr">
         <is>
@@ -6012,10 +6010,10 @@
         </is>
       </c>
       <c r="J123" s="9" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.787</v>
       </c>
       <c r="K123" s="9" t="n">
-        <v>0.983</v>
+        <v>0.804</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" s="14" t="inlineStr"/>
@@ -6028,39 +6026,39 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>0245</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>MNHLDG</t>
         </is>
       </c>
       <c r="D124" s="9" t="n">
-        <v>0.705</v>
-      </c>
-      <c r="E124" s="16" t="n">
-        <v>0.0217</v>
+        <v>3.87</v>
+      </c>
+      <c r="E124" s="15" t="n">
+        <v>-0.0102</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>735000</v>
+        <v>976800</v>
       </c>
       <c r="G124" s="12" t="n">
-        <v>0.23</v>
+        <v>0.34</v>
       </c>
       <c r="H124" t="n">
-        <v>41.23</v>
-      </c>
-      <c r="I124" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.8</v>
+      </c>
+      <c r="I124" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J124" s="9" t="n">
-        <v>0.746</v>
+        <v>3.875</v>
       </c>
       <c r="K124" s="9" t="n">
-        <v>0.747</v>
+        <v>3.63</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="14" t="inlineStr"/>
@@ -6073,28 +6071,28 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>UWC</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D125" s="9" t="n">
-        <v>7.65</v>
+        <v>0.89</v>
       </c>
       <c r="E125" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>727400</v>
+        <v>941600</v>
       </c>
       <c r="G125" s="12" t="n">
-        <v>0.18</v>
+        <v>0.38</v>
       </c>
       <c r="H125" t="n">
-        <v>61.58</v>
+        <v>23.79</v>
       </c>
       <c r="I125" s="13" t="inlineStr">
         <is>
@@ -6102,10 +6100,10 @@
         </is>
       </c>
       <c r="J125" s="9" t="n">
-        <v>7.374</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="K125" s="9" t="n">
-        <v>6.846</v>
+        <v>0.983</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="14" t="inlineStr"/>
@@ -6118,39 +6116,39 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>5302</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>ATECH</t>
         </is>
       </c>
       <c r="D126" s="9" t="n">
-        <v>2.72</v>
+        <v>0.8</v>
       </c>
       <c r="E126" s="16" t="n">
-        <v>0.0074</v>
+        <v>0.0256</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>709400</v>
+        <v>938500</v>
       </c>
       <c r="G126" s="12" t="n">
-        <v>0.14</v>
+        <v>0.43</v>
       </c>
       <c r="H126" t="n">
-        <v>40.24</v>
-      </c>
-      <c r="I126" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.99</v>
+      </c>
+      <c r="I126" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J126" s="9" t="n">
-        <v>2.908</v>
+        <v>0.777</v>
       </c>
       <c r="K126" s="9" t="n">
-        <v>2.86</v>
+        <v>0.765</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="14" t="inlineStr"/>
@@ -6163,28 +6161,28 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>UWC</t>
         </is>
       </c>
       <c r="D127" s="9" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="E127" s="16" t="n">
-        <v>0.0072</v>
+        <v>7.65</v>
+      </c>
+      <c r="E127" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>706000</v>
+        <v>936600</v>
       </c>
       <c r="G127" s="12" t="n">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="H127" t="n">
-        <v>35.93</v>
+        <v>61.58</v>
       </c>
       <c r="I127" s="13" t="inlineStr">
         <is>
@@ -6192,10 +6190,10 @@
         </is>
       </c>
       <c r="J127" s="9" t="n">
-        <v>2.933</v>
+        <v>7.374</v>
       </c>
       <c r="K127" s="9" t="n">
-        <v>3.026</v>
+        <v>6.846</v>
       </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" s="14" t="inlineStr"/>
@@ -6208,39 +6206,39 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>0277</t>
+          <t>0240</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>CLOUDPT</t>
+          <t>CORAZA</t>
         </is>
       </c>
       <c r="D128" s="9" t="n">
-        <v>0.505</v>
+        <v>1.31</v>
       </c>
       <c r="E128" s="16" t="n">
-        <v>0.01</v>
+        <v>0.0077</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>689300</v>
+        <v>931300</v>
       </c>
       <c r="G128" s="12" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="H128" t="n">
-        <v>55.44</v>
-      </c>
-      <c r="I128" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.5</v>
+      </c>
+      <c r="I128" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J128" s="9" t="n">
-        <v>0.495</v>
+        <v>1.245</v>
       </c>
       <c r="K128" s="9" t="n">
-        <v>0.483</v>
+        <v>1.164</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="14" t="inlineStr"/>
@@ -6268,10 +6266,10 @@
         <v>0</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>629000</v>
+        <v>900600</v>
       </c>
       <c r="G129" s="12" t="n">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="H129" t="n">
         <v>33.44</v>
@@ -6298,28 +6296,28 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>SEG</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D130" s="9" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E130" s="15" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.7</v>
+      </c>
+      <c r="E130" s="16" t="n">
+        <v>0.0145</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>620000</v>
+        <v>870700</v>
       </c>
       <c r="G130" s="12" t="n">
-        <v>0.52</v>
+        <v>0.27</v>
       </c>
       <c r="H130" t="n">
-        <v>36.25</v>
+        <v>40.09</v>
       </c>
       <c r="I130" s="13" t="inlineStr">
         <is>
@@ -6327,10 +6325,10 @@
         </is>
       </c>
       <c r="J130" s="9" t="n">
-        <v>0.631</v>
+        <v>0.746</v>
       </c>
       <c r="K130" s="9" t="n">
-        <v>0.63</v>
+        <v>0.747</v>
       </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" s="14" t="inlineStr"/>
@@ -6343,39 +6341,39 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>0045</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>DUFU</t>
+          <t>SSB8</t>
         </is>
       </c>
       <c r="D131" s="9" t="n">
-        <v>3.13</v>
+        <v>0.65</v>
       </c>
       <c r="E131" s="16" t="n">
-        <v>0.0162</v>
+        <v>0.0156</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>610300</v>
+        <v>827400</v>
       </c>
       <c r="G131" s="12" t="n">
-        <v>0.19</v>
+        <v>0.22</v>
       </c>
       <c r="H131" t="n">
-        <v>57.42</v>
-      </c>
-      <c r="I131" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.56</v>
+      </c>
+      <c r="I131" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J131" s="9" t="n">
-        <v>3.034</v>
+        <v>0.64</v>
       </c>
       <c r="K131" s="9" t="n">
-        <v>2.839</v>
+        <v>0.609</v>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" s="14" t="inlineStr"/>
@@ -6388,28 +6386,28 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>5223</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>MENTIGA</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D132" s="9" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E132" s="16" t="n">
-        <v>0.3793</v>
+        <v>1.08</v>
+      </c>
+      <c r="E132" s="15" t="n">
+        <v>-0.0092</v>
       </c>
       <c r="F132" s="11" t="n">
-        <v>608500</v>
+        <v>813600</v>
       </c>
       <c r="G132" s="12" t="n">
-        <v>27.53</v>
+        <v>0.2</v>
       </c>
       <c r="H132" t="n">
-        <v>74.09</v>
+        <v>57.29</v>
       </c>
       <c r="I132" s="17" t="inlineStr">
         <is>
@@ -6417,10 +6415,10 @@
         </is>
       </c>
       <c r="J132" s="9" t="n">
-        <v>0.61</v>
+        <v>1.043</v>
       </c>
       <c r="K132" s="9" t="n">
-        <v>0.642</v>
+        <v>0.887</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="14" t="inlineStr"/>
@@ -6433,39 +6431,39 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>0271</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>WELLS</t>
+          <t>MBSB</t>
         </is>
       </c>
       <c r="D133" s="9" t="n">
-        <v>0.535</v>
+        <v>0.54</v>
       </c>
       <c r="E133" s="15" t="n">
-        <v>-0.0183</v>
+        <v>-0.0182</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>607700</v>
+        <v>786000</v>
       </c>
       <c r="G133" s="12" t="n">
-        <v>0.55</v>
+        <v>0.23</v>
       </c>
       <c r="H133" t="n">
-        <v>33.07</v>
-      </c>
-      <c r="I133" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.5</v>
+      </c>
+      <c r="I133" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J133" s="9" t="n">
-        <v>0.573</v>
+        <v>0.549</v>
       </c>
       <c r="K133" s="9" t="n">
-        <v>0.616</v>
+        <v>0.577</v>
       </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" s="14" t="inlineStr"/>
@@ -6487,19 +6485,19 @@
         </is>
       </c>
       <c r="D134" s="9" t="n">
-        <v>10.58</v>
+        <v>10.68</v>
       </c>
       <c r="E134" s="15" t="n">
-        <v>-0.0149</v>
+        <v>-0.005600000000000001</v>
       </c>
       <c r="F134" s="11" t="n">
-        <v>601200</v>
+        <v>772400</v>
       </c>
       <c r="G134" s="12" t="n">
-        <v>0.17</v>
+        <v>0.21</v>
       </c>
       <c r="H134" t="n">
-        <v>58.01</v>
+        <v>60.31</v>
       </c>
       <c r="I134" s="13" t="inlineStr">
         <is>
@@ -6507,10 +6505,10 @@
         </is>
       </c>
       <c r="J134" s="9" t="n">
-        <v>10.389</v>
+        <v>10.399</v>
       </c>
       <c r="K134" s="9" t="n">
-        <v>9.659000000000001</v>
+        <v>9.661</v>
       </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" s="14" t="inlineStr"/>
@@ -6523,39 +6521,39 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>SKYECHIP</t>
         </is>
       </c>
       <c r="D135" s="9" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="E135" s="10" t="n">
-        <v>0</v>
+        <v>2.78</v>
+      </c>
+      <c r="E135" s="16" t="n">
+        <v>0.0072</v>
       </c>
       <c r="F135" s="11" t="n">
-        <v>596500</v>
+        <v>772000</v>
       </c>
       <c r="G135" s="12" t="n">
-        <v>0.16</v>
+        <v>0.24</v>
       </c>
       <c r="H135" t="n">
-        <v>61.55</v>
-      </c>
-      <c r="I135" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.93</v>
+      </c>
+      <c r="I135" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J135" s="9" t="n">
-        <v>0.489</v>
+        <v>2.933</v>
       </c>
       <c r="K135" s="9" t="n">
-        <v>0.459</v>
+        <v>3.026</v>
       </c>
       <c r="L135" t="inlineStr"/>
       <c r="M135" s="14" t="inlineStr"/>
@@ -6568,39 +6566,39 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D136" s="9" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="E136" s="15" t="n">
-        <v>-0.006999999999999999</v>
+        <v>1.7</v>
+      </c>
+      <c r="E136" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F136" s="11" t="n">
-        <v>595100</v>
+        <v>766700</v>
       </c>
       <c r="G136" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="H136" t="n">
-        <v>56.6</v>
-      </c>
-      <c r="I136" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.09</v>
+      </c>
+      <c r="I136" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J136" s="9" t="n">
-        <v>2.799</v>
+        <v>1.746</v>
       </c>
       <c r="K136" s="9" t="n">
-        <v>2.636</v>
+        <v>1.774</v>
       </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" s="14" t="inlineStr"/>
@@ -6613,39 +6611,39 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>0045</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>SSB8</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D137" s="9" t="n">
-        <v>0.65</v>
+        <v>2.73</v>
       </c>
       <c r="E137" s="16" t="n">
-        <v>0.0156</v>
+        <v>0.0111</v>
       </c>
       <c r="F137" s="11" t="n">
-        <v>584800</v>
+        <v>761700</v>
       </c>
       <c r="G137" s="12" t="n">
         <v>0.15</v>
       </c>
       <c r="H137" t="n">
-        <v>55.56</v>
-      </c>
-      <c r="I137" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.83</v>
+      </c>
+      <c r="I137" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J137" s="9" t="n">
-        <v>0.64</v>
+        <v>2.909</v>
       </c>
       <c r="K137" s="9" t="n">
-        <v>0.609</v>
+        <v>2.86</v>
       </c>
       <c r="L137" t="inlineStr"/>
       <c r="M137" s="14" t="inlineStr"/>
@@ -6658,28 +6656,28 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>9059</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>TSH</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D138" s="9" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="E138" s="10" t="n">
-        <v>0</v>
+        <v>2.85</v>
+      </c>
+      <c r="E138" s="15" t="n">
+        <v>-0.006999999999999999</v>
       </c>
       <c r="F138" s="11" t="n">
-        <v>557600</v>
+        <v>760300</v>
       </c>
       <c r="G138" s="12" t="n">
-        <v>0.25</v>
+        <v>0.08</v>
       </c>
       <c r="H138" t="n">
-        <v>30.53</v>
+        <v>56.6</v>
       </c>
       <c r="I138" s="13" t="inlineStr">
         <is>
@@ -6687,10 +6685,10 @@
         </is>
       </c>
       <c r="J138" s="9" t="n">
-        <v>1.261</v>
+        <v>2.799</v>
       </c>
       <c r="K138" s="9" t="n">
-        <v>1.309</v>
+        <v>2.636</v>
       </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" s="14" t="inlineStr"/>
@@ -6703,39 +6701,39 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>IHH</t>
         </is>
       </c>
       <c r="D139" s="9" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E139" s="15" t="n">
-        <v>-0.0234</v>
+        <v>8.109999999999999</v>
+      </c>
+      <c r="E139" s="16" t="n">
+        <v>0.0163</v>
       </c>
       <c r="F139" s="11" t="n">
-        <v>557500</v>
+        <v>730600</v>
       </c>
       <c r="G139" s="12" t="n">
-        <v>0.21</v>
+        <v>0.19</v>
       </c>
       <c r="H139" t="n">
-        <v>46.09</v>
-      </c>
-      <c r="I139" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.97</v>
+      </c>
+      <c r="I139" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J139" s="9" t="n">
-        <v>0.637</v>
+        <v>7.903</v>
       </c>
       <c r="K139" s="9" t="n">
-        <v>0.617</v>
+        <v>7.99</v>
       </c>
       <c r="L139" t="inlineStr"/>
       <c r="M139" s="14" t="inlineStr"/>
@@ -6748,28 +6746,28 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>7160</t>
+          <t>5223</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>PENTA</t>
+          <t>MENTIGA</t>
         </is>
       </c>
       <c r="D140" s="9" t="n">
-        <v>5.47</v>
-      </c>
-      <c r="E140" s="15" t="n">
-        <v>-0.0073</v>
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="E140" s="16" t="n">
+        <v>0.3966</v>
       </c>
       <c r="F140" s="11" t="n">
-        <v>554800</v>
+        <v>727500</v>
       </c>
       <c r="G140" s="12" t="n">
-        <v>0.15</v>
+        <v>32.92</v>
       </c>
       <c r="H140" t="n">
-        <v>50.32</v>
+        <v>74.69</v>
       </c>
       <c r="I140" s="17" t="inlineStr">
         <is>
@@ -6777,10 +6775,10 @@
         </is>
       </c>
       <c r="J140" s="9" t="n">
-        <v>5.506</v>
+        <v>0.611</v>
       </c>
       <c r="K140" s="9" t="n">
-        <v>5.386</v>
+        <v>0.642</v>
       </c>
       <c r="L140" t="inlineStr"/>
       <c r="M140" s="14" t="inlineStr"/>
@@ -6793,28 +6791,28 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>5246</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>WPRTS</t>
         </is>
       </c>
       <c r="D141" s="9" t="n">
-        <v>0.895</v>
-      </c>
-      <c r="E141" s="15" t="n">
-        <v>-0.011</v>
+        <v>6.76</v>
+      </c>
+      <c r="E141" s="16" t="n">
+        <v>0.004500000000000001</v>
       </c>
       <c r="F141" s="11" t="n">
-        <v>549700</v>
+        <v>687000</v>
       </c>
       <c r="G141" s="12" t="n">
-        <v>0.18</v>
+        <v>0.15</v>
       </c>
       <c r="H141" t="n">
-        <v>41.46</v>
+        <v>49.84</v>
       </c>
       <c r="I141" s="13" t="inlineStr">
         <is>
@@ -6822,10 +6820,10 @@
         </is>
       </c>
       <c r="J141" s="9" t="n">
-        <v>0.909</v>
+        <v>6.761</v>
       </c>
       <c r="K141" s="9" t="n">
-        <v>0.96</v>
+        <v>6.839</v>
       </c>
       <c r="L141" t="inlineStr"/>
       <c r="M141" s="14" t="inlineStr"/>
@@ -6838,28 +6836,28 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>9792</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>SEG</t>
         </is>
       </c>
       <c r="D142" s="9" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="E142" s="10" t="n">
-        <v>0</v>
+        <v>0.625</v>
+      </c>
+      <c r="E142" s="15" t="n">
+        <v>-0.007900000000000001</v>
       </c>
       <c r="F142" s="11" t="n">
-        <v>545900</v>
+        <v>680000</v>
       </c>
       <c r="G142" s="12" t="n">
-        <v>0.14</v>
+        <v>0.57</v>
       </c>
       <c r="H142" t="n">
-        <v>31.13</v>
+        <v>36.25</v>
       </c>
       <c r="I142" s="13" t="inlineStr">
         <is>
@@ -6867,10 +6865,10 @@
         </is>
       </c>
       <c r="J142" s="9" t="n">
-        <v>0.984</v>
+        <v>0.631</v>
       </c>
       <c r="K142" s="9" t="n">
-        <v>1.062</v>
+        <v>0.63</v>
       </c>
       <c r="L142" t="inlineStr"/>
       <c r="M142" s="14" t="inlineStr"/>
@@ -6883,28 +6881,28 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>MBSB</t>
+          <t>DUFU</t>
         </is>
       </c>
       <c r="D143" s="9" t="n">
-        <v>0.545</v>
-      </c>
-      <c r="E143" s="15" t="n">
-        <v>-0.0091</v>
+        <v>3.14</v>
+      </c>
+      <c r="E143" s="16" t="n">
+        <v>0.0195</v>
       </c>
       <c r="F143" s="11" t="n">
-        <v>523800</v>
+        <v>665800</v>
       </c>
       <c r="G143" s="12" t="n">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
       <c r="H143" t="n">
-        <v>43.84</v>
+        <v>57.8</v>
       </c>
       <c r="I143" s="13" t="inlineStr">
         <is>
@@ -6912,10 +6910,10 @@
         </is>
       </c>
       <c r="J143" s="9" t="n">
-        <v>0.55</v>
+        <v>3.035</v>
       </c>
       <c r="K143" s="9" t="n">
-        <v>0.577</v>
+        <v>2.84</v>
       </c>
       <c r="L143" t="inlineStr"/>
       <c r="M143" s="14" t="inlineStr"/>
@@ -6928,28 +6926,28 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>5258</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>BIMB</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="D144" s="9" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="E144" s="10" t="n">
-        <v>0</v>
+        <v>5.97</v>
+      </c>
+      <c r="E144" s="16" t="n">
+        <v>0.008399999999999999</v>
       </c>
       <c r="F144" s="11" t="n">
-        <v>518400</v>
+        <v>660000</v>
       </c>
       <c r="G144" s="12" t="n">
-        <v>0.66</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H144" t="n">
-        <v>37.42</v>
+        <v>37.65</v>
       </c>
       <c r="I144" s="13" t="inlineStr">
         <is>
@@ -6957,10 +6955,10 @@
         </is>
       </c>
       <c r="J144" s="9" t="n">
-        <v>2.05</v>
+        <v>6.107</v>
       </c>
       <c r="K144" s="9" t="n">
-        <v>2.09</v>
+        <v>6.363</v>
       </c>
       <c r="L144" t="inlineStr"/>
       <c r="M144" s="14" t="inlineStr"/>
@@ -6973,28 +6971,28 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>5916</t>
+          <t>7160</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>MSC</t>
+          <t>PENTA</t>
         </is>
       </c>
       <c r="D145" s="9" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="E145" s="16" t="n">
-        <v>0.0184</v>
+        <v>5.49</v>
+      </c>
+      <c r="E145" s="15" t="n">
+        <v>-0.0036</v>
       </c>
       <c r="F145" s="11" t="n">
-        <v>500000</v>
+        <v>655300</v>
       </c>
       <c r="G145" s="12" t="n">
-        <v>0.47</v>
+        <v>0.18</v>
       </c>
       <c r="H145" t="n">
-        <v>46.45</v>
+        <v>50.84</v>
       </c>
       <c r="I145" s="17" t="inlineStr">
         <is>
@@ -7002,16 +7000,691 @@
         </is>
       </c>
       <c r="J145" s="9" t="n">
-        <v>1.671</v>
+        <v>5.508</v>
       </c>
       <c r="K145" s="9" t="n">
-        <v>1.798</v>
+        <v>5.387</v>
       </c>
       <c r="L145" t="inlineStr"/>
       <c r="M145" s="14" t="inlineStr"/>
     </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>4383</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>JTIASA</t>
+        </is>
+      </c>
+      <c r="D146" s="9" t="n">
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="E146" s="16" t="n">
+        <v>0.0108</v>
+      </c>
+      <c r="F146" s="11" t="n">
+        <v>655200</v>
+      </c>
+      <c r="G146" s="12" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H146" t="n">
+        <v>38.21</v>
+      </c>
+      <c r="I146" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J146" s="9" t="n">
+        <v>0.956</v>
+      </c>
+      <c r="K146" s="9" t="n">
+        <v>1.012</v>
+      </c>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" s="14" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>0271</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>WELLS</t>
+        </is>
+      </c>
+      <c r="D147" s="9" t="n">
+        <v>0.535</v>
+      </c>
+      <c r="E147" s="15" t="n">
+        <v>-0.0183</v>
+      </c>
+      <c r="F147" s="11" t="n">
+        <v>607700</v>
+      </c>
+      <c r="G147" s="12" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="H147" t="n">
+        <v>33.07</v>
+      </c>
+      <c r="I147" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J147" s="9" t="n">
+        <v>0.573</v>
+      </c>
+      <c r="K147" s="9" t="n">
+        <v>0.616</v>
+      </c>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" s="14" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>0368</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>OXB</t>
+        </is>
+      </c>
+      <c r="D148" s="9" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="E148" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F148" s="11" t="n">
+        <v>596500</v>
+      </c>
+      <c r="G148" s="12" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H148" t="n">
+        <v>61.55</v>
+      </c>
+      <c r="I148" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J148" s="9" t="n">
+        <v>0.489</v>
+      </c>
+      <c r="K148" s="9" t="n">
+        <v>0.459</v>
+      </c>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" s="14" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>0338</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>KOPI</t>
+        </is>
+      </c>
+      <c r="D149" s="9" t="n">
+        <v>0.895</v>
+      </c>
+      <c r="E149" s="15" t="n">
+        <v>-0.011</v>
+      </c>
+      <c r="F149" s="11" t="n">
+        <v>592700</v>
+      </c>
+      <c r="G149" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H149" t="n">
+        <v>41.46</v>
+      </c>
+      <c r="I149" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J149" s="9" t="n">
+        <v>0.909</v>
+      </c>
+      <c r="K149" s="9" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" s="14" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>0151</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>KGB</t>
+        </is>
+      </c>
+      <c r="D150" s="9" t="n">
+        <v>8.49</v>
+      </c>
+      <c r="E150" s="15" t="n">
+        <v>-0.0012</v>
+      </c>
+      <c r="F150" s="11" t="n">
+        <v>578200</v>
+      </c>
+      <c r="G150" s="12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H150" t="n">
+        <v>44.82</v>
+      </c>
+      <c r="I150" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J150" s="9" t="n">
+        <v>8.691000000000001</v>
+      </c>
+      <c r="K150" s="9" t="n">
+        <v>8.698</v>
+      </c>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" s="14" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>5317</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>CPETECH</t>
+        </is>
+      </c>
+      <c r="D151" s="9" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="E151" s="15" t="n">
+        <v>-0.0159</v>
+      </c>
+      <c r="F151" s="11" t="n">
+        <v>569200</v>
+      </c>
+      <c r="G151" s="12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H151" t="n">
+        <v>46.99</v>
+      </c>
+      <c r="I151" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J151" s="9" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="K151" s="9" t="n">
+        <v>1.213</v>
+      </c>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" s="14" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>9059</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>TSH</t>
+        </is>
+      </c>
+      <c r="D152" s="9" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="E152" s="16" t="n">
+        <v>0.008500000000000001</v>
+      </c>
+      <c r="F152" s="11" t="n">
+        <v>568100</v>
+      </c>
+      <c r="G152" s="12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H152" t="n">
+        <v>33</v>
+      </c>
+      <c r="I152" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J152" s="9" t="n">
+        <v>1.262</v>
+      </c>
+      <c r="K152" s="9" t="n">
+        <v>1.309</v>
+      </c>
+      <c r="L152" t="inlineStr"/>
+      <c r="M152" s="14" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>0112</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>MIKROMB</t>
+        </is>
+      </c>
+      <c r="D153" s="9" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="E153" s="15" t="n">
+        <v>-0.0234</v>
+      </c>
+      <c r="F153" s="11" t="n">
+        <v>557500</v>
+      </c>
+      <c r="G153" s="12" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H153" t="n">
+        <v>46.09</v>
+      </c>
+      <c r="I153" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J153" s="9" t="n">
+        <v>0.637</v>
+      </c>
+      <c r="K153" s="9" t="n">
+        <v>0.617</v>
+      </c>
+      <c r="L153" t="inlineStr"/>
+      <c r="M153" s="14" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>5258</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>BIMB</t>
+        </is>
+      </c>
+      <c r="D154" s="9" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="E154" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F154" s="11" t="n">
+        <v>556700</v>
+      </c>
+      <c r="G154" s="12" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="H154" t="n">
+        <v>37.42</v>
+      </c>
+      <c r="I154" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J154" s="9" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="K154" s="9" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="L154" t="inlineStr"/>
+      <c r="M154" s="14" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>5916</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>MSC</t>
+        </is>
+      </c>
+      <c r="D155" s="9" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="E155" s="16" t="n">
+        <v>0.0123</v>
+      </c>
+      <c r="F155" s="11" t="n">
+        <v>551400</v>
+      </c>
+      <c r="G155" s="12" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="H155" t="n">
+        <v>45.36</v>
+      </c>
+      <c r="I155" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J155" s="9" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="K155" s="9" t="n">
+        <v>1.798</v>
+      </c>
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" s="14" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>0128</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>FRONTKN</t>
+        </is>
+      </c>
+      <c r="D156" s="9" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="E156" s="16" t="n">
+        <v>0.0098</v>
+      </c>
+      <c r="F156" s="11" t="n">
+        <v>551300</v>
+      </c>
+      <c r="G156" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H156" t="n">
+        <v>55.93</v>
+      </c>
+      <c r="I156" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J156" s="9" t="n">
+        <v>5.068</v>
+      </c>
+      <c r="K156" s="9" t="n">
+        <v>5.062</v>
+      </c>
+      <c r="L156" t="inlineStr"/>
+      <c r="M156" s="14" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>8583</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>MAHSING</t>
+        </is>
+      </c>
+      <c r="D157" s="9" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="E157" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F157" s="11" t="n">
+        <v>549900</v>
+      </c>
+      <c r="G157" s="12" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H157" t="n">
+        <v>31.13</v>
+      </c>
+      <c r="I157" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J157" s="9" t="n">
+        <v>0.984</v>
+      </c>
+      <c r="K157" s="9" t="n">
+        <v>1.062</v>
+      </c>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" s="14" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>7293</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>YINSON</t>
+        </is>
+      </c>
+      <c r="D158" s="9" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="E158" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F158" s="11" t="n">
+        <v>545900</v>
+      </c>
+      <c r="G158" s="12" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H158" t="n">
+        <v>57.62</v>
+      </c>
+      <c r="I158" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J158" s="9" t="n">
+        <v>2.103</v>
+      </c>
+      <c r="K158" s="9" t="n">
+        <v>2.051</v>
+      </c>
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" s="14" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>5141</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>DAYANG</t>
+        </is>
+      </c>
+      <c r="D159" s="9" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="E159" s="16" t="n">
+        <v>0.0074</v>
+      </c>
+      <c r="F159" s="11" t="n">
+        <v>524600</v>
+      </c>
+      <c r="G159" s="12" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H159" t="n">
+        <v>33.89</v>
+      </c>
+      <c r="I159" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J159" s="9" t="n">
+        <v>1.431</v>
+      </c>
+      <c r="K159" s="9" t="n">
+        <v>1.481</v>
+      </c>
+      <c r="L159" t="inlineStr"/>
+      <c r="M159" s="14" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>0391</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>AMBEST</t>
+        </is>
+      </c>
+      <c r="D160" s="9" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="E160" s="16" t="n">
+        <v>0.0308</v>
+      </c>
+      <c r="F160" s="11" t="n">
+        <v>514200</v>
+      </c>
+      <c r="G160" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H160" t="n">
+        <v>51.86</v>
+      </c>
+      <c r="I160" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J160" s="9" t="n">
+        <v>1.341</v>
+      </c>
+      <c r="K160" s="9" t="n">
+        <v>1.265</v>
+      </c>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M145"/>
+  <autoFilter ref="A1:M160"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-14/bursa-report-2026-10-14.xlsx
+++ b/docs/downloads/2026-10-14/bursa-report-2026-10-14.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-14" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-14'!$A$1:$M$160</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-14'!$A$1:$M$183</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -38,10 +38,10 @@
       <color rgb="000CA30C"/>
     </font>
     <font>
-      <color rgb="00898781"/>
+      <color rgb="00D03B3B"/>
     </font>
     <font>
-      <color rgb="00D03B3B"/>
+      <color rgb="00898781"/>
     </font>
   </fonts>
   <fills count="4">
@@ -92,7 +92,7 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M160"/>
+  <dimension ref="A1:M183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -566,19 +566,19 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.036</v>
+        <v>0.027</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>3545800</v>
+        <v>3793900</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>0.88</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>59.41</v>
+        <v>58.07</v>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>2.199</v>
+        <v>2.197</v>
       </c>
       <c r="K2" s="3" t="n">
         <v>2.145</v>
@@ -598,7 +598,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>SAR转多，现价2.3高于50日均线2.145，RSI 59.41未超买，信号偏可靠。</t>
+          <t>现价RM 2.28高于50日均线RM 2.145，RSI 58.07处中性偏上区间，未超买，SAR转多信号技术面尚属合理。</t>
         </is>
       </c>
     </row>
@@ -610,31 +610,40 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0477</t>
+          <t>0138</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>EcoSys (Malaysia) Berhad</t>
+          <t>ZETRIX</t>
         </is>
       </c>
       <c r="D3" s="9" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.055</v>
       </c>
       <c r="E3" s="10" t="n">
-        <v>0</v>
+        <v>-0.1538</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>143529300</v>
-      </c>
-      <c r="G3" s="12" t="n"/>
+        <v>156858900</v>
+      </c>
+      <c r="G3" s="12" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="H3" t="n">
+        <v>20.87</v>
+      </c>
       <c r="I3" s="13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J3" s="9" t="n"/>
-      <c r="K3" s="9" t="n"/>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J3" s="9" t="n">
+        <v>0.146</v>
+      </c>
+      <c r="K3" s="9" t="n">
+        <v>0.36</v>
+      </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" s="14" t="inlineStr"/>
     </row>
@@ -646,40 +655,31 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0138</t>
+          <t>0477</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ZETRIX</t>
+          <t>EcoSys (Malaysia) Berhad</t>
         </is>
       </c>
       <c r="D4" s="9" t="n">
-        <v>0.06</v>
+        <v>0.845</v>
       </c>
       <c r="E4" s="15" t="n">
-        <v>-0.07690000000000001</v>
+        <v>0</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>132888800</v>
-      </c>
-      <c r="G4" s="12" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="H4" t="n">
-        <v>21.31</v>
-      </c>
+        <v>149255300</v>
+      </c>
+      <c r="G4" s="12" t="n"/>
       <c r="I4" s="13" t="inlineStr">
         <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J4" s="9" t="n">
-        <v>0.147</v>
-      </c>
-      <c r="K4" s="9" t="n">
-        <v>0.36</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J4" s="9" t="n"/>
+      <c r="K4" s="9" t="n"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" s="14" t="inlineStr"/>
     </row>
@@ -702,14 +702,14 @@
       <c r="D5" s="9" t="n">
         <v>0.145</v>
       </c>
-      <c r="E5" s="15" t="n">
+      <c r="E5" s="10" t="n">
         <v>-0.0333</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>58919600</v>
+        <v>59737600</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="H5" t="n">
         <v>43.8</v>
@@ -745,19 +745,19 @@
         </is>
       </c>
       <c r="D6" s="9" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="E6" s="16" t="n">
-        <v>0.0175</v>
+        <v>0.0292</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>38368000</v>
+        <v>43844600</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>0.59</v>
+        <v>0.67</v>
       </c>
       <c r="H6" t="n">
-        <v>64.34</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="I6" s="17" t="inlineStr">
         <is>
@@ -765,7 +765,7 @@
         </is>
       </c>
       <c r="J6" s="9" t="n">
-        <v>0.799</v>
+        <v>0.8</v>
       </c>
       <c r="K6" s="9" t="n">
         <v>0.721</v>
@@ -790,19 +790,19 @@
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.41</v>
+        <v>0.405</v>
       </c>
       <c r="E7" s="16" t="n">
-        <v>0.0513</v>
+        <v>0.0385</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>36731000</v>
+        <v>39881900</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>0.99</v>
+        <v>1.07</v>
       </c>
       <c r="H7" t="n">
-        <v>74.70999999999999</v>
+        <v>73.73999999999999</v>
       </c>
       <c r="I7" s="17" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="J7" s="9" t="n">
-        <v>0.368</v>
+        <v>0.367</v>
       </c>
       <c r="K7" s="9" t="n">
         <v>0.256</v>
@@ -837,14 +837,14 @@
       <c r="D8" s="9" t="n">
         <v>0.34</v>
       </c>
-      <c r="E8" s="10" t="n">
+      <c r="E8" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>29482000</v>
+        <v>30313500</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="H8" t="n">
         <v>71.22</v>
@@ -882,14 +882,14 @@
       <c r="D9" s="9" t="n">
         <v>0.155</v>
       </c>
-      <c r="E9" s="10" t="n">
+      <c r="E9" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>17460000</v>
+        <v>21685000</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>0.52</v>
+        <v>0.64</v>
       </c>
       <c r="H9" t="n">
         <v>48.61</v>
@@ -916,39 +916,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>7020</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ASTEEL</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>0.105</v>
-      </c>
-      <c r="E10" s="16" t="n">
-        <v>0.05</v>
+        <v>1.41</v>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>-0.0208</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>15697400</v>
+        <v>18031400</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>5.72</v>
+        <v>1.98</v>
       </c>
       <c r="H10" t="n">
-        <v>57.96</v>
-      </c>
-      <c r="I10" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>18.65</v>
+      </c>
+      <c r="I10" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J10" s="9" t="n">
-        <v>0.097</v>
+        <v>1.778</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>0.08699999999999999</v>
+        <v>1.984</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="14" t="inlineStr"/>
@@ -961,39 +961,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>7020</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>ASTEEL</t>
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="E11" s="15" t="n">
-        <v>-0.0105</v>
+        <v>0.105</v>
+      </c>
+      <c r="E11" s="16" t="n">
+        <v>0.05</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>15449200</v>
+        <v>16010800</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>0.44</v>
+        <v>5.84</v>
       </c>
       <c r="H11" t="n">
-        <v>44.59</v>
-      </c>
-      <c r="I11" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.96</v>
+      </c>
+      <c r="I11" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J11" s="9" t="n">
-        <v>0.489</v>
+        <v>0.097</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>0.482</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="14" t="inlineStr"/>
@@ -1006,28 +1006,28 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="E12" s="15" t="n">
-        <v>-0.0069</v>
+        <v>0.47</v>
+      </c>
+      <c r="E12" s="10" t="n">
+        <v>-0.0105</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>14074600</v>
+        <v>15996200</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>1.55</v>
+        <v>0.45</v>
       </c>
       <c r="H12" t="n">
-        <v>19.18</v>
+        <v>44.59</v>
       </c>
       <c r="I12" s="13" t="inlineStr">
         <is>
@@ -1035,10 +1035,10 @@
         </is>
       </c>
       <c r="J12" s="9" t="n">
-        <v>1.78</v>
+        <v>0.489</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>1.985</v>
+        <v>0.482</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="14" t="inlineStr"/>
@@ -1051,39 +1051,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>0.625</v>
+        <v>3.87</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>0</v>
+        <v>-0.0561</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>12375500</v>
+        <v>13189000</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>0.49</v>
+        <v>1.49</v>
       </c>
       <c r="H13" t="n">
-        <v>68.89</v>
-      </c>
-      <c r="I13" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.31</v>
+      </c>
+      <c r="I13" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J13" s="9" t="n">
-        <v>0.593</v>
+        <v>3.988</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>0.516</v>
+        <v>3.507</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="14" t="inlineStr"/>
@@ -1096,39 +1096,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>3.88</v>
+        <v>0.625</v>
       </c>
       <c r="E14" s="15" t="n">
-        <v>-0.0537</v>
+        <v>0</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>11905600</v>
+        <v>12821000</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>1.34</v>
+        <v>0.51</v>
       </c>
       <c r="H14" t="n">
-        <v>49.64</v>
-      </c>
-      <c r="I14" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>68.89</v>
+      </c>
+      <c r="I14" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J14" s="9" t="n">
-        <v>3.989</v>
+        <v>0.593</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>3.507</v>
+        <v>0.516</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="14" t="inlineStr"/>
@@ -1150,19 +1150,19 @@
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>0.725</v>
-      </c>
-      <c r="E15" s="15" t="n">
-        <v>-0.09939999999999999</v>
+        <v>0.735</v>
+      </c>
+      <c r="E15" s="10" t="n">
+        <v>-0.08699999999999999</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>10758600</v>
+        <v>12046700</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>0.76</v>
+        <v>0.85</v>
       </c>
       <c r="H15" t="n">
-        <v>45.09</v>
+        <v>46.36</v>
       </c>
       <c r="I15" s="13" t="inlineStr">
         <is>
@@ -1170,10 +1170,10 @@
         </is>
       </c>
       <c r="J15" s="9" t="n">
-        <v>0.77</v>
+        <v>0.771</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>0.72</v>
+        <v>0.721</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="14" t="inlineStr"/>
@@ -1186,28 +1186,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>0.435</v>
-      </c>
-      <c r="E16" s="10" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="E16" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>10237700</v>
+        <v>11870200</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>0.5</v>
+        <v>0.39</v>
       </c>
       <c r="H16" t="n">
-        <v>59.15</v>
+        <v>62.88</v>
       </c>
       <c r="I16" s="17" t="inlineStr">
         <is>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="J16" s="9" t="n">
-        <v>0.415</v>
+        <v>1.899</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>0.356</v>
+        <v>1.697</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="14" t="inlineStr"/>
@@ -1231,28 +1231,28 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>2.07</v>
+        <v>0.445</v>
       </c>
       <c r="E17" s="16" t="n">
-        <v>0.0049</v>
+        <v>0.023</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>9983300</v>
+        <v>11641100</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>0.33</v>
+        <v>0.57</v>
       </c>
       <c r="H17" t="n">
-        <v>63.29</v>
+        <v>61.25</v>
       </c>
       <c r="I17" s="17" t="inlineStr">
         <is>
@@ -1260,10 +1260,10 @@
         </is>
       </c>
       <c r="J17" s="9" t="n">
-        <v>1.9</v>
+        <v>0.416</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>1.697</v>
+        <v>0.357</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="14" t="inlineStr"/>
@@ -1285,19 +1285,19 @@
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>0.31</v>
+        <v>0.315</v>
       </c>
       <c r="E18" s="15" t="n">
-        <v>-0.0159</v>
+        <v>0</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>8029100</v>
+        <v>10642400</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>0.41</v>
+        <v>0.55</v>
       </c>
       <c r="H18" t="n">
-        <v>55</v>
+        <v>61.97</v>
       </c>
       <c r="I18" s="17" t="inlineStr">
         <is>
@@ -1321,28 +1321,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E19" s="10" t="n">
-        <v>0</v>
+        <v>7.59</v>
+      </c>
+      <c r="E19" s="16" t="n">
+        <v>0.012</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>7470700</v>
+        <v>9561700</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>0.49</v>
+        <v>0.65</v>
       </c>
       <c r="H19" t="n">
-        <v>50.46</v>
+        <v>48.47</v>
       </c>
       <c r="I19" s="17" t="inlineStr">
         <is>
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="J19" s="9" t="n">
-        <v>0.774</v>
+        <v>7.597</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>0.775</v>
+        <v>7.718</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="14" t="inlineStr"/>
@@ -1366,39 +1366,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>7079</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>TWL</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="E20" s="16" t="n">
-        <v>0.25</v>
+        <v>0.775</v>
+      </c>
+      <c r="E20" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>7414600</v>
+        <v>8831700</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>0.42</v>
+        <v>0.58</v>
       </c>
       <c r="H20" t="n">
-        <v>51.85</v>
-      </c>
-      <c r="I20" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.46</v>
+      </c>
+      <c r="I20" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J20" s="9" t="n">
-        <v>0.024</v>
+        <v>0.774</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>0.025</v>
+        <v>0.775</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="14" t="inlineStr"/>
@@ -1411,39 +1411,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>0051</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>CUSCAPI</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>0.38</v>
+        <v>0.045</v>
       </c>
       <c r="E21" s="16" t="n">
-        <v>0.027</v>
+        <v>0.125</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>7202800</v>
+        <v>8768500</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>1.02</v>
+        <v>0.63</v>
       </c>
       <c r="H21" t="n">
-        <v>61.86</v>
-      </c>
-      <c r="I21" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.83</v>
+      </c>
+      <c r="I21" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J21" s="9" t="n">
-        <v>0.37</v>
+        <v>0.05</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>0.369</v>
+        <v>0.067</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="14" t="inlineStr"/>
@@ -1456,28 +1456,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>7.61</v>
-      </c>
-      <c r="E22" s="16" t="n">
-        <v>0.0147</v>
+        <v>0.62</v>
+      </c>
+      <c r="E22" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>7098900</v>
+        <v>7666000</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>0.48</v>
+        <v>0.72</v>
       </c>
       <c r="H22" t="n">
-        <v>49.28</v>
+        <v>54.39</v>
       </c>
       <c r="I22" s="17" t="inlineStr">
         <is>
@@ -1485,10 +1485,10 @@
         </is>
       </c>
       <c r="J22" s="9" t="n">
-        <v>7.599</v>
+        <v>0.614</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>7.719</v>
+        <v>0.613</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="14" t="inlineStr"/>
@@ -1501,39 +1501,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AVANGAAD</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>0.295</v>
+        <v>0.865</v>
       </c>
       <c r="E23" s="10" t="n">
-        <v>0</v>
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>6462700</v>
+        <v>7663800</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>2.28</v>
+        <v>0.39</v>
       </c>
       <c r="H23" t="n">
-        <v>49.15</v>
-      </c>
-      <c r="I23" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.29</v>
+      </c>
+      <c r="I23" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J23" s="9" t="n">
-        <v>0.295</v>
+        <v>0.868</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>0.296</v>
+        <v>0.869</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="14" t="inlineStr"/>
@@ -1546,39 +1546,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>IOICORP</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="E24" s="15" t="n">
-        <v>-0.0022</v>
+        <v>0.38</v>
+      </c>
+      <c r="E24" s="16" t="n">
+        <v>0.027</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>6406500</v>
+        <v>7649600</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>0.67</v>
+        <v>1.08</v>
       </c>
       <c r="H24" t="n">
-        <v>39.27</v>
-      </c>
-      <c r="I24" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.86</v>
+      </c>
+      <c r="I24" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J24" s="9" t="n">
-        <v>4.644</v>
+        <v>0.37</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>4.63</v>
+        <v>0.369</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="14" t="inlineStr"/>
@@ -1591,33 +1591,40 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0476</t>
+          <t>7079</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>SLG</t>
+          <t>TWL</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="E25" s="16" t="n">
         <v>0.25</v>
       </c>
-      <c r="E25" s="10" t="n">
-        <v>0</v>
-      </c>
       <c r="F25" s="11" t="n">
-        <v>6368300</v>
+        <v>7414600</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="I25" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J25" s="9" t="n"/>
-      <c r="K25" s="9" t="n"/>
+        <v>0.42</v>
+      </c>
+      <c r="H25" t="n">
+        <v>51.85</v>
+      </c>
+      <c r="I25" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J25" s="9" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="K25" s="9" t="n">
+        <v>0.025</v>
+      </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="14" t="inlineStr"/>
     </row>
@@ -1629,28 +1636,28 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0034</t>
+          <t>9377</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>MMAG</t>
+          <t>FSBM</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="E26" s="15" t="n">
-        <v>-0.2</v>
+        <v>0.09</v>
+      </c>
+      <c r="E26" s="16" t="n">
+        <v>0.0588</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>6236300</v>
+        <v>6901100</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>1.44</v>
+        <v>0.32</v>
       </c>
       <c r="H26" t="n">
-        <v>44.58</v>
+        <v>37.74</v>
       </c>
       <c r="I26" s="17" t="inlineStr">
         <is>
@@ -1658,10 +1665,10 @@
         </is>
       </c>
       <c r="J26" s="9" t="n">
-        <v>0.024</v>
+        <v>0.103</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>0.026</v>
+        <v>0.142</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="14" t="inlineStr"/>
@@ -1683,19 +1690,19 @@
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>0.355</v>
-      </c>
-      <c r="E27" s="15" t="n">
-        <v>-0.0139</v>
+        <v>0.35</v>
+      </c>
+      <c r="E27" s="10" t="n">
+        <v>-0.0278</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>5991200</v>
+        <v>6874600</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>0.7</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H27" t="n">
-        <v>55.26</v>
+        <v>53.1</v>
       </c>
       <c r="I27" s="13" t="inlineStr">
         <is>
@@ -1703,7 +1710,7 @@
         </is>
       </c>
       <c r="J27" s="9" t="n">
-        <v>0.349</v>
+        <v>0.348</v>
       </c>
       <c r="K27" s="9" t="n">
         <v>0.33</v>
@@ -1719,39 +1726,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>IOICORP</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="E28" s="10" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="E28" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>5929900</v>
+        <v>6841000</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0.55</v>
+        <v>0.72</v>
       </c>
       <c r="H28" t="n">
-        <v>54.39</v>
-      </c>
-      <c r="I28" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.09</v>
+      </c>
+      <c r="I28" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J28" s="9" t="n">
-        <v>0.614</v>
+        <v>4.645</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>0.613</v>
+        <v>4.63</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="14" t="inlineStr"/>
@@ -1764,39 +1771,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>0.175</v>
-      </c>
-      <c r="E29" s="15" t="n">
-        <v>-0.0278</v>
+        <v>0.4</v>
+      </c>
+      <c r="E29" s="10" t="n">
+        <v>-0.0123</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>5796900</v>
+        <v>6810200</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0.25</v>
+        <v>0.54</v>
       </c>
       <c r="H29" t="n">
-        <v>40.7</v>
-      </c>
-      <c r="I29" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.4</v>
+      </c>
+      <c r="I29" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J29" s="9" t="n">
-        <v>0.192</v>
+        <v>0.389</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>0.185</v>
+        <v>0.377</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="14" t="inlineStr"/>
@@ -1809,40 +1816,33 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>0476</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>SLG</t>
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>0.4</v>
+        <v>0.25</v>
       </c>
       <c r="E30" s="15" t="n">
-        <v>-0.0123</v>
+        <v>0</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>5612600</v>
+        <v>6776700</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="H30" t="n">
-        <v>54.4</v>
+        <v>0.23</v>
       </c>
       <c r="I30" s="17" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J30" s="9" t="n">
-        <v>0.389</v>
-      </c>
-      <c r="K30" s="9" t="n">
-        <v>0.377</v>
-      </c>
+      <c r="J30" s="9" t="n"/>
+      <c r="K30" s="9" t="n"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="14" t="inlineStr"/>
     </row>
@@ -1854,39 +1854,39 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="E31" s="16" t="n">
-        <v>0.008</v>
+        <v>2.68</v>
+      </c>
+      <c r="E31" s="10" t="n">
+        <v>-0.0111</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>5491700</v>
+        <v>6731400</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>0.55</v>
+        <v>0.37</v>
       </c>
       <c r="H31" t="n">
-        <v>41.98</v>
-      </c>
-      <c r="I31" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.71</v>
+      </c>
+      <c r="I31" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J31" s="9" t="n">
-        <v>1.31</v>
+        <v>2.656</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>1.311</v>
+        <v>2.533</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="14" t="inlineStr"/>
@@ -1899,39 +1899,39 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="E32" s="15" t="n">
-        <v>-0.0074</v>
+        <v>0.175</v>
+      </c>
+      <c r="E32" s="10" t="n">
+        <v>-0.0278</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>5378300</v>
+        <v>6636200</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="H32" t="n">
-        <v>54.42</v>
-      </c>
-      <c r="I32" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.7</v>
+      </c>
+      <c r="I32" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J32" s="9" t="n">
-        <v>2.657</v>
+        <v>0.192</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>2.533</v>
+        <v>0.185</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="14" t="inlineStr"/>
@@ -1944,28 +1944,28 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>0.865</v>
+        <v>0.82</v>
       </c>
       <c r="E33" s="15" t="n">
-        <v>-0.005699999999999999</v>
+        <v>0</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>5346800</v>
+        <v>6618800</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>0.27</v>
+        <v>0.4</v>
       </c>
       <c r="H33" t="n">
-        <v>46.29</v>
+        <v>58.27</v>
       </c>
       <c r="I33" s="17" t="inlineStr">
         <is>
@@ -1973,10 +1973,10 @@
         </is>
       </c>
       <c r="J33" s="9" t="n">
-        <v>0.868</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>0.869</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="14" t="inlineStr"/>
@@ -1989,39 +1989,39 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="E34" s="16" t="n">
-        <v>0.0052</v>
+        <v>0.295</v>
+      </c>
+      <c r="E34" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>5178100</v>
+        <v>6462700</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>0.88</v>
+        <v>2.28</v>
       </c>
       <c r="H34" t="n">
-        <v>49.36</v>
-      </c>
-      <c r="I34" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.15</v>
+      </c>
+      <c r="I34" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J34" s="9" t="n">
-        <v>1.926</v>
+        <v>0.295</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>1.954</v>
+        <v>0.296</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="14" t="inlineStr"/>
@@ -2034,39 +2034,39 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>0034</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>MMAG</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="E35" s="15" t="n">
-        <v>-0.08470000000000001</v>
+        <v>0.02</v>
+      </c>
+      <c r="E35" s="10" t="n">
+        <v>-0.2</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>5120400</v>
+        <v>6236300</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>1.18</v>
+        <v>1.44</v>
       </c>
       <c r="H35" t="n">
-        <v>56.85</v>
-      </c>
-      <c r="I35" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>44.58</v>
+      </c>
+      <c r="I35" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J35" s="9" t="n">
-        <v>2.764</v>
+        <v>0.024</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>2.132</v>
+        <v>0.026</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="14" t="inlineStr"/>
@@ -2079,33 +2079,40 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0473</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>EVOCOM</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E36" s="10" t="n">
-        <v>0</v>
+        <v>1.94</v>
+      </c>
+      <c r="E36" s="16" t="n">
+        <v>0.0104</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>4979600</v>
+        <v>6158600</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="I36" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J36" s="9" t="n"/>
-      <c r="K36" s="9" t="n"/>
+        <v>1.05</v>
+      </c>
+      <c r="H36" t="n">
+        <v>51.08</v>
+      </c>
+      <c r="I36" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J36" s="9" t="n">
+        <v>1.927</v>
+      </c>
+      <c r="K36" s="9" t="n">
+        <v>1.954</v>
+      </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="14" t="inlineStr"/>
     </row>
@@ -2117,28 +2124,28 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>0223</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>SAMAIDEN</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="E37" s="16" t="n">
-        <v>0.009399999999999999</v>
+        <v>2.8</v>
+      </c>
+      <c r="E37" s="10" t="n">
+        <v>-0.08789999999999999</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>4960900</v>
+        <v>5935400</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0.5</v>
+        <v>1.36</v>
       </c>
       <c r="H37" t="n">
-        <v>50.92</v>
+        <v>56.45</v>
       </c>
       <c r="I37" s="13" t="inlineStr">
         <is>
@@ -2146,10 +2153,10 @@
         </is>
       </c>
       <c r="J37" s="9" t="n">
-        <v>1.068</v>
+        <v>2.763</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>1.04</v>
+        <v>2.132</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="14" t="inlineStr"/>
@@ -2162,28 +2169,28 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="E38" s="10" t="n">
-        <v>0</v>
+        <v>4.75</v>
+      </c>
+      <c r="E38" s="16" t="n">
+        <v>0.0106</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>4856500</v>
+        <v>5789100</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>0.29</v>
+        <v>0.34</v>
       </c>
       <c r="H38" t="n">
-        <v>58.27</v>
+        <v>50.43</v>
       </c>
       <c r="I38" s="17" t="inlineStr">
         <is>
@@ -2191,10 +2198,10 @@
         </is>
       </c>
       <c r="J38" s="9" t="n">
-        <v>0.8129999999999999</v>
+        <v>4.718</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>0.8080000000000001</v>
+        <v>4.87</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="14" t="inlineStr"/>
@@ -2216,19 +2223,19 @@
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="E39" s="15" t="n">
-        <v>-0.0101</v>
+        <v>4.89</v>
+      </c>
+      <c r="E39" s="10" t="n">
+        <v>-0.0121</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>4846800</v>
+        <v>5660200</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>0.19</v>
+        <v>0.22</v>
       </c>
       <c r="H39" t="n">
-        <v>50.88</v>
+        <v>50.37</v>
       </c>
       <c r="I39" s="13" t="inlineStr">
         <is>
@@ -2239,7 +2246,7 @@
         <v>4.932</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>4.698</v>
+        <v>4.697</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="14" t="inlineStr"/>
@@ -2252,39 +2259,39 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>7195</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>BNASTRA</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>2.71</v>
+        <v>1.26</v>
       </c>
       <c r="E40" s="16" t="n">
-        <v>0.0037</v>
+        <v>0.008</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>4652500</v>
+        <v>5574100</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>4.28</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H40" t="n">
-        <v>82.95</v>
-      </c>
-      <c r="I40" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.98</v>
+      </c>
+      <c r="I40" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J40" s="9" t="n">
-        <v>2.54</v>
+        <v>1.31</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>2.386</v>
+        <v>1.311</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="14" t="inlineStr"/>
@@ -2297,39 +2304,39 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>AMBANK</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>0.585</v>
+        <v>6.4</v>
       </c>
       <c r="E41" s="16" t="n">
-        <v>0.0086</v>
+        <v>0.0207</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>4619400</v>
+        <v>5465200</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>0.23</v>
+        <v>0.96</v>
       </c>
       <c r="H41" t="n">
-        <v>52.99</v>
-      </c>
-      <c r="I41" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.21</v>
+      </c>
+      <c r="I41" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J41" s="9" t="n">
-        <v>0.583</v>
+        <v>6.424</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>0.532</v>
+        <v>6.804</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="14" t="inlineStr"/>
@@ -2342,39 +2349,39 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="E42" s="16" t="n">
-        <v>0.1357</v>
+        <v>0.0189</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>4545200</v>
+        <v>5408800</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>1.29</v>
+        <v>0.55</v>
       </c>
       <c r="H42" t="n">
-        <v>86.79000000000001</v>
-      </c>
-      <c r="I42" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.4</v>
+      </c>
+      <c r="I42" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J42" s="9" t="n">
-        <v>0.758</v>
+        <v>1.069</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>0.525</v>
+        <v>1.04</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="14" t="inlineStr"/>
@@ -2387,40 +2394,33 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>0473</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>EVOCOM</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="E43" s="15" t="n">
-        <v>-0.0678</v>
+        <v>0</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>4428600</v>
+        <v>5271900</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="H43" t="n">
-        <v>53.65</v>
+        <v>0.37</v>
       </c>
       <c r="I43" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J43" s="9" t="n">
-        <v>1.103</v>
-      </c>
-      <c r="K43" s="9" t="n">
-        <v>0.86</v>
-      </c>
+      <c r="J43" s="9" t="n"/>
+      <c r="K43" s="9" t="n"/>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="14" t="inlineStr"/>
     </row>
@@ -2432,39 +2432,39 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D44" s="9" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="E44" s="10" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="E44" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>4330900</v>
+        <v>5185300</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>2.62</v>
+        <v>0.26</v>
       </c>
       <c r="H44" t="n">
-        <v>39.24</v>
-      </c>
-      <c r="I44" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.1</v>
+      </c>
+      <c r="I44" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J44" s="9" t="n">
-        <v>0.419</v>
+        <v>0.583</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>0.437</v>
+        <v>0.532</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="14" t="inlineStr"/>
@@ -2477,39 +2477,39 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="E45" s="10" t="n">
-        <v>0</v>
+        <v>1.1</v>
+      </c>
+      <c r="E45" s="16" t="n">
+        <v>0.1055</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>4099800</v>
+        <v>5051400</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>0.38</v>
+        <v>1.43</v>
       </c>
       <c r="H45" t="n">
-        <v>33.84</v>
-      </c>
-      <c r="I45" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>86.13</v>
+      </c>
+      <c r="I45" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J45" s="9" t="n">
-        <v>0.399</v>
+        <v>0.755</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>0.408</v>
+        <v>0.524</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="14" t="inlineStr"/>
@@ -2522,39 +2522,39 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>0096</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>NEXGRAM</t>
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="E46" s="16" t="n">
-        <v>0.0331</v>
+        <v>0.045</v>
+      </c>
+      <c r="E46" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>4046900</v>
+        <v>5009600</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0.42</v>
+        <v>2.52</v>
       </c>
       <c r="H46" t="n">
-        <v>57</v>
-      </c>
-      <c r="I46" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.31</v>
+      </c>
+      <c r="I46" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J46" s="9" t="n">
-        <v>3.61</v>
+        <v>0.042</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>2.872</v>
+        <v>0.047</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="14" t="inlineStr"/>
@@ -2567,28 +2567,28 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>7195</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>BNASTRA</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>4.79</v>
+        <v>2.71</v>
       </c>
       <c r="E47" s="16" t="n">
-        <v>0.0191</v>
+        <v>0.0037</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>4038400</v>
+        <v>4655300</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>0.24</v>
+        <v>4.28</v>
       </c>
       <c r="H47" t="n">
-        <v>53.81</v>
+        <v>82.95</v>
       </c>
       <c r="I47" s="17" t="inlineStr">
         <is>
@@ -2596,10 +2596,10 @@
         </is>
       </c>
       <c r="J47" s="9" t="n">
-        <v>4.722</v>
+        <v>2.54</v>
       </c>
       <c r="K47" s="9" t="n">
-        <v>4.871</v>
+        <v>2.386</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="14" t="inlineStr"/>
@@ -2612,28 +2612,28 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>0340</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>NORTHERN</t>
         </is>
       </c>
       <c r="D48" s="9" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="E48" s="16" t="n">
-        <v>0.0108</v>
+        <v>1.09</v>
+      </c>
+      <c r="E48" s="10" t="n">
+        <v>-0.07629999999999999</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>4034200</v>
+        <v>4624900</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>0.73</v>
+        <v>0.59</v>
       </c>
       <c r="H48" t="n">
-        <v>62.32</v>
+        <v>52.9</v>
       </c>
       <c r="I48" s="13" t="inlineStr">
         <is>
@@ -2641,10 +2641,10 @@
         </is>
       </c>
       <c r="J48" s="9" t="n">
-        <v>0.912</v>
+        <v>1.103</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>0.869</v>
+        <v>0.86</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="14" t="inlineStr"/>
@@ -2657,39 +2657,39 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="E49" s="15" t="n">
-        <v>-0.004699999999999999</v>
+        <v>0.4</v>
+      </c>
+      <c r="E49" s="10" t="n">
+        <v>-0.0244</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>3955200</v>
+        <v>4583800</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>0.2</v>
+        <v>2.77</v>
       </c>
       <c r="H49" t="n">
-        <v>53.98</v>
-      </c>
-      <c r="I49" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.91</v>
+      </c>
+      <c r="I49" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J49" s="9" t="n">
-        <v>2.111</v>
+        <v>0.418</v>
       </c>
       <c r="K49" s="9" t="n">
-        <v>2.094</v>
+        <v>0.437</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="14" t="inlineStr"/>
@@ -2702,39 +2702,39 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D50" s="9" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="E50" s="15" t="n">
-        <v>-0.0692</v>
+        <v>2.11</v>
+      </c>
+      <c r="E50" s="10" t="n">
+        <v>-0.014</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>3945300</v>
+        <v>4549000</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>1.21</v>
+        <v>0.23</v>
       </c>
       <c r="H50" t="n">
-        <v>50.47</v>
-      </c>
-      <c r="I50" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.82</v>
+      </c>
+      <c r="I50" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J50" s="9" t="n">
-        <v>1.252</v>
+        <v>2.109</v>
       </c>
       <c r="K50" s="9" t="n">
-        <v>1.04</v>
+        <v>2.094</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="14" t="inlineStr"/>
@@ -2747,28 +2747,28 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>AMBANK</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>6.45</v>
-      </c>
-      <c r="E51" s="16" t="n">
-        <v>0.0287</v>
+        <v>1.2</v>
+      </c>
+      <c r="E51" s="10" t="n">
+        <v>-0.07690000000000001</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>3681800</v>
+        <v>4474600</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>0.65</v>
+        <v>1.37</v>
       </c>
       <c r="H51" t="n">
-        <v>47.84</v>
+        <v>49.61</v>
       </c>
       <c r="I51" s="13" t="inlineStr">
         <is>
@@ -2776,10 +2776,10 @@
         </is>
       </c>
       <c r="J51" s="9" t="n">
-        <v>6.429</v>
+        <v>1.251</v>
       </c>
       <c r="K51" s="9" t="n">
-        <v>6.805</v>
+        <v>1.04</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="14" t="inlineStr"/>
@@ -2792,28 +2792,28 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D52" s="9" t="n">
-        <v>0.455</v>
+        <v>3.7</v>
       </c>
       <c r="E52" s="16" t="n">
-        <v>0.0111</v>
+        <v>0.0193</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>3595800</v>
+        <v>4431300</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>0.09</v>
+        <v>0.46</v>
       </c>
       <c r="H52" t="n">
-        <v>25.7</v>
+        <v>55.93</v>
       </c>
       <c r="I52" s="13" t="inlineStr">
         <is>
@@ -2821,10 +2821,10 @@
         </is>
       </c>
       <c r="J52" s="9" t="n">
-        <v>0.525</v>
+        <v>3.605</v>
       </c>
       <c r="K52" s="9" t="n">
-        <v>0.713</v>
+        <v>2.871</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="14" t="inlineStr"/>
@@ -2852,10 +2852,10 @@
         <v>0.001</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>3573500</v>
+        <v>4355700</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>0.27</v>
+        <v>0.32</v>
       </c>
       <c r="H53" t="n">
         <v>44.4</v>
@@ -2882,39 +2882,39 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D54" s="9" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="E54" s="15" t="n">
-        <v>-0.0303</v>
+        <v>2.07</v>
+      </c>
+      <c r="E54" s="10" t="n">
+        <v>-0.0048</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>3555600</v>
+        <v>4342500</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>0.49</v>
+        <v>0.29</v>
       </c>
       <c r="H54" t="n">
-        <v>68.45</v>
-      </c>
-      <c r="I54" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.74</v>
+      </c>
+      <c r="I54" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J54" s="9" t="n">
-        <v>0.299</v>
+        <v>2.189</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>0.278</v>
+        <v>2.225</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="14" t="inlineStr"/>
@@ -2927,28 +2927,28 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0258</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>AGMO</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>0.29</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E55" s="16" t="n">
-        <v>0.0175</v>
+        <v>0.0108</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>3442500</v>
+        <v>4202200</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>4.58</v>
+        <v>0.76</v>
       </c>
       <c r="H55" t="n">
-        <v>53.95</v>
+        <v>62.32</v>
       </c>
       <c r="I55" s="13" t="inlineStr">
         <is>
@@ -2956,10 +2956,10 @@
         </is>
       </c>
       <c r="J55" s="9" t="n">
-        <v>0.28</v>
+        <v>0.912</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>0.301</v>
+        <v>0.869</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="14" t="inlineStr"/>
@@ -2972,28 +2972,28 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D56" s="9" t="n">
-        <v>0.215</v>
-      </c>
-      <c r="E56" s="10" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="E56" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>3440000</v>
+        <v>4102100</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>0.13</v>
+        <v>0.38</v>
       </c>
       <c r="H56" t="n">
-        <v>30.12</v>
+        <v>33.84</v>
       </c>
       <c r="I56" s="13" t="inlineStr">
         <is>
@@ -3001,10 +3001,10 @@
         </is>
       </c>
       <c r="J56" s="9" t="n">
-        <v>0.241</v>
+        <v>0.399</v>
       </c>
       <c r="K56" s="9" t="n">
-        <v>0.295</v>
+        <v>0.408</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="14" t="inlineStr"/>
@@ -3017,39 +3017,39 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>WCT</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="E57" s="15" t="n">
-        <v>-0.0159</v>
+        <v>0.32</v>
+      </c>
+      <c r="E57" s="10" t="n">
+        <v>-0.0303</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>3391000</v>
+        <v>4005400</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>0.68</v>
+        <v>0.55</v>
       </c>
       <c r="H57" t="n">
-        <v>24.94</v>
-      </c>
-      <c r="I57" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>68.45</v>
+      </c>
+      <c r="I57" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J57" s="9" t="n">
-        <v>0.35</v>
+        <v>0.299</v>
       </c>
       <c r="K57" s="9" t="n">
-        <v>0.379</v>
+        <v>0.278</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="14" t="inlineStr"/>
@@ -3062,28 +3062,28 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>VELESTO</t>
         </is>
       </c>
       <c r="D58" s="9" t="n">
-        <v>0.475</v>
-      </c>
-      <c r="E58" s="10" t="n">
-        <v>0</v>
+        <v>0.225</v>
+      </c>
+      <c r="E58" s="16" t="n">
+        <v>0.04650000000000001</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>3347000</v>
+        <v>3925600</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>0.48</v>
+        <v>0.19</v>
       </c>
       <c r="H58" t="n">
-        <v>22.56</v>
+        <v>48.41</v>
       </c>
       <c r="I58" s="13" t="inlineStr">
         <is>
@@ -3091,10 +3091,10 @@
         </is>
       </c>
       <c r="J58" s="9" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.224</v>
       </c>
       <c r="K58" s="9" t="n">
-        <v>0.629</v>
+        <v>0.24</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="14" t="inlineStr"/>
@@ -3107,28 +3107,28 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>VELESTO</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="E59" s="16" t="n">
-        <v>0.04650000000000001</v>
+        <v>2.76</v>
+      </c>
+      <c r="E59" s="10" t="n">
+        <v>-0.0213</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>3335000</v>
+        <v>3883700</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>0.16</v>
+        <v>0.28</v>
       </c>
       <c r="H59" t="n">
-        <v>48.41</v>
+        <v>48.59</v>
       </c>
       <c r="I59" s="13" t="inlineStr">
         <is>
@@ -3136,10 +3136,10 @@
         </is>
       </c>
       <c r="J59" s="9" t="n">
-        <v>0.224</v>
+        <v>2.794</v>
       </c>
       <c r="K59" s="9" t="n">
-        <v>0.24</v>
+        <v>2.721</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="14" t="inlineStr"/>
@@ -3152,28 +3152,28 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="E60" s="16" t="n">
-        <v>0.0048</v>
+        <v>0.475</v>
+      </c>
+      <c r="E60" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>3230900</v>
+        <v>3750200</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>0.22</v>
+        <v>0.54</v>
       </c>
       <c r="H60" t="n">
-        <v>38.63</v>
+        <v>22.56</v>
       </c>
       <c r="I60" s="13" t="inlineStr">
         <is>
@@ -3181,10 +3181,10 @@
         </is>
       </c>
       <c r="J60" s="9" t="n">
-        <v>2.191</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="K60" s="9" t="n">
-        <v>2.225</v>
+        <v>0.629</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="14" t="inlineStr"/>
@@ -3197,28 +3197,28 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>0.495</v>
-      </c>
-      <c r="E61" s="15" t="n">
-        <v>-0.01</v>
+        <v>0.445</v>
+      </c>
+      <c r="E61" s="10" t="n">
+        <v>-0.0111</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>3203900</v>
+        <v>3718800</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>0.38</v>
+        <v>0.1</v>
       </c>
       <c r="H61" t="n">
-        <v>42.01</v>
+        <v>23.61</v>
       </c>
       <c r="I61" s="13" t="inlineStr">
         <is>
@@ -3226,10 +3226,10 @@
         </is>
       </c>
       <c r="J61" s="9" t="n">
-        <v>0.517</v>
+        <v>0.524</v>
       </c>
       <c r="K61" s="9" t="n">
-        <v>0.529</v>
+        <v>0.713</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="14" t="inlineStr"/>
@@ -3242,28 +3242,28 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D62" s="9" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="E62" s="16" t="n">
-        <v>0.016</v>
+        <v>0.315</v>
+      </c>
+      <c r="E62" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>2970200</v>
+        <v>3697400</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>0.77</v>
+        <v>0.74</v>
       </c>
       <c r="H62" t="n">
-        <v>25.43</v>
+        <v>26.24</v>
       </c>
       <c r="I62" s="13" t="inlineStr">
         <is>
@@ -3271,10 +3271,10 @@
         </is>
       </c>
       <c r="J62" s="9" t="n">
-        <v>1.442</v>
+        <v>0.351</v>
       </c>
       <c r="K62" s="9" t="n">
-        <v>1.59</v>
+        <v>0.379</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="14" t="inlineStr"/>
@@ -3287,28 +3287,28 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="E63" s="15" t="n">
-        <v>-0.0083</v>
+        <v>0.21</v>
+      </c>
+      <c r="E63" s="10" t="n">
+        <v>-0.0233</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>2951200</v>
+        <v>3630500</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>0.37</v>
+        <v>0.14</v>
       </c>
       <c r="H63" t="n">
-        <v>37.03</v>
+        <v>28.68</v>
       </c>
       <c r="I63" s="13" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="J63" s="9" t="n">
-        <v>1.246</v>
+        <v>0.24</v>
       </c>
       <c r="K63" s="9" t="n">
-        <v>1.342</v>
+        <v>0.295</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="14" t="inlineStr"/>
@@ -3332,39 +3332,39 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>5336</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>CKI</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D64" s="9" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="E64" s="16" t="n">
-        <v>0.0137</v>
+        <v>0.495</v>
+      </c>
+      <c r="E64" s="10" t="n">
+        <v>-0.01</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>2950600</v>
+        <v>3565100</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>1.92</v>
+        <v>0.42</v>
       </c>
       <c r="H64" t="n">
-        <v>51.33</v>
-      </c>
-      <c r="I64" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.01</v>
+      </c>
+      <c r="I64" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J64" s="9" t="n">
-        <v>0.364</v>
+        <v>0.517</v>
       </c>
       <c r="K64" s="9" t="n">
-        <v>0.387</v>
+        <v>0.529</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="14" t="inlineStr"/>
@@ -3377,28 +3377,28 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>0258</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>AGMO</t>
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>1.18</v>
+        <v>0.29</v>
       </c>
       <c r="E65" s="16" t="n">
-        <v>0.0172</v>
+        <v>0.0175</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>2942000</v>
+        <v>3489300</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>0.38</v>
+        <v>4.65</v>
       </c>
       <c r="H65" t="n">
-        <v>53.23</v>
+        <v>53.95</v>
       </c>
       <c r="I65" s="13" t="inlineStr">
         <is>
@@ -3406,10 +3406,10 @@
         </is>
       </c>
       <c r="J65" s="9" t="n">
-        <v>1.162</v>
+        <v>0.28</v>
       </c>
       <c r="K65" s="9" t="n">
-        <v>1.127</v>
+        <v>0.301</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="14" t="inlineStr"/>
@@ -3422,39 +3422,39 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D66" s="9" t="n">
-        <v>0.805</v>
-      </c>
-      <c r="E66" s="10" t="n">
-        <v>0</v>
+        <v>1.26</v>
+      </c>
+      <c r="E66" s="16" t="n">
+        <v>0.008</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>2912100</v>
+        <v>3357600</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>0.49</v>
+        <v>0.87</v>
       </c>
       <c r="H66" t="n">
-        <v>66.90000000000001</v>
-      </c>
-      <c r="I66" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>23.74</v>
+      </c>
+      <c r="I66" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J66" s="9" t="n">
-        <v>0.791</v>
+        <v>1.441</v>
       </c>
       <c r="K66" s="9" t="n">
-        <v>0.768</v>
+        <v>1.59</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="14" t="inlineStr"/>
@@ -3467,28 +3467,28 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>7243</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>MAGMA</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D67" s="9" t="n">
-        <v>0.285</v>
+        <v>1.18</v>
       </c>
       <c r="E67" s="16" t="n">
-        <v>0.0556</v>
+        <v>0.0172</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>2891000</v>
+        <v>3250200</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>4.19</v>
+        <v>0.42</v>
       </c>
       <c r="H67" t="n">
-        <v>53.17</v>
+        <v>53.23</v>
       </c>
       <c r="I67" s="13" t="inlineStr">
         <is>
@@ -3496,10 +3496,10 @@
         </is>
       </c>
       <c r="J67" s="9" t="n">
-        <v>0.281</v>
+        <v>1.162</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>0.285</v>
+        <v>1.127</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="14" t="inlineStr"/>
@@ -3512,28 +3512,28 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D68" s="9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="E68" s="15" t="n">
-        <v>-0.0095</v>
+        <v>1.2</v>
+      </c>
+      <c r="E68" s="10" t="n">
+        <v>-0.0083</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>2802200</v>
+        <v>3140800</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="H68" t="n">
-        <v>49.14</v>
+        <v>37.03</v>
       </c>
       <c r="I68" s="13" t="inlineStr">
         <is>
@@ -3541,10 +3541,10 @@
         </is>
       </c>
       <c r="J68" s="9" t="n">
-        <v>1.069</v>
+        <v>1.246</v>
       </c>
       <c r="K68" s="9" t="n">
-        <v>0.9409999999999999</v>
+        <v>1.342</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="14" t="inlineStr"/>
@@ -3566,19 +3566,19 @@
         </is>
       </c>
       <c r="D69" s="9" t="n">
-        <v>0.675</v>
-      </c>
-      <c r="E69" s="16" t="n">
-        <v>0.0075</v>
+        <v>0.67</v>
+      </c>
+      <c r="E69" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>2764900</v>
+        <v>3138200</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>0.31</v>
+        <v>0.35</v>
       </c>
       <c r="H69" t="n">
-        <v>47.36</v>
+        <v>46.36</v>
       </c>
       <c r="I69" s="13" t="inlineStr">
         <is>
@@ -3586,7 +3586,7 @@
         </is>
       </c>
       <c r="J69" s="9" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="K69" s="9" t="n">
         <v>0.6860000000000001</v>
@@ -3602,39 +3602,39 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D70" s="9" t="n">
-        <v>2.99</v>
+        <v>1.04</v>
       </c>
       <c r="E70" s="10" t="n">
-        <v>0</v>
+        <v>-0.0095</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>2698000</v>
+        <v>2980200</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>0.85</v>
+        <v>0.35</v>
       </c>
       <c r="H70" t="n">
-        <v>79.09999999999999</v>
-      </c>
-      <c r="I70" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.14</v>
+      </c>
+      <c r="I70" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J70" s="9" t="n">
-        <v>2.732</v>
+        <v>1.069</v>
       </c>
       <c r="K70" s="9" t="n">
-        <v>2.357</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="14" t="inlineStr"/>
@@ -3647,39 +3647,39 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>5336</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>CKI</t>
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>0.655</v>
-      </c>
-      <c r="E71" s="10" t="n">
-        <v>0</v>
+        <v>0.37</v>
+      </c>
+      <c r="E71" s="16" t="n">
+        <v>0.0137</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>2657600</v>
+        <v>2953800</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>0.3</v>
+        <v>1.92</v>
       </c>
       <c r="H71" t="n">
-        <v>49.29</v>
-      </c>
-      <c r="I71" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.33</v>
+      </c>
+      <c r="I71" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J71" s="9" t="n">
-        <v>0.669</v>
+        <v>0.364</v>
       </c>
       <c r="K71" s="9" t="n">
-        <v>0.617</v>
+        <v>0.387</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="14" t="inlineStr"/>
@@ -3692,28 +3692,28 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0388</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>SEMICO</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D72" s="9" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="E72" s="10" t="n">
+        <v>0.805</v>
+      </c>
+      <c r="E72" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>2535000</v>
+        <v>2922700</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>0.82</v>
+        <v>0.49</v>
       </c>
       <c r="H72" t="n">
-        <v>64.41</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="I72" s="17" t="inlineStr">
         <is>
@@ -3721,10 +3721,10 @@
         </is>
       </c>
       <c r="J72" s="9" t="n">
-        <v>0.615</v>
+        <v>0.791</v>
       </c>
       <c r="K72" s="9" t="n">
-        <v>0.602</v>
+        <v>0.768</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="14" t="inlineStr"/>
@@ -3737,38 +3737,40 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0471</t>
+          <t>7243</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>PIONEER</t>
+          <t>MAGMA</t>
         </is>
       </c>
       <c r="D73" s="9" t="n">
-        <v>0.33</v>
+        <v>0.285</v>
       </c>
       <c r="E73" s="16" t="n">
-        <v>0.0476</v>
+        <v>0.0556</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>2409200</v>
+        <v>2891000</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>0.26</v>
+        <v>4.19</v>
       </c>
       <c r="H73" t="n">
-        <v>58.79</v>
-      </c>
-      <c r="I73" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.17</v>
+      </c>
+      <c r="I73" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J73" s="9" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="K73" s="9" t="n"/>
+        <v>0.281</v>
+      </c>
+      <c r="K73" s="9" t="n">
+        <v>0.285</v>
+      </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="14" t="inlineStr"/>
     </row>
@@ -3780,28 +3782,28 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>0470</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>BFIELD</t>
         </is>
       </c>
       <c r="D74" s="9" t="n">
-        <v>0.605</v>
-      </c>
-      <c r="E74" s="16" t="n">
-        <v>0.0083</v>
+        <v>0.445</v>
+      </c>
+      <c r="E74" s="10" t="n">
+        <v>-0.022</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>2387900</v>
+        <v>2864800</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>0.57</v>
+        <v>0.26</v>
       </c>
       <c r="H74" t="n">
-        <v>52.64</v>
+        <v>27.3</v>
       </c>
       <c r="I74" s="13" t="inlineStr">
         <is>
@@ -3809,11 +3811,9 @@
         </is>
       </c>
       <c r="J74" s="9" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="K74" s="9" t="n">
-        <v>0.585</v>
-      </c>
+        <v>0.471</v>
+      </c>
+      <c r="K74" s="9" t="n"/>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="14" t="inlineStr"/>
     </row>
@@ -3825,39 +3825,39 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D75" s="9" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="E75" s="15" t="n">
-        <v>-0.0142</v>
+        <v>7.34</v>
+      </c>
+      <c r="E75" s="16" t="n">
+        <v>0.0124</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>2379300</v>
+        <v>2787900</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>0.17</v>
+        <v>0.36</v>
       </c>
       <c r="H75" t="n">
-        <v>50.17</v>
-      </c>
-      <c r="I75" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>44.29</v>
+      </c>
+      <c r="I75" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J75" s="9" t="n">
-        <v>2.796</v>
+        <v>7.376</v>
       </c>
       <c r="K75" s="9" t="n">
-        <v>2.721</v>
+        <v>7.687</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="14" t="inlineStr"/>
@@ -3870,28 +3870,28 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D76" s="9" t="n">
-        <v>5.48</v>
+        <v>0.655</v>
       </c>
       <c r="E76" s="15" t="n">
-        <v>-0.0036</v>
+        <v>0</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>2266300</v>
+        <v>2781400</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>0.16</v>
+        <v>0.32</v>
       </c>
       <c r="H76" t="n">
-        <v>45.95</v>
+        <v>49.29</v>
       </c>
       <c r="I76" s="13" t="inlineStr">
         <is>
@@ -3899,10 +3899,10 @@
         </is>
       </c>
       <c r="J76" s="9" t="n">
-        <v>5.606</v>
+        <v>0.669</v>
       </c>
       <c r="K76" s="9" t="n">
-        <v>5.388</v>
+        <v>0.617</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="14" t="inlineStr"/>
@@ -3915,28 +3915,28 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D77" s="9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="E77" s="15" t="n">
-        <v>-0.0377</v>
+        <v>0.885</v>
+      </c>
+      <c r="E77" s="10" t="n">
+        <v>-0.038</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>2110400</v>
+        <v>2767000</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>0.46</v>
+        <v>0.33</v>
       </c>
       <c r="H77" t="n">
-        <v>48.75</v>
+        <v>43.35</v>
       </c>
       <c r="I77" s="13" t="inlineStr">
         <is>
@@ -3944,10 +3944,10 @@
         </is>
       </c>
       <c r="J77" s="9" t="n">
-        <v>1.057</v>
+        <v>0.948</v>
       </c>
       <c r="K77" s="9" t="n">
-        <v>0.919</v>
+        <v>0.836</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="14" t="inlineStr"/>
@@ -3960,39 +3960,39 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0272</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>TTVHB</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D78" s="9" t="n">
-        <v>0.245</v>
-      </c>
-      <c r="E78" s="10" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="E78" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>2083400</v>
+        <v>2759400</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>0.89</v>
+        <v>0.87</v>
       </c>
       <c r="H78" t="n">
-        <v>47.66</v>
-      </c>
-      <c r="I78" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I78" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J78" s="9" t="n">
-        <v>0.25</v>
+        <v>2.732</v>
       </c>
       <c r="K78" s="9" t="n">
-        <v>0.255</v>
+        <v>2.357</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="14" t="inlineStr"/>
@@ -4005,28 +4005,28 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0233</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>PEKAT</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D79" s="9" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="E79" s="15" t="n">
-        <v>-0.079</v>
+        <v>5.45</v>
+      </c>
+      <c r="E79" s="10" t="n">
+        <v>-0.0091</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>2057700</v>
+        <v>2721300</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>0.63</v>
+        <v>0.19</v>
       </c>
       <c r="H79" t="n">
-        <v>55.63</v>
+        <v>44.82</v>
       </c>
       <c r="I79" s="13" t="inlineStr">
         <is>
@@ -4034,10 +4034,10 @@
         </is>
       </c>
       <c r="J79" s="9" t="n">
-        <v>2.67</v>
+        <v>5.603</v>
       </c>
       <c r="K79" s="9" t="n">
-        <v>2.206</v>
+        <v>5.387</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="14" t="inlineStr"/>
@@ -4050,39 +4050,39 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D80" s="9" t="n">
-        <v>7.34</v>
+        <v>0.605</v>
       </c>
       <c r="E80" s="16" t="n">
-        <v>0.0124</v>
+        <v>0.0083</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>2009000</v>
+        <v>2632100</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>0.26</v>
+        <v>0.63</v>
       </c>
       <c r="H80" t="n">
-        <v>44.29</v>
-      </c>
-      <c r="I80" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.64</v>
+      </c>
+      <c r="I80" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J80" s="9" t="n">
-        <v>7.376</v>
+        <v>0.6</v>
       </c>
       <c r="K80" s="9" t="n">
-        <v>7.687</v>
+        <v>0.585</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="14" t="inlineStr"/>
@@ -4095,28 +4095,28 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>0388</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>SEMICO</t>
         </is>
       </c>
       <c r="D81" s="9" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="E81" s="16" t="n">
-        <v>0.0189</v>
+        <v>0.62</v>
+      </c>
+      <c r="E81" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>1964500</v>
+        <v>2535000</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>0.29</v>
+        <v>0.82</v>
       </c>
       <c r="H81" t="n">
-        <v>48.09</v>
+        <v>64.41</v>
       </c>
       <c r="I81" s="17" t="inlineStr">
         <is>
@@ -4124,10 +4124,10 @@
         </is>
       </c>
       <c r="J81" s="9" t="n">
-        <v>1.614</v>
+        <v>0.615</v>
       </c>
       <c r="K81" s="9" t="n">
-        <v>1.709</v>
+        <v>0.602</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="14" t="inlineStr"/>
@@ -4140,28 +4140,28 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0470</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>BFIELD</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D82" s="9" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="E82" s="15" t="n">
-        <v>-0.011</v>
+        <v>0.875</v>
+      </c>
+      <c r="E82" s="10" t="n">
+        <v>-0.0489</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>1956800</v>
+        <v>2490000</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>0.18</v>
+        <v>1.79</v>
       </c>
       <c r="H82" t="n">
-        <v>30.03</v>
+        <v>44.21</v>
       </c>
       <c r="I82" s="13" t="inlineStr">
         <is>
@@ -4169,9 +4169,11 @@
         </is>
       </c>
       <c r="J82" s="9" t="n">
-        <v>0.472</v>
-      </c>
-      <c r="K82" s="9" t="n"/>
+        <v>0.919</v>
+      </c>
+      <c r="K82" s="9" t="n">
+        <v>0.862</v>
+      </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="14" t="inlineStr"/>
     </row>
@@ -4183,28 +4185,28 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>5323</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>JPG</t>
         </is>
       </c>
       <c r="D83" s="9" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E83" s="15" t="n">
-        <v>-0.0064</v>
+        <v>1.7</v>
+      </c>
+      <c r="E83" s="10" t="n">
+        <v>-0.0116</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>1826800</v>
+        <v>2449400</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>0.22</v>
+        <v>0.38</v>
       </c>
       <c r="H83" t="n">
-        <v>49.19</v>
+        <v>34.64</v>
       </c>
       <c r="I83" s="13" t="inlineStr">
         <is>
@@ -4212,10 +4214,10 @@
         </is>
       </c>
       <c r="J83" s="9" t="n">
-        <v>0.779</v>
+        <v>1.794</v>
       </c>
       <c r="K83" s="9" t="n">
-        <v>0.773</v>
+        <v>1.909</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="14" t="inlineStr"/>
@@ -4228,39 +4230,39 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D84" s="9" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="E84" s="15" t="n">
-        <v>-0.0122</v>
+        <v>1.61</v>
+      </c>
+      <c r="E84" s="16" t="n">
+        <v>0.0126</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>1757400</v>
+        <v>2411400</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>0.14</v>
+        <v>0.36</v>
       </c>
       <c r="H84" t="n">
-        <v>48.22</v>
-      </c>
-      <c r="I84" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.72</v>
+      </c>
+      <c r="I84" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J84" s="9" t="n">
-        <v>2.459</v>
+        <v>1.613</v>
       </c>
       <c r="K84" s="9" t="n">
-        <v>2.367</v>
+        <v>1.709</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="14" t="inlineStr"/>
@@ -4273,40 +4275,38 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>0471</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>PIONEER</t>
         </is>
       </c>
       <c r="D85" s="9" t="n">
-        <v>7.34</v>
+        <v>0.33</v>
       </c>
       <c r="E85" s="16" t="n">
-        <v>0.005500000000000001</v>
+        <v>0.0476</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>1719100</v>
+        <v>2409200</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>0.17</v>
+        <v>0.26</v>
       </c>
       <c r="H85" t="n">
-        <v>34.85</v>
-      </c>
-      <c r="I85" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.79</v>
+      </c>
+      <c r="I85" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J85" s="9" t="n">
-        <v>7.521</v>
-      </c>
-      <c r="K85" s="9" t="n">
-        <v>8.026999999999999</v>
-      </c>
+        <v>0.305</v>
+      </c>
+      <c r="K85" s="9" t="n"/>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="14" t="inlineStr"/>
     </row>
@@ -4318,28 +4318,28 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D86" s="9" t="n">
-        <v>0.905</v>
-      </c>
-      <c r="E86" s="15" t="n">
-        <v>-0.0163</v>
+        <v>7.34</v>
+      </c>
+      <c r="E86" s="16" t="n">
+        <v>0.005500000000000001</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>1679700</v>
+        <v>2400500</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>0.2</v>
+        <v>0.23</v>
       </c>
       <c r="H86" t="n">
-        <v>46.02</v>
+        <v>34.85</v>
       </c>
       <c r="I86" s="13" t="inlineStr">
         <is>
@@ -4347,10 +4347,10 @@
         </is>
       </c>
       <c r="J86" s="9" t="n">
-        <v>0.95</v>
+        <v>7.521</v>
       </c>
       <c r="K86" s="9" t="n">
-        <v>0.837</v>
+        <v>8.026999999999999</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="14" t="inlineStr"/>
@@ -4363,39 +4363,39 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>0100</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>KPJ</t>
+          <t>ESCERAM</t>
         </is>
       </c>
       <c r="D87" s="9" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="E87" s="16" t="n">
-        <v>0.0244</v>
+        <v>0.225</v>
+      </c>
+      <c r="E87" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>1662600</v>
+        <v>2298100</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>0.31</v>
+        <v>1.34</v>
       </c>
       <c r="H87" t="n">
-        <v>42.82</v>
-      </c>
-      <c r="I87" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>74.25</v>
+      </c>
+      <c r="I87" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J87" s="9" t="n">
-        <v>2.572</v>
+        <v>0.193</v>
       </c>
       <c r="K87" s="9" t="n">
-        <v>2.75</v>
+        <v>0.186</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="14" t="inlineStr"/>
@@ -4408,28 +4408,28 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>0233</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>PEKAT</t>
         </is>
       </c>
       <c r="D88" s="9" t="n">
-        <v>0.475</v>
+        <v>2.7</v>
       </c>
       <c r="E88" s="10" t="n">
-        <v>0</v>
+        <v>-0.0722</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>1634300</v>
+        <v>2290500</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>0.21</v>
+        <v>0.7</v>
       </c>
       <c r="H88" t="n">
-        <v>29.95</v>
+        <v>56.74</v>
       </c>
       <c r="I88" s="13" t="inlineStr">
         <is>
@@ -4437,10 +4437,10 @@
         </is>
       </c>
       <c r="J88" s="9" t="n">
-        <v>0.511</v>
+        <v>2.672</v>
       </c>
       <c r="K88" s="9" t="n">
-        <v>0.5649999999999999</v>
+        <v>2.206</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="14" t="inlineStr"/>
@@ -4453,28 +4453,28 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0376</t>
+          <t>0296</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>IAB</t>
+          <t>HEGROUP</t>
         </is>
       </c>
       <c r="D89" s="9" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="E89" s="15" t="n">
-        <v>-0.008500000000000001</v>
+        <v>1.01</v>
+      </c>
+      <c r="E89" s="10" t="n">
+        <v>-0.0472</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>1626700</v>
+        <v>2266900</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>0.72</v>
+        <v>0.49</v>
       </c>
       <c r="H89" t="n">
-        <v>40.26</v>
+        <v>47.39</v>
       </c>
       <c r="I89" s="13" t="inlineStr">
         <is>
@@ -4482,10 +4482,10 @@
         </is>
       </c>
       <c r="J89" s="9" t="n">
-        <v>1.251</v>
+        <v>1.056</v>
       </c>
       <c r="K89" s="9" t="n">
-        <v>1.309</v>
+        <v>0.919</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="14" t="inlineStr"/>
@@ -4498,40 +4498,33 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>0475</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>GBBOND</t>
         </is>
       </c>
       <c r="D90" s="9" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="E90" s="16" t="n">
-        <v>0.025</v>
+        <v>0.205</v>
+      </c>
+      <c r="E90" s="10" t="n">
+        <v>-0.04650000000000001</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>1626600</v>
+        <v>2187900</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="H90" t="n">
-        <v>58.53</v>
-      </c>
-      <c r="I90" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J90" s="9" t="n">
-        <v>1.172</v>
-      </c>
-      <c r="K90" s="9" t="n">
-        <v>1.176</v>
-      </c>
+        <v>0.15</v>
+      </c>
+      <c r="I90" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J90" s="9" t="n"/>
+      <c r="K90" s="9" t="n"/>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="14" t="inlineStr"/>
     </row>
@@ -4543,39 +4536,39 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0056</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>NCT</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D91" s="9" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.775</v>
       </c>
       <c r="E91" s="10" t="n">
-        <v>0</v>
+        <v>-0.0064</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>1523700</v>
+        <v>2106800</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>0.7</v>
+        <v>0.26</v>
       </c>
       <c r="H91" t="n">
-        <v>48.27</v>
-      </c>
-      <c r="I91" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.19</v>
+      </c>
+      <c r="I91" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J91" s="9" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.779</v>
       </c>
       <c r="K91" s="9" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.773</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="14" t="inlineStr"/>
@@ -4588,28 +4581,28 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>0272</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>TTVHB</t>
         </is>
       </c>
       <c r="D92" s="9" t="n">
-        <v>2.57</v>
+        <v>0.245</v>
       </c>
       <c r="E92" s="15" t="n">
-        <v>-0.0039</v>
+        <v>0</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>1513700</v>
+        <v>2093400</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>0.24</v>
+        <v>0.9</v>
       </c>
       <c r="H92" t="n">
-        <v>46.48</v>
+        <v>47.66</v>
       </c>
       <c r="I92" s="13" t="inlineStr">
         <is>
@@ -4617,10 +4610,10 @@
         </is>
       </c>
       <c r="J92" s="9" t="n">
-        <v>2.627</v>
+        <v>0.25</v>
       </c>
       <c r="K92" s="9" t="n">
-        <v>2.597</v>
+        <v>0.255</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="14" t="inlineStr"/>
@@ -4633,39 +4626,39 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0278</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>EDELTEQ</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D93" s="9" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="E93" s="16" t="n">
-        <v>0.03700000000000001</v>
+        <v>2.42</v>
+      </c>
+      <c r="E93" s="10" t="n">
+        <v>-0.0163</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>1504400</v>
+        <v>2007500</v>
       </c>
       <c r="G93" s="12" t="n">
-        <v>0.32</v>
+        <v>0.16</v>
       </c>
       <c r="H93" t="n">
-        <v>62.11</v>
-      </c>
-      <c r="I93" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.91</v>
+      </c>
+      <c r="I93" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J93" s="9" t="n">
-        <v>0.374</v>
+        <v>2.458</v>
       </c>
       <c r="K93" s="9" t="n">
-        <v>0.354</v>
+        <v>2.367</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="14" t="inlineStr"/>
@@ -4678,28 +4671,28 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D94" s="9" t="n">
-        <v>0.425</v>
+        <v>4.33</v>
       </c>
       <c r="E94" s="16" t="n">
-        <v>0.0119</v>
+        <v>0.0023</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>1481500</v>
+        <v>1983600</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>0.22</v>
+        <v>0.31</v>
       </c>
       <c r="H94" t="n">
-        <v>50.96</v>
+        <v>47.58</v>
       </c>
       <c r="I94" s="17" t="inlineStr">
         <is>
@@ -4707,10 +4700,10 @@
         </is>
       </c>
       <c r="J94" s="9" t="n">
-        <v>0.427</v>
+        <v>4.355</v>
       </c>
       <c r="K94" s="9" t="n">
-        <v>0.415</v>
+        <v>4.441</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="14" t="inlineStr"/>
@@ -4723,39 +4716,39 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D95" s="9" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="E95" s="10" t="n">
-        <v>0</v>
+        <v>1.23</v>
+      </c>
+      <c r="E95" s="16" t="n">
+        <v>0.025</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>1481500</v>
+        <v>1790100</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>1.06</v>
+        <v>0.31</v>
       </c>
       <c r="H95" t="n">
-        <v>51.78</v>
-      </c>
-      <c r="I95" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.53</v>
+      </c>
+      <c r="I95" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J95" s="9" t="n">
-        <v>0.923</v>
+        <v>1.172</v>
       </c>
       <c r="K95" s="9" t="n">
-        <v>0.863</v>
+        <v>1.176</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="14" t="inlineStr"/>
@@ -4768,39 +4761,39 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0398</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>GDGROUP</t>
+          <t>KPJ</t>
         </is>
       </c>
       <c r="D96" s="9" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="E96" s="10" t="n">
-        <v>0</v>
+        <v>2.51</v>
+      </c>
+      <c r="E96" s="16" t="n">
+        <v>0.0203</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>1474500</v>
+        <v>1767500</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>1.65</v>
+        <v>0.33</v>
       </c>
       <c r="H96" t="n">
-        <v>57.12</v>
-      </c>
-      <c r="I96" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.94</v>
+      </c>
+      <c r="I96" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J96" s="9" t="n">
-        <v>0.381</v>
+        <v>2.571</v>
       </c>
       <c r="K96" s="9" t="n">
-        <v>0.379</v>
+        <v>2.75</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="14" t="inlineStr"/>
@@ -4813,39 +4806,39 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>TENAGA</t>
         </is>
       </c>
       <c r="D97" s="9" t="n">
-        <v>0.63</v>
+        <v>13</v>
       </c>
       <c r="E97" s="10" t="n">
-        <v>0</v>
+        <v>-0.0031</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>1465300</v>
+        <v>1758200</v>
       </c>
       <c r="G97" s="12" t="n">
-        <v>0.28</v>
+        <v>0.19</v>
       </c>
       <c r="H97" t="n">
-        <v>65.61</v>
-      </c>
-      <c r="I97" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>44.83</v>
+      </c>
+      <c r="I97" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J97" s="9" t="n">
-        <v>0.553</v>
+        <v>13.027</v>
       </c>
       <c r="K97" s="9" t="n">
-        <v>0.458</v>
+        <v>13.493</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="14" t="inlineStr"/>
@@ -4858,28 +4851,28 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>0278</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>EDELTEQ</t>
         </is>
       </c>
       <c r="D98" s="9" t="n">
-        <v>4.34</v>
+        <v>0.42</v>
       </c>
       <c r="E98" s="16" t="n">
-        <v>0.0046</v>
+        <v>0.03700000000000001</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>1463600</v>
+        <v>1734700</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>0.23</v>
+        <v>0.37</v>
       </c>
       <c r="H98" t="n">
-        <v>48.01</v>
+        <v>62.11</v>
       </c>
       <c r="I98" s="17" t="inlineStr">
         <is>
@@ -4887,10 +4880,10 @@
         </is>
       </c>
       <c r="J98" s="9" t="n">
-        <v>4.356</v>
+        <v>0.374</v>
       </c>
       <c r="K98" s="9" t="n">
-        <v>4.441</v>
+        <v>0.354</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="14" t="inlineStr"/>
@@ -4903,28 +4896,28 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>5329</t>
+          <t>0056</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>AZAMJAYA</t>
+          <t>NCT</t>
         </is>
       </c>
       <c r="D99" s="9" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="E99" s="16" t="n">
-        <v>0.0421</v>
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E99" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>1445500</v>
+        <v>1733700</v>
       </c>
       <c r="G99" s="12" t="n">
-        <v>15.94</v>
+        <v>0.79</v>
       </c>
       <c r="H99" t="n">
-        <v>54.39</v>
+        <v>48.27</v>
       </c>
       <c r="I99" s="17" t="inlineStr">
         <is>
@@ -4932,10 +4925,10 @@
         </is>
       </c>
       <c r="J99" s="9" t="n">
-        <v>0.969</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="K99" s="9" t="n">
-        <v>0.978</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="14" t="inlineStr"/>
@@ -4948,39 +4941,39 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>5337</t>
+          <t>0398</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>ECOSHOP</t>
+          <t>GDGROUP</t>
         </is>
       </c>
       <c r="D100" s="9" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="E100" s="15" t="n">
-        <v>-0.0069</v>
+        <v>0.38</v>
+      </c>
+      <c r="E100" s="10" t="n">
+        <v>-0.013</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>1400000</v>
+        <v>1731500</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>0.33</v>
+        <v>1.94</v>
       </c>
       <c r="H100" t="n">
-        <v>40.99</v>
-      </c>
-      <c r="I100" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.68</v>
+      </c>
+      <c r="I100" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J100" s="9" t="n">
-        <v>1.453</v>
+        <v>0.381</v>
       </c>
       <c r="K100" s="9" t="n">
-        <v>1.467</v>
+        <v>0.379</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="14" t="inlineStr"/>
@@ -5004,14 +4997,14 @@
       <c r="D101" s="9" t="n">
         <v>0.57</v>
       </c>
-      <c r="E101" s="15" t="n">
+      <c r="E101" s="10" t="n">
         <v>-0.0172</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>1366000</v>
+        <v>1728500</v>
       </c>
       <c r="G101" s="12" t="n">
-        <v>0.34</v>
+        <v>0.43</v>
       </c>
       <c r="H101" t="n">
         <v>40.78</v>
@@ -5038,39 +5031,39 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>0376</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>TENAGA</t>
+          <t>IAB</t>
         </is>
       </c>
       <c r="D102" s="9" t="n">
-        <v>13.04</v>
+        <v>1.16</v>
       </c>
       <c r="E102" s="10" t="n">
-        <v>0</v>
+        <v>-0.0169</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>1346200</v>
+        <v>1721900</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>0.14</v>
+        <v>0.76</v>
       </c>
       <c r="H102" t="n">
-        <v>46.5</v>
-      </c>
-      <c r="I102" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.49</v>
+      </c>
+      <c r="I102" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J102" s="9" t="n">
-        <v>13.031</v>
+        <v>1.25</v>
       </c>
       <c r="K102" s="9" t="n">
-        <v>13.494</v>
+        <v>1.308</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="14" t="inlineStr"/>
@@ -5083,28 +5076,28 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>7498</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>RALCO</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D103" s="9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="E103" s="10" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="E103" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>1301700</v>
+        <v>1704900</v>
       </c>
       <c r="G103" s="12" t="n">
-        <v>1.99</v>
+        <v>0.25</v>
       </c>
       <c r="H103" t="n">
-        <v>55.9</v>
+        <v>49.55</v>
       </c>
       <c r="I103" s="17" t="inlineStr">
         <is>
@@ -5112,10 +5105,10 @@
         </is>
       </c>
       <c r="J103" s="9" t="n">
-        <v>0.999</v>
+        <v>0.426</v>
       </c>
       <c r="K103" s="9" t="n">
-        <v>0.982</v>
+        <v>0.415</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="14" t="inlineStr"/>
@@ -5128,28 +5121,28 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D104" s="9" t="n">
-        <v>0.535</v>
-      </c>
-      <c r="E104" s="16" t="n">
-        <v>0.009399999999999999</v>
+        <v>0.63</v>
+      </c>
+      <c r="E104" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>1286700</v>
+        <v>1677400</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>0.09</v>
+        <v>0.32</v>
       </c>
       <c r="H104" t="n">
-        <v>55.88</v>
+        <v>65.61</v>
       </c>
       <c r="I104" s="13" t="inlineStr">
         <is>
@@ -5157,10 +5150,10 @@
         </is>
       </c>
       <c r="J104" s="9" t="n">
-        <v>0.519</v>
+        <v>0.553</v>
       </c>
       <c r="K104" s="9" t="n">
-        <v>0.45</v>
+        <v>0.458</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="14" t="inlineStr"/>
@@ -5173,39 +5166,39 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>0100</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>ESCERAM</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D105" s="9" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="E105" s="15" t="n">
-        <v>-0.0222</v>
+        <v>0.47</v>
+      </c>
+      <c r="E105" s="10" t="n">
+        <v>-0.0105</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>1283500</v>
+        <v>1634500</v>
       </c>
       <c r="G105" s="12" t="n">
-        <v>0.75</v>
+        <v>0.21</v>
       </c>
       <c r="H105" t="n">
-        <v>69.75</v>
-      </c>
-      <c r="I105" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>28.83</v>
+      </c>
+      <c r="I105" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J105" s="9" t="n">
-        <v>0.193</v>
+        <v>0.511</v>
       </c>
       <c r="K105" s="9" t="n">
-        <v>0.186</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="14" t="inlineStr"/>
@@ -5218,39 +5211,39 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>0291</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>CHB</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D106" s="9" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="E106" s="15" t="n">
-        <v>-0.0603</v>
+        <v>6.74</v>
+      </c>
+      <c r="E106" s="16" t="n">
+        <v>0.0369</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>1253700</v>
+        <v>1607800</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.29</v>
       </c>
       <c r="H106" t="n">
-        <v>61.35</v>
-      </c>
-      <c r="I106" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.46</v>
+      </c>
+      <c r="I106" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J106" s="9" t="n">
-        <v>2.534</v>
+        <v>6.074</v>
       </c>
       <c r="K106" s="9" t="n">
-        <v>2.212</v>
+        <v>5.86</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="14" t="inlineStr"/>
@@ -5263,39 +5256,39 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D107" s="9" t="n">
-        <v>6.68</v>
-      </c>
-      <c r="E107" s="16" t="n">
-        <v>0.0277</v>
+        <v>2.56</v>
+      </c>
+      <c r="E107" s="10" t="n">
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>1253100</v>
+        <v>1604600</v>
       </c>
       <c r="G107" s="12" t="n">
-        <v>0.23</v>
+        <v>0.26</v>
       </c>
       <c r="H107" t="n">
-        <v>60.8</v>
-      </c>
-      <c r="I107" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.83</v>
+      </c>
+      <c r="I107" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J107" s="9" t="n">
-        <v>6.068</v>
+        <v>2.626</v>
       </c>
       <c r="K107" s="9" t="n">
-        <v>5.859</v>
+        <v>2.597</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="14" t="inlineStr"/>
@@ -5308,28 +5301,28 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>5337</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>ECOSHOP</t>
         </is>
       </c>
       <c r="D108" s="9" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="E108" s="15" t="n">
-        <v>-0.0066</v>
+        <v>1.43</v>
+      </c>
+      <c r="E108" s="10" t="n">
+        <v>-0.0069</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>1249300</v>
+        <v>1498900</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>0.18</v>
+        <v>0.35</v>
       </c>
       <c r="H108" t="n">
-        <v>54.72</v>
+        <v>40.99</v>
       </c>
       <c r="I108" s="13" t="inlineStr">
         <is>
@@ -5337,10 +5330,10 @@
         </is>
       </c>
       <c r="J108" s="9" t="n">
-        <v>0.743</v>
+        <v>1.453</v>
       </c>
       <c r="K108" s="9" t="n">
-        <v>0.665</v>
+        <v>1.467</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="14" t="inlineStr"/>
@@ -5353,28 +5346,28 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>0468</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>UNIPAC</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D109" s="9" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="E109" s="15" t="n">
-        <v>-0.0213</v>
+        <v>0.74</v>
+      </c>
+      <c r="E109" s="10" t="n">
+        <v>-0.0199</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>1246800</v>
+        <v>1478800</v>
       </c>
       <c r="G109" s="12" t="n">
-        <v>0.14</v>
+        <v>0.21</v>
       </c>
       <c r="H109" t="n">
-        <v>24.97</v>
+        <v>52.84</v>
       </c>
       <c r="I109" s="13" t="inlineStr">
         <is>
@@ -5382,9 +5375,11 @@
         </is>
       </c>
       <c r="J109" s="9" t="n">
-        <v>0.257</v>
-      </c>
-      <c r="K109" s="9" t="n"/>
+        <v>0.742</v>
+      </c>
+      <c r="K109" s="9" t="n">
+        <v>0.665</v>
+      </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="14" t="inlineStr"/>
     </row>
@@ -5396,39 +5391,39 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>5329</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>AZAMJAYA</t>
         </is>
       </c>
       <c r="D110" s="9" t="n">
-        <v>0.795</v>
-      </c>
-      <c r="E110" s="10" t="n">
-        <v>0</v>
+        <v>0.99</v>
+      </c>
+      <c r="E110" s="16" t="n">
+        <v>0.0421</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>1232600</v>
+        <v>1445500</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>0.19</v>
+        <v>15.94</v>
       </c>
       <c r="H110" t="n">
-        <v>62.06</v>
-      </c>
-      <c r="I110" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.39</v>
+      </c>
+      <c r="I110" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J110" s="9" t="n">
-        <v>0.764</v>
+        <v>0.969</v>
       </c>
       <c r="K110" s="9" t="n">
-        <v>0.676</v>
+        <v>0.978</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="14" t="inlineStr"/>
@@ -5441,28 +5436,28 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>0245</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>MNHLDG</t>
         </is>
       </c>
       <c r="D111" s="9" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="E111" s="15" t="n">
-        <v>-0.0061</v>
+        <v>3.81</v>
+      </c>
+      <c r="E111" s="10" t="n">
+        <v>-0.0256</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>1204300</v>
+        <v>1397800</v>
       </c>
       <c r="G111" s="12" t="n">
-        <v>0.32</v>
+        <v>0.49</v>
       </c>
       <c r="H111" t="n">
-        <v>50.94</v>
+        <v>49.4</v>
       </c>
       <c r="I111" s="17" t="inlineStr">
         <is>
@@ -5470,10 +5465,10 @@
         </is>
       </c>
       <c r="J111" s="9" t="n">
-        <v>0.827</v>
+        <v>3.87</v>
       </c>
       <c r="K111" s="9" t="n">
-        <v>0.77</v>
+        <v>3.629</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="14" t="inlineStr"/>
@@ -5486,28 +5481,28 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>0104</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>GENETEC</t>
+          <t>DATASONIC</t>
         </is>
       </c>
       <c r="D112" s="9" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="E112" s="16" t="n">
-        <v>0.0164</v>
+        <v>0.295</v>
+      </c>
+      <c r="E112" s="10" t="n">
+        <v>-0.0167</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>1190100</v>
+        <v>1396900</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>0.19</v>
+        <v>0.11</v>
       </c>
       <c r="H112" t="n">
-        <v>43.28</v>
+        <v>51.87</v>
       </c>
       <c r="I112" s="13" t="inlineStr">
         <is>
@@ -5515,10 +5510,10 @@
         </is>
       </c>
       <c r="J112" s="9" t="n">
-        <v>0.322</v>
+        <v>0.292</v>
       </c>
       <c r="K112" s="9" t="n">
-        <v>0.338</v>
+        <v>0.282</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="14" t="inlineStr"/>
@@ -5531,28 +5526,28 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>5932</t>
+          <t>0097</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>BPURI</t>
+          <t>VITROX</t>
         </is>
       </c>
       <c r="D113" s="9" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="E113" s="15" t="n">
-        <v>-0.0233</v>
+        <v>10.68</v>
+      </c>
+      <c r="E113" s="10" t="n">
+        <v>-0.005600000000000001</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>1179600</v>
+        <v>1385300</v>
       </c>
       <c r="G113" s="12" t="n">
-        <v>2.62</v>
+        <v>0.38</v>
       </c>
       <c r="H113" t="n">
-        <v>35.94</v>
+        <v>60.31</v>
       </c>
       <c r="I113" s="13" t="inlineStr">
         <is>
@@ -5560,10 +5555,10 @@
         </is>
       </c>
       <c r="J113" s="9" t="n">
-        <v>0.225</v>
+        <v>10.399</v>
       </c>
       <c r="K113" s="9" t="n">
-        <v>0.233</v>
+        <v>9.661</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="14" t="inlineStr"/>
@@ -5585,19 +5580,19 @@
         </is>
       </c>
       <c r="D114" s="9" t="n">
-        <v>0.595</v>
+        <v>0.59</v>
       </c>
       <c r="E114" s="16" t="n">
-        <v>0.0259</v>
+        <v>0.0172</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>1175200</v>
+        <v>1368300</v>
       </c>
       <c r="G114" s="12" t="n">
-        <v>0.23</v>
+        <v>0.27</v>
       </c>
       <c r="H114" t="n">
-        <v>64.37</v>
+        <v>63.36</v>
       </c>
       <c r="I114" s="13" t="inlineStr">
         <is>
@@ -5621,28 +5616,28 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>5195</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>CENSOF</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D115" s="9" t="n">
-        <v>0.21</v>
+        <v>0.88</v>
       </c>
       <c r="E115" s="10" t="n">
-        <v>0</v>
+        <v>-0.0112</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>1146600</v>
+        <v>1357600</v>
       </c>
       <c r="G115" s="12" t="n">
-        <v>0.52</v>
+        <v>0.55</v>
       </c>
       <c r="H115" t="n">
-        <v>46.19</v>
+        <v>22.06</v>
       </c>
       <c r="I115" s="13" t="inlineStr">
         <is>
@@ -5650,10 +5645,10 @@
         </is>
       </c>
       <c r="J115" s="9" t="n">
-        <v>0.218</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="K115" s="9" t="n">
-        <v>0.208</v>
+        <v>0.983</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="14" t="inlineStr"/>
@@ -5666,39 +5661,39 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>AWC</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D116" s="9" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.305</v>
       </c>
       <c r="E116" s="15" t="n">
-        <v>-0.0072</v>
+        <v>0</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>1144200</v>
+        <v>1346600</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v>0.49</v>
+        <v>0.21</v>
       </c>
       <c r="H116" t="n">
-        <v>64.98999999999999</v>
-      </c>
-      <c r="I116" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.49</v>
+      </c>
+      <c r="I116" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J116" s="9" t="n">
-        <v>0.636</v>
+        <v>0.321</v>
       </c>
       <c r="K116" s="9" t="n">
-        <v>0.543</v>
+        <v>0.338</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="14" t="inlineStr"/>
@@ -5711,28 +5706,28 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>0291</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>CHB</t>
         </is>
       </c>
       <c r="D117" s="9" t="n">
-        <v>0.74</v>
+        <v>2.65</v>
       </c>
       <c r="E117" s="10" t="n">
-        <v>0</v>
+        <v>-0.0603</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>1121000</v>
+        <v>1342500</v>
       </c>
       <c r="G117" s="12" t="n">
-        <v>0.51</v>
+        <v>0.87</v>
       </c>
       <c r="H117" t="n">
-        <v>54.93</v>
+        <v>61.35</v>
       </c>
       <c r="I117" s="13" t="inlineStr">
         <is>
@@ -5740,10 +5735,10 @@
         </is>
       </c>
       <c r="J117" s="9" t="n">
-        <v>0.723</v>
+        <v>2.534</v>
       </c>
       <c r="K117" s="9" t="n">
-        <v>0.699</v>
+        <v>2.212</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="14" t="inlineStr"/>
@@ -5756,28 +5751,28 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D118" s="9" t="n">
-        <v>0.365</v>
-      </c>
-      <c r="E118" s="10" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="E118" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>1117200</v>
+        <v>1333600</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="H118" t="n">
-        <v>57.29</v>
+        <v>55.05</v>
       </c>
       <c r="I118" s="13" t="inlineStr">
         <is>
@@ -5785,10 +5780,10 @@
         </is>
       </c>
       <c r="J118" s="9" t="n">
-        <v>0.357</v>
+        <v>0.519</v>
       </c>
       <c r="K118" s="9" t="n">
-        <v>0.325</v>
+        <v>0.449</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="14" t="inlineStr"/>
@@ -5801,28 +5796,28 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>DATASONIC</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D119" s="9" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E119" s="15" t="n">
-        <v>-0.0167</v>
+        <v>0.8</v>
+      </c>
+      <c r="E119" s="16" t="n">
+        <v>0.0063</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>1081900</v>
+        <v>1303800</v>
       </c>
       <c r="G119" s="12" t="n">
-        <v>0.08</v>
+        <v>0.2</v>
       </c>
       <c r="H119" t="n">
-        <v>51.87</v>
+        <v>62.86</v>
       </c>
       <c r="I119" s="13" t="inlineStr">
         <is>
@@ -5830,10 +5825,10 @@
         </is>
       </c>
       <c r="J119" s="9" t="n">
-        <v>0.292</v>
+        <v>0.764</v>
       </c>
       <c r="K119" s="9" t="n">
-        <v>0.282</v>
+        <v>0.676</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="14" t="inlineStr"/>
@@ -5846,39 +5841,39 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>7498</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>MRCB</t>
+          <t>RALCO</t>
         </is>
       </c>
       <c r="D120" s="9" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="E120" s="16" t="n">
-        <v>0.0189</v>
+        <v>1.01</v>
+      </c>
+      <c r="E120" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>1033400</v>
+        <v>1301700</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>0.13</v>
+        <v>1.99</v>
       </c>
       <c r="H120" t="n">
-        <v>34.49</v>
-      </c>
-      <c r="I120" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.9</v>
+      </c>
+      <c r="I120" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J120" s="9" t="n">
-        <v>0.284</v>
+        <v>0.999</v>
       </c>
       <c r="K120" s="9" t="n">
-        <v>0.305</v>
+        <v>0.982</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="14" t="inlineStr"/>
@@ -5891,39 +5886,39 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>0373</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>VERDANT</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D121" s="9" t="n">
-        <v>0.235</v>
-      </c>
-      <c r="E121" s="15" t="n">
-        <v>-0.0408</v>
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="E121" s="10" t="n">
+        <v>-0.0121</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>1031000</v>
+        <v>1277400</v>
       </c>
       <c r="G121" s="12" t="n">
-        <v>0.21</v>
+        <v>0.34</v>
       </c>
       <c r="H121" t="n">
-        <v>45.82</v>
-      </c>
-      <c r="I121" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.04</v>
+      </c>
+      <c r="I121" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J121" s="9" t="n">
-        <v>0.249</v>
+        <v>0.827</v>
       </c>
       <c r="K121" s="9" t="n">
-        <v>0.222</v>
+        <v>0.77</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="14" t="inlineStr"/>
@@ -5936,40 +5931,38 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>7943</t>
+          <t>0468</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>GREENTEC</t>
+          <t>UNIPAC</t>
         </is>
       </c>
       <c r="D122" s="9" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="E122" s="15" t="n">
-        <v>-0.0333</v>
+        <v>0.23</v>
+      </c>
+      <c r="E122" s="10" t="n">
+        <v>-0.0213</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>1007000</v>
+        <v>1276800</v>
       </c>
       <c r="G122" s="12" t="n">
-        <v>0.92</v>
+        <v>0.14</v>
       </c>
       <c r="H122" t="n">
-        <v>66.97</v>
-      </c>
-      <c r="I122" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>24.97</v>
+      </c>
+      <c r="I122" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J122" s="9" t="n">
         <v>0.257</v>
       </c>
-      <c r="K122" s="9" t="n">
-        <v>0.211</v>
-      </c>
+      <c r="K122" s="9" t="n"/>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="14" t="inlineStr"/>
     </row>
@@ -5981,28 +5974,28 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>0146</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>MALAKOF</t>
+          <t>JFTECH</t>
         </is>
       </c>
       <c r="D123" s="9" t="n">
-        <v>0.765</v>
-      </c>
-      <c r="E123" s="15" t="n">
-        <v>-0.0129</v>
+        <v>0.75</v>
+      </c>
+      <c r="E123" s="16" t="n">
+        <v>0.0135</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>990900</v>
+        <v>1236800</v>
       </c>
       <c r="G123" s="12" t="n">
-        <v>0.23</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H123" t="n">
-        <v>42.45</v>
+        <v>56.46</v>
       </c>
       <c r="I123" s="13" t="inlineStr">
         <is>
@@ -6010,10 +6003,10 @@
         </is>
       </c>
       <c r="J123" s="9" t="n">
-        <v>0.787</v>
+        <v>0.724</v>
       </c>
       <c r="K123" s="9" t="n">
-        <v>0.804</v>
+        <v>0.699</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" s="14" t="inlineStr"/>
@@ -6026,39 +6019,39 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>5932</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>BPURI</t>
         </is>
       </c>
       <c r="D124" s="9" t="n">
-        <v>3.87</v>
-      </c>
-      <c r="E124" s="15" t="n">
-        <v>-0.0102</v>
+        <v>0.21</v>
+      </c>
+      <c r="E124" s="10" t="n">
+        <v>-0.0233</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>976800</v>
+        <v>1179600</v>
       </c>
       <c r="G124" s="12" t="n">
-        <v>0.34</v>
+        <v>2.62</v>
       </c>
       <c r="H124" t="n">
-        <v>52.8</v>
-      </c>
-      <c r="I124" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.94</v>
+      </c>
+      <c r="I124" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J124" s="9" t="n">
-        <v>3.875</v>
+        <v>0.225</v>
       </c>
       <c r="K124" s="9" t="n">
-        <v>3.63</v>
+        <v>0.233</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="14" t="inlineStr"/>
@@ -6071,39 +6064,39 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>AWC</t>
         </is>
       </c>
       <c r="D125" s="9" t="n">
-        <v>0.89</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="E125" s="10" t="n">
-        <v>0</v>
+        <v>-0.0072</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>941600</v>
+        <v>1162100</v>
       </c>
       <c r="G125" s="12" t="n">
-        <v>0.38</v>
+        <v>0.5</v>
       </c>
       <c r="H125" t="n">
-        <v>23.79</v>
-      </c>
-      <c r="I125" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.98999999999999</v>
+      </c>
+      <c r="I125" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J125" s="9" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.636</v>
       </c>
       <c r="K125" s="9" t="n">
-        <v>0.983</v>
+        <v>0.543</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="14" t="inlineStr"/>
@@ -6116,39 +6109,39 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>ATECH</t>
+          <t>MALAKOF</t>
         </is>
       </c>
       <c r="D126" s="9" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E126" s="16" t="n">
-        <v>0.0256</v>
+        <v>0.765</v>
+      </c>
+      <c r="E126" s="10" t="n">
+        <v>-0.0129</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>938500</v>
+        <v>1156800</v>
       </c>
       <c r="G126" s="12" t="n">
-        <v>0.43</v>
+        <v>0.27</v>
       </c>
       <c r="H126" t="n">
-        <v>56.99</v>
-      </c>
-      <c r="I126" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.45</v>
+      </c>
+      <c r="I126" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J126" s="9" t="n">
-        <v>0.777</v>
+        <v>0.787</v>
       </c>
       <c r="K126" s="9" t="n">
-        <v>0.765</v>
+        <v>0.804</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="14" t="inlineStr"/>
@@ -6161,28 +6154,28 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>5195</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>UWC</t>
+          <t>CENSOF</t>
         </is>
       </c>
       <c r="D127" s="9" t="n">
-        <v>7.65</v>
-      </c>
-      <c r="E127" s="10" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="E127" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>936600</v>
+        <v>1153600</v>
       </c>
       <c r="G127" s="12" t="n">
-        <v>0.23</v>
+        <v>0.52</v>
       </c>
       <c r="H127" t="n">
-        <v>61.58</v>
+        <v>46.19</v>
       </c>
       <c r="I127" s="13" t="inlineStr">
         <is>
@@ -6190,10 +6183,10 @@
         </is>
       </c>
       <c r="J127" s="9" t="n">
-        <v>7.374</v>
+        <v>0.218</v>
       </c>
       <c r="K127" s="9" t="n">
-        <v>6.846</v>
+        <v>0.208</v>
       </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" s="14" t="inlineStr"/>
@@ -6206,39 +6199,39 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>0353</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>WESTRVR</t>
         </is>
       </c>
       <c r="D128" s="9" t="n">
-        <v>1.31</v>
+        <v>0.405</v>
       </c>
       <c r="E128" s="16" t="n">
-        <v>0.0077</v>
+        <v>0.0125</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>931300</v>
+        <v>1144000</v>
       </c>
       <c r="G128" s="12" t="n">
-        <v>0.4</v>
+        <v>0.31</v>
       </c>
       <c r="H128" t="n">
-        <v>60.5</v>
-      </c>
-      <c r="I128" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.38</v>
+      </c>
+      <c r="I128" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J128" s="9" t="n">
-        <v>1.245</v>
+        <v>0.418</v>
       </c>
       <c r="K128" s="9" t="n">
-        <v>1.164</v>
+        <v>0.376</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="14" t="inlineStr"/>
@@ -6251,28 +6244,28 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>IOIPG</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D129" s="9" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="E129" s="10" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="E129" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>900600</v>
+        <v>1141800</v>
       </c>
       <c r="G129" s="12" t="n">
         <v>0.13</v>
       </c>
       <c r="H129" t="n">
-        <v>33.44</v>
+        <v>47.42</v>
       </c>
       <c r="I129" s="13" t="inlineStr">
         <is>
@@ -6280,10 +6273,10 @@
         </is>
       </c>
       <c r="J129" s="9" t="n">
-        <v>3.425</v>
+        <v>0.278</v>
       </c>
       <c r="K129" s="9" t="n">
-        <v>3.632</v>
+        <v>0.3</v>
       </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" s="14" t="inlineStr"/>
@@ -6296,28 +6289,28 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="D130" s="9" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E130" s="16" t="n">
-        <v>0.0145</v>
+        <v>0.33</v>
+      </c>
+      <c r="E130" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>870700</v>
+        <v>1120700</v>
       </c>
       <c r="G130" s="12" t="n">
-        <v>0.27</v>
+        <v>0.22</v>
       </c>
       <c r="H130" t="n">
-        <v>40.09</v>
+        <v>39.5</v>
       </c>
       <c r="I130" s="13" t="inlineStr">
         <is>
@@ -6325,10 +6318,10 @@
         </is>
       </c>
       <c r="J130" s="9" t="n">
-        <v>0.746</v>
+        <v>0.336</v>
       </c>
       <c r="K130" s="9" t="n">
-        <v>0.747</v>
+        <v>0.343</v>
       </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" s="14" t="inlineStr"/>
@@ -6341,39 +6334,39 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>0045</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>SSB8</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D131" s="9" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="E131" s="16" t="n">
-        <v>0.0156</v>
+        <v>0.365</v>
+      </c>
+      <c r="E131" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>827400</v>
+        <v>1117200</v>
       </c>
       <c r="G131" s="12" t="n">
-        <v>0.22</v>
+        <v>0.12</v>
       </c>
       <c r="H131" t="n">
-        <v>55.56</v>
-      </c>
-      <c r="I131" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>57.29</v>
+      </c>
+      <c r="I131" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J131" s="9" t="n">
-        <v>0.64</v>
+        <v>0.357</v>
       </c>
       <c r="K131" s="9" t="n">
-        <v>0.609</v>
+        <v>0.325</v>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" s="14" t="inlineStr"/>
@@ -6386,39 +6379,39 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D132" s="9" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="E132" s="15" t="n">
-        <v>-0.0092</v>
+        <v>0.27</v>
+      </c>
+      <c r="E132" s="16" t="n">
+        <v>0.0189</v>
       </c>
       <c r="F132" s="11" t="n">
-        <v>813600</v>
+        <v>1069400</v>
       </c>
       <c r="G132" s="12" t="n">
-        <v>0.2</v>
+        <v>0.13</v>
       </c>
       <c r="H132" t="n">
-        <v>57.29</v>
-      </c>
-      <c r="I132" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.49</v>
+      </c>
+      <c r="I132" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J132" s="9" t="n">
-        <v>1.043</v>
+        <v>0.284</v>
       </c>
       <c r="K132" s="9" t="n">
-        <v>0.887</v>
+        <v>0.305</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="14" t="inlineStr"/>
@@ -6431,39 +6424,39 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>MBSB</t>
+          <t>IHH</t>
         </is>
       </c>
       <c r="D133" s="9" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="E133" s="15" t="n">
-        <v>-0.0182</v>
+        <v>8.09</v>
+      </c>
+      <c r="E133" s="16" t="n">
+        <v>0.0138</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>786000</v>
+        <v>1062600</v>
       </c>
       <c r="G133" s="12" t="n">
-        <v>0.23</v>
+        <v>0.27</v>
       </c>
       <c r="H133" t="n">
-        <v>41.5</v>
-      </c>
-      <c r="I133" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.14</v>
+      </c>
+      <c r="I133" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J133" s="9" t="n">
-        <v>0.549</v>
+        <v>7.901</v>
       </c>
       <c r="K133" s="9" t="n">
-        <v>0.577</v>
+        <v>7.99</v>
       </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" s="14" t="inlineStr"/>
@@ -6476,28 +6469,28 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>0097</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>VITROX</t>
+          <t>IOIPG</t>
         </is>
       </c>
       <c r="D134" s="9" t="n">
-        <v>10.68</v>
+        <v>3.3</v>
       </c>
       <c r="E134" s="15" t="n">
-        <v>-0.005600000000000001</v>
+        <v>0</v>
       </c>
       <c r="F134" s="11" t="n">
-        <v>772400</v>
+        <v>1032600</v>
       </c>
       <c r="G134" s="12" t="n">
-        <v>0.21</v>
+        <v>0.15</v>
       </c>
       <c r="H134" t="n">
-        <v>60.31</v>
+        <v>33.44</v>
       </c>
       <c r="I134" s="13" t="inlineStr">
         <is>
@@ -6505,10 +6498,10 @@
         </is>
       </c>
       <c r="J134" s="9" t="n">
-        <v>10.399</v>
+        <v>3.425</v>
       </c>
       <c r="K134" s="9" t="n">
-        <v>9.661</v>
+        <v>3.632</v>
       </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" s="14" t="inlineStr"/>
@@ -6521,28 +6514,28 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>0373</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>VERDANT</t>
         </is>
       </c>
       <c r="D135" s="9" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="E135" s="16" t="n">
-        <v>0.0072</v>
+        <v>0.235</v>
+      </c>
+      <c r="E135" s="10" t="n">
+        <v>-0.0408</v>
       </c>
       <c r="F135" s="11" t="n">
-        <v>772000</v>
+        <v>1031000</v>
       </c>
       <c r="G135" s="12" t="n">
-        <v>0.24</v>
+        <v>0.21</v>
       </c>
       <c r="H135" t="n">
-        <v>35.93</v>
+        <v>45.82</v>
       </c>
       <c r="I135" s="13" t="inlineStr">
         <is>
@@ -6550,10 +6543,10 @@
         </is>
       </c>
       <c r="J135" s="9" t="n">
-        <v>2.933</v>
+        <v>0.249</v>
       </c>
       <c r="K135" s="9" t="n">
-        <v>3.026</v>
+        <v>0.222</v>
       </c>
       <c r="L135" t="inlineStr"/>
       <c r="M135" s="14" t="inlineStr"/>
@@ -6566,28 +6559,28 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D136" s="9" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="E136" s="10" t="n">
-        <v>0</v>
+        <v>0.695</v>
+      </c>
+      <c r="E136" s="16" t="n">
+        <v>0.0072</v>
       </c>
       <c r="F136" s="11" t="n">
-        <v>766700</v>
+        <v>1019300</v>
       </c>
       <c r="G136" s="12" t="n">
-        <v>0.16</v>
+        <v>0.32</v>
       </c>
       <c r="H136" t="n">
-        <v>42.09</v>
+        <v>38.91</v>
       </c>
       <c r="I136" s="13" t="inlineStr">
         <is>
@@ -6595,10 +6588,10 @@
         </is>
       </c>
       <c r="J136" s="9" t="n">
-        <v>1.746</v>
+        <v>0.745</v>
       </c>
       <c r="K136" s="9" t="n">
-        <v>1.774</v>
+        <v>0.747</v>
       </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" s="14" t="inlineStr"/>
@@ -6611,39 +6604,39 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>0240</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>CORAZA</t>
         </is>
       </c>
       <c r="D137" s="9" t="n">
-        <v>2.73</v>
+        <v>1.31</v>
       </c>
       <c r="E137" s="16" t="n">
-        <v>0.0111</v>
+        <v>0.0077</v>
       </c>
       <c r="F137" s="11" t="n">
-        <v>761700</v>
+        <v>1007700</v>
       </c>
       <c r="G137" s="12" t="n">
-        <v>0.15</v>
+        <v>0.43</v>
       </c>
       <c r="H137" t="n">
-        <v>40.83</v>
-      </c>
-      <c r="I137" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.5</v>
+      </c>
+      <c r="I137" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J137" s="9" t="n">
-        <v>2.909</v>
+        <v>1.245</v>
       </c>
       <c r="K137" s="9" t="n">
-        <v>2.86</v>
+        <v>1.164</v>
       </c>
       <c r="L137" t="inlineStr"/>
       <c r="M137" s="14" t="inlineStr"/>
@@ -6656,39 +6649,39 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>7943</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>GREENTEC</t>
         </is>
       </c>
       <c r="D138" s="9" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="E138" s="15" t="n">
-        <v>-0.006999999999999999</v>
+        <v>0.29</v>
+      </c>
+      <c r="E138" s="10" t="n">
+        <v>-0.0333</v>
       </c>
       <c r="F138" s="11" t="n">
-        <v>760300</v>
+        <v>1007000</v>
       </c>
       <c r="G138" s="12" t="n">
-        <v>0.08</v>
+        <v>0.92</v>
       </c>
       <c r="H138" t="n">
-        <v>56.6</v>
-      </c>
-      <c r="I138" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.97</v>
+      </c>
+      <c r="I138" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J138" s="9" t="n">
-        <v>2.799</v>
+        <v>0.257</v>
       </c>
       <c r="K138" s="9" t="n">
-        <v>2.636</v>
+        <v>0.211</v>
       </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" s="14" t="inlineStr"/>
@@ -6701,39 +6694,39 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>IHH</t>
+          <t>UWC</t>
         </is>
       </c>
       <c r="D139" s="9" t="n">
-        <v>8.109999999999999</v>
-      </c>
-      <c r="E139" s="16" t="n">
-        <v>0.0163</v>
+        <v>7.65</v>
+      </c>
+      <c r="E139" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F139" s="11" t="n">
-        <v>730600</v>
+        <v>998300</v>
       </c>
       <c r="G139" s="12" t="n">
-        <v>0.19</v>
+        <v>0.24</v>
       </c>
       <c r="H139" t="n">
-        <v>60.97</v>
-      </c>
-      <c r="I139" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>61.58</v>
+      </c>
+      <c r="I139" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J139" s="9" t="n">
-        <v>7.903</v>
+        <v>7.374</v>
       </c>
       <c r="K139" s="9" t="n">
-        <v>7.99</v>
+        <v>6.846</v>
       </c>
       <c r="L139" t="inlineStr"/>
       <c r="M139" s="14" t="inlineStr"/>
@@ -6746,39 +6739,39 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>5223</t>
+          <t>5246</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>MENTIGA</t>
+          <t>WPRTS</t>
         </is>
       </c>
       <c r="D140" s="9" t="n">
-        <v>0.8100000000000001</v>
+        <v>6.76</v>
       </c>
       <c r="E140" s="16" t="n">
-        <v>0.3966</v>
+        <v>0.004500000000000001</v>
       </c>
       <c r="F140" s="11" t="n">
-        <v>727500</v>
+        <v>996200</v>
       </c>
       <c r="G140" s="12" t="n">
-        <v>32.92</v>
+        <v>0.22</v>
       </c>
       <c r="H140" t="n">
-        <v>74.69</v>
-      </c>
-      <c r="I140" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.84</v>
+      </c>
+      <c r="I140" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J140" s="9" t="n">
-        <v>0.611</v>
+        <v>6.761</v>
       </c>
       <c r="K140" s="9" t="n">
-        <v>0.642</v>
+        <v>6.839</v>
       </c>
       <c r="L140" t="inlineStr"/>
       <c r="M140" s="14" t="inlineStr"/>
@@ -6791,39 +6784,39 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>5246</t>
+          <t>5302</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>WPRTS</t>
+          <t>ATECH</t>
         </is>
       </c>
       <c r="D141" s="9" t="n">
-        <v>6.76</v>
+        <v>0.8</v>
       </c>
       <c r="E141" s="16" t="n">
-        <v>0.004500000000000001</v>
+        <v>0.0256</v>
       </c>
       <c r="F141" s="11" t="n">
-        <v>687000</v>
+        <v>971300</v>
       </c>
       <c r="G141" s="12" t="n">
-        <v>0.15</v>
+        <v>0.44</v>
       </c>
       <c r="H141" t="n">
-        <v>49.84</v>
-      </c>
-      <c r="I141" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.99</v>
+      </c>
+      <c r="I141" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J141" s="9" t="n">
-        <v>6.761</v>
+        <v>0.777</v>
       </c>
       <c r="K141" s="9" t="n">
-        <v>6.839</v>
+        <v>0.765</v>
       </c>
       <c r="L141" t="inlineStr"/>
       <c r="M141" s="14" t="inlineStr"/>
@@ -6836,28 +6829,28 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>0128</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>SEG</t>
+          <t>FRONTKN</t>
         </is>
       </c>
       <c r="D142" s="9" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E142" s="15" t="n">
-        <v>-0.007900000000000001</v>
+        <v>5.15</v>
+      </c>
+      <c r="E142" s="16" t="n">
+        <v>0.0118</v>
       </c>
       <c r="F142" s="11" t="n">
-        <v>680000</v>
+        <v>951700</v>
       </c>
       <c r="G142" s="12" t="n">
-        <v>0.57</v>
+        <v>0.22</v>
       </c>
       <c r="H142" t="n">
-        <v>36.25</v>
+        <v>56.5</v>
       </c>
       <c r="I142" s="13" t="inlineStr">
         <is>
@@ -6865,10 +6858,10 @@
         </is>
       </c>
       <c r="J142" s="9" t="n">
-        <v>0.631</v>
+        <v>5.069</v>
       </c>
       <c r="K142" s="9" t="n">
-        <v>0.63</v>
+        <v>5.062</v>
       </c>
       <c r="L142" t="inlineStr"/>
       <c r="M142" s="14" t="inlineStr"/>
@@ -6881,28 +6874,28 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>DUFU</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D143" s="9" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="E143" s="16" t="n">
-        <v>0.0195</v>
+        <v>2.7</v>
+      </c>
+      <c r="E143" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F143" s="11" t="n">
-        <v>665800</v>
+        <v>951600</v>
       </c>
       <c r="G143" s="12" t="n">
-        <v>0.21</v>
+        <v>0.19</v>
       </c>
       <c r="H143" t="n">
-        <v>57.8</v>
+        <v>39.03</v>
       </c>
       <c r="I143" s="13" t="inlineStr">
         <is>
@@ -6910,10 +6903,10 @@
         </is>
       </c>
       <c r="J143" s="9" t="n">
-        <v>3.035</v>
+        <v>2.906</v>
       </c>
       <c r="K143" s="9" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="L143" t="inlineStr"/>
       <c r="M143" s="14" t="inlineStr"/>
@@ -6926,28 +6919,28 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>4383</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>SDG</t>
+          <t>JTIASA</t>
         </is>
       </c>
       <c r="D144" s="9" t="n">
-        <v>5.97</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E144" s="16" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.0162</v>
       </c>
       <c r="F144" s="11" t="n">
-        <v>660000</v>
+        <v>941200</v>
       </c>
       <c r="G144" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.34</v>
       </c>
       <c r="H144" t="n">
-        <v>37.65</v>
+        <v>40.19</v>
       </c>
       <c r="I144" s="13" t="inlineStr">
         <is>
@@ -6955,10 +6948,10 @@
         </is>
       </c>
       <c r="J144" s="9" t="n">
-        <v>6.107</v>
+        <v>0.957</v>
       </c>
       <c r="K144" s="9" t="n">
-        <v>6.363</v>
+        <v>1.012</v>
       </c>
       <c r="L144" t="inlineStr"/>
       <c r="M144" s="14" t="inlineStr"/>
@@ -6971,28 +6964,28 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>7160</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>PENTA</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D145" s="9" t="n">
-        <v>5.49</v>
-      </c>
-      <c r="E145" s="15" t="n">
-        <v>-0.0036</v>
+        <v>1.08</v>
+      </c>
+      <c r="E145" s="10" t="n">
+        <v>-0.0092</v>
       </c>
       <c r="F145" s="11" t="n">
-        <v>655300</v>
+        <v>926400</v>
       </c>
       <c r="G145" s="12" t="n">
-        <v>0.18</v>
+        <v>0.23</v>
       </c>
       <c r="H145" t="n">
-        <v>50.84</v>
+        <v>57.29</v>
       </c>
       <c r="I145" s="17" t="inlineStr">
         <is>
@@ -7000,10 +6993,10 @@
         </is>
       </c>
       <c r="J145" s="9" t="n">
-        <v>5.508</v>
+        <v>1.043</v>
       </c>
       <c r="K145" s="9" t="n">
-        <v>5.387</v>
+        <v>0.887</v>
       </c>
       <c r="L145" t="inlineStr"/>
       <c r="M145" s="14" t="inlineStr"/>
@@ -7016,28 +7009,28 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>4383</t>
+          <t>9059</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>JTIASA</t>
+          <t>TSH</t>
         </is>
       </c>
       <c r="D146" s="9" t="n">
-        <v>0.9350000000000001</v>
-      </c>
-      <c r="E146" s="16" t="n">
-        <v>0.0108</v>
+        <v>1.18</v>
+      </c>
+      <c r="E146" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F146" s="11" t="n">
-        <v>655200</v>
+        <v>924700</v>
       </c>
       <c r="G146" s="12" t="n">
-        <v>0.24</v>
+        <v>0.41</v>
       </c>
       <c r="H146" t="n">
-        <v>38.21</v>
+        <v>30.53</v>
       </c>
       <c r="I146" s="13" t="inlineStr">
         <is>
@@ -7045,10 +7038,10 @@
         </is>
       </c>
       <c r="J146" s="9" t="n">
-        <v>0.956</v>
+        <v>1.261</v>
       </c>
       <c r="K146" s="9" t="n">
-        <v>1.012</v>
+        <v>1.309</v>
       </c>
       <c r="L146" t="inlineStr"/>
       <c r="M146" s="14" t="inlineStr"/>
@@ -7061,28 +7054,28 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>0271</t>
+          <t>0045</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>WELLS</t>
+          <t>SSB8</t>
         </is>
       </c>
       <c r="D147" s="9" t="n">
-        <v>0.535</v>
-      </c>
-      <c r="E147" s="15" t="n">
-        <v>-0.0183</v>
+        <v>0.65</v>
+      </c>
+      <c r="E147" s="16" t="n">
+        <v>0.0156</v>
       </c>
       <c r="F147" s="11" t="n">
-        <v>607700</v>
+        <v>902400</v>
       </c>
       <c r="G147" s="12" t="n">
-        <v>0.55</v>
+        <v>0.24</v>
       </c>
       <c r="H147" t="n">
-        <v>33.07</v>
+        <v>55.56</v>
       </c>
       <c r="I147" s="17" t="inlineStr">
         <is>
@@ -7090,10 +7083,10 @@
         </is>
       </c>
       <c r="J147" s="9" t="n">
-        <v>0.573</v>
+        <v>0.64</v>
       </c>
       <c r="K147" s="9" t="n">
-        <v>0.616</v>
+        <v>0.609</v>
       </c>
       <c r="L147" t="inlineStr"/>
       <c r="M147" s="14" t="inlineStr"/>
@@ -7106,28 +7099,28 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D148" s="9" t="n">
-        <v>0.52</v>
+        <v>2.85</v>
       </c>
       <c r="E148" s="10" t="n">
-        <v>0</v>
+        <v>-0.006999999999999999</v>
       </c>
       <c r="F148" s="11" t="n">
-        <v>596500</v>
+        <v>894800</v>
       </c>
       <c r="G148" s="12" t="n">
-        <v>0.16</v>
+        <v>0.1</v>
       </c>
       <c r="H148" t="n">
-        <v>61.55</v>
+        <v>56.6</v>
       </c>
       <c r="I148" s="17" t="inlineStr">
         <is>
@@ -7135,10 +7128,10 @@
         </is>
       </c>
       <c r="J148" s="9" t="n">
-        <v>0.489</v>
+        <v>2.799</v>
       </c>
       <c r="K148" s="9" t="n">
-        <v>0.459</v>
+        <v>2.636</v>
       </c>
       <c r="L148" t="inlineStr"/>
       <c r="M148" s="14" t="inlineStr"/>
@@ -7151,28 +7144,28 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>SKYECHIP</t>
         </is>
       </c>
       <c r="D149" s="9" t="n">
-        <v>0.895</v>
-      </c>
-      <c r="E149" s="15" t="n">
-        <v>-0.011</v>
+        <v>2.77</v>
+      </c>
+      <c r="E149" s="16" t="n">
+        <v>0.0036</v>
       </c>
       <c r="F149" s="11" t="n">
-        <v>592700</v>
+        <v>864000</v>
       </c>
       <c r="G149" s="12" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="H149" t="n">
-        <v>41.46</v>
+        <v>34.92</v>
       </c>
       <c r="I149" s="13" t="inlineStr">
         <is>
@@ -7180,10 +7173,10 @@
         </is>
       </c>
       <c r="J149" s="9" t="n">
-        <v>0.909</v>
+        <v>2.932</v>
       </c>
       <c r="K149" s="9" t="n">
-        <v>0.96</v>
+        <v>3.026</v>
       </c>
       <c r="L149" t="inlineStr"/>
       <c r="M149" s="14" t="inlineStr"/>
@@ -7196,28 +7189,28 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>0151</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>KGB</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D150" s="9" t="n">
-        <v>8.49</v>
+        <v>0.865</v>
       </c>
       <c r="E150" s="15" t="n">
-        <v>-0.0012</v>
+        <v>0</v>
       </c>
       <c r="F150" s="11" t="n">
-        <v>578200</v>
+        <v>848000</v>
       </c>
       <c r="G150" s="12" t="n">
-        <v>0.25</v>
+        <v>0.27</v>
       </c>
       <c r="H150" t="n">
-        <v>44.82</v>
+        <v>51.92</v>
       </c>
       <c r="I150" s="13" t="inlineStr">
         <is>
@@ -7225,10 +7218,10 @@
         </is>
       </c>
       <c r="J150" s="9" t="n">
-        <v>8.691000000000001</v>
+        <v>0.865</v>
       </c>
       <c r="K150" s="9" t="n">
-        <v>8.698</v>
+        <v>0.859</v>
       </c>
       <c r="L150" t="inlineStr"/>
       <c r="M150" s="14" t="inlineStr"/>
@@ -7241,39 +7234,39 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D151" s="9" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="E151" s="15" t="n">
-        <v>-0.0159</v>
+        <v>0.51</v>
+      </c>
+      <c r="E151" s="10" t="n">
+        <v>-0.0192</v>
       </c>
       <c r="F151" s="11" t="n">
-        <v>569200</v>
+        <v>839400</v>
       </c>
       <c r="G151" s="12" t="n">
-        <v>0.17</v>
+        <v>0.22</v>
       </c>
       <c r="H151" t="n">
-        <v>46.99</v>
-      </c>
-      <c r="I151" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.44</v>
+      </c>
+      <c r="I151" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J151" s="9" t="n">
-        <v>1.29</v>
+        <v>0.488</v>
       </c>
       <c r="K151" s="9" t="n">
-        <v>1.213</v>
+        <v>0.458</v>
       </c>
       <c r="L151" t="inlineStr"/>
       <c r="M151" s="14" t="inlineStr"/>
@@ -7286,28 +7279,28 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>9059</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>TSH</t>
+          <t>SPSETIA</t>
         </is>
       </c>
       <c r="D152" s="9" t="n">
-        <v>1.19</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E152" s="16" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.0073</v>
       </c>
       <c r="F152" s="11" t="n">
-        <v>568100</v>
+        <v>838400</v>
       </c>
       <c r="G152" s="12" t="n">
-        <v>0.25</v>
+        <v>0.12</v>
       </c>
       <c r="H152" t="n">
-        <v>33</v>
+        <v>29.43</v>
       </c>
       <c r="I152" s="13" t="inlineStr">
         <is>
@@ -7315,10 +7308,10 @@
         </is>
       </c>
       <c r="J152" s="9" t="n">
-        <v>1.262</v>
+        <v>0.739</v>
       </c>
       <c r="K152" s="9" t="n">
-        <v>1.309</v>
+        <v>0.806</v>
       </c>
       <c r="L152" t="inlineStr"/>
       <c r="M152" s="14" t="inlineStr"/>
@@ -7331,28 +7324,28 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="D153" s="9" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E153" s="15" t="n">
-        <v>-0.0234</v>
+        <v>5.96</v>
+      </c>
+      <c r="E153" s="16" t="n">
+        <v>0.0068</v>
       </c>
       <c r="F153" s="11" t="n">
-        <v>557500</v>
+        <v>832900</v>
       </c>
       <c r="G153" s="12" t="n">
-        <v>0.21</v>
+        <v>0.09</v>
       </c>
       <c r="H153" t="n">
-        <v>46.09</v>
+        <v>36.86</v>
       </c>
       <c r="I153" s="13" t="inlineStr">
         <is>
@@ -7360,10 +7353,10 @@
         </is>
       </c>
       <c r="J153" s="9" t="n">
-        <v>0.637</v>
+        <v>6.106</v>
       </c>
       <c r="K153" s="9" t="n">
-        <v>0.617</v>
+        <v>6.362</v>
       </c>
       <c r="L153" t="inlineStr"/>
       <c r="M153" s="14" t="inlineStr"/>
@@ -7376,28 +7369,28 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>5258</t>
+          <t>5248</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>BIMB</t>
+          <t>BAUTO</t>
         </is>
       </c>
       <c r="D154" s="9" t="n">
-        <v>2.02</v>
+        <v>0.895</v>
       </c>
       <c r="E154" s="10" t="n">
-        <v>0</v>
+        <v>-0.011</v>
       </c>
       <c r="F154" s="11" t="n">
-        <v>556700</v>
+        <v>827400</v>
       </c>
       <c r="G154" s="12" t="n">
-        <v>0.71</v>
+        <v>0.53</v>
       </c>
       <c r="H154" t="n">
-        <v>37.42</v>
+        <v>38.69</v>
       </c>
       <c r="I154" s="13" t="inlineStr">
         <is>
@@ -7405,10 +7398,10 @@
         </is>
       </c>
       <c r="J154" s="9" t="n">
-        <v>2.05</v>
+        <v>0.917</v>
       </c>
       <c r="K154" s="9" t="n">
-        <v>2.09</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="L154" t="inlineStr"/>
       <c r="M154" s="14" t="inlineStr"/>
@@ -7421,39 +7414,39 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>5916</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>MSC</t>
+          <t>MBSB</t>
         </is>
       </c>
       <c r="D155" s="9" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="E155" s="16" t="n">
-        <v>0.0123</v>
+        <v>0.54</v>
+      </c>
+      <c r="E155" s="10" t="n">
+        <v>-0.0182</v>
       </c>
       <c r="F155" s="11" t="n">
-        <v>551400</v>
+        <v>807700</v>
       </c>
       <c r="G155" s="12" t="n">
-        <v>0.51</v>
+        <v>0.24</v>
       </c>
       <c r="H155" t="n">
-        <v>45.36</v>
-      </c>
-      <c r="I155" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.5</v>
+      </c>
+      <c r="I155" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J155" s="9" t="n">
-        <v>1.67</v>
+        <v>0.549</v>
       </c>
       <c r="K155" s="9" t="n">
-        <v>1.798</v>
+        <v>0.577</v>
       </c>
       <c r="L155" t="inlineStr"/>
       <c r="M155" s="14" t="inlineStr"/>
@@ -7466,28 +7459,28 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>0128</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>FRONTKN</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D156" s="9" t="n">
-        <v>5.14</v>
-      </c>
-      <c r="E156" s="16" t="n">
-        <v>0.0098</v>
+        <v>1.7</v>
+      </c>
+      <c r="E156" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F156" s="11" t="n">
-        <v>551300</v>
+        <v>787100</v>
       </c>
       <c r="G156" s="12" t="n">
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
       <c r="H156" t="n">
-        <v>55.93</v>
+        <v>42.09</v>
       </c>
       <c r="I156" s="13" t="inlineStr">
         <is>
@@ -7495,10 +7488,10 @@
         </is>
       </c>
       <c r="J156" s="9" t="n">
-        <v>5.068</v>
+        <v>1.746</v>
       </c>
       <c r="K156" s="9" t="n">
-        <v>5.062</v>
+        <v>1.774</v>
       </c>
       <c r="L156" t="inlineStr"/>
       <c r="M156" s="14" t="inlineStr"/>
@@ -7511,28 +7504,28 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>CPETECH</t>
         </is>
       </c>
       <c r="D157" s="9" t="n">
-        <v>0.95</v>
+        <v>1.22</v>
       </c>
       <c r="E157" s="10" t="n">
-        <v>0</v>
+        <v>-0.0317</v>
       </c>
       <c r="F157" s="11" t="n">
-        <v>549900</v>
+        <v>767400</v>
       </c>
       <c r="G157" s="12" t="n">
-        <v>0.14</v>
+        <v>0.23</v>
       </c>
       <c r="H157" t="n">
-        <v>31.13</v>
+        <v>45.43</v>
       </c>
       <c r="I157" s="13" t="inlineStr">
         <is>
@@ -7540,10 +7533,10 @@
         </is>
       </c>
       <c r="J157" s="9" t="n">
-        <v>0.984</v>
+        <v>1.288</v>
       </c>
       <c r="K157" s="9" t="n">
-        <v>1.062</v>
+        <v>1.213</v>
       </c>
       <c r="L157" t="inlineStr"/>
       <c r="M157" s="14" t="inlineStr"/>
@@ -7556,39 +7549,39 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>7293</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>YINSON</t>
+          <t>DUFU</t>
         </is>
       </c>
       <c r="D158" s="9" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="E158" s="10" t="n">
-        <v>0</v>
+        <v>3.1</v>
+      </c>
+      <c r="E158" s="16" t="n">
+        <v>0.006500000000000001</v>
       </c>
       <c r="F158" s="11" t="n">
-        <v>545900</v>
+        <v>766100</v>
       </c>
       <c r="G158" s="12" t="n">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="H158" t="n">
-        <v>57.62</v>
-      </c>
-      <c r="I158" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>56.22</v>
+      </c>
+      <c r="I158" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J158" s="9" t="n">
-        <v>2.103</v>
+        <v>3.031</v>
       </c>
       <c r="K158" s="9" t="n">
-        <v>2.051</v>
+        <v>2.839</v>
       </c>
       <c r="L158" t="inlineStr"/>
       <c r="M158" s="14" t="inlineStr"/>
@@ -7601,39 +7594,39 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>5223</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>DAYANG</t>
+          <t>MENTIGA</t>
         </is>
       </c>
       <c r="D159" s="9" t="n">
-        <v>1.37</v>
+        <v>0.8</v>
       </c>
       <c r="E159" s="16" t="n">
-        <v>0.0074</v>
+        <v>0.3793</v>
       </c>
       <c r="F159" s="11" t="n">
-        <v>524600</v>
+        <v>748000</v>
       </c>
       <c r="G159" s="12" t="n">
-        <v>0.24</v>
+        <v>33.85</v>
       </c>
       <c r="H159" t="n">
-        <v>33.89</v>
-      </c>
-      <c r="I159" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>74.09</v>
+      </c>
+      <c r="I159" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J159" s="9" t="n">
-        <v>1.431</v>
+        <v>0.61</v>
       </c>
       <c r="K159" s="9" t="n">
-        <v>1.481</v>
+        <v>0.642</v>
       </c>
       <c r="L159" t="inlineStr"/>
       <c r="M159" s="14" t="inlineStr"/>
@@ -7646,45 +7639,1080 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>0391</t>
+          <t>7160</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>AMBEST</t>
+          <t>PENTA</t>
         </is>
       </c>
       <c r="D160" s="9" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="E160" s="16" t="n">
-        <v>0.0308</v>
+        <v>5.44</v>
+      </c>
+      <c r="E160" s="10" t="n">
+        <v>-0.0127</v>
       </c>
       <c r="F160" s="11" t="n">
-        <v>514200</v>
+        <v>744600</v>
       </c>
       <c r="G160" s="12" t="n">
         <v>0.2</v>
       </c>
       <c r="H160" t="n">
-        <v>51.86</v>
-      </c>
-      <c r="I160" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.56</v>
+      </c>
+      <c r="I160" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J160" s="9" t="n">
-        <v>1.341</v>
+        <v>5.503</v>
       </c>
       <c r="K160" s="9" t="n">
-        <v>1.265</v>
+        <v>5.386</v>
       </c>
       <c r="L160" t="inlineStr"/>
       <c r="M160" s="14" t="inlineStr"/>
     </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>5258</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>BIMB</t>
+        </is>
+      </c>
+      <c r="D161" s="9" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="E161" s="10" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="F161" s="11" t="n">
+        <v>728100</v>
+      </c>
+      <c r="G161" s="12" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="H161" t="n">
+        <v>35.29</v>
+      </c>
+      <c r="I161" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J161" s="9" t="n">
+        <v>2.049</v>
+      </c>
+      <c r="K161" s="9" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="L161" t="inlineStr"/>
+      <c r="M161" s="14" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>0375</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>THMY</t>
+        </is>
+      </c>
+      <c r="D162" s="9" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="E162" s="16" t="n">
+        <v>0.009599999999999999</v>
+      </c>
+      <c r="F162" s="11" t="n">
+        <v>713900</v>
+      </c>
+      <c r="G162" s="12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H162" t="n">
+        <v>51.87</v>
+      </c>
+      <c r="I162" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J162" s="9" t="n">
+        <v>2.117</v>
+      </c>
+      <c r="K162" s="9" t="n">
+        <v>1.979</v>
+      </c>
+      <c r="L162" t="inlineStr"/>
+      <c r="M162" s="14" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>0391</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>AMBEST</t>
+        </is>
+      </c>
+      <c r="D163" s="9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="E163" s="16" t="n">
+        <v>0.0231</v>
+      </c>
+      <c r="F163" s="11" t="n">
+        <v>710200</v>
+      </c>
+      <c r="G163" s="12" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H163" t="n">
+        <v>50.54</v>
+      </c>
+      <c r="I163" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J163" s="9" t="n">
+        <v>1.341</v>
+      </c>
+      <c r="K163" s="9" t="n">
+        <v>1.265</v>
+      </c>
+      <c r="L163" t="inlineStr"/>
+      <c r="M163" s="14" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>0338</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>KOPI</t>
+        </is>
+      </c>
+      <c r="D164" s="9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E164" s="10" t="n">
+        <v>-0.005500000000000001</v>
+      </c>
+      <c r="F164" s="11" t="n">
+        <v>709100</v>
+      </c>
+      <c r="G164" s="12" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H164" t="n">
+        <v>43.06</v>
+      </c>
+      <c r="I164" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J164" s="9" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="K164" s="9" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="L164" t="inlineStr"/>
+      <c r="M164" s="14" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>9792</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>SEG</t>
+        </is>
+      </c>
+      <c r="D165" s="9" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="E165" s="10" t="n">
+        <v>-0.007900000000000001</v>
+      </c>
+      <c r="F165" s="11" t="n">
+        <v>680000</v>
+      </c>
+      <c r="G165" s="12" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="H165" t="n">
+        <v>36.25</v>
+      </c>
+      <c r="I165" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J165" s="9" t="n">
+        <v>0.631</v>
+      </c>
+      <c r="K165" s="9" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="L165" t="inlineStr"/>
+      <c r="M165" s="14" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>0151</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>KGB</t>
+        </is>
+      </c>
+      <c r="D166" s="9" t="n">
+        <v>8.48</v>
+      </c>
+      <c r="E166" s="10" t="n">
+        <v>-0.0024</v>
+      </c>
+      <c r="F166" s="11" t="n">
+        <v>665800</v>
+      </c>
+      <c r="G166" s="12" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H166" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="I166" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J166" s="9" t="n">
+        <v>8.69</v>
+      </c>
+      <c r="K166" s="9" t="n">
+        <v>8.698</v>
+      </c>
+      <c r="L166" t="inlineStr"/>
+      <c r="M166" s="14" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>4863</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>TM</t>
+        </is>
+      </c>
+      <c r="D167" s="9" t="n">
+        <v>7.84</v>
+      </c>
+      <c r="E167" s="10" t="n">
+        <v>-0.0076</v>
+      </c>
+      <c r="F167" s="11" t="n">
+        <v>655900</v>
+      </c>
+      <c r="G167" s="12" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H167" t="n">
+        <v>47.43</v>
+      </c>
+      <c r="I167" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J167" s="9" t="n">
+        <v>7.89</v>
+      </c>
+      <c r="K167" s="9" t="n">
+        <v>7.864</v>
+      </c>
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" s="14" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>0265</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>INFOM</t>
+        </is>
+      </c>
+      <c r="D168" s="9" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="E168" s="16" t="n">
+        <v>0.0503</v>
+      </c>
+      <c r="F168" s="11" t="n">
+        <v>654500</v>
+      </c>
+      <c r="G168" s="12" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="H168" t="n">
+        <v>71.94</v>
+      </c>
+      <c r="I168" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J168" s="9" t="n">
+        <v>1.754</v>
+      </c>
+      <c r="K168" s="9" t="n">
+        <v>1.628</v>
+      </c>
+      <c r="L168" t="inlineStr"/>
+      <c r="M168" s="14" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>5141</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>DAYANG</t>
+        </is>
+      </c>
+      <c r="D169" s="9" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="E169" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F169" s="11" t="n">
+        <v>646300</v>
+      </c>
+      <c r="G169" s="12" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H169" t="n">
+        <v>31.14</v>
+      </c>
+      <c r="I169" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J169" s="9" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="K169" s="9" t="n">
+        <v>1.481</v>
+      </c>
+      <c r="L169" t="inlineStr"/>
+      <c r="M169" s="14" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>0271</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>WELLS</t>
+        </is>
+      </c>
+      <c r="D170" s="9" t="n">
+        <v>0.535</v>
+      </c>
+      <c r="E170" s="10" t="n">
+        <v>-0.0183</v>
+      </c>
+      <c r="F170" s="11" t="n">
+        <v>607700</v>
+      </c>
+      <c r="G170" s="12" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="H170" t="n">
+        <v>33.07</v>
+      </c>
+      <c r="I170" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J170" s="9" t="n">
+        <v>0.573</v>
+      </c>
+      <c r="K170" s="9" t="n">
+        <v>0.616</v>
+      </c>
+      <c r="L170" t="inlineStr"/>
+      <c r="M170" s="14" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>8583</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>MAHSING</t>
+        </is>
+      </c>
+      <c r="D171" s="9" t="n">
+        <v>0.945</v>
+      </c>
+      <c r="E171" s="10" t="n">
+        <v>-0.0053</v>
+      </c>
+      <c r="F171" s="11" t="n">
+        <v>595500</v>
+      </c>
+      <c r="G171" s="12" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H171" t="n">
+        <v>30.03</v>
+      </c>
+      <c r="I171" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J171" s="9" t="n">
+        <v>0.984</v>
+      </c>
+      <c r="K171" s="9" t="n">
+        <v>1.062</v>
+      </c>
+      <c r="L171" t="inlineStr"/>
+      <c r="M171" s="14" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>6947</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>CDB</t>
+        </is>
+      </c>
+      <c r="D172" s="9" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="E172" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F172" s="11" t="n">
+        <v>571500</v>
+      </c>
+      <c r="G172" s="12" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H172" t="n">
+        <v>39.69</v>
+      </c>
+      <c r="I172" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J172" s="9" t="n">
+        <v>2.569</v>
+      </c>
+      <c r="K172" s="9" t="n">
+        <v>2.708</v>
+      </c>
+      <c r="L172" t="inlineStr"/>
+      <c r="M172" s="14" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>5326</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>99SMART</t>
+        </is>
+      </c>
+      <c r="D173" s="9" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="E173" s="10" t="n">
+        <v>-0.0032</v>
+      </c>
+      <c r="F173" s="11" t="n">
+        <v>571200</v>
+      </c>
+      <c r="G173" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H173" t="n">
+        <v>38.11</v>
+      </c>
+      <c r="I173" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J173" s="9" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="K173" s="9" t="n">
+        <v>3.359</v>
+      </c>
+      <c r="L173" t="inlineStr"/>
+      <c r="M173" s="14" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>0112</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>MIKROMB</t>
+        </is>
+      </c>
+      <c r="D174" s="9" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="E174" s="10" t="n">
+        <v>-0.0234</v>
+      </c>
+      <c r="F174" s="11" t="n">
+        <v>568000</v>
+      </c>
+      <c r="G174" s="12" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H174" t="n">
+        <v>46.09</v>
+      </c>
+      <c r="I174" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J174" s="9" t="n">
+        <v>0.637</v>
+      </c>
+      <c r="K174" s="9" t="n">
+        <v>0.617</v>
+      </c>
+      <c r="L174" t="inlineStr"/>
+      <c r="M174" s="14" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>5916</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>MSC</t>
+        </is>
+      </c>
+      <c r="D175" s="9" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="E175" s="16" t="n">
+        <v>0.0123</v>
+      </c>
+      <c r="F175" s="11" t="n">
+        <v>562500</v>
+      </c>
+      <c r="G175" s="12" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="H175" t="n">
+        <v>45.36</v>
+      </c>
+      <c r="I175" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J175" s="9" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="K175" s="9" t="n">
+        <v>1.798</v>
+      </c>
+      <c r="L175" t="inlineStr"/>
+      <c r="M175" s="14" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>7293</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>YINSON</t>
+        </is>
+      </c>
+      <c r="D176" s="9" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="E176" s="16" t="n">
+        <v>0.004699999999999999</v>
+      </c>
+      <c r="F176" s="11" t="n">
+        <v>560500</v>
+      </c>
+      <c r="G176" s="12" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H176" t="n">
+        <v>58.6</v>
+      </c>
+      <c r="I176" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J176" s="9" t="n">
+        <v>2.104</v>
+      </c>
+      <c r="K176" s="9" t="n">
+        <v>2.051</v>
+      </c>
+      <c r="L176" t="inlineStr"/>
+      <c r="M176" s="14" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>7174</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>CAB</t>
+        </is>
+      </c>
+      <c r="D177" s="9" t="n">
+        <v>0.585</v>
+      </c>
+      <c r="E177" s="10" t="n">
+        <v>-0.008500000000000001</v>
+      </c>
+      <c r="F177" s="11" t="n">
+        <v>557300</v>
+      </c>
+      <c r="G177" s="12" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="H177" t="n">
+        <v>55</v>
+      </c>
+      <c r="I177" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J177" s="9" t="n">
+        <v>0.582</v>
+      </c>
+      <c r="K177" s="9" t="n">
+        <v>0.545</v>
+      </c>
+      <c r="L177" t="inlineStr"/>
+      <c r="M177" s="14" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>5053</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>OSK</t>
+        </is>
+      </c>
+      <c r="D178" s="9" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="E178" s="16" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="F178" s="11" t="n">
+        <v>540200</v>
+      </c>
+      <c r="G178" s="12" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="H178" t="n">
+        <v>34.85</v>
+      </c>
+      <c r="I178" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J178" s="9" t="n">
+        <v>1.755</v>
+      </c>
+      <c r="K178" s="9" t="n">
+        <v>1.902</v>
+      </c>
+      <c r="L178" t="inlineStr"/>
+      <c r="M178" s="14" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>5211</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>SUNWAY</t>
+        </is>
+      </c>
+      <c r="D179" s="9" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="E179" s="16" t="n">
+        <v>0.0114</v>
+      </c>
+      <c r="F179" s="11" t="n">
+        <v>536100</v>
+      </c>
+      <c r="G179" s="12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H179" t="n">
+        <v>44.36</v>
+      </c>
+      <c r="I179" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J179" s="9" t="n">
+        <v>4.475</v>
+      </c>
+      <c r="K179" s="9" t="n">
+        <v>4.774</v>
+      </c>
+      <c r="L179" t="inlineStr"/>
+      <c r="M179" s="14" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>5331</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>PGLOBAL</t>
+        </is>
+      </c>
+      <c r="D180" s="9" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="E180" s="10" t="n">
+        <v>-0.024</v>
+      </c>
+      <c r="F180" s="11" t="n">
+        <v>532700</v>
+      </c>
+      <c r="G180" s="12" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="H180" t="n">
+        <v>71.29000000000001</v>
+      </c>
+      <c r="I180" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J180" s="9" t="n">
+        <v>0.5610000000000001</v>
+      </c>
+      <c r="K180" s="9" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="L180" t="inlineStr"/>
+      <c r="M180" s="14" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>0249</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>LGMS</t>
+        </is>
+      </c>
+      <c r="D181" s="9" t="n">
+        <v>0.535</v>
+      </c>
+      <c r="E181" s="10" t="n">
+        <v>-0.009300000000000001</v>
+      </c>
+      <c r="F181" s="11" t="n">
+        <v>523300</v>
+      </c>
+      <c r="G181" s="12" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="H181" t="n">
+        <v>55.22</v>
+      </c>
+      <c r="I181" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J181" s="9" t="n">
+        <v>0.528</v>
+      </c>
+      <c r="K181" s="9" t="n">
+        <v>0.506</v>
+      </c>
+      <c r="L181" t="inlineStr"/>
+      <c r="M181" s="14" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>5162</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>VSTECS</t>
+        </is>
+      </c>
+      <c r="D182" s="9" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="E182" s="10" t="n">
+        <v>-0.0063</v>
+      </c>
+      <c r="F182" s="11" t="n">
+        <v>518200</v>
+      </c>
+      <c r="G182" s="12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H182" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="I182" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J182" s="9" t="n">
+        <v>1.652</v>
+      </c>
+      <c r="K182" s="9" t="n">
+        <v>1.674</v>
+      </c>
+      <c r="L182" t="inlineStr"/>
+      <c r="M182" s="14" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>5176</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>SUNREIT</t>
+        </is>
+      </c>
+      <c r="D183" s="9" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="E183" s="16" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F183" s="11" t="n">
+        <v>503100</v>
+      </c>
+      <c r="G183" s="12" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H183" t="n">
+        <v>43.54</v>
+      </c>
+      <c r="I183" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J183" s="9" t="n">
+        <v>2.049</v>
+      </c>
+      <c r="K183" s="9" t="n">
+        <v>2.077</v>
+      </c>
+      <c r="L183" t="inlineStr"/>
+      <c r="M183" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M160"/>
+  <autoFilter ref="A1:M183"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-14/bursa-report-2026-10-14.xlsx
+++ b/docs/downloads/2026-10-14/bursa-report-2026-10-14.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-14" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-14'!$A$1:$M$183</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-14'!$A$1:$M$193</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M183"/>
+  <dimension ref="A1:M193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -572,10 +572,10 @@
         <v>0.027</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>3793900</v>
+        <v>4002200</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.99</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>58.07</v>
@@ -598,7 +598,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>现价RM 2.28高于50日均线RM 2.145，RSI 58.07处中性偏上区间，未超买，SAR转多信号技术面尚属合理。</t>
+          <t>SAR转多信号，RSI 58.07未超买，现价高于50日均线约6.3%，技术面信号偏可靠。</t>
         </is>
       </c>
     </row>
@@ -625,10 +625,10 @@
         <v>-0.1538</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>156858900</v>
+        <v>208537800</v>
       </c>
       <c r="G3" s="12" t="n">
-        <v>0.36</v>
+        <v>0.47</v>
       </c>
       <c r="H3" t="n">
         <v>20.87</v>
@@ -664,13 +664,13 @@
         </is>
       </c>
       <c r="D4" s="9" t="n">
-        <v>0.845</v>
+        <v>0.795</v>
       </c>
       <c r="E4" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>149255300</v>
+        <v>158942400</v>
       </c>
       <c r="G4" s="12" t="n"/>
       <c r="I4" s="13" t="inlineStr">
@@ -706,10 +706,10 @@
         <v>-0.0333</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>59737600</v>
+        <v>61449700</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>0.85</v>
+        <v>0.88</v>
       </c>
       <c r="H5" t="n">
         <v>43.8</v>
@@ -745,19 +745,19 @@
         </is>
       </c>
       <c r="D6" s="9" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="E6" s="16" t="n">
-        <v>0.0292</v>
+        <v>0.0409</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>43844600</v>
+        <v>50631900</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>0.67</v>
+        <v>0.78</v>
       </c>
       <c r="H6" t="n">
-        <v>65.40000000000001</v>
+        <v>66.39</v>
       </c>
       <c r="I6" s="17" t="inlineStr">
         <is>
@@ -765,7 +765,7 @@
         </is>
       </c>
       <c r="J6" s="9" t="n">
-        <v>0.8</v>
+        <v>0.801</v>
       </c>
       <c r="K6" s="9" t="n">
         <v>0.721</v>
@@ -796,10 +796,10 @@
         <v>0.0385</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>39881900</v>
+        <v>42730000</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="H7" t="n">
         <v>73.73999999999999</v>
@@ -826,28 +826,28 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>0095</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>0.34</v>
+        <v>0.155</v>
       </c>
       <c r="E8" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>30313500</v>
+        <v>36069100</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>0.42</v>
+        <v>1.07</v>
       </c>
       <c r="H8" t="n">
-        <v>71.22</v>
+        <v>48.61</v>
       </c>
       <c r="I8" s="17" t="inlineStr">
         <is>
@@ -855,10 +855,10 @@
         </is>
       </c>
       <c r="J8" s="9" t="n">
-        <v>0.294</v>
+        <v>0.155</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>0.251</v>
+        <v>0.157</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="14" t="inlineStr"/>
@@ -871,28 +871,28 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0095</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MAG</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="E9" s="15" t="n">
-        <v>0</v>
+        <v>0.335</v>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>-0.0147</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>21685000</v>
+        <v>30707700</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>0.64</v>
+        <v>0.43</v>
       </c>
       <c r="H9" t="n">
-        <v>48.61</v>
+        <v>68.87</v>
       </c>
       <c r="I9" s="17" t="inlineStr">
         <is>
@@ -900,10 +900,10 @@
         </is>
       </c>
       <c r="J9" s="9" t="n">
-        <v>0.155</v>
+        <v>0.293</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>0.157</v>
+        <v>0.251</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="14" t="inlineStr"/>
@@ -931,10 +931,10 @@
         <v>-0.0208</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>18031400</v>
+        <v>22134100</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>1.98</v>
+        <v>2.43</v>
       </c>
       <c r="H10" t="n">
         <v>18.65</v>
@@ -961,39 +961,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>7020</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ASTEEL</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>0.105</v>
-      </c>
-      <c r="E11" s="16" t="n">
-        <v>0.05</v>
+        <v>0.47</v>
+      </c>
+      <c r="E11" s="10" t="n">
+        <v>-0.0105</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>16010800</v>
+        <v>16294600</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>5.84</v>
+        <v>0.46</v>
       </c>
       <c r="H11" t="n">
-        <v>57.96</v>
-      </c>
-      <c r="I11" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.59</v>
+      </c>
+      <c r="I11" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J11" s="9" t="n">
-        <v>0.097</v>
+        <v>0.489</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.482</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="14" t="inlineStr"/>
@@ -1006,39 +1006,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>7020</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>ASTEEL</t>
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="E12" s="10" t="n">
-        <v>-0.0105</v>
+        <v>0.105</v>
+      </c>
+      <c r="E12" s="16" t="n">
+        <v>0.05</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>15996200</v>
+        <v>16252600</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>0.45</v>
+        <v>5.93</v>
       </c>
       <c r="H12" t="n">
-        <v>44.59</v>
-      </c>
-      <c r="I12" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.96</v>
+      </c>
+      <c r="I12" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J12" s="9" t="n">
-        <v>0.489</v>
+        <v>0.097</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>0.482</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="14" t="inlineStr"/>
@@ -1060,19 +1060,19 @@
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>3.87</v>
+        <v>3.89</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>-0.0561</v>
+        <v>-0.0512</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>13189000</v>
+        <v>14154700</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>1.49</v>
+        <v>1.6</v>
       </c>
       <c r="H13" t="n">
-        <v>49.31</v>
+        <v>49.97</v>
       </c>
       <c r="I13" s="13" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         </is>
       </c>
       <c r="J13" s="9" t="n">
-        <v>3.988</v>
+        <v>3.99</v>
       </c>
       <c r="K13" s="9" t="n">
         <v>3.507</v>
@@ -1111,7 +1111,7 @@
         <v>0</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>12821000</v>
+        <v>12866600</v>
       </c>
       <c r="G14" s="12" t="n">
         <v>0.51</v>
@@ -1150,19 +1150,19 @@
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>0.735</v>
+        <v>0.73</v>
       </c>
       <c r="E15" s="10" t="n">
-        <v>-0.08699999999999999</v>
+        <v>-0.09320000000000001</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>12046700</v>
+        <v>12692700</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>0.85</v>
+        <v>0.89</v>
       </c>
       <c r="H15" t="n">
-        <v>46.36</v>
+        <v>45.71</v>
       </c>
       <c r="I15" s="13" t="inlineStr">
         <is>
@@ -1170,10 +1170,10 @@
         </is>
       </c>
       <c r="J15" s="9" t="n">
-        <v>0.771</v>
+        <v>0.77</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>0.721</v>
+        <v>0.72</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="14" t="inlineStr"/>
@@ -1195,19 +1195,19 @@
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="E16" s="15" t="n">
-        <v>0</v>
+        <v>2.09</v>
+      </c>
+      <c r="E16" s="16" t="n">
+        <v>0.0146</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>11870200</v>
+        <v>12343200</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="H16" t="n">
-        <v>62.88</v>
+        <v>64.08</v>
       </c>
       <c r="I16" s="17" t="inlineStr">
         <is>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="J16" s="9" t="n">
-        <v>1.899</v>
+        <v>1.902</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>1.697</v>
+        <v>1.698</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="14" t="inlineStr"/>
@@ -1246,10 +1246,10 @@
         <v>0.023</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>11641100</v>
+        <v>12101500</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
       <c r="H17" t="n">
         <v>61.25</v>
@@ -1291,10 +1291,10 @@
         <v>0</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>10642400</v>
+        <v>11667300</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>0.55</v>
+        <v>0.6</v>
       </c>
       <c r="H18" t="n">
         <v>61.97</v>
@@ -1330,19 +1330,19 @@
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>7.59</v>
+        <v>7.6</v>
       </c>
       <c r="E19" s="16" t="n">
-        <v>0.012</v>
+        <v>0.0133</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>9561700</v>
+        <v>10937600</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>0.65</v>
+        <v>0.74</v>
       </c>
       <c r="H19" t="n">
-        <v>48.47</v>
+        <v>48.88</v>
       </c>
       <c r="I19" s="17" t="inlineStr">
         <is>
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="J19" s="9" t="n">
-        <v>7.597</v>
+        <v>7.598</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>7.718</v>
+        <v>7.719</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="14" t="inlineStr"/>
@@ -1366,28 +1366,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E20" s="15" t="n">
-        <v>0</v>
+        <v>0.865</v>
+      </c>
+      <c r="E20" s="10" t="n">
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>8831700</v>
+        <v>10679500</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="H20" t="n">
-        <v>50.46</v>
+        <v>46.29</v>
       </c>
       <c r="I20" s="17" t="inlineStr">
         <is>
@@ -1395,10 +1395,10 @@
         </is>
       </c>
       <c r="J20" s="9" t="n">
-        <v>0.774</v>
+        <v>0.868</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>0.775</v>
+        <v>0.869</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="14" t="inlineStr"/>
@@ -1426,10 +1426,10 @@
         <v>0.125</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>8768500</v>
+        <v>10178900</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>0.63</v>
+        <v>0.73</v>
       </c>
       <c r="H21" t="n">
         <v>38.83</v>
@@ -1456,28 +1456,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>0.62</v>
+        <v>0.775</v>
       </c>
       <c r="E22" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>7666000</v>
+        <v>9253500</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>0.72</v>
+        <v>0.61</v>
       </c>
       <c r="H22" t="n">
-        <v>54.39</v>
+        <v>50.46</v>
       </c>
       <c r="I22" s="17" t="inlineStr">
         <is>
@@ -1485,10 +1485,10 @@
         </is>
       </c>
       <c r="J22" s="9" t="n">
-        <v>0.614</v>
+        <v>0.774</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>0.613</v>
+        <v>0.775</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="14" t="inlineStr"/>
@@ -1501,28 +1501,28 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E23" s="10" t="n">
-        <v>-0.005699999999999999</v>
+        <v>0.62</v>
+      </c>
+      <c r="E23" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>7663800</v>
+        <v>8809400</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>0.39</v>
+        <v>0.82</v>
       </c>
       <c r="H23" t="n">
-        <v>46.29</v>
+        <v>54.39</v>
       </c>
       <c r="I23" s="17" t="inlineStr">
         <is>
@@ -1530,10 +1530,10 @@
         </is>
       </c>
       <c r="J23" s="9" t="n">
-        <v>0.868</v>
+        <v>0.614</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>0.869</v>
+        <v>0.613</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="14" t="inlineStr"/>
@@ -1546,28 +1546,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="E24" s="16" t="n">
-        <v>0.027</v>
+        <v>0.4</v>
+      </c>
+      <c r="E24" s="10" t="n">
+        <v>-0.0123</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>7649600</v>
+        <v>8316700</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>1.08</v>
+        <v>0.66</v>
       </c>
       <c r="H24" t="n">
-        <v>61.86</v>
+        <v>54.4</v>
       </c>
       <c r="I24" s="17" t="inlineStr">
         <is>
@@ -1575,10 +1575,10 @@
         </is>
       </c>
       <c r="J24" s="9" t="n">
-        <v>0.37</v>
+        <v>0.389</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>0.369</v>
+        <v>0.377</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="14" t="inlineStr"/>
@@ -1591,39 +1591,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>7079</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>TWL</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>0.025</v>
+        <v>0.38</v>
       </c>
       <c r="E25" s="16" t="n">
-        <v>0.25</v>
+        <v>0.027</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>7414600</v>
+        <v>7652300</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>0.42</v>
+        <v>1.08</v>
       </c>
       <c r="H25" t="n">
-        <v>51.85</v>
-      </c>
-      <c r="I25" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.86</v>
+      </c>
+      <c r="I25" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J25" s="9" t="n">
-        <v>0.024</v>
+        <v>0.37</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>0.025</v>
+        <v>0.369</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="14" t="inlineStr"/>
@@ -1636,28 +1636,28 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>9377</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>FSBM</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="E26" s="16" t="n">
-        <v>0.0588</v>
+        <v>2.69</v>
+      </c>
+      <c r="E26" s="10" t="n">
+        <v>-0.0074</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>6901100</v>
+        <v>7632800</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>0.32</v>
+        <v>0.42</v>
       </c>
       <c r="H26" t="n">
-        <v>37.74</v>
+        <v>54.42</v>
       </c>
       <c r="I26" s="17" t="inlineStr">
         <is>
@@ -1665,10 +1665,10 @@
         </is>
       </c>
       <c r="J26" s="9" t="n">
-        <v>0.103</v>
+        <v>2.657</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>0.142</v>
+        <v>2.533</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="14" t="inlineStr"/>
@@ -1690,19 +1690,19 @@
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>0.35</v>
+        <v>0.355</v>
       </c>
       <c r="E27" s="10" t="n">
-        <v>-0.0278</v>
+        <v>-0.0139</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>6874600</v>
+        <v>7550400</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.88</v>
       </c>
       <c r="H27" t="n">
-        <v>53.1</v>
+        <v>55.26</v>
       </c>
       <c r="I27" s="13" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         </is>
       </c>
       <c r="J27" s="9" t="n">
-        <v>0.348</v>
+        <v>0.349</v>
       </c>
       <c r="K27" s="9" t="n">
         <v>0.33</v>
@@ -1726,40 +1726,33 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>0476</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>IOICORP</t>
+          <t>SLG</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>4.56</v>
+        <v>0.25</v>
       </c>
       <c r="E28" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>6841000</v>
+        <v>7532700</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="H28" t="n">
-        <v>40.09</v>
-      </c>
-      <c r="I28" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J28" s="9" t="n">
-        <v>4.645</v>
-      </c>
-      <c r="K28" s="9" t="n">
-        <v>4.63</v>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="I28" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J28" s="9" t="n"/>
+      <c r="K28" s="9" t="n"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="14" t="inlineStr"/>
     </row>
@@ -1771,39 +1764,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>7079</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>TWL</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E29" s="10" t="n">
-        <v>-0.0123</v>
+        <v>0.025</v>
+      </c>
+      <c r="E29" s="16" t="n">
+        <v>0.25</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>6810200</v>
+        <v>7414600</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0.54</v>
+        <v>0.42</v>
       </c>
       <c r="H29" t="n">
-        <v>54.4</v>
-      </c>
-      <c r="I29" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.85</v>
+      </c>
+      <c r="I29" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J29" s="9" t="n">
-        <v>0.389</v>
+        <v>0.024</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>0.377</v>
+        <v>0.025</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="14" t="inlineStr"/>
@@ -1816,33 +1809,40 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0476</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>SLG</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>0.25</v>
+        <v>0.82</v>
       </c>
       <c r="E30" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>6776700</v>
+        <v>7377000</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>0.23</v>
+        <v>0.45</v>
+      </c>
+      <c r="H30" t="n">
+        <v>58.27</v>
       </c>
       <c r="I30" s="17" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J30" s="9" t="n"/>
-      <c r="K30" s="9" t="n"/>
+      <c r="J30" s="9" t="n">
+        <v>0.8129999999999999</v>
+      </c>
+      <c r="K30" s="9" t="n">
+        <v>0.8080000000000001</v>
+      </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="14" t="inlineStr"/>
     </row>
@@ -1854,39 +1854,39 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>IOICORP</t>
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="E31" s="10" t="n">
-        <v>-0.0111</v>
+        <v>4.57</v>
+      </c>
+      <c r="E31" s="16" t="n">
+        <v>0.0022</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>6731400</v>
+        <v>7175700</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>0.37</v>
+        <v>0.75</v>
       </c>
       <c r="H31" t="n">
-        <v>53.71</v>
-      </c>
-      <c r="I31" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.31</v>
+      </c>
+      <c r="I31" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J31" s="9" t="n">
-        <v>2.656</v>
+        <v>4.646</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>2.533</v>
+        <v>4.63</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="14" t="inlineStr"/>
@@ -1899,39 +1899,39 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>9377</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>FSBM</t>
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>0.175</v>
-      </c>
-      <c r="E32" s="10" t="n">
-        <v>-0.0278</v>
+        <v>0.09</v>
+      </c>
+      <c r="E32" s="16" t="n">
+        <v>0.0588</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>6636200</v>
+        <v>7051100</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>0.28</v>
+        <v>0.33</v>
       </c>
       <c r="H32" t="n">
-        <v>40.7</v>
-      </c>
-      <c r="I32" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>37.74</v>
+      </c>
+      <c r="I32" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J32" s="9" t="n">
-        <v>0.192</v>
+        <v>0.103</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>0.185</v>
+        <v>0.142</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="14" t="inlineStr"/>
@@ -1944,28 +1944,28 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="E33" s="15" t="n">
-        <v>0</v>
+        <v>4.75</v>
+      </c>
+      <c r="E33" s="16" t="n">
+        <v>0.0106</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>6618800</v>
+        <v>6975500</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="H33" t="n">
-        <v>58.27</v>
+        <v>50.43</v>
       </c>
       <c r="I33" s="17" t="inlineStr">
         <is>
@@ -1973,10 +1973,10 @@
         </is>
       </c>
       <c r="J33" s="9" t="n">
-        <v>0.8129999999999999</v>
+        <v>4.718</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>0.8080000000000001</v>
+        <v>4.87</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="14" t="inlineStr"/>
@@ -1989,28 +1989,28 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>AVANGAAD</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E34" s="15" t="n">
-        <v>0</v>
+        <v>0.175</v>
+      </c>
+      <c r="E34" s="10" t="n">
+        <v>-0.0278</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>6462700</v>
+        <v>6763600</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>2.28</v>
+        <v>0.29</v>
       </c>
       <c r="H34" t="n">
-        <v>49.15</v>
+        <v>40.7</v>
       </c>
       <c r="I34" s="13" t="inlineStr">
         <is>
@@ -2018,10 +2018,10 @@
         </is>
       </c>
       <c r="J34" s="9" t="n">
-        <v>0.295</v>
+        <v>0.192</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>0.296</v>
+        <v>0.185</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="14" t="inlineStr"/>
@@ -2034,28 +2034,28 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0034</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>MMAG</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="E35" s="10" t="n">
-        <v>-0.2</v>
+        <v>1.93</v>
+      </c>
+      <c r="E35" s="16" t="n">
+        <v>0.0052</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>6236300</v>
+        <v>6653800</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>1.44</v>
+        <v>1.13</v>
       </c>
       <c r="H35" t="n">
-        <v>44.58</v>
+        <v>49.36</v>
       </c>
       <c r="I35" s="17" t="inlineStr">
         <is>
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="J35" s="9" t="n">
-        <v>0.024</v>
+        <v>1.926</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>0.026</v>
+        <v>1.954</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="14" t="inlineStr"/>
@@ -2079,39 +2079,39 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="E36" s="16" t="n">
-        <v>0.0104</v>
+        <v>0.295</v>
+      </c>
+      <c r="E36" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>6158600</v>
+        <v>6462700</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>1.05</v>
+        <v>2.28</v>
       </c>
       <c r="H36" t="n">
-        <v>51.08</v>
-      </c>
-      <c r="I36" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.15</v>
+      </c>
+      <c r="I36" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J36" s="9" t="n">
-        <v>1.927</v>
+        <v>0.295</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>1.954</v>
+        <v>0.296</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="14" t="inlineStr"/>
@@ -2133,19 +2133,19 @@
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="E37" s="10" t="n">
-        <v>-0.08789999999999999</v>
+        <v>-0.08470000000000001</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>5935400</v>
+        <v>6349200</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="H37" t="n">
-        <v>56.45</v>
+        <v>56.85</v>
       </c>
       <c r="I37" s="13" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         </is>
       </c>
       <c r="J37" s="9" t="n">
-        <v>2.763</v>
+        <v>2.764</v>
       </c>
       <c r="K37" s="9" t="n">
         <v>2.132</v>
@@ -2169,28 +2169,28 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>0034</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>MMAG</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="E38" s="16" t="n">
-        <v>0.0106</v>
+        <v>0.02</v>
+      </c>
+      <c r="E38" s="10" t="n">
+        <v>-0.2</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>5789100</v>
+        <v>6236300</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>0.34</v>
+        <v>1.44</v>
       </c>
       <c r="H38" t="n">
-        <v>50.43</v>
+        <v>44.58</v>
       </c>
       <c r="I38" s="17" t="inlineStr">
         <is>
@@ -2198,10 +2198,10 @@
         </is>
       </c>
       <c r="J38" s="9" t="n">
-        <v>4.718</v>
+        <v>0.024</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>4.87</v>
+        <v>0.026</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="14" t="inlineStr"/>
@@ -2214,28 +2214,28 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>4.89</v>
-      </c>
-      <c r="E39" s="10" t="n">
-        <v>-0.0121</v>
+        <v>1.09</v>
+      </c>
+      <c r="E39" s="16" t="n">
+        <v>0.0283</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>5660200</v>
+        <v>6117400</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>0.22</v>
+        <v>0.62</v>
       </c>
       <c r="H39" t="n">
-        <v>50.37</v>
+        <v>53.79</v>
       </c>
       <c r="I39" s="13" t="inlineStr">
         <is>
@@ -2243,10 +2243,10 @@
         </is>
       </c>
       <c r="J39" s="9" t="n">
-        <v>4.932</v>
+        <v>1.07</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>4.697</v>
+        <v>1.04</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="14" t="inlineStr"/>
@@ -2259,28 +2259,28 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="E40" s="16" t="n">
-        <v>0.008</v>
+        <v>4.87</v>
+      </c>
+      <c r="E40" s="10" t="n">
+        <v>-0.0162</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>5574100</v>
+        <v>6061000</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.24</v>
       </c>
       <c r="H40" t="n">
-        <v>41.98</v>
+        <v>49.38</v>
       </c>
       <c r="I40" s="13" t="inlineStr">
         <is>
@@ -2288,10 +2288,10 @@
         </is>
       </c>
       <c r="J40" s="9" t="n">
-        <v>1.31</v>
+        <v>4.93</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>1.311</v>
+        <v>4.697</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="14" t="inlineStr"/>
@@ -2304,39 +2304,39 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>AMBANK</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>6.4</v>
+        <v>0.59</v>
       </c>
       <c r="E41" s="16" t="n">
-        <v>0.0207</v>
+        <v>0.0172</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>5465200</v>
+        <v>5833400</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>0.96</v>
+        <v>0.29</v>
       </c>
       <c r="H41" t="n">
-        <v>45.21</v>
-      </c>
-      <c r="I41" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.84</v>
+      </c>
+      <c r="I41" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J41" s="9" t="n">
-        <v>6.424</v>
+        <v>0.584</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>6.804</v>
+        <v>0.532</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="14" t="inlineStr"/>
@@ -2349,28 +2349,28 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>AMBANK</t>
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>1.08</v>
+        <v>6.39</v>
       </c>
       <c r="E42" s="16" t="n">
-        <v>0.0189</v>
+        <v>0.0191</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>5408800</v>
+        <v>5819800</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>0.55</v>
+        <v>1.02</v>
       </c>
       <c r="H42" t="n">
-        <v>52.4</v>
+        <v>44.65</v>
       </c>
       <c r="I42" s="13" t="inlineStr">
         <is>
@@ -2378,10 +2378,10 @@
         </is>
       </c>
       <c r="J42" s="9" t="n">
-        <v>1.069</v>
+        <v>6.423</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>1.04</v>
+        <v>6.804</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="14" t="inlineStr"/>
@@ -2394,33 +2394,40 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0473</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>EVOCOM</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E43" s="15" t="n">
-        <v>0</v>
+        <v>1.26</v>
+      </c>
+      <c r="E43" s="16" t="n">
+        <v>0.008</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>5271900</v>
+        <v>5736900</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>0.37</v>
+        <v>0.58</v>
+      </c>
+      <c r="H43" t="n">
+        <v>41.98</v>
       </c>
       <c r="I43" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J43" s="9" t="n"/>
-      <c r="K43" s="9" t="n"/>
+      <c r="J43" s="9" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="K43" s="9" t="n">
+        <v>1.311</v>
+      </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="14" t="inlineStr"/>
     </row>
@@ -2432,28 +2439,28 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D44" s="9" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="E44" s="15" t="n">
-        <v>0</v>
+        <v>1.15</v>
+      </c>
+      <c r="E44" s="16" t="n">
+        <v>0.1558</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>5185300</v>
+        <v>5443900</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0.26</v>
+        <v>1.54</v>
       </c>
       <c r="H44" t="n">
-        <v>52.1</v>
+        <v>87.19</v>
       </c>
       <c r="I44" s="17" t="inlineStr">
         <is>
@@ -2461,10 +2468,10 @@
         </is>
       </c>
       <c r="J44" s="9" t="n">
-        <v>0.583</v>
+        <v>0.76</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>0.532</v>
+        <v>0.525</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="14" t="inlineStr"/>
@@ -2477,40 +2484,33 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>0473</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>EVOCOM</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="E45" s="16" t="n">
-        <v>0.1055</v>
+        <v>0.1</v>
+      </c>
+      <c r="E45" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>5051400</v>
+        <v>5372100</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="H45" t="n">
-        <v>86.13</v>
-      </c>
-      <c r="I45" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J45" s="9" t="n">
-        <v>0.755</v>
-      </c>
-      <c r="K45" s="9" t="n">
-        <v>0.524</v>
-      </c>
+        <v>0.38</v>
+      </c>
+      <c r="I45" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J45" s="9" t="n"/>
+      <c r="K45" s="9" t="n"/>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="14" t="inlineStr"/>
     </row>
@@ -2522,39 +2522,39 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0096</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>NEXGRAM</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="E46" s="15" t="n">
-        <v>0</v>
+        <v>1.25</v>
+      </c>
+      <c r="E46" s="10" t="n">
+        <v>-0.0385</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>5009600</v>
+        <v>5347400</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>2.52</v>
+        <v>1.64</v>
       </c>
       <c r="H46" t="n">
-        <v>55.31</v>
-      </c>
-      <c r="I46" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>54.24</v>
+      </c>
+      <c r="I46" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J46" s="9" t="n">
-        <v>0.042</v>
+        <v>1.256</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>0.047</v>
+        <v>1.041</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="14" t="inlineStr"/>
@@ -2567,39 +2567,39 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>7195</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>BNASTRA</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="E47" s="16" t="n">
-        <v>0.0037</v>
+        <v>0.475</v>
+      </c>
+      <c r="E47" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>4655300</v>
+        <v>5330300</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>4.28</v>
+        <v>0.77</v>
       </c>
       <c r="H47" t="n">
-        <v>82.95</v>
-      </c>
-      <c r="I47" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>22.56</v>
+      </c>
+      <c r="I47" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J47" s="9" t="n">
-        <v>2.54</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="K47" s="9" t="n">
-        <v>2.386</v>
+        <v>0.629</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="14" t="inlineStr"/>
@@ -2612,28 +2612,28 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D48" s="9" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="E48" s="10" t="n">
-        <v>-0.07629999999999999</v>
+        <v>9.970000000000001</v>
+      </c>
+      <c r="E48" s="16" t="n">
+        <v>0.001</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>4624900</v>
+        <v>5326900</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>0.59</v>
+        <v>0.4</v>
       </c>
       <c r="H48" t="n">
-        <v>52.9</v>
+        <v>44.4</v>
       </c>
       <c r="I48" s="13" t="inlineStr">
         <is>
@@ -2641,10 +2641,10 @@
         </is>
       </c>
       <c r="J48" s="9" t="n">
-        <v>1.103</v>
+        <v>10.006</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>0.86</v>
+        <v>10.178</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="14" t="inlineStr"/>
@@ -2657,39 +2657,39 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>0096</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>NEXGRAM</t>
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E49" s="10" t="n">
-        <v>-0.0244</v>
+        <v>0.045</v>
+      </c>
+      <c r="E49" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>4583800</v>
+        <v>5009600</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>2.77</v>
+        <v>2.52</v>
       </c>
       <c r="H49" t="n">
-        <v>33.91</v>
-      </c>
-      <c r="I49" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.31</v>
+      </c>
+      <c r="I49" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J49" s="9" t="n">
-        <v>0.418</v>
+        <v>0.042</v>
       </c>
       <c r="K49" s="9" t="n">
-        <v>0.437</v>
+        <v>0.047</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="14" t="inlineStr"/>
@@ -2702,39 +2702,39 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>0340</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>NORTHERN</t>
         </is>
       </c>
       <c r="D50" s="9" t="n">
-        <v>2.11</v>
+        <v>1.09</v>
       </c>
       <c r="E50" s="10" t="n">
-        <v>-0.014</v>
+        <v>-0.07629999999999999</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>4549000</v>
+        <v>4707600</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>0.23</v>
+        <v>0.6</v>
       </c>
       <c r="H50" t="n">
-        <v>50.82</v>
-      </c>
-      <c r="I50" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.9</v>
+      </c>
+      <c r="I50" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J50" s="9" t="n">
-        <v>2.109</v>
+        <v>1.103</v>
       </c>
       <c r="K50" s="9" t="n">
-        <v>2.094</v>
+        <v>0.86</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="14" t="inlineStr"/>
@@ -2747,39 +2747,39 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>7195</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>BNASTRA</t>
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="E51" s="10" t="n">
-        <v>-0.07690000000000001</v>
+        <v>2.7</v>
+      </c>
+      <c r="E51" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>4474600</v>
+        <v>4672300</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>1.37</v>
+        <v>4.3</v>
       </c>
       <c r="H51" t="n">
-        <v>49.61</v>
-      </c>
-      <c r="I51" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>82.43000000000001</v>
+      </c>
+      <c r="I51" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J51" s="9" t="n">
-        <v>1.251</v>
+        <v>2.539</v>
       </c>
       <c r="K51" s="9" t="n">
-        <v>1.04</v>
+        <v>2.386</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="14" t="inlineStr"/>
@@ -2792,39 +2792,39 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D52" s="9" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="E52" s="16" t="n">
-        <v>0.0193</v>
+        <v>2.12</v>
+      </c>
+      <c r="E52" s="10" t="n">
+        <v>-0.009300000000000001</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>4431300</v>
+        <v>4672200</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>0.46</v>
+        <v>0.23</v>
       </c>
       <c r="H52" t="n">
-        <v>55.93</v>
-      </c>
-      <c r="I52" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.35</v>
+      </c>
+      <c r="I52" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J52" s="9" t="n">
-        <v>3.605</v>
+        <v>2.11</v>
       </c>
       <c r="K52" s="9" t="n">
-        <v>2.871</v>
+        <v>2.094</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="14" t="inlineStr"/>
@@ -2837,28 +2837,28 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D53" s="9" t="n">
-        <v>9.970000000000001</v>
+        <v>3.73</v>
       </c>
       <c r="E53" s="16" t="n">
-        <v>0.001</v>
+        <v>0.0275</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>4355700</v>
+        <v>4608300</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>0.32</v>
+        <v>0.47</v>
       </c>
       <c r="H53" t="n">
-        <v>44.4</v>
+        <v>56.58</v>
       </c>
       <c r="I53" s="13" t="inlineStr">
         <is>
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="J53" s="9" t="n">
-        <v>10.006</v>
+        <v>3.608</v>
       </c>
       <c r="K53" s="9" t="n">
-        <v>10.178</v>
+        <v>2.871</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="14" t="inlineStr"/>
@@ -2882,28 +2882,28 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D54" s="9" t="n">
-        <v>2.07</v>
+        <v>2.78</v>
       </c>
       <c r="E54" s="10" t="n">
-        <v>-0.0048</v>
+        <v>-0.0142</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>4342500</v>
+        <v>4601700</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>0.29</v>
+        <v>0.33</v>
       </c>
       <c r="H54" t="n">
-        <v>36.74</v>
+        <v>50.17</v>
       </c>
       <c r="I54" s="13" t="inlineStr">
         <is>
@@ -2911,10 +2911,10 @@
         </is>
       </c>
       <c r="J54" s="9" t="n">
-        <v>2.189</v>
+        <v>2.796</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>2.225</v>
+        <v>2.721</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="14" t="inlineStr"/>
@@ -2927,28 +2927,28 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="E55" s="16" t="n">
-        <v>0.0108</v>
+        <v>0.4</v>
+      </c>
+      <c r="E55" s="10" t="n">
+        <v>-0.0244</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>4202200</v>
+        <v>4584400</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>0.76</v>
+        <v>2.77</v>
       </c>
       <c r="H55" t="n">
-        <v>62.32</v>
+        <v>33.91</v>
       </c>
       <c r="I55" s="13" t="inlineStr">
         <is>
@@ -2956,10 +2956,10 @@
         </is>
       </c>
       <c r="J55" s="9" t="n">
-        <v>0.912</v>
+        <v>0.418</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>0.869</v>
+        <v>0.437</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="14" t="inlineStr"/>
@@ -2972,28 +2972,28 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D56" s="9" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="E56" s="15" t="n">
-        <v>0</v>
+        <v>2.07</v>
+      </c>
+      <c r="E56" s="10" t="n">
+        <v>-0.0048</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>4102100</v>
+        <v>4431900</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>0.38</v>
+        <v>0.3</v>
       </c>
       <c r="H56" t="n">
-        <v>33.84</v>
+        <v>36.74</v>
       </c>
       <c r="I56" s="13" t="inlineStr">
         <is>
@@ -3001,10 +3001,10 @@
         </is>
       </c>
       <c r="J56" s="9" t="n">
-        <v>0.399</v>
+        <v>2.189</v>
       </c>
       <c r="K56" s="9" t="n">
-        <v>0.408</v>
+        <v>2.225</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="14" t="inlineStr"/>
@@ -3017,39 +3017,39 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="E57" s="10" t="n">
-        <v>-0.0303</v>
+        <v>0.945</v>
+      </c>
+      <c r="E57" s="16" t="n">
+        <v>0.0161</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>4005400</v>
+        <v>4356300</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>0.55</v>
+        <v>0.79</v>
       </c>
       <c r="H57" t="n">
-        <v>68.45</v>
-      </c>
-      <c r="I57" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>63.48</v>
+      </c>
+      <c r="I57" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J57" s="9" t="n">
-        <v>0.299</v>
+        <v>0.912</v>
       </c>
       <c r="K57" s="9" t="n">
-        <v>0.278</v>
+        <v>0.869</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="14" t="inlineStr"/>
@@ -3062,28 +3062,28 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>VELESTO</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D58" s="9" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="E58" s="16" t="n">
-        <v>0.04650000000000001</v>
+        <v>0.39</v>
+      </c>
+      <c r="E58" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>3925600</v>
+        <v>4257800</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>0.19</v>
+        <v>0.39</v>
       </c>
       <c r="H58" t="n">
-        <v>48.41</v>
+        <v>33.84</v>
       </c>
       <c r="I58" s="13" t="inlineStr">
         <is>
@@ -3091,10 +3091,10 @@
         </is>
       </c>
       <c r="J58" s="9" t="n">
-        <v>0.224</v>
+        <v>0.399</v>
       </c>
       <c r="K58" s="9" t="n">
-        <v>0.24</v>
+        <v>0.408</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="14" t="inlineStr"/>
@@ -3107,28 +3107,28 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="E59" s="10" t="n">
-        <v>-0.0213</v>
+        <v>0.22</v>
+      </c>
+      <c r="E59" s="16" t="n">
+        <v>0.0233</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>3883700</v>
+        <v>4221000</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>0.28</v>
+        <v>0.16</v>
       </c>
       <c r="H59" t="n">
-        <v>48.59</v>
+        <v>33.45</v>
       </c>
       <c r="I59" s="13" t="inlineStr">
         <is>
@@ -3136,10 +3136,10 @@
         </is>
       </c>
       <c r="J59" s="9" t="n">
-        <v>2.794</v>
+        <v>0.241</v>
       </c>
       <c r="K59" s="9" t="n">
-        <v>2.721</v>
+        <v>0.295</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="14" t="inlineStr"/>
@@ -3152,28 +3152,28 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>VELESTO</t>
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>0.475</v>
-      </c>
-      <c r="E60" s="15" t="n">
-        <v>0</v>
+        <v>0.225</v>
+      </c>
+      <c r="E60" s="16" t="n">
+        <v>0.04650000000000001</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>3750200</v>
+        <v>4210900</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>0.54</v>
+        <v>0.2</v>
       </c>
       <c r="H60" t="n">
-        <v>22.56</v>
+        <v>48.41</v>
       </c>
       <c r="I60" s="13" t="inlineStr">
         <is>
@@ -3181,10 +3181,10 @@
         </is>
       </c>
       <c r="J60" s="9" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.224</v>
       </c>
       <c r="K60" s="9" t="n">
-        <v>0.629</v>
+        <v>0.24</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="14" t="inlineStr"/>
@@ -3197,28 +3197,28 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>0.445</v>
-      </c>
-      <c r="E61" s="10" t="n">
-        <v>-0.0111</v>
+        <v>1.26</v>
+      </c>
+      <c r="E61" s="16" t="n">
+        <v>0.008</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>3718800</v>
+        <v>4210400</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="H61" t="n">
-        <v>23.61</v>
+        <v>23.74</v>
       </c>
       <c r="I61" s="13" t="inlineStr">
         <is>
@@ -3226,10 +3226,10 @@
         </is>
       </c>
       <c r="J61" s="9" t="n">
-        <v>0.524</v>
+        <v>1.441</v>
       </c>
       <c r="K61" s="9" t="n">
-        <v>0.713</v>
+        <v>1.59</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="14" t="inlineStr"/>
@@ -3242,39 +3242,39 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>WCT</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D62" s="9" t="n">
         <v>0.315</v>
       </c>
-      <c r="E62" s="15" t="n">
-        <v>0</v>
+      <c r="E62" s="10" t="n">
+        <v>-0.0455</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>3697400</v>
+        <v>4040400</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>0.74</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H62" t="n">
-        <v>26.24</v>
-      </c>
-      <c r="I62" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.22</v>
+      </c>
+      <c r="I62" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J62" s="9" t="n">
-        <v>0.351</v>
+        <v>0.299</v>
       </c>
       <c r="K62" s="9" t="n">
-        <v>0.379</v>
+        <v>0.278</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="14" t="inlineStr"/>
@@ -3287,28 +3287,28 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="E63" s="10" t="n">
-        <v>-0.0233</v>
+        <v>0.45</v>
+      </c>
+      <c r="E63" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>3630500</v>
+        <v>3985900</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>0.14</v>
+        <v>0.1</v>
       </c>
       <c r="H63" t="n">
-        <v>28.68</v>
+        <v>24.11</v>
       </c>
       <c r="I63" s="13" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="J63" s="9" t="n">
-        <v>0.24</v>
+        <v>0.524</v>
       </c>
       <c r="K63" s="9" t="n">
-        <v>0.295</v>
+        <v>0.713</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="14" t="inlineStr"/>
@@ -3332,28 +3332,28 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D64" s="9" t="n">
-        <v>0.495</v>
+        <v>0.31</v>
       </c>
       <c r="E64" s="10" t="n">
-        <v>-0.01</v>
+        <v>-0.0159</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>3565100</v>
+        <v>3799600</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>0.42</v>
+        <v>0.76</v>
       </c>
       <c r="H64" t="n">
-        <v>42.01</v>
+        <v>24.94</v>
       </c>
       <c r="I64" s="13" t="inlineStr">
         <is>
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="J64" s="9" t="n">
-        <v>0.517</v>
+        <v>0.35</v>
       </c>
       <c r="K64" s="9" t="n">
-        <v>0.529</v>
+        <v>0.379</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="14" t="inlineStr"/>
@@ -3377,28 +3377,28 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0258</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>AGMO</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="E65" s="16" t="n">
-        <v>0.0175</v>
+        <v>0.495</v>
+      </c>
+      <c r="E65" s="10" t="n">
+        <v>-0.01</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>3489300</v>
+        <v>3759900</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>4.65</v>
+        <v>0.45</v>
       </c>
       <c r="H65" t="n">
-        <v>53.95</v>
+        <v>42.01</v>
       </c>
       <c r="I65" s="13" t="inlineStr">
         <is>
@@ -3406,10 +3406,10 @@
         </is>
       </c>
       <c r="J65" s="9" t="n">
-        <v>0.28</v>
+        <v>0.517</v>
       </c>
       <c r="K65" s="9" t="n">
-        <v>0.301</v>
+        <v>0.529</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="14" t="inlineStr"/>
@@ -3422,28 +3422,28 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>0258</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>AGMO</t>
         </is>
       </c>
       <c r="D66" s="9" t="n">
-        <v>1.26</v>
+        <v>0.29</v>
       </c>
       <c r="E66" s="16" t="n">
-        <v>0.008</v>
+        <v>0.0175</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>3357600</v>
+        <v>3589500</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>0.87</v>
+        <v>4.78</v>
       </c>
       <c r="H66" t="n">
-        <v>23.74</v>
+        <v>53.95</v>
       </c>
       <c r="I66" s="13" t="inlineStr">
         <is>
@@ -3451,10 +3451,10 @@
         </is>
       </c>
       <c r="J66" s="9" t="n">
-        <v>1.441</v>
+        <v>0.28</v>
       </c>
       <c r="K66" s="9" t="n">
-        <v>1.59</v>
+        <v>0.301</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="14" t="inlineStr"/>
@@ -3467,39 +3467,39 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D67" s="9" t="n">
-        <v>1.18</v>
+        <v>7.34</v>
       </c>
       <c r="E67" s="16" t="n">
-        <v>0.0172</v>
+        <v>0.0124</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>3250200</v>
+        <v>3511000</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>0.42</v>
+        <v>0.45</v>
       </c>
       <c r="H67" t="n">
-        <v>53.23</v>
-      </c>
-      <c r="I67" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>44.29</v>
+      </c>
+      <c r="I67" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J67" s="9" t="n">
-        <v>1.162</v>
+        <v>7.376</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>1.127</v>
+        <v>7.687</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="14" t="inlineStr"/>
@@ -3527,10 +3527,10 @@
         <v>-0.0083</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>3140800</v>
+        <v>3484200</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="H68" t="n">
         <v>37.03</v>
@@ -3557,28 +3557,28 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D69" s="9" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="E69" s="15" t="n">
-        <v>0</v>
+        <v>0.89</v>
+      </c>
+      <c r="E69" s="10" t="n">
+        <v>-0.0326</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>3138200</v>
+        <v>3460500</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>0.35</v>
+        <v>0.42</v>
       </c>
       <c r="H69" t="n">
-        <v>46.36</v>
+        <v>43.99</v>
       </c>
       <c r="I69" s="13" t="inlineStr">
         <is>
@@ -3586,10 +3586,10 @@
         </is>
       </c>
       <c r="J69" s="9" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.948</v>
       </c>
       <c r="K69" s="9" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.836</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="14" t="inlineStr"/>
@@ -3602,28 +3602,28 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D70" s="9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="E70" s="10" t="n">
-        <v>-0.0095</v>
+        <v>1.19</v>
+      </c>
+      <c r="E70" s="16" t="n">
+        <v>0.0259</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>2980200</v>
+        <v>3436000</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>0.35</v>
+        <v>0.45</v>
       </c>
       <c r="H70" t="n">
-        <v>49.14</v>
+        <v>54.4</v>
       </c>
       <c r="I70" s="13" t="inlineStr">
         <is>
@@ -3631,10 +3631,10 @@
         </is>
       </c>
       <c r="J70" s="9" t="n">
-        <v>1.069</v>
+        <v>1.163</v>
       </c>
       <c r="K70" s="9" t="n">
-        <v>0.9409999999999999</v>
+        <v>1.127</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="14" t="inlineStr"/>
@@ -3647,39 +3647,39 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>5336</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>CKI</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="E71" s="16" t="n">
-        <v>0.0137</v>
+        <v>5.45</v>
+      </c>
+      <c r="E71" s="10" t="n">
+        <v>-0.0091</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>2953800</v>
+        <v>3338400</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>1.92</v>
+        <v>0.24</v>
       </c>
       <c r="H71" t="n">
-        <v>51.33</v>
-      </c>
-      <c r="I71" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.82</v>
+      </c>
+      <c r="I71" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J71" s="9" t="n">
-        <v>0.364</v>
+        <v>5.603</v>
       </c>
       <c r="K71" s="9" t="n">
-        <v>0.387</v>
+        <v>5.387</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="14" t="inlineStr"/>
@@ -3692,39 +3692,39 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D72" s="9" t="n">
-        <v>0.805</v>
-      </c>
-      <c r="E72" s="15" t="n">
-        <v>0</v>
+        <v>1.04</v>
+      </c>
+      <c r="E72" s="10" t="n">
+        <v>-0.0095</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>2922700</v>
+        <v>3336700</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>0.49</v>
+        <v>0.39</v>
       </c>
       <c r="H72" t="n">
-        <v>66.90000000000001</v>
-      </c>
-      <c r="I72" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.14</v>
+      </c>
+      <c r="I72" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J72" s="9" t="n">
-        <v>0.791</v>
+        <v>1.069</v>
       </c>
       <c r="K72" s="9" t="n">
-        <v>0.768</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="14" t="inlineStr"/>
@@ -3737,39 +3737,39 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>7243</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>MAGMA</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D73" s="9" t="n">
-        <v>0.285</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E73" s="16" t="n">
-        <v>0.0556</v>
+        <v>0.0062</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>2891000</v>
+        <v>3329900</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>4.19</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H73" t="n">
-        <v>53.17</v>
-      </c>
-      <c r="I73" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>69.31999999999999</v>
+      </c>
+      <c r="I73" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J73" s="9" t="n">
-        <v>0.281</v>
+        <v>0.792</v>
       </c>
       <c r="K73" s="9" t="n">
-        <v>0.285</v>
+        <v>0.768</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="14" t="inlineStr"/>
@@ -3782,28 +3782,28 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0470</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>BFIELD</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D74" s="9" t="n">
-        <v>0.445</v>
-      </c>
-      <c r="E74" s="10" t="n">
-        <v>-0.022</v>
+        <v>0.67</v>
+      </c>
+      <c r="E74" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>2864800</v>
+        <v>3281500</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>0.26</v>
+        <v>0.37</v>
       </c>
       <c r="H74" t="n">
-        <v>27.3</v>
+        <v>46.36</v>
       </c>
       <c r="I74" s="13" t="inlineStr">
         <is>
@@ -3811,9 +3811,11 @@
         </is>
       </c>
       <c r="J74" s="9" t="n">
-        <v>0.471</v>
-      </c>
-      <c r="K74" s="9" t="n"/>
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="K74" s="9" t="n">
+        <v>0.6860000000000001</v>
+      </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="14" t="inlineStr"/>
     </row>
@@ -3825,40 +3827,38 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>0470</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>BFIELD</t>
         </is>
       </c>
       <c r="D75" s="9" t="n">
-        <v>7.34</v>
-      </c>
-      <c r="E75" s="16" t="n">
-        <v>0.0124</v>
+        <v>0.45</v>
+      </c>
+      <c r="E75" s="10" t="n">
+        <v>-0.011</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>2787900</v>
+        <v>3059400</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>0.36</v>
+        <v>0.27</v>
       </c>
       <c r="H75" t="n">
-        <v>44.29</v>
-      </c>
-      <c r="I75" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>30.03</v>
+      </c>
+      <c r="I75" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J75" s="9" t="n">
-        <v>7.376</v>
-      </c>
-      <c r="K75" s="9" t="n">
-        <v>7.687</v>
-      </c>
+        <v>0.472</v>
+      </c>
+      <c r="K75" s="9" t="n"/>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="14" t="inlineStr"/>
     </row>
@@ -3870,39 +3870,39 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>5336</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>CKI</t>
         </is>
       </c>
       <c r="D76" s="9" t="n">
-        <v>0.655</v>
-      </c>
-      <c r="E76" s="15" t="n">
-        <v>0</v>
+        <v>0.37</v>
+      </c>
+      <c r="E76" s="16" t="n">
+        <v>0.0137</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>2781400</v>
+        <v>2975000</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>0.32</v>
+        <v>1.93</v>
       </c>
       <c r="H76" t="n">
-        <v>49.29</v>
-      </c>
-      <c r="I76" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.33</v>
+      </c>
+      <c r="I76" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J76" s="9" t="n">
-        <v>0.669</v>
+        <v>0.364</v>
       </c>
       <c r="K76" s="9" t="n">
-        <v>0.617</v>
+        <v>0.387</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="14" t="inlineStr"/>
@@ -3915,39 +3915,39 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D77" s="9" t="n">
-        <v>0.885</v>
-      </c>
-      <c r="E77" s="10" t="n">
-        <v>-0.038</v>
+        <v>3.01</v>
+      </c>
+      <c r="E77" s="16" t="n">
+        <v>0.0067</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>2767000</v>
+        <v>2945600</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>0.33</v>
+        <v>0.93</v>
       </c>
       <c r="H77" t="n">
-        <v>43.35</v>
-      </c>
-      <c r="I77" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>79.75</v>
+      </c>
+      <c r="I77" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J77" s="9" t="n">
-        <v>0.948</v>
+        <v>2.734</v>
       </c>
       <c r="K77" s="9" t="n">
-        <v>0.836</v>
+        <v>2.358</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="14" t="inlineStr"/>
@@ -3960,39 +3960,39 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>7243</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>MAGMA</t>
         </is>
       </c>
       <c r="D78" s="9" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="E78" s="15" t="n">
-        <v>0</v>
+        <v>0.285</v>
+      </c>
+      <c r="E78" s="16" t="n">
+        <v>0.0556</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>2759400</v>
+        <v>2891000</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>0.87</v>
+        <v>4.19</v>
       </c>
       <c r="H78" t="n">
-        <v>79.09999999999999</v>
-      </c>
-      <c r="I78" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.17</v>
+      </c>
+      <c r="I78" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J78" s="9" t="n">
-        <v>2.732</v>
+        <v>0.281</v>
       </c>
       <c r="K78" s="9" t="n">
-        <v>2.357</v>
+        <v>0.285</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="14" t="inlineStr"/>
@@ -4005,40 +4005,38 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>0471</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>PIONEER</t>
         </is>
       </c>
       <c r="D79" s="9" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="E79" s="10" t="n">
-        <v>-0.0091</v>
+        <v>0.33</v>
+      </c>
+      <c r="E79" s="16" t="n">
+        <v>0.0476</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>2721300</v>
+        <v>2816900</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>0.19</v>
+        <v>0.31</v>
       </c>
       <c r="H79" t="n">
-        <v>44.82</v>
-      </c>
-      <c r="I79" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.79</v>
+      </c>
+      <c r="I79" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J79" s="9" t="n">
-        <v>5.603</v>
-      </c>
-      <c r="K79" s="9" t="n">
-        <v>5.387</v>
-      </c>
+        <v>0.305</v>
+      </c>
+      <c r="K79" s="9" t="n"/>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="14" t="inlineStr"/>
     </row>
@@ -4050,28 +4048,28 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D80" s="9" t="n">
-        <v>0.605</v>
-      </c>
-      <c r="E80" s="16" t="n">
-        <v>0.0083</v>
+        <v>0.655</v>
+      </c>
+      <c r="E80" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>2632100</v>
+        <v>2816700</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>0.63</v>
+        <v>0.32</v>
       </c>
       <c r="H80" t="n">
-        <v>52.64</v>
+        <v>49.29</v>
       </c>
       <c r="I80" s="13" t="inlineStr">
         <is>
@@ -4079,10 +4077,10 @@
         </is>
       </c>
       <c r="J80" s="9" t="n">
-        <v>0.6</v>
+        <v>0.669</v>
       </c>
       <c r="K80" s="9" t="n">
-        <v>0.585</v>
+        <v>0.617</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="14" t="inlineStr"/>
@@ -4095,39 +4093,39 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0388</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>SEMICO</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D81" s="9" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="E81" s="15" t="n">
-        <v>0</v>
+        <v>0.61</v>
+      </c>
+      <c r="E81" s="16" t="n">
+        <v>0.0167</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>2535000</v>
+        <v>2739400</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>0.82</v>
+        <v>0.65</v>
       </c>
       <c r="H81" t="n">
-        <v>64.41</v>
-      </c>
-      <c r="I81" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.75</v>
+      </c>
+      <c r="I81" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J81" s="9" t="n">
-        <v>0.615</v>
+        <v>0.601</v>
       </c>
       <c r="K81" s="9" t="n">
-        <v>0.602</v>
+        <v>0.585</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="14" t="inlineStr"/>
@@ -4140,39 +4138,39 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>0100</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>ESCERAM</t>
         </is>
       </c>
       <c r="D82" s="9" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="E82" s="10" t="n">
-        <v>-0.0489</v>
+        <v>0.225</v>
+      </c>
+      <c r="E82" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>2490000</v>
+        <v>2725400</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>1.79</v>
+        <v>1.58</v>
       </c>
       <c r="H82" t="n">
-        <v>44.21</v>
-      </c>
-      <c r="I82" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>74.25</v>
+      </c>
+      <c r="I82" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J82" s="9" t="n">
-        <v>0.919</v>
+        <v>0.193</v>
       </c>
       <c r="K82" s="9" t="n">
-        <v>0.862</v>
+        <v>0.186</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="14" t="inlineStr"/>
@@ -4185,28 +4183,28 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>5323</t>
+          <t>0233</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>JPG</t>
+          <t>PEKAT</t>
         </is>
       </c>
       <c r="D83" s="9" t="n">
-        <v>1.7</v>
+        <v>2.7</v>
       </c>
       <c r="E83" s="10" t="n">
-        <v>-0.0116</v>
+        <v>-0.0722</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>2449400</v>
+        <v>2637500</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>0.38</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H83" t="n">
-        <v>34.64</v>
+        <v>56.74</v>
       </c>
       <c r="I83" s="13" t="inlineStr">
         <is>
@@ -4214,10 +4212,10 @@
         </is>
       </c>
       <c r="J83" s="9" t="n">
-        <v>1.794</v>
+        <v>2.672</v>
       </c>
       <c r="K83" s="9" t="n">
-        <v>1.909</v>
+        <v>2.206</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="14" t="inlineStr"/>
@@ -4245,10 +4243,10 @@
         <v>0.0126</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>2411400</v>
+        <v>2624500</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>0.36</v>
+        <v>0.39</v>
       </c>
       <c r="H84" t="n">
         <v>46.72</v>
@@ -4275,38 +4273,40 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0471</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>PIONEER</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D85" s="9" t="n">
-        <v>0.33</v>
+        <v>7.32</v>
       </c>
       <c r="E85" s="16" t="n">
-        <v>0.0476</v>
+        <v>0.0027</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>2409200</v>
+        <v>2623300</v>
       </c>
       <c r="G85" s="12" t="n">
         <v>0.26</v>
       </c>
       <c r="H85" t="n">
-        <v>58.79</v>
-      </c>
-      <c r="I85" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.52</v>
+      </c>
+      <c r="I85" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J85" s="9" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="K85" s="9" t="n"/>
+        <v>7.52</v>
+      </c>
+      <c r="K85" s="9" t="n">
+        <v>8.026999999999999</v>
+      </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="14" t="inlineStr"/>
     </row>
@@ -4318,28 +4318,28 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D86" s="9" t="n">
-        <v>7.34</v>
+        <v>0.64</v>
       </c>
       <c r="E86" s="16" t="n">
-        <v>0.005500000000000001</v>
+        <v>0.0159</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>2400500</v>
+        <v>2605300</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>0.23</v>
+        <v>0.5</v>
       </c>
       <c r="H86" t="n">
-        <v>34.85</v>
+        <v>66.54000000000001</v>
       </c>
       <c r="I86" s="13" t="inlineStr">
         <is>
@@ -4347,10 +4347,10 @@
         </is>
       </c>
       <c r="J86" s="9" t="n">
-        <v>7.521</v>
+        <v>0.554</v>
       </c>
       <c r="K86" s="9" t="n">
-        <v>8.026999999999999</v>
+        <v>0.458</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="14" t="inlineStr"/>
@@ -4363,39 +4363,39 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0100</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>ESCERAM</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D87" s="9" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="E87" s="15" t="n">
-        <v>0</v>
+        <v>0.775</v>
+      </c>
+      <c r="E87" s="10" t="n">
+        <v>-0.0064</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>2298100</v>
+        <v>2578800</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>1.34</v>
+        <v>0.31</v>
       </c>
       <c r="H87" t="n">
-        <v>74.25</v>
-      </c>
-      <c r="I87" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.19</v>
+      </c>
+      <c r="I87" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J87" s="9" t="n">
-        <v>0.193</v>
+        <v>0.779</v>
       </c>
       <c r="K87" s="9" t="n">
-        <v>0.186</v>
+        <v>0.773</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="14" t="inlineStr"/>
@@ -4408,28 +4408,28 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0233</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>PEKAT</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D88" s="9" t="n">
-        <v>2.7</v>
+        <v>0.89</v>
       </c>
       <c r="E88" s="10" t="n">
-        <v>-0.0722</v>
+        <v>-0.0326</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>2290500</v>
+        <v>2575500</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>0.7</v>
+        <v>1.85</v>
       </c>
       <c r="H88" t="n">
-        <v>56.74</v>
+        <v>46.48</v>
       </c>
       <c r="I88" s="13" t="inlineStr">
         <is>
@@ -4437,10 +4437,10 @@
         </is>
       </c>
       <c r="J88" s="9" t="n">
-        <v>2.672</v>
+        <v>0.92</v>
       </c>
       <c r="K88" s="9" t="n">
-        <v>2.206</v>
+        <v>0.862</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="14" t="inlineStr"/>
@@ -4453,28 +4453,28 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>5323</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>JPG</t>
         </is>
       </c>
       <c r="D89" s="9" t="n">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="E89" s="10" t="n">
-        <v>-0.0472</v>
+        <v>-0.0116</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>2266900</v>
+        <v>2572600</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>0.49</v>
+        <v>0.4</v>
       </c>
       <c r="H89" t="n">
-        <v>47.39</v>
+        <v>34.64</v>
       </c>
       <c r="I89" s="13" t="inlineStr">
         <is>
@@ -4482,10 +4482,10 @@
         </is>
       </c>
       <c r="J89" s="9" t="n">
-        <v>1.056</v>
+        <v>1.794</v>
       </c>
       <c r="K89" s="9" t="n">
-        <v>0.919</v>
+        <v>1.909</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="14" t="inlineStr"/>
@@ -4498,33 +4498,40 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0475</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>GBBOND</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D90" s="9" t="n">
-        <v>0.205</v>
+        <v>2.41</v>
       </c>
       <c r="E90" s="10" t="n">
-        <v>-0.04650000000000001</v>
+        <v>-0.0203</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>2187900</v>
+        <v>2540700</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
+      </c>
+      <c r="H90" t="n">
+        <v>45.68</v>
       </c>
       <c r="I90" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J90" s="9" t="n"/>
-      <c r="K90" s="9" t="n"/>
+      <c r="J90" s="9" t="n">
+        <v>2.457</v>
+      </c>
+      <c r="K90" s="9" t="n">
+        <v>2.367</v>
+      </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="14" t="inlineStr"/>
     </row>
@@ -4536,39 +4543,39 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>0388</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>SEMICO</t>
         </is>
       </c>
       <c r="D91" s="9" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E91" s="10" t="n">
-        <v>-0.0064</v>
+        <v>0.62</v>
+      </c>
+      <c r="E91" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>2106800</v>
+        <v>2535000</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>0.26</v>
+        <v>0.82</v>
       </c>
       <c r="H91" t="n">
-        <v>49.19</v>
-      </c>
-      <c r="I91" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.41</v>
+      </c>
+      <c r="I91" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J91" s="9" t="n">
-        <v>0.779</v>
+        <v>0.615</v>
       </c>
       <c r="K91" s="9" t="n">
-        <v>0.773</v>
+        <v>0.602</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="14" t="inlineStr"/>
@@ -4581,28 +4588,28 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0272</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>TTVHB</t>
+          <t>KPJ</t>
         </is>
       </c>
       <c r="D92" s="9" t="n">
-        <v>0.245</v>
-      </c>
-      <c r="E92" s="15" t="n">
-        <v>0</v>
+        <v>2.51</v>
+      </c>
+      <c r="E92" s="16" t="n">
+        <v>0.0203</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>2093400</v>
+        <v>2439000</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>0.9</v>
+        <v>0.46</v>
       </c>
       <c r="H92" t="n">
-        <v>47.66</v>
+        <v>41.94</v>
       </c>
       <c r="I92" s="13" t="inlineStr">
         <is>
@@ -4610,10 +4617,10 @@
         </is>
       </c>
       <c r="J92" s="9" t="n">
-        <v>0.25</v>
+        <v>2.571</v>
       </c>
       <c r="K92" s="9" t="n">
-        <v>0.255</v>
+        <v>2.75</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="14" t="inlineStr"/>
@@ -4626,39 +4633,39 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D93" s="9" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="E93" s="10" t="n">
-        <v>-0.0163</v>
+        <v>4.34</v>
+      </c>
+      <c r="E93" s="16" t="n">
+        <v>0.0046</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>2007500</v>
+        <v>2422800</v>
       </c>
       <c r="G93" s="12" t="n">
-        <v>0.16</v>
+        <v>0.37</v>
       </c>
       <c r="H93" t="n">
-        <v>46.91</v>
-      </c>
-      <c r="I93" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.01</v>
+      </c>
+      <c r="I93" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J93" s="9" t="n">
-        <v>2.458</v>
+        <v>4.356</v>
       </c>
       <c r="K93" s="9" t="n">
-        <v>2.367</v>
+        <v>4.441</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="14" t="inlineStr"/>
@@ -4671,28 +4678,28 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>0056</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>NCT</t>
         </is>
       </c>
       <c r="D94" s="9" t="n">
-        <v>4.33</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="E94" s="16" t="n">
-        <v>0.0023</v>
+        <v>0.0089</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>1983600</v>
+        <v>2409700</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>0.31</v>
+        <v>1.1</v>
       </c>
       <c r="H94" t="n">
-        <v>47.58</v>
+        <v>51.23</v>
       </c>
       <c r="I94" s="17" t="inlineStr">
         <is>
@@ -4700,10 +4707,10 @@
         </is>
       </c>
       <c r="J94" s="9" t="n">
-        <v>4.355</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="K94" s="9" t="n">
-        <v>4.441</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="14" t="inlineStr"/>
@@ -4716,28 +4723,28 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>TENAGA</t>
         </is>
       </c>
       <c r="D95" s="9" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="E95" s="16" t="n">
-        <v>0.025</v>
+        <v>12.98</v>
+      </c>
+      <c r="E95" s="10" t="n">
+        <v>-0.0046</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>1790100</v>
+        <v>2315500</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>0.31</v>
+        <v>0.25</v>
       </c>
       <c r="H95" t="n">
-        <v>58.53</v>
+        <v>44.04</v>
       </c>
       <c r="I95" s="17" t="inlineStr">
         <is>
@@ -4745,10 +4752,10 @@
         </is>
       </c>
       <c r="J95" s="9" t="n">
-        <v>1.172</v>
+        <v>13.025</v>
       </c>
       <c r="K95" s="9" t="n">
-        <v>1.176</v>
+        <v>13.492</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="14" t="inlineStr"/>
@@ -4761,28 +4768,28 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>0296</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>KPJ</t>
+          <t>HEGROUP</t>
         </is>
       </c>
       <c r="D96" s="9" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="E96" s="16" t="n">
-        <v>0.0203</v>
+        <v>1</v>
+      </c>
+      <c r="E96" s="10" t="n">
+        <v>-0.0566</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>1767500</v>
+        <v>2310300</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="H96" t="n">
-        <v>41.94</v>
+        <v>46.1</v>
       </c>
       <c r="I96" s="13" t="inlineStr">
         <is>
@@ -4790,10 +4797,10 @@
         </is>
       </c>
       <c r="J96" s="9" t="n">
-        <v>2.571</v>
+        <v>1.055</v>
       </c>
       <c r="K96" s="9" t="n">
-        <v>2.75</v>
+        <v>0.919</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="14" t="inlineStr"/>
@@ -4806,40 +4813,33 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>0475</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>TENAGA</t>
+          <t>GBBOND</t>
         </is>
       </c>
       <c r="D97" s="9" t="n">
-        <v>13</v>
+        <v>0.205</v>
       </c>
       <c r="E97" s="10" t="n">
-        <v>-0.0031</v>
+        <v>-0.04650000000000001</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>1758200</v>
+        <v>2218000</v>
       </c>
       <c r="G97" s="12" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="H97" t="n">
-        <v>44.83</v>
-      </c>
-      <c r="I97" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J97" s="9" t="n">
-        <v>13.027</v>
-      </c>
-      <c r="K97" s="9" t="n">
-        <v>13.493</v>
-      </c>
+        <v>0.16</v>
+      </c>
+      <c r="I97" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J97" s="9" t="n"/>
+      <c r="K97" s="9" t="n"/>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="14" t="inlineStr"/>
     </row>
@@ -4851,39 +4851,39 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>0278</t>
+          <t>0272</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>EDELTEQ</t>
+          <t>TTVHB</t>
         </is>
       </c>
       <c r="D98" s="9" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="E98" s="16" t="n">
-        <v>0.03700000000000001</v>
+        <v>0.24</v>
+      </c>
+      <c r="E98" s="10" t="n">
+        <v>-0.0204</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>1734700</v>
+        <v>2173500</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>0.37</v>
+        <v>0.93</v>
       </c>
       <c r="H98" t="n">
-        <v>62.11</v>
-      </c>
-      <c r="I98" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.88</v>
+      </c>
+      <c r="I98" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J98" s="9" t="n">
-        <v>0.374</v>
+        <v>0.25</v>
       </c>
       <c r="K98" s="9" t="n">
-        <v>0.354</v>
+        <v>0.255</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="14" t="inlineStr"/>
@@ -4896,28 +4896,28 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0056</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>NCT</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D99" s="9" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.42</v>
       </c>
       <c r="E99" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>1733700</v>
+        <v>2169400</v>
       </c>
       <c r="G99" s="12" t="n">
-        <v>0.79</v>
+        <v>0.32</v>
       </c>
       <c r="H99" t="n">
-        <v>48.27</v>
+        <v>49.55</v>
       </c>
       <c r="I99" s="17" t="inlineStr">
         <is>
@@ -4925,10 +4925,10 @@
         </is>
       </c>
       <c r="J99" s="9" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.426</v>
       </c>
       <c r="K99" s="9" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.415</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="14" t="inlineStr"/>
@@ -4941,28 +4941,28 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0398</t>
+          <t>0278</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>GDGROUP</t>
+          <t>EDELTEQ</t>
         </is>
       </c>
       <c r="D100" s="9" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="E100" s="10" t="n">
-        <v>-0.013</v>
+        <v>0.425</v>
+      </c>
+      <c r="E100" s="16" t="n">
+        <v>0.04940000000000001</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>1731500</v>
+        <v>2149900</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>1.94</v>
+        <v>0.46</v>
       </c>
       <c r="H100" t="n">
-        <v>49.68</v>
+        <v>62.89</v>
       </c>
       <c r="I100" s="17" t="inlineStr">
         <is>
@@ -4970,10 +4970,10 @@
         </is>
       </c>
       <c r="J100" s="9" t="n">
-        <v>0.381</v>
+        <v>0.375</v>
       </c>
       <c r="K100" s="9" t="n">
-        <v>0.379</v>
+        <v>0.354</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="14" t="inlineStr"/>
@@ -4986,39 +4986,39 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0372</t>
+          <t>0398</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>CHEEDING</t>
+          <t>GDGROUP</t>
         </is>
       </c>
       <c r="D101" s="9" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="E101" s="10" t="n">
-        <v>-0.0172</v>
+        <v>0.385</v>
+      </c>
+      <c r="E101" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>1728500</v>
+        <v>2078500</v>
       </c>
       <c r="G101" s="12" t="n">
-        <v>0.43</v>
+        <v>2.33</v>
       </c>
       <c r="H101" t="n">
-        <v>40.78</v>
-      </c>
-      <c r="I101" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.12</v>
+      </c>
+      <c r="I101" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J101" s="9" t="n">
-        <v>0.606</v>
+        <v>0.381</v>
       </c>
       <c r="K101" s="9" t="n">
-        <v>0.606</v>
+        <v>0.379</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="14" t="inlineStr"/>
@@ -5031,39 +5031,39 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0376</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>IAB</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D102" s="9" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="E102" s="10" t="n">
-        <v>-0.0169</v>
+        <v>1.23</v>
+      </c>
+      <c r="E102" s="16" t="n">
+        <v>0.025</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>1721900</v>
+        <v>1980100</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>0.76</v>
+        <v>0.34</v>
       </c>
       <c r="H102" t="n">
-        <v>39.49</v>
-      </c>
-      <c r="I102" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.53</v>
+      </c>
+      <c r="I102" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J102" s="9" t="n">
-        <v>1.25</v>
+        <v>1.172</v>
       </c>
       <c r="K102" s="9" t="n">
-        <v>1.308</v>
+        <v>1.176</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="14" t="inlineStr"/>
@@ -5076,39 +5076,39 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>0097</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>VITROX</t>
         </is>
       </c>
       <c r="D103" s="9" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="E103" s="15" t="n">
-        <v>0</v>
+        <v>10.68</v>
+      </c>
+      <c r="E103" s="10" t="n">
+        <v>-0.005600000000000001</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>1704900</v>
+        <v>1903100</v>
       </c>
       <c r="G103" s="12" t="n">
-        <v>0.25</v>
+        <v>0.53</v>
       </c>
       <c r="H103" t="n">
-        <v>49.55</v>
-      </c>
-      <c r="I103" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>60.31</v>
+      </c>
+      <c r="I103" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J103" s="9" t="n">
-        <v>0.426</v>
+        <v>10.399</v>
       </c>
       <c r="K103" s="9" t="n">
-        <v>0.415</v>
+        <v>9.661</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="14" t="inlineStr"/>
@@ -5121,39 +5121,39 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D104" s="9" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E104" s="15" t="n">
-        <v>0</v>
+        <v>6.77</v>
+      </c>
+      <c r="E104" s="16" t="n">
+        <v>0.0415</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>1677400</v>
+        <v>1901800</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>0.32</v>
+        <v>0.35</v>
       </c>
       <c r="H104" t="n">
-        <v>65.61</v>
-      </c>
-      <c r="I104" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.79</v>
+      </c>
+      <c r="I104" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J104" s="9" t="n">
-        <v>0.553</v>
+        <v>6.077</v>
       </c>
       <c r="K104" s="9" t="n">
-        <v>0.458</v>
+        <v>5.86</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="14" t="inlineStr"/>
@@ -5166,28 +5166,28 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D105" s="9" t="n">
-        <v>0.47</v>
+        <v>0.88</v>
       </c>
       <c r="E105" s="10" t="n">
-        <v>-0.0105</v>
+        <v>-0.0112</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>1634500</v>
+        <v>1898000</v>
       </c>
       <c r="G105" s="12" t="n">
-        <v>0.21</v>
+        <v>0.76</v>
       </c>
       <c r="H105" t="n">
-        <v>28.83</v>
+        <v>22.06</v>
       </c>
       <c r="I105" s="13" t="inlineStr">
         <is>
@@ -5195,10 +5195,10 @@
         </is>
       </c>
       <c r="J105" s="9" t="n">
-        <v>0.511</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="K105" s="9" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.983</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="14" t="inlineStr"/>
@@ -5211,39 +5211,39 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>0372</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>CHEEDING</t>
         </is>
       </c>
       <c r="D106" s="9" t="n">
-        <v>6.74</v>
-      </c>
-      <c r="E106" s="16" t="n">
-        <v>0.0369</v>
+        <v>0.57</v>
+      </c>
+      <c r="E106" s="10" t="n">
+        <v>-0.0172</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>1607800</v>
+        <v>1897600</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>0.29</v>
+        <v>0.48</v>
       </c>
       <c r="H106" t="n">
-        <v>61.46</v>
-      </c>
-      <c r="I106" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.78</v>
+      </c>
+      <c r="I106" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J106" s="9" t="n">
-        <v>6.074</v>
+        <v>0.606</v>
       </c>
       <c r="K106" s="9" t="n">
-        <v>5.86</v>
+        <v>0.606</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="14" t="inlineStr"/>
@@ -5256,28 +5256,28 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>0376</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>IAB</t>
         </is>
       </c>
       <c r="D107" s="9" t="n">
-        <v>2.56</v>
+        <v>1.15</v>
       </c>
       <c r="E107" s="10" t="n">
-        <v>-0.007800000000000001</v>
+        <v>-0.0254</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>1604600</v>
+        <v>1839600</v>
       </c>
       <c r="G107" s="12" t="n">
-        <v>0.26</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H107" t="n">
-        <v>45.83</v>
+        <v>38.75</v>
       </c>
       <c r="I107" s="13" t="inlineStr">
         <is>
@@ -5285,10 +5285,10 @@
         </is>
       </c>
       <c r="J107" s="9" t="n">
-        <v>2.626</v>
+        <v>1.249</v>
       </c>
       <c r="K107" s="9" t="n">
-        <v>2.597</v>
+        <v>1.308</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="14" t="inlineStr"/>
@@ -5301,28 +5301,28 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>5337</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>ECOSHOP</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D108" s="9" t="n">
-        <v>1.43</v>
+        <v>2.57</v>
       </c>
       <c r="E108" s="10" t="n">
-        <v>-0.0069</v>
+        <v>-0.0039</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>1498900</v>
+        <v>1834100</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>0.35</v>
+        <v>0.29</v>
       </c>
       <c r="H108" t="n">
-        <v>40.99</v>
+        <v>46.48</v>
       </c>
       <c r="I108" s="13" t="inlineStr">
         <is>
@@ -5330,10 +5330,10 @@
         </is>
       </c>
       <c r="J108" s="9" t="n">
-        <v>1.453</v>
+        <v>2.627</v>
       </c>
       <c r="K108" s="9" t="n">
-        <v>1.467</v>
+        <v>2.597</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="14" t="inlineStr"/>
@@ -5346,28 +5346,28 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D109" s="9" t="n">
-        <v>0.74</v>
+        <v>0.47</v>
       </c>
       <c r="E109" s="10" t="n">
-        <v>-0.0199</v>
+        <v>-0.0105</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>1478800</v>
+        <v>1695900</v>
       </c>
       <c r="G109" s="12" t="n">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="H109" t="n">
-        <v>52.84</v>
+        <v>28.83</v>
       </c>
       <c r="I109" s="13" t="inlineStr">
         <is>
@@ -5375,10 +5375,10 @@
         </is>
       </c>
       <c r="J109" s="9" t="n">
-        <v>0.742</v>
+        <v>0.511</v>
       </c>
       <c r="K109" s="9" t="n">
-        <v>0.665</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="14" t="inlineStr"/>
@@ -5391,28 +5391,28 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>5329</t>
+          <t>0245</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>AZAMJAYA</t>
+          <t>MNHLDG</t>
         </is>
       </c>
       <c r="D110" s="9" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="E110" s="16" t="n">
-        <v>0.0421</v>
+        <v>3.84</v>
+      </c>
+      <c r="E110" s="10" t="n">
+        <v>-0.0179</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>1445500</v>
+        <v>1636500</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>15.94</v>
+        <v>0.58</v>
       </c>
       <c r="H110" t="n">
-        <v>54.39</v>
+        <v>51.04</v>
       </c>
       <c r="I110" s="17" t="inlineStr">
         <is>
@@ -5420,10 +5420,10 @@
         </is>
       </c>
       <c r="J110" s="9" t="n">
-        <v>0.969</v>
+        <v>3.873</v>
       </c>
       <c r="K110" s="9" t="n">
-        <v>0.978</v>
+        <v>3.63</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="14" t="inlineStr"/>
@@ -5436,39 +5436,39 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>5337</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>ECOSHOP</t>
         </is>
       </c>
       <c r="D111" s="9" t="n">
-        <v>3.81</v>
+        <v>1.43</v>
       </c>
       <c r="E111" s="10" t="n">
-        <v>-0.0256</v>
+        <v>-0.0069</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>1397800</v>
+        <v>1603500</v>
       </c>
       <c r="G111" s="12" t="n">
-        <v>0.49</v>
+        <v>0.38</v>
       </c>
       <c r="H111" t="n">
-        <v>49.4</v>
-      </c>
-      <c r="I111" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.99</v>
+      </c>
+      <c r="I111" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J111" s="9" t="n">
-        <v>3.87</v>
+        <v>1.453</v>
       </c>
       <c r="K111" s="9" t="n">
-        <v>3.629</v>
+        <v>1.467</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="14" t="inlineStr"/>
@@ -5481,28 +5481,28 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>DATASONIC</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D112" s="9" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E112" s="10" t="n">
-        <v>-0.0167</v>
+        <v>0.53</v>
+      </c>
+      <c r="E112" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>1396900</v>
+        <v>1603100</v>
       </c>
       <c r="G112" s="12" t="n">
         <v>0.11</v>
       </c>
       <c r="H112" t="n">
-        <v>51.87</v>
+        <v>55.05</v>
       </c>
       <c r="I112" s="13" t="inlineStr">
         <is>
@@ -5510,10 +5510,10 @@
         </is>
       </c>
       <c r="J112" s="9" t="n">
-        <v>0.292</v>
+        <v>0.519</v>
       </c>
       <c r="K112" s="9" t="n">
-        <v>0.282</v>
+        <v>0.449</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="14" t="inlineStr"/>
@@ -5526,28 +5526,28 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>0097</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>VITROX</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D113" s="9" t="n">
-        <v>10.68</v>
-      </c>
-      <c r="E113" s="10" t="n">
-        <v>-0.005600000000000001</v>
+        <v>0.595</v>
+      </c>
+      <c r="E113" s="16" t="n">
+        <v>0.0259</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>1385300</v>
+        <v>1599800</v>
       </c>
       <c r="G113" s="12" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
       <c r="H113" t="n">
-        <v>60.31</v>
+        <v>64.37</v>
       </c>
       <c r="I113" s="13" t="inlineStr">
         <is>
@@ -5555,10 +5555,10 @@
         </is>
       </c>
       <c r="J113" s="9" t="n">
-        <v>10.399</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="K113" s="9" t="n">
-        <v>9.661</v>
+        <v>0.506</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="14" t="inlineStr"/>
@@ -5571,28 +5571,28 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D114" s="9" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="E114" s="16" t="n">
-        <v>0.0172</v>
+        <v>0.865</v>
+      </c>
+      <c r="E114" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>1368300</v>
+        <v>1573000</v>
       </c>
       <c r="G114" s="12" t="n">
-        <v>0.27</v>
+        <v>0.49</v>
       </c>
       <c r="H114" t="n">
-        <v>63.36</v>
+        <v>51.92</v>
       </c>
       <c r="I114" s="13" t="inlineStr">
         <is>
@@ -5600,10 +5600,10 @@
         </is>
       </c>
       <c r="J114" s="9" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.865</v>
       </c>
       <c r="K114" s="9" t="n">
-        <v>0.506</v>
+        <v>0.859</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="14" t="inlineStr"/>
@@ -5616,28 +5616,28 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D115" s="9" t="n">
-        <v>0.88</v>
+        <v>0.74</v>
       </c>
       <c r="E115" s="10" t="n">
-        <v>-0.0112</v>
+        <v>-0.0199</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>1357600</v>
+        <v>1541800</v>
       </c>
       <c r="G115" s="12" t="n">
-        <v>0.55</v>
+        <v>0.22</v>
       </c>
       <c r="H115" t="n">
-        <v>22.06</v>
+        <v>52.84</v>
       </c>
       <c r="I115" s="13" t="inlineStr">
         <is>
@@ -5645,10 +5645,10 @@
         </is>
       </c>
       <c r="J115" s="9" t="n">
-        <v>0.9389999999999999</v>
+        <v>0.742</v>
       </c>
       <c r="K115" s="9" t="n">
-        <v>0.983</v>
+        <v>0.665</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="14" t="inlineStr"/>
@@ -5661,39 +5661,39 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>0104</t>
+          <t>5329</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>GENETEC</t>
+          <t>AZAMJAYA</t>
         </is>
       </c>
       <c r="D116" s="9" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="E116" s="15" t="n">
-        <v>0</v>
+        <v>0.96</v>
+      </c>
+      <c r="E116" s="16" t="n">
+        <v>0.0105</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>1346600</v>
+        <v>1474500</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v>0.21</v>
+        <v>16.26</v>
       </c>
       <c r="H116" t="n">
-        <v>40.49</v>
-      </c>
-      <c r="I116" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.94</v>
+      </c>
+      <c r="I116" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J116" s="9" t="n">
-        <v>0.321</v>
+        <v>0.966</v>
       </c>
       <c r="K116" s="9" t="n">
-        <v>0.338</v>
+        <v>0.977</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="14" t="inlineStr"/>
@@ -5706,28 +5706,28 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>0291</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>CHB</t>
+          <t>DATASONIC</t>
         </is>
       </c>
       <c r="D117" s="9" t="n">
-        <v>2.65</v>
+        <v>0.295</v>
       </c>
       <c r="E117" s="10" t="n">
-        <v>-0.0603</v>
+        <v>-0.0167</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>1342500</v>
+        <v>1440400</v>
       </c>
       <c r="G117" s="12" t="n">
-        <v>0.87</v>
+        <v>0.11</v>
       </c>
       <c r="H117" t="n">
-        <v>61.35</v>
+        <v>51.87</v>
       </c>
       <c r="I117" s="13" t="inlineStr">
         <is>
@@ -5735,10 +5735,10 @@
         </is>
       </c>
       <c r="J117" s="9" t="n">
-        <v>2.534</v>
+        <v>0.292</v>
       </c>
       <c r="K117" s="9" t="n">
-        <v>2.212</v>
+        <v>0.282</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="14" t="inlineStr"/>
@@ -5751,28 +5751,28 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>0146</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>JFTECH</t>
         </is>
       </c>
       <c r="D118" s="9" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="E118" s="15" t="n">
-        <v>0</v>
+        <v>0.745</v>
+      </c>
+      <c r="E118" s="16" t="n">
+        <v>0.0068</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>1333600</v>
+        <v>1420700</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v>0.09</v>
+        <v>0.65</v>
       </c>
       <c r="H118" t="n">
-        <v>55.05</v>
+        <v>55.71</v>
       </c>
       <c r="I118" s="13" t="inlineStr">
         <is>
@@ -5780,10 +5780,10 @@
         </is>
       </c>
       <c r="J118" s="9" t="n">
-        <v>0.519</v>
+        <v>0.724</v>
       </c>
       <c r="K118" s="9" t="n">
-        <v>0.449</v>
+        <v>0.699</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="14" t="inlineStr"/>
@@ -5796,28 +5796,28 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>IOIPG</t>
         </is>
       </c>
       <c r="D119" s="9" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E119" s="16" t="n">
-        <v>0.0063</v>
+        <v>3.3</v>
+      </c>
+      <c r="E119" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>1303800</v>
+        <v>1401800</v>
       </c>
       <c r="G119" s="12" t="n">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="H119" t="n">
-        <v>62.86</v>
+        <v>33.44</v>
       </c>
       <c r="I119" s="13" t="inlineStr">
         <is>
@@ -5825,10 +5825,10 @@
         </is>
       </c>
       <c r="J119" s="9" t="n">
-        <v>0.764</v>
+        <v>3.425</v>
       </c>
       <c r="K119" s="9" t="n">
-        <v>0.676</v>
+        <v>3.632</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="14" t="inlineStr"/>
@@ -5841,39 +5841,39 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>7498</t>
+          <t>0291</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>RALCO</t>
+          <t>CHB</t>
         </is>
       </c>
       <c r="D120" s="9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="E120" s="15" t="n">
-        <v>0</v>
+        <v>2.65</v>
+      </c>
+      <c r="E120" s="10" t="n">
+        <v>-0.0603</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>1301700</v>
+        <v>1387800</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>1.99</v>
+        <v>0.9</v>
       </c>
       <c r="H120" t="n">
-        <v>55.9</v>
-      </c>
-      <c r="I120" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>61.35</v>
+      </c>
+      <c r="I120" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J120" s="9" t="n">
-        <v>0.999</v>
+        <v>2.534</v>
       </c>
       <c r="K120" s="9" t="n">
-        <v>0.982</v>
+        <v>2.212</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="14" t="inlineStr"/>
@@ -5886,39 +5886,39 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D121" s="9" t="n">
-        <v>0.8149999999999999</v>
-      </c>
-      <c r="E121" s="10" t="n">
-        <v>-0.0121</v>
+        <v>0.795</v>
+      </c>
+      <c r="E121" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>1277400</v>
+        <v>1371600</v>
       </c>
       <c r="G121" s="12" t="n">
-        <v>0.34</v>
+        <v>0.21</v>
       </c>
       <c r="H121" t="n">
-        <v>50.04</v>
-      </c>
-      <c r="I121" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>62.06</v>
+      </c>
+      <c r="I121" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J121" s="9" t="n">
-        <v>0.827</v>
+        <v>0.764</v>
       </c>
       <c r="K121" s="9" t="n">
-        <v>0.77</v>
+        <v>0.676</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="14" t="inlineStr"/>
@@ -5931,28 +5931,28 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>0468</t>
+          <t>0128</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>UNIPAC</t>
+          <t>FRONTKN</t>
         </is>
       </c>
       <c r="D122" s="9" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="E122" s="10" t="n">
-        <v>-0.0213</v>
+        <v>5.14</v>
+      </c>
+      <c r="E122" s="16" t="n">
+        <v>0.0098</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>1276800</v>
+        <v>1356100</v>
       </c>
       <c r="G122" s="12" t="n">
-        <v>0.14</v>
+        <v>0.31</v>
       </c>
       <c r="H122" t="n">
-        <v>24.97</v>
+        <v>55.93</v>
       </c>
       <c r="I122" s="13" t="inlineStr">
         <is>
@@ -5960,9 +5960,11 @@
         </is>
       </c>
       <c r="J122" s="9" t="n">
-        <v>0.257</v>
-      </c>
-      <c r="K122" s="9" t="n"/>
+        <v>5.068</v>
+      </c>
+      <c r="K122" s="9" t="n">
+        <v>5.062</v>
+      </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="14" t="inlineStr"/>
     </row>
@@ -5974,28 +5976,28 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D123" s="9" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="E123" s="16" t="n">
-        <v>0.0135</v>
+        <v>0.305</v>
+      </c>
+      <c r="E123" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>1236800</v>
+        <v>1354000</v>
       </c>
       <c r="G123" s="12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.22</v>
       </c>
       <c r="H123" t="n">
-        <v>56.46</v>
+        <v>40.49</v>
       </c>
       <c r="I123" s="13" t="inlineStr">
         <is>
@@ -6003,10 +6005,10 @@
         </is>
       </c>
       <c r="J123" s="9" t="n">
-        <v>0.724</v>
+        <v>0.321</v>
       </c>
       <c r="K123" s="9" t="n">
-        <v>0.699</v>
+        <v>0.338</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" s="14" t="inlineStr"/>
@@ -6019,28 +6021,28 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>5932</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>BPURI</t>
+          <t>MALAKOF</t>
         </is>
       </c>
       <c r="D124" s="9" t="n">
-        <v>0.21</v>
+        <v>0.765</v>
       </c>
       <c r="E124" s="10" t="n">
-        <v>-0.0233</v>
+        <v>-0.0129</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>1179600</v>
+        <v>1352300</v>
       </c>
       <c r="G124" s="12" t="n">
-        <v>2.62</v>
+        <v>0.31</v>
       </c>
       <c r="H124" t="n">
-        <v>35.94</v>
+        <v>42.45</v>
       </c>
       <c r="I124" s="13" t="inlineStr">
         <is>
@@ -6048,10 +6050,10 @@
         </is>
       </c>
       <c r="J124" s="9" t="n">
-        <v>0.225</v>
+        <v>0.787</v>
       </c>
       <c r="K124" s="9" t="n">
-        <v>0.233</v>
+        <v>0.804</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="14" t="inlineStr"/>
@@ -6064,39 +6066,39 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>AWC</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="D125" s="9" t="n">
-        <v>0.6850000000000001</v>
-      </c>
-      <c r="E125" s="10" t="n">
-        <v>-0.0072</v>
+        <v>5.98</v>
+      </c>
+      <c r="E125" s="16" t="n">
+        <v>0.0101</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>1162100</v>
+        <v>1338600</v>
       </c>
       <c r="G125" s="12" t="n">
-        <v>0.5</v>
+        <v>0.14</v>
       </c>
       <c r="H125" t="n">
-        <v>64.98999999999999</v>
-      </c>
-      <c r="I125" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.41</v>
+      </c>
+      <c r="I125" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J125" s="9" t="n">
-        <v>0.636</v>
+        <v>6.108</v>
       </c>
       <c r="K125" s="9" t="n">
-        <v>0.543</v>
+        <v>6.363</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="14" t="inlineStr"/>
@@ -6109,28 +6111,28 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>5195</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>MALAKOF</t>
+          <t>CENSOF</t>
         </is>
       </c>
       <c r="D126" s="9" t="n">
-        <v>0.765</v>
+        <v>0.205</v>
       </c>
       <c r="E126" s="10" t="n">
-        <v>-0.0129</v>
+        <v>-0.0238</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>1156800</v>
+        <v>1330600</v>
       </c>
       <c r="G126" s="12" t="n">
-        <v>0.27</v>
+        <v>0.6</v>
       </c>
       <c r="H126" t="n">
-        <v>42.45</v>
+        <v>43.5</v>
       </c>
       <c r="I126" s="13" t="inlineStr">
         <is>
@@ -6138,10 +6140,10 @@
         </is>
       </c>
       <c r="J126" s="9" t="n">
-        <v>0.787</v>
+        <v>0.218</v>
       </c>
       <c r="K126" s="9" t="n">
-        <v>0.804</v>
+        <v>0.208</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="14" t="inlineStr"/>
@@ -6154,39 +6156,39 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>5195</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>CENSOF</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D127" s="9" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="E127" s="15" t="n">
-        <v>0</v>
+        <v>0.82</v>
+      </c>
+      <c r="E127" s="10" t="n">
+        <v>-0.0061</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>1153600</v>
+        <v>1319300</v>
       </c>
       <c r="G127" s="12" t="n">
-        <v>0.52</v>
+        <v>0.35</v>
       </c>
       <c r="H127" t="n">
-        <v>46.19</v>
-      </c>
-      <c r="I127" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.94</v>
+      </c>
+      <c r="I127" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J127" s="9" t="n">
-        <v>0.218</v>
+        <v>0.827</v>
       </c>
       <c r="K127" s="9" t="n">
-        <v>0.208</v>
+        <v>0.77</v>
       </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" s="14" t="inlineStr"/>
@@ -6199,39 +6201,39 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>0353</t>
+          <t>7498</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>WESTRVR</t>
+          <t>RALCO</t>
         </is>
       </c>
       <c r="D128" s="9" t="n">
-        <v>0.405</v>
-      </c>
-      <c r="E128" s="16" t="n">
-        <v>0.0125</v>
+        <v>1.01</v>
+      </c>
+      <c r="E128" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>1144000</v>
+        <v>1301700</v>
       </c>
       <c r="G128" s="12" t="n">
-        <v>0.31</v>
+        <v>1.99</v>
       </c>
       <c r="H128" t="n">
-        <v>49.38</v>
-      </c>
-      <c r="I128" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.9</v>
+      </c>
+      <c r="I128" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J128" s="9" t="n">
-        <v>0.418</v>
+        <v>0.999</v>
       </c>
       <c r="K128" s="9" t="n">
-        <v>0.376</v>
+        <v>0.982</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="14" t="inlineStr"/>
@@ -6244,39 +6246,39 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>0337</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>SET</t>
         </is>
       </c>
       <c r="D129" s="9" t="n">
-        <v>0.275</v>
+        <v>0.255</v>
       </c>
       <c r="E129" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>1141800</v>
+        <v>1296800</v>
       </c>
       <c r="G129" s="12" t="n">
-        <v>0.13</v>
+        <v>0.7</v>
       </c>
       <c r="H129" t="n">
-        <v>47.42</v>
-      </c>
-      <c r="I129" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.29</v>
+      </c>
+      <c r="I129" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J129" s="9" t="n">
-        <v>0.278</v>
+        <v>0.24</v>
       </c>
       <c r="K129" s="9" t="n">
-        <v>0.3</v>
+        <v>0.243</v>
       </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" s="14" t="inlineStr"/>
@@ -6289,28 +6291,28 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>0468</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>UNIPAC</t>
         </is>
       </c>
       <c r="D130" s="9" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="E130" s="15" t="n">
-        <v>0</v>
+        <v>0.23</v>
+      </c>
+      <c r="E130" s="10" t="n">
+        <v>-0.0213</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>1120700</v>
+        <v>1295000</v>
       </c>
       <c r="G130" s="12" t="n">
-        <v>0.22</v>
+        <v>0.14</v>
       </c>
       <c r="H130" t="n">
-        <v>39.5</v>
+        <v>24.97</v>
       </c>
       <c r="I130" s="13" t="inlineStr">
         <is>
@@ -6318,11 +6320,9 @@
         </is>
       </c>
       <c r="J130" s="9" t="n">
-        <v>0.336</v>
-      </c>
-      <c r="K130" s="9" t="n">
-        <v>0.343</v>
-      </c>
+        <v>0.257</v>
+      </c>
+      <c r="K130" s="9" t="n"/>
       <c r="L130" t="inlineStr"/>
       <c r="M130" s="14" t="inlineStr"/>
     </row>
@@ -6334,28 +6334,28 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>5246</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>WPRTS</t>
         </is>
       </c>
       <c r="D131" s="9" t="n">
-        <v>0.365</v>
-      </c>
-      <c r="E131" s="15" t="n">
-        <v>0</v>
+        <v>6.75</v>
+      </c>
+      <c r="E131" s="16" t="n">
+        <v>0.003</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>1117200</v>
+        <v>1286100</v>
       </c>
       <c r="G131" s="12" t="n">
-        <v>0.12</v>
+        <v>0.29</v>
       </c>
       <c r="H131" t="n">
-        <v>57.29</v>
+        <v>49.22</v>
       </c>
       <c r="I131" s="13" t="inlineStr">
         <is>
@@ -6363,10 +6363,10 @@
         </is>
       </c>
       <c r="J131" s="9" t="n">
-        <v>0.357</v>
+        <v>6.76</v>
       </c>
       <c r="K131" s="9" t="n">
-        <v>0.325</v>
+        <v>6.839</v>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" s="14" t="inlineStr"/>
@@ -6379,39 +6379,39 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>MRCB</t>
+          <t>IHH</t>
         </is>
       </c>
       <c r="D132" s="9" t="n">
-        <v>0.27</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="E132" s="16" t="n">
-        <v>0.0189</v>
+        <v>0.0075</v>
       </c>
       <c r="F132" s="11" t="n">
-        <v>1069400</v>
+        <v>1284000</v>
       </c>
       <c r="G132" s="12" t="n">
-        <v>0.13</v>
+        <v>0.33</v>
       </c>
       <c r="H132" t="n">
-        <v>34.49</v>
-      </c>
-      <c r="I132" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.92</v>
+      </c>
+      <c r="I132" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J132" s="9" t="n">
-        <v>0.284</v>
+        <v>7.896</v>
       </c>
       <c r="K132" s="9" t="n">
-        <v>0.305</v>
+        <v>7.989</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="14" t="inlineStr"/>
@@ -6424,39 +6424,39 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>0353</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>IHH</t>
+          <t>WESTRVR</t>
         </is>
       </c>
       <c r="D133" s="9" t="n">
-        <v>8.09</v>
+        <v>0.41</v>
       </c>
       <c r="E133" s="16" t="n">
-        <v>0.0138</v>
+        <v>0.025</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>1062600</v>
+        <v>1275800</v>
       </c>
       <c r="G133" s="12" t="n">
-        <v>0.27</v>
+        <v>0.35</v>
       </c>
       <c r="H133" t="n">
-        <v>60.14</v>
-      </c>
-      <c r="I133" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.62</v>
+      </c>
+      <c r="I133" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J133" s="9" t="n">
-        <v>7.901</v>
+        <v>0.418</v>
       </c>
       <c r="K133" s="9" t="n">
-        <v>7.99</v>
+        <v>0.376</v>
       </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" s="14" t="inlineStr"/>
@@ -6469,39 +6469,39 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>5302</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>IOIPG</t>
+          <t>ATECH</t>
         </is>
       </c>
       <c r="D134" s="9" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="E134" s="15" t="n">
-        <v>0</v>
+        <v>0.805</v>
+      </c>
+      <c r="E134" s="16" t="n">
+        <v>0.0321</v>
       </c>
       <c r="F134" s="11" t="n">
-        <v>1032600</v>
+        <v>1270000</v>
       </c>
       <c r="G134" s="12" t="n">
-        <v>0.15</v>
+        <v>0.58</v>
       </c>
       <c r="H134" t="n">
-        <v>33.44</v>
-      </c>
-      <c r="I134" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58</v>
+      </c>
+      <c r="I134" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J134" s="9" t="n">
-        <v>3.425</v>
+        <v>0.777</v>
       </c>
       <c r="K134" s="9" t="n">
-        <v>3.632</v>
+        <v>0.766</v>
       </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" s="14" t="inlineStr"/>
@@ -6514,28 +6514,28 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>0373</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>VERDANT</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D135" s="9" t="n">
-        <v>0.235</v>
+        <v>0.27</v>
       </c>
       <c r="E135" s="10" t="n">
-        <v>-0.0408</v>
+        <v>-0.0182</v>
       </c>
       <c r="F135" s="11" t="n">
-        <v>1031000</v>
+        <v>1255700</v>
       </c>
       <c r="G135" s="12" t="n">
-        <v>0.21</v>
+        <v>0.15</v>
       </c>
       <c r="H135" t="n">
-        <v>45.82</v>
+        <v>45.23</v>
       </c>
       <c r="I135" s="13" t="inlineStr">
         <is>
@@ -6543,10 +6543,10 @@
         </is>
       </c>
       <c r="J135" s="9" t="n">
-        <v>0.249</v>
+        <v>0.278</v>
       </c>
       <c r="K135" s="9" t="n">
-        <v>0.222</v>
+        <v>0.3</v>
       </c>
       <c r="L135" t="inlineStr"/>
       <c r="M135" s="14" t="inlineStr"/>
@@ -6559,28 +6559,28 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>5248</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>BAUTO</t>
         </is>
       </c>
       <c r="D136" s="9" t="n">
-        <v>0.695</v>
-      </c>
-      <c r="E136" s="16" t="n">
-        <v>0.0072</v>
+        <v>0.895</v>
+      </c>
+      <c r="E136" s="10" t="n">
+        <v>-0.011</v>
       </c>
       <c r="F136" s="11" t="n">
-        <v>1019300</v>
+        <v>1238100</v>
       </c>
       <c r="G136" s="12" t="n">
-        <v>0.32</v>
+        <v>0.79</v>
       </c>
       <c r="H136" t="n">
-        <v>38.91</v>
+        <v>38.69</v>
       </c>
       <c r="I136" s="13" t="inlineStr">
         <is>
@@ -6588,10 +6588,10 @@
         </is>
       </c>
       <c r="J136" s="9" t="n">
-        <v>0.745</v>
+        <v>0.917</v>
       </c>
       <c r="K136" s="9" t="n">
-        <v>0.747</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" s="14" t="inlineStr"/>
@@ -6604,28 +6604,28 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>AWC</t>
         </is>
       </c>
       <c r="D137" s="9" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="E137" s="16" t="n">
-        <v>0.0077</v>
+        <v>0.6850000000000001</v>
+      </c>
+      <c r="E137" s="10" t="n">
+        <v>-0.0072</v>
       </c>
       <c r="F137" s="11" t="n">
-        <v>1007700</v>
+        <v>1235200</v>
       </c>
       <c r="G137" s="12" t="n">
-        <v>0.43</v>
+        <v>0.53</v>
       </c>
       <c r="H137" t="n">
-        <v>60.5</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="I137" s="17" t="inlineStr">
         <is>
@@ -6633,10 +6633,10 @@
         </is>
       </c>
       <c r="J137" s="9" t="n">
-        <v>1.245</v>
+        <v>0.636</v>
       </c>
       <c r="K137" s="9" t="n">
-        <v>1.164</v>
+        <v>0.543</v>
       </c>
       <c r="L137" t="inlineStr"/>
       <c r="M137" s="14" t="inlineStr"/>
@@ -6649,39 +6649,39 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>7943</t>
+          <t>5932</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>GREENTEC</t>
+          <t>BPURI</t>
         </is>
       </c>
       <c r="D138" s="9" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="E138" s="10" t="n">
-        <v>-0.0333</v>
+        <v>0.215</v>
+      </c>
+      <c r="E138" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F138" s="11" t="n">
-        <v>1007000</v>
+        <v>1180700</v>
       </c>
       <c r="G138" s="12" t="n">
-        <v>0.92</v>
+        <v>2.62</v>
       </c>
       <c r="H138" t="n">
-        <v>66.97</v>
-      </c>
-      <c r="I138" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.87</v>
+      </c>
+      <c r="I138" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J138" s="9" t="n">
-        <v>0.257</v>
+        <v>0.225</v>
       </c>
       <c r="K138" s="9" t="n">
-        <v>0.211</v>
+        <v>0.233</v>
       </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" s="14" t="inlineStr"/>
@@ -6703,19 +6703,19 @@
         </is>
       </c>
       <c r="D139" s="9" t="n">
-        <v>7.65</v>
-      </c>
-      <c r="E139" s="15" t="n">
-        <v>0</v>
+        <v>7.66</v>
+      </c>
+      <c r="E139" s="16" t="n">
+        <v>0.0013</v>
       </c>
       <c r="F139" s="11" t="n">
-        <v>998300</v>
+        <v>1170800</v>
       </c>
       <c r="G139" s="12" t="n">
-        <v>0.24</v>
+        <v>0.28</v>
       </c>
       <c r="H139" t="n">
-        <v>61.58</v>
+        <v>61.77</v>
       </c>
       <c r="I139" s="13" t="inlineStr">
         <is>
@@ -6723,7 +6723,7 @@
         </is>
       </c>
       <c r="J139" s="9" t="n">
-        <v>7.374</v>
+        <v>7.375</v>
       </c>
       <c r="K139" s="9" t="n">
         <v>6.846</v>
@@ -6739,28 +6739,28 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>5246</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>WPRTS</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D140" s="9" t="n">
-        <v>6.76</v>
-      </c>
-      <c r="E140" s="16" t="n">
-        <v>0.004500000000000001</v>
+        <v>1.7</v>
+      </c>
+      <c r="E140" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F140" s="11" t="n">
-        <v>996200</v>
+        <v>1137500</v>
       </c>
       <c r="G140" s="12" t="n">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="H140" t="n">
-        <v>49.84</v>
+        <v>42.09</v>
       </c>
       <c r="I140" s="13" t="inlineStr">
         <is>
@@ -6768,10 +6768,10 @@
         </is>
       </c>
       <c r="J140" s="9" t="n">
-        <v>6.761</v>
+        <v>1.746</v>
       </c>
       <c r="K140" s="9" t="n">
-        <v>6.839</v>
+        <v>1.774</v>
       </c>
       <c r="L140" t="inlineStr"/>
       <c r="M140" s="14" t="inlineStr"/>
@@ -6784,39 +6784,39 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>ATECH</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D141" s="9" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E141" s="16" t="n">
-        <v>0.0256</v>
+        <v>0.365</v>
+      </c>
+      <c r="E141" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F141" s="11" t="n">
-        <v>971300</v>
+        <v>1122200</v>
       </c>
       <c r="G141" s="12" t="n">
-        <v>0.44</v>
+        <v>0.12</v>
       </c>
       <c r="H141" t="n">
-        <v>56.99</v>
-      </c>
-      <c r="I141" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>57.29</v>
+      </c>
+      <c r="I141" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J141" s="9" t="n">
-        <v>0.777</v>
+        <v>0.357</v>
       </c>
       <c r="K141" s="9" t="n">
-        <v>0.765</v>
+        <v>0.325</v>
       </c>
       <c r="L141" t="inlineStr"/>
       <c r="M141" s="14" t="inlineStr"/>
@@ -6829,28 +6829,28 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>0128</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>FRONTKN</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="D142" s="9" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="E142" s="16" t="n">
-        <v>0.0118</v>
+        <v>0.33</v>
+      </c>
+      <c r="E142" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F142" s="11" t="n">
-        <v>951700</v>
+        <v>1120700</v>
       </c>
       <c r="G142" s="12" t="n">
         <v>0.22</v>
       </c>
       <c r="H142" t="n">
-        <v>56.5</v>
+        <v>39.5</v>
       </c>
       <c r="I142" s="13" t="inlineStr">
         <is>
@@ -6858,10 +6858,10 @@
         </is>
       </c>
       <c r="J142" s="9" t="n">
-        <v>5.069</v>
+        <v>0.336</v>
       </c>
       <c r="K142" s="9" t="n">
-        <v>5.062</v>
+        <v>0.343</v>
       </c>
       <c r="L142" t="inlineStr"/>
       <c r="M142" s="14" t="inlineStr"/>
@@ -6874,39 +6874,39 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>0240</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>CORAZA</t>
         </is>
       </c>
       <c r="D143" s="9" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="E143" s="15" t="n">
-        <v>0</v>
+        <v>1.33</v>
+      </c>
+      <c r="E143" s="16" t="n">
+        <v>0.0231</v>
       </c>
       <c r="F143" s="11" t="n">
-        <v>951600</v>
+        <v>1114800</v>
       </c>
       <c r="G143" s="12" t="n">
-        <v>0.19</v>
+        <v>0.47</v>
       </c>
       <c r="H143" t="n">
-        <v>39.03</v>
-      </c>
-      <c r="I143" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.13</v>
+      </c>
+      <c r="I143" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J143" s="9" t="n">
-        <v>2.906</v>
+        <v>1.247</v>
       </c>
       <c r="K143" s="9" t="n">
-        <v>2.86</v>
+        <v>1.165</v>
       </c>
       <c r="L143" t="inlineStr"/>
       <c r="M143" s="14" t="inlineStr"/>
@@ -6919,28 +6919,28 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>4383</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>JTIASA</t>
+          <t>SPSETIA</t>
         </is>
       </c>
       <c r="D144" s="9" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E144" s="16" t="n">
-        <v>0.0162</v>
+        <v>0.0073</v>
       </c>
       <c r="F144" s="11" t="n">
-        <v>941200</v>
+        <v>1100000</v>
       </c>
       <c r="G144" s="12" t="n">
-        <v>0.34</v>
+        <v>0.16</v>
       </c>
       <c r="H144" t="n">
-        <v>40.19</v>
+        <v>29.43</v>
       </c>
       <c r="I144" s="13" t="inlineStr">
         <is>
@@ -6948,10 +6948,10 @@
         </is>
       </c>
       <c r="J144" s="9" t="n">
-        <v>0.957</v>
+        <v>0.739</v>
       </c>
       <c r="K144" s="9" t="n">
-        <v>1.012</v>
+        <v>0.806</v>
       </c>
       <c r="L144" t="inlineStr"/>
       <c r="M144" s="14" t="inlineStr"/>
@@ -6964,39 +6964,39 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D145" s="9" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="E145" s="10" t="n">
-        <v>-0.0092</v>
+        <v>0.27</v>
+      </c>
+      <c r="E145" s="16" t="n">
+        <v>0.0189</v>
       </c>
       <c r="F145" s="11" t="n">
-        <v>926400</v>
+        <v>1088600</v>
       </c>
       <c r="G145" s="12" t="n">
-        <v>0.23</v>
+        <v>0.14</v>
       </c>
       <c r="H145" t="n">
-        <v>57.29</v>
-      </c>
-      <c r="I145" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.49</v>
+      </c>
+      <c r="I145" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J145" s="9" t="n">
-        <v>1.043</v>
+        <v>0.284</v>
       </c>
       <c r="K145" s="9" t="n">
-        <v>0.887</v>
+        <v>0.305</v>
       </c>
       <c r="L145" t="inlineStr"/>
       <c r="M145" s="14" t="inlineStr"/>
@@ -7009,28 +7009,28 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>9059</t>
+          <t>0151</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>TSH</t>
+          <t>KGB</t>
         </is>
       </c>
       <c r="D146" s="9" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="E146" s="15" t="n">
-        <v>0</v>
+        <v>8.68</v>
+      </c>
+      <c r="E146" s="16" t="n">
+        <v>0.0212</v>
       </c>
       <c r="F146" s="11" t="n">
-        <v>924700</v>
+        <v>1075100</v>
       </c>
       <c r="G146" s="12" t="n">
-        <v>0.41</v>
+        <v>0.47</v>
       </c>
       <c r="H146" t="n">
-        <v>30.53</v>
+        <v>49.72</v>
       </c>
       <c r="I146" s="13" t="inlineStr">
         <is>
@@ -7038,10 +7038,10 @@
         </is>
       </c>
       <c r="J146" s="9" t="n">
-        <v>1.261</v>
+        <v>8.709</v>
       </c>
       <c r="K146" s="9" t="n">
-        <v>1.309</v>
+        <v>8.702</v>
       </c>
       <c r="L146" t="inlineStr"/>
       <c r="M146" s="14" t="inlineStr"/>
@@ -7054,39 +7054,39 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>0045</t>
+          <t>0298</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>SSB8</t>
+          <t>WENTEL</t>
         </is>
       </c>
       <c r="D147" s="9" t="n">
-        <v>0.65</v>
+        <v>0.24</v>
       </c>
       <c r="E147" s="16" t="n">
-        <v>0.0156</v>
+        <v>0.0213</v>
       </c>
       <c r="F147" s="11" t="n">
-        <v>902400</v>
+        <v>1073400</v>
       </c>
       <c r="G147" s="12" t="n">
-        <v>0.24</v>
+        <v>0.64</v>
       </c>
       <c r="H147" t="n">
-        <v>55.56</v>
-      </c>
-      <c r="I147" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.75</v>
+      </c>
+      <c r="I147" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J147" s="9" t="n">
-        <v>0.64</v>
+        <v>0.258</v>
       </c>
       <c r="K147" s="9" t="n">
-        <v>0.609</v>
+        <v>0.276</v>
       </c>
       <c r="L147" t="inlineStr"/>
       <c r="M147" s="14" t="inlineStr"/>
@@ -7099,39 +7099,39 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>0373</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>VERDANT</t>
         </is>
       </c>
       <c r="D148" s="9" t="n">
-        <v>2.85</v>
+        <v>0.235</v>
       </c>
       <c r="E148" s="10" t="n">
-        <v>-0.006999999999999999</v>
+        <v>-0.0408</v>
       </c>
       <c r="F148" s="11" t="n">
-        <v>894800</v>
+        <v>1066000</v>
       </c>
       <c r="G148" s="12" t="n">
-        <v>0.1</v>
+        <v>0.22</v>
       </c>
       <c r="H148" t="n">
-        <v>56.6</v>
-      </c>
-      <c r="I148" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.82</v>
+      </c>
+      <c r="I148" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J148" s="9" t="n">
-        <v>2.799</v>
+        <v>0.249</v>
       </c>
       <c r="K148" s="9" t="n">
-        <v>2.636</v>
+        <v>0.222</v>
       </c>
       <c r="L148" t="inlineStr"/>
       <c r="M148" s="14" t="inlineStr"/>
@@ -7144,28 +7144,28 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>0285</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>MERSEC</t>
         </is>
       </c>
       <c r="D149" s="9" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="E149" s="16" t="n">
-        <v>0.0036</v>
+        <v>0.27</v>
+      </c>
+      <c r="E149" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F149" s="11" t="n">
-        <v>864000</v>
+        <v>1054400</v>
       </c>
       <c r="G149" s="12" t="n">
-        <v>0.27</v>
+        <v>0.96</v>
       </c>
       <c r="H149" t="n">
-        <v>34.92</v>
+        <v>41.54</v>
       </c>
       <c r="I149" s="13" t="inlineStr">
         <is>
@@ -7173,10 +7173,10 @@
         </is>
       </c>
       <c r="J149" s="9" t="n">
-        <v>2.932</v>
+        <v>0.272</v>
       </c>
       <c r="K149" s="9" t="n">
-        <v>3.026</v>
+        <v>0.276</v>
       </c>
       <c r="L149" t="inlineStr"/>
       <c r="M149" s="14" t="inlineStr"/>
@@ -7189,39 +7189,39 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>0239</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>ECOMATE</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D150" s="9" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E150" s="15" t="n">
-        <v>0</v>
+        <v>1.1</v>
+      </c>
+      <c r="E150" s="16" t="n">
+        <v>0.0092</v>
       </c>
       <c r="F150" s="11" t="n">
-        <v>848000</v>
+        <v>1051400</v>
       </c>
       <c r="G150" s="12" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="H150" t="n">
-        <v>51.92</v>
-      </c>
-      <c r="I150" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.17</v>
+      </c>
+      <c r="I150" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J150" s="9" t="n">
-        <v>0.865</v>
+        <v>1.045</v>
       </c>
       <c r="K150" s="9" t="n">
-        <v>0.859</v>
+        <v>0.888</v>
       </c>
       <c r="L150" t="inlineStr"/>
       <c r="M150" s="14" t="inlineStr"/>
@@ -7234,39 +7234,39 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D151" s="9" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="E151" s="10" t="n">
-        <v>-0.0192</v>
+        <v>0.695</v>
+      </c>
+      <c r="E151" s="16" t="n">
+        <v>0.0072</v>
       </c>
       <c r="F151" s="11" t="n">
-        <v>839400</v>
+        <v>1051300</v>
       </c>
       <c r="G151" s="12" t="n">
-        <v>0.22</v>
+        <v>0.33</v>
       </c>
       <c r="H151" t="n">
-        <v>58.44</v>
-      </c>
-      <c r="I151" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.91</v>
+      </c>
+      <c r="I151" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J151" s="9" t="n">
-        <v>0.488</v>
+        <v>0.745</v>
       </c>
       <c r="K151" s="9" t="n">
-        <v>0.458</v>
+        <v>0.747</v>
       </c>
       <c r="L151" t="inlineStr"/>
       <c r="M151" s="14" t="inlineStr"/>
@@ -7279,28 +7279,28 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>SPSETIA</t>
+          <t>SKYECHIP</t>
         </is>
       </c>
       <c r="D152" s="9" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="E152" s="16" t="n">
-        <v>0.0073</v>
+        <v>2.76</v>
+      </c>
+      <c r="E152" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F152" s="11" t="n">
-        <v>838400</v>
+        <v>1042600</v>
       </c>
       <c r="G152" s="12" t="n">
-        <v>0.12</v>
+        <v>0.32</v>
       </c>
       <c r="H152" t="n">
-        <v>29.43</v>
+        <v>33.88</v>
       </c>
       <c r="I152" s="13" t="inlineStr">
         <is>
@@ -7308,10 +7308,10 @@
         </is>
       </c>
       <c r="J152" s="9" t="n">
-        <v>0.739</v>
+        <v>2.931</v>
       </c>
       <c r="K152" s="9" t="n">
-        <v>0.806</v>
+        <v>3.026</v>
       </c>
       <c r="L152" t="inlineStr"/>
       <c r="M152" s="14" t="inlineStr"/>
@@ -7324,28 +7324,28 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>SDG</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D153" s="9" t="n">
-        <v>5.96</v>
+        <v>2.71</v>
       </c>
       <c r="E153" s="16" t="n">
-        <v>0.0068</v>
+        <v>0.0037</v>
       </c>
       <c r="F153" s="11" t="n">
-        <v>832900</v>
+        <v>1008500</v>
       </c>
       <c r="G153" s="12" t="n">
-        <v>0.09</v>
+        <v>0.2</v>
       </c>
       <c r="H153" t="n">
-        <v>36.86</v>
+        <v>39.64</v>
       </c>
       <c r="I153" s="13" t="inlineStr">
         <is>
@@ -7353,10 +7353,10 @@
         </is>
       </c>
       <c r="J153" s="9" t="n">
-        <v>6.106</v>
+        <v>2.907</v>
       </c>
       <c r="K153" s="9" t="n">
-        <v>6.362</v>
+        <v>2.86</v>
       </c>
       <c r="L153" t="inlineStr"/>
       <c r="M153" s="14" t="inlineStr"/>
@@ -7369,39 +7369,39 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>5248</t>
+          <t>7943</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>BAUTO</t>
+          <t>GREENTEC</t>
         </is>
       </c>
       <c r="D154" s="9" t="n">
-        <v>0.895</v>
+        <v>0.29</v>
       </c>
       <c r="E154" s="10" t="n">
-        <v>-0.011</v>
+        <v>-0.0333</v>
       </c>
       <c r="F154" s="11" t="n">
-        <v>827400</v>
+        <v>1007000</v>
       </c>
       <c r="G154" s="12" t="n">
-        <v>0.53</v>
+        <v>0.92</v>
       </c>
       <c r="H154" t="n">
-        <v>38.69</v>
-      </c>
-      <c r="I154" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.97</v>
+      </c>
+      <c r="I154" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J154" s="9" t="n">
-        <v>0.917</v>
+        <v>0.257</v>
       </c>
       <c r="K154" s="9" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.211</v>
       </c>
       <c r="L154" t="inlineStr"/>
       <c r="M154" s="14" t="inlineStr"/>
@@ -7414,39 +7414,39 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>7160</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>MBSB</t>
+          <t>PENTA</t>
         </is>
       </c>
       <c r="D155" s="9" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="E155" s="10" t="n">
-        <v>-0.0182</v>
+        <v>5.52</v>
+      </c>
+      <c r="E155" s="16" t="n">
+        <v>0.0018</v>
       </c>
       <c r="F155" s="11" t="n">
-        <v>807700</v>
+        <v>995200</v>
       </c>
       <c r="G155" s="12" t="n">
-        <v>0.24</v>
+        <v>0.27</v>
       </c>
       <c r="H155" t="n">
-        <v>41.5</v>
-      </c>
-      <c r="I155" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.62</v>
+      </c>
+      <c r="I155" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J155" s="9" t="n">
-        <v>0.549</v>
+        <v>5.511</v>
       </c>
       <c r="K155" s="9" t="n">
-        <v>0.577</v>
+        <v>5.387</v>
       </c>
       <c r="L155" t="inlineStr"/>
       <c r="M155" s="14" t="inlineStr"/>
@@ -7459,28 +7459,28 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>4383</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>JTIASA</t>
         </is>
       </c>
       <c r="D156" s="9" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="E156" s="15" t="n">
-        <v>0</v>
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="E156" s="16" t="n">
+        <v>0.0162</v>
       </c>
       <c r="F156" s="11" t="n">
-        <v>787100</v>
+        <v>974100</v>
       </c>
       <c r="G156" s="12" t="n">
-        <v>0.16</v>
+        <v>0.35</v>
       </c>
       <c r="H156" t="n">
-        <v>42.09</v>
+        <v>40.19</v>
       </c>
       <c r="I156" s="13" t="inlineStr">
         <is>
@@ -7488,10 +7488,10 @@
         </is>
       </c>
       <c r="J156" s="9" t="n">
-        <v>1.746</v>
+        <v>0.957</v>
       </c>
       <c r="K156" s="9" t="n">
-        <v>1.774</v>
+        <v>1.012</v>
       </c>
       <c r="L156" t="inlineStr"/>
       <c r="M156" s="14" t="inlineStr"/>
@@ -7504,28 +7504,28 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D157" s="9" t="n">
-        <v>1.22</v>
+        <v>2.84</v>
       </c>
       <c r="E157" s="10" t="n">
-        <v>-0.0317</v>
+        <v>-0.0105</v>
       </c>
       <c r="F157" s="11" t="n">
-        <v>767400</v>
+        <v>970900</v>
       </c>
       <c r="G157" s="12" t="n">
-        <v>0.23</v>
+        <v>0.11</v>
       </c>
       <c r="H157" t="n">
-        <v>45.43</v>
+        <v>55.83</v>
       </c>
       <c r="I157" s="13" t="inlineStr">
         <is>
@@ -7533,10 +7533,10 @@
         </is>
       </c>
       <c r="J157" s="9" t="n">
-        <v>1.288</v>
+        <v>2.798</v>
       </c>
       <c r="K157" s="9" t="n">
-        <v>1.213</v>
+        <v>2.636</v>
       </c>
       <c r="L157" t="inlineStr"/>
       <c r="M157" s="14" t="inlineStr"/>
@@ -7549,28 +7549,28 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>9059</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>DUFU</t>
+          <t>TSH</t>
         </is>
       </c>
       <c r="D158" s="9" t="n">
-        <v>3.1</v>
+        <v>1.19</v>
       </c>
       <c r="E158" s="16" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="F158" s="11" t="n">
-        <v>766100</v>
+        <v>941600</v>
       </c>
       <c r="G158" s="12" t="n">
-        <v>0.24</v>
+        <v>0.41</v>
       </c>
       <c r="H158" t="n">
-        <v>56.22</v>
+        <v>33</v>
       </c>
       <c r="I158" s="13" t="inlineStr">
         <is>
@@ -7578,10 +7578,10 @@
         </is>
       </c>
       <c r="J158" s="9" t="n">
-        <v>3.031</v>
+        <v>1.262</v>
       </c>
       <c r="K158" s="9" t="n">
-        <v>2.839</v>
+        <v>1.309</v>
       </c>
       <c r="L158" t="inlineStr"/>
       <c r="M158" s="14" t="inlineStr"/>
@@ -7594,39 +7594,39 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>5223</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>MENTIGA</t>
+          <t>DUFU</t>
         </is>
       </c>
       <c r="D159" s="9" t="n">
-        <v>0.8</v>
+        <v>3.12</v>
       </c>
       <c r="E159" s="16" t="n">
-        <v>0.3793</v>
+        <v>0.013</v>
       </c>
       <c r="F159" s="11" t="n">
-        <v>748000</v>
+        <v>916000</v>
       </c>
       <c r="G159" s="12" t="n">
-        <v>33.85</v>
+        <v>0.29</v>
       </c>
       <c r="H159" t="n">
-        <v>74.09</v>
-      </c>
-      <c r="I159" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>57.02</v>
+      </c>
+      <c r="I159" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J159" s="9" t="n">
-        <v>0.61</v>
+        <v>3.033</v>
       </c>
       <c r="K159" s="9" t="n">
-        <v>0.642</v>
+        <v>2.839</v>
       </c>
       <c r="L159" t="inlineStr"/>
       <c r="M159" s="14" t="inlineStr"/>
@@ -7639,28 +7639,28 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>7160</t>
+          <t>0045</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>PENTA</t>
+          <t>SSB8</t>
         </is>
       </c>
       <c r="D160" s="9" t="n">
-        <v>5.44</v>
-      </c>
-      <c r="E160" s="10" t="n">
-        <v>-0.0127</v>
+        <v>0.65</v>
+      </c>
+      <c r="E160" s="16" t="n">
+        <v>0.0156</v>
       </c>
       <c r="F160" s="11" t="n">
-        <v>744600</v>
+        <v>912400</v>
       </c>
       <c r="G160" s="12" t="n">
-        <v>0.2</v>
+        <v>0.24</v>
       </c>
       <c r="H160" t="n">
-        <v>49.56</v>
+        <v>55.56</v>
       </c>
       <c r="I160" s="17" t="inlineStr">
         <is>
@@ -7668,10 +7668,10 @@
         </is>
       </c>
       <c r="J160" s="9" t="n">
-        <v>5.503</v>
+        <v>0.64</v>
       </c>
       <c r="K160" s="9" t="n">
-        <v>5.386</v>
+        <v>0.609</v>
       </c>
       <c r="L160" t="inlineStr"/>
       <c r="M160" s="14" t="inlineStr"/>
@@ -7684,28 +7684,28 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>5258</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>BIMB</t>
+          <t>CPETECH</t>
         </is>
       </c>
       <c r="D161" s="9" t="n">
-        <v>2.01</v>
+        <v>1.24</v>
       </c>
       <c r="E161" s="10" t="n">
-        <v>-0.005</v>
+        <v>-0.0159</v>
       </c>
       <c r="F161" s="11" t="n">
-        <v>728100</v>
+        <v>905000</v>
       </c>
       <c r="G161" s="12" t="n">
-        <v>0.93</v>
+        <v>0.27</v>
       </c>
       <c r="H161" t="n">
-        <v>35.29</v>
+        <v>46.99</v>
       </c>
       <c r="I161" s="13" t="inlineStr">
         <is>
@@ -7713,10 +7713,10 @@
         </is>
       </c>
       <c r="J161" s="9" t="n">
-        <v>2.049</v>
+        <v>1.29</v>
       </c>
       <c r="K161" s="9" t="n">
-        <v>2.09</v>
+        <v>1.213</v>
       </c>
       <c r="L161" t="inlineStr"/>
       <c r="M161" s="14" t="inlineStr"/>
@@ -7729,39 +7729,39 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>0375</t>
+          <t>4863</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>THMY</t>
+          <t>TM</t>
         </is>
       </c>
       <c r="D162" s="9" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="E162" s="16" t="n">
-        <v>0.009599999999999999</v>
+        <v>7.82</v>
+      </c>
+      <c r="E162" s="10" t="n">
+        <v>-0.0101</v>
       </c>
       <c r="F162" s="11" t="n">
-        <v>713900</v>
+        <v>903700</v>
       </c>
       <c r="G162" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="H162" t="n">
-        <v>51.87</v>
-      </c>
-      <c r="I162" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.32</v>
+      </c>
+      <c r="I162" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J162" s="9" t="n">
-        <v>2.117</v>
+        <v>7.888</v>
       </c>
       <c r="K162" s="9" t="n">
-        <v>1.979</v>
+        <v>7.864</v>
       </c>
       <c r="L162" t="inlineStr"/>
       <c r="M162" s="14" t="inlineStr"/>
@@ -7774,28 +7774,28 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>0391</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>AMBEST</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D163" s="9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="E163" s="16" t="n">
-        <v>0.0231</v>
+        <v>0.895</v>
+      </c>
+      <c r="E163" s="10" t="n">
+        <v>-0.011</v>
       </c>
       <c r="F163" s="11" t="n">
-        <v>710200</v>
+        <v>883400</v>
       </c>
       <c r="G163" s="12" t="n">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="H163" t="n">
-        <v>50.54</v>
+        <v>41.46</v>
       </c>
       <c r="I163" s="13" t="inlineStr">
         <is>
@@ -7803,10 +7803,10 @@
         </is>
       </c>
       <c r="J163" s="9" t="n">
-        <v>1.341</v>
+        <v>0.909</v>
       </c>
       <c r="K163" s="9" t="n">
-        <v>1.265</v>
+        <v>0.96</v>
       </c>
       <c r="L163" t="inlineStr"/>
       <c r="M163" s="14" t="inlineStr"/>
@@ -7819,39 +7819,39 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D164" s="9" t="n">
-        <v>0.9</v>
+        <v>0.515</v>
       </c>
       <c r="E164" s="10" t="n">
-        <v>-0.005500000000000001</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="F164" s="11" t="n">
-        <v>709100</v>
+        <v>869400</v>
       </c>
       <c r="G164" s="12" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="H164" t="n">
-        <v>43.06</v>
-      </c>
-      <c r="I164" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.96</v>
+      </c>
+      <c r="I164" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J164" s="9" t="n">
-        <v>0.91</v>
+        <v>0.489</v>
       </c>
       <c r="K164" s="9" t="n">
-        <v>0.96</v>
+        <v>0.459</v>
       </c>
       <c r="L164" t="inlineStr"/>
       <c r="M164" s="14" t="inlineStr"/>
@@ -7864,39 +7864,39 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>5236</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>SEG</t>
+          <t>MATRIX</t>
         </is>
       </c>
       <c r="D165" s="9" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E165" s="10" t="n">
-        <v>-0.007900000000000001</v>
+        <v>1.09</v>
+      </c>
+      <c r="E165" s="16" t="n">
+        <v>0.0187</v>
       </c>
       <c r="F165" s="11" t="n">
-        <v>680000</v>
+        <v>856300</v>
       </c>
       <c r="G165" s="12" t="n">
-        <v>0.57</v>
+        <v>0.68</v>
       </c>
       <c r="H165" t="n">
-        <v>36.25</v>
-      </c>
-      <c r="I165" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>45.75</v>
+      </c>
+      <c r="I165" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J165" s="9" t="n">
-        <v>0.631</v>
+        <v>1.097</v>
       </c>
       <c r="K165" s="9" t="n">
-        <v>0.63</v>
+        <v>1.14</v>
       </c>
       <c r="L165" t="inlineStr"/>
       <c r="M165" s="14" t="inlineStr"/>
@@ -7909,28 +7909,28 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>0151</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>KGB</t>
+          <t>MAHSING</t>
         </is>
       </c>
       <c r="D166" s="9" t="n">
-        <v>8.48</v>
+        <v>0.945</v>
       </c>
       <c r="E166" s="10" t="n">
-        <v>-0.0024</v>
+        <v>-0.0053</v>
       </c>
       <c r="F166" s="11" t="n">
-        <v>665800</v>
+        <v>856000</v>
       </c>
       <c r="G166" s="12" t="n">
-        <v>0.29</v>
+        <v>0.22</v>
       </c>
       <c r="H166" t="n">
-        <v>44.6</v>
+        <v>30.03</v>
       </c>
       <c r="I166" s="13" t="inlineStr">
         <is>
@@ -7938,10 +7938,10 @@
         </is>
       </c>
       <c r="J166" s="9" t="n">
-        <v>8.69</v>
+        <v>0.984</v>
       </c>
       <c r="K166" s="9" t="n">
-        <v>8.698</v>
+        <v>1.062</v>
       </c>
       <c r="L166" t="inlineStr"/>
       <c r="M166" s="14" t="inlineStr"/>
@@ -7954,39 +7954,39 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>4863</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>TM</t>
+          <t>MBSB</t>
         </is>
       </c>
       <c r="D167" s="9" t="n">
-        <v>7.84</v>
+        <v>0.535</v>
       </c>
       <c r="E167" s="10" t="n">
-        <v>-0.0076</v>
+        <v>-0.0273</v>
       </c>
       <c r="F167" s="11" t="n">
-        <v>655900</v>
+        <v>841900</v>
       </c>
       <c r="G167" s="12" t="n">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="H167" t="n">
-        <v>47.43</v>
-      </c>
-      <c r="I167" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.4</v>
+      </c>
+      <c r="I167" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J167" s="9" t="n">
-        <v>7.89</v>
+        <v>0.549</v>
       </c>
       <c r="K167" s="9" t="n">
-        <v>7.864</v>
+        <v>0.577</v>
       </c>
       <c r="L167" t="inlineStr"/>
       <c r="M167" s="14" t="inlineStr"/>
@@ -7999,28 +7999,28 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>0265</t>
+          <t>0375</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>INFOM</t>
+          <t>THMY</t>
         </is>
       </c>
       <c r="D168" s="9" t="n">
-        <v>1.88</v>
+        <v>2.12</v>
       </c>
       <c r="E168" s="16" t="n">
-        <v>0.0503</v>
+        <v>0.0144</v>
       </c>
       <c r="F168" s="11" t="n">
-        <v>654500</v>
+        <v>831500</v>
       </c>
       <c r="G168" s="12" t="n">
-        <v>0.92</v>
+        <v>0.35</v>
       </c>
       <c r="H168" t="n">
-        <v>71.94</v>
+        <v>52.42</v>
       </c>
       <c r="I168" s="13" t="inlineStr">
         <is>
@@ -8028,10 +8028,10 @@
         </is>
       </c>
       <c r="J168" s="9" t="n">
-        <v>1.754</v>
+        <v>2.118</v>
       </c>
       <c r="K168" s="9" t="n">
-        <v>1.628</v>
+        <v>1.98</v>
       </c>
       <c r="L168" t="inlineStr"/>
       <c r="M168" s="14" t="inlineStr"/>
@@ -8044,28 +8044,28 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>5258</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>DAYANG</t>
+          <t>BIMB</t>
         </is>
       </c>
       <c r="D169" s="9" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="E169" s="15" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="E169" s="10" t="n">
+        <v>-0.009899999999999999</v>
       </c>
       <c r="F169" s="11" t="n">
-        <v>646300</v>
+        <v>826200</v>
       </c>
       <c r="G169" s="12" t="n">
-        <v>0.29</v>
+        <v>1.06</v>
       </c>
       <c r="H169" t="n">
-        <v>31.14</v>
+        <v>33.38</v>
       </c>
       <c r="I169" s="13" t="inlineStr">
         <is>
@@ -8073,10 +8073,10 @@
         </is>
       </c>
       <c r="J169" s="9" t="n">
-        <v>1.43</v>
+        <v>2.048</v>
       </c>
       <c r="K169" s="9" t="n">
-        <v>1.481</v>
+        <v>2.089</v>
       </c>
       <c r="L169" t="inlineStr"/>
       <c r="M169" s="14" t="inlineStr"/>
@@ -8089,28 +8089,28 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>0271</t>
+          <t>5223</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>WELLS</t>
+          <t>MENTIGA</t>
         </is>
       </c>
       <c r="D170" s="9" t="n">
-        <v>0.535</v>
-      </c>
-      <c r="E170" s="10" t="n">
-        <v>-0.0183</v>
+        <v>0.79</v>
+      </c>
+      <c r="E170" s="16" t="n">
+        <v>0.3621</v>
       </c>
       <c r="F170" s="11" t="n">
-        <v>607700</v>
+        <v>802100</v>
       </c>
       <c r="G170" s="12" t="n">
-        <v>0.55</v>
+        <v>36.29</v>
       </c>
       <c r="H170" t="n">
-        <v>33.07</v>
+        <v>73.45</v>
       </c>
       <c r="I170" s="17" t="inlineStr">
         <is>
@@ -8118,10 +8118,10 @@
         </is>
       </c>
       <c r="J170" s="9" t="n">
-        <v>0.573</v>
+        <v>0.609</v>
       </c>
       <c r="K170" s="9" t="n">
-        <v>0.616</v>
+        <v>0.642</v>
       </c>
       <c r="L170" t="inlineStr"/>
       <c r="M170" s="14" t="inlineStr"/>
@@ -8134,28 +8134,28 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>0265</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>INFOM</t>
         </is>
       </c>
       <c r="D171" s="9" t="n">
-        <v>0.945</v>
-      </c>
-      <c r="E171" s="10" t="n">
-        <v>-0.0053</v>
+        <v>1.87</v>
+      </c>
+      <c r="E171" s="16" t="n">
+        <v>0.0447</v>
       </c>
       <c r="F171" s="11" t="n">
-        <v>595500</v>
+        <v>782500</v>
       </c>
       <c r="G171" s="12" t="n">
-        <v>0.16</v>
+        <v>1.1</v>
       </c>
       <c r="H171" t="n">
-        <v>30.03</v>
+        <v>71.20999999999999</v>
       </c>
       <c r="I171" s="13" t="inlineStr">
         <is>
@@ -8163,10 +8163,10 @@
         </is>
       </c>
       <c r="J171" s="9" t="n">
-        <v>0.984</v>
+        <v>1.753</v>
       </c>
       <c r="K171" s="9" t="n">
-        <v>1.062</v>
+        <v>1.627</v>
       </c>
       <c r="L171" t="inlineStr"/>
       <c r="M171" s="14" t="inlineStr"/>
@@ -8179,39 +8179,39 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>6947</t>
+          <t>0336</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>CDB</t>
+          <t>WINSTAR</t>
         </is>
       </c>
       <c r="D172" s="9" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="E172" s="15" t="n">
-        <v>0</v>
+        <v>0.63</v>
+      </c>
+      <c r="E172" s="10" t="n">
+        <v>-0.0156</v>
       </c>
       <c r="F172" s="11" t="n">
-        <v>571500</v>
+        <v>769800</v>
       </c>
       <c r="G172" s="12" t="n">
-        <v>0.18</v>
+        <v>1.27</v>
       </c>
       <c r="H172" t="n">
-        <v>39.69</v>
-      </c>
-      <c r="I172" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.73</v>
+      </c>
+      <c r="I172" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J172" s="9" t="n">
-        <v>2.569</v>
+        <v>0.643</v>
       </c>
       <c r="K172" s="9" t="n">
-        <v>2.708</v>
+        <v>0.63</v>
       </c>
       <c r="L172" t="inlineStr"/>
       <c r="M172" s="14" t="inlineStr"/>
@@ -8224,28 +8224,28 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>5326</t>
+          <t>5053</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>99SMART</t>
+          <t>OSK</t>
         </is>
       </c>
       <c r="D173" s="9" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="E173" s="10" t="n">
-        <v>-0.0032</v>
+        <v>1.69</v>
+      </c>
+      <c r="E173" s="16" t="n">
+        <v>0.0181</v>
       </c>
       <c r="F173" s="11" t="n">
-        <v>571200</v>
+        <v>748400</v>
       </c>
       <c r="G173" s="12" t="n">
-        <v>0.13</v>
+        <v>0.5</v>
       </c>
       <c r="H173" t="n">
-        <v>38.11</v>
+        <v>36.53</v>
       </c>
       <c r="I173" s="13" t="inlineStr">
         <is>
@@ -8253,10 +8253,10 @@
         </is>
       </c>
       <c r="J173" s="9" t="n">
-        <v>3.17</v>
+        <v>1.756</v>
       </c>
       <c r="K173" s="9" t="n">
-        <v>3.359</v>
+        <v>1.902</v>
       </c>
       <c r="L173" t="inlineStr"/>
       <c r="M173" s="14" t="inlineStr"/>
@@ -8269,28 +8269,28 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>0391</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>AMBEST</t>
         </is>
       </c>
       <c r="D174" s="9" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E174" s="10" t="n">
-        <v>-0.0234</v>
+        <v>1.33</v>
+      </c>
+      <c r="E174" s="16" t="n">
+        <v>0.0231</v>
       </c>
       <c r="F174" s="11" t="n">
-        <v>568000</v>
+        <v>746800</v>
       </c>
       <c r="G174" s="12" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="H174" t="n">
-        <v>46.09</v>
+        <v>50.54</v>
       </c>
       <c r="I174" s="13" t="inlineStr">
         <is>
@@ -8298,10 +8298,10 @@
         </is>
       </c>
       <c r="J174" s="9" t="n">
-        <v>0.637</v>
+        <v>1.341</v>
       </c>
       <c r="K174" s="9" t="n">
-        <v>0.617</v>
+        <v>1.265</v>
       </c>
       <c r="L174" t="inlineStr"/>
       <c r="M174" s="14" t="inlineStr"/>
@@ -8314,28 +8314,28 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>5916</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>MSC</t>
+          <t>SUNWAY</t>
         </is>
       </c>
       <c r="D175" s="9" t="n">
-        <v>1.65</v>
+        <v>4.45</v>
       </c>
       <c r="E175" s="16" t="n">
-        <v>0.0123</v>
+        <v>0.0114</v>
       </c>
       <c r="F175" s="11" t="n">
-        <v>562500</v>
+        <v>745000</v>
       </c>
       <c r="G175" s="12" t="n">
-        <v>0.52</v>
+        <v>0.13</v>
       </c>
       <c r="H175" t="n">
-        <v>45.36</v>
+        <v>44.36</v>
       </c>
       <c r="I175" s="17" t="inlineStr">
         <is>
@@ -8343,10 +8343,10 @@
         </is>
       </c>
       <c r="J175" s="9" t="n">
-        <v>1.67</v>
+        <v>4.475</v>
       </c>
       <c r="K175" s="9" t="n">
-        <v>1.798</v>
+        <v>4.774</v>
       </c>
       <c r="L175" t="inlineStr"/>
       <c r="M175" s="14" t="inlineStr"/>
@@ -8359,39 +8359,39 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>7293</t>
+          <t>5141</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>YINSON</t>
+          <t>DAYANG</t>
         </is>
       </c>
       <c r="D176" s="9" t="n">
-        <v>2.16</v>
+        <v>1.37</v>
       </c>
       <c r="E176" s="16" t="n">
-        <v>0.004699999999999999</v>
+        <v>0.0074</v>
       </c>
       <c r="F176" s="11" t="n">
-        <v>560500</v>
+        <v>721600</v>
       </c>
       <c r="G176" s="12" t="n">
-        <v>0.24</v>
+        <v>0.32</v>
       </c>
       <c r="H176" t="n">
-        <v>58.6</v>
-      </c>
-      <c r="I176" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.89</v>
+      </c>
+      <c r="I176" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J176" s="9" t="n">
-        <v>2.104</v>
+        <v>1.431</v>
       </c>
       <c r="K176" s="9" t="n">
-        <v>2.051</v>
+        <v>1.481</v>
       </c>
       <c r="L176" t="inlineStr"/>
       <c r="M176" s="14" t="inlineStr"/>
@@ -8404,28 +8404,28 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>7174</t>
+          <t>9792</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>CAB</t>
+          <t>SEG</t>
         </is>
       </c>
       <c r="D177" s="9" t="n">
-        <v>0.585</v>
+        <v>0.625</v>
       </c>
       <c r="E177" s="10" t="n">
-        <v>-0.008500000000000001</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="F177" s="11" t="n">
-        <v>557300</v>
+        <v>718500</v>
       </c>
       <c r="G177" s="12" t="n">
-        <v>0.43</v>
+        <v>0.6</v>
       </c>
       <c r="H177" t="n">
-        <v>55</v>
+        <v>36.25</v>
       </c>
       <c r="I177" s="13" t="inlineStr">
         <is>
@@ -8433,10 +8433,10 @@
         </is>
       </c>
       <c r="J177" s="9" t="n">
-        <v>0.582</v>
+        <v>0.631</v>
       </c>
       <c r="K177" s="9" t="n">
-        <v>0.545</v>
+        <v>0.63</v>
       </c>
       <c r="L177" t="inlineStr"/>
       <c r="M177" s="14" t="inlineStr"/>
@@ -8449,39 +8449,39 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>5053</t>
+          <t>6947</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>OSK</t>
+          <t>CDB</t>
         </is>
       </c>
       <c r="D178" s="9" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="E178" s="16" t="n">
-        <v>0.012</v>
+        <v>2.53</v>
+      </c>
+      <c r="E178" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F178" s="11" t="n">
-        <v>540200</v>
+        <v>707000</v>
       </c>
       <c r="G178" s="12" t="n">
-        <v>0.36</v>
+        <v>0.22</v>
       </c>
       <c r="H178" t="n">
-        <v>34.85</v>
-      </c>
-      <c r="I178" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>39.69</v>
+      </c>
+      <c r="I178" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J178" s="9" t="n">
-        <v>1.755</v>
+        <v>2.569</v>
       </c>
       <c r="K178" s="9" t="n">
-        <v>1.902</v>
+        <v>2.708</v>
       </c>
       <c r="L178" t="inlineStr"/>
       <c r="M178" s="14" t="inlineStr"/>
@@ -8494,28 +8494,28 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>5211</t>
+          <t>5331</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>SUNWAY</t>
+          <t>PGLOBAL</t>
         </is>
       </c>
       <c r="D179" s="9" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="E179" s="16" t="n">
-        <v>0.0114</v>
+        <v>0.605</v>
+      </c>
+      <c r="E179" s="10" t="n">
+        <v>-0.032</v>
       </c>
       <c r="F179" s="11" t="n">
-        <v>536100</v>
+        <v>682700</v>
       </c>
       <c r="G179" s="12" t="n">
-        <v>0.09</v>
+        <v>0.88</v>
       </c>
       <c r="H179" t="n">
-        <v>44.36</v>
+        <v>69.01000000000001</v>
       </c>
       <c r="I179" s="17" t="inlineStr">
         <is>
@@ -8523,10 +8523,10 @@
         </is>
       </c>
       <c r="J179" s="9" t="n">
-        <v>4.475</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="K179" s="9" t="n">
-        <v>4.774</v>
+        <v>0.52</v>
       </c>
       <c r="L179" t="inlineStr"/>
       <c r="M179" s="14" t="inlineStr"/>
@@ -8539,39 +8539,39 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>5331</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>PGLOBAL</t>
+          <t>SUNREIT</t>
         </is>
       </c>
       <c r="D180" s="9" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="E180" s="10" t="n">
-        <v>-0.024</v>
+        <v>2.03</v>
+      </c>
+      <c r="E180" s="16" t="n">
+        <v>0.01</v>
       </c>
       <c r="F180" s="11" t="n">
-        <v>532700</v>
+        <v>628500</v>
       </c>
       <c r="G180" s="12" t="n">
-        <v>0.68</v>
+        <v>0.19</v>
       </c>
       <c r="H180" t="n">
-        <v>71.29000000000001</v>
-      </c>
-      <c r="I180" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.39</v>
+      </c>
+      <c r="I180" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J180" s="9" t="n">
-        <v>0.5610000000000001</v>
+        <v>2.05</v>
       </c>
       <c r="K180" s="9" t="n">
-        <v>0.52</v>
+        <v>2.077</v>
       </c>
       <c r="L180" t="inlineStr"/>
       <c r="M180" s="14" t="inlineStr"/>
@@ -8584,39 +8584,39 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>0249</t>
+          <t>7174</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>LGMS</t>
+          <t>CAB</t>
         </is>
       </c>
       <c r="D181" s="9" t="n">
-        <v>0.535</v>
-      </c>
-      <c r="E181" s="10" t="n">
-        <v>-0.009300000000000001</v>
+        <v>0.59</v>
+      </c>
+      <c r="E181" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F181" s="11" t="n">
-        <v>523300</v>
+        <v>613400</v>
       </c>
       <c r="G181" s="12" t="n">
-        <v>0.49</v>
+        <v>0.47</v>
       </c>
       <c r="H181" t="n">
-        <v>55.22</v>
-      </c>
-      <c r="I181" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>57.19</v>
+      </c>
+      <c r="I181" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J181" s="9" t="n">
-        <v>0.528</v>
+        <v>0.582</v>
       </c>
       <c r="K181" s="9" t="n">
-        <v>0.506</v>
+        <v>0.545</v>
       </c>
       <c r="L181" t="inlineStr"/>
       <c r="M181" s="14" t="inlineStr"/>
@@ -8629,39 +8629,39 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>5162</t>
+          <t>0271</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>VSTECS</t>
+          <t>WELLS</t>
         </is>
       </c>
       <c r="D182" s="9" t="n">
-        <v>1.59</v>
+        <v>0.535</v>
       </c>
       <c r="E182" s="10" t="n">
-        <v>-0.0063</v>
+        <v>-0.0183</v>
       </c>
       <c r="F182" s="11" t="n">
-        <v>518200</v>
+        <v>607700</v>
       </c>
       <c r="G182" s="12" t="n">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="H182" t="n">
-        <v>43.3</v>
-      </c>
-      <c r="I182" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>33.07</v>
+      </c>
+      <c r="I182" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J182" s="9" t="n">
-        <v>1.652</v>
+        <v>0.573</v>
       </c>
       <c r="K182" s="9" t="n">
-        <v>1.674</v>
+        <v>0.616</v>
       </c>
       <c r="L182" t="inlineStr"/>
       <c r="M182" s="14" t="inlineStr"/>
@@ -8674,28 +8674,28 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>5326</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>SUNREIT</t>
+          <t>99SMART</t>
         </is>
       </c>
       <c r="D183" s="9" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="E183" s="16" t="n">
-        <v>0.005</v>
+        <v>3.07</v>
+      </c>
+      <c r="E183" s="10" t="n">
+        <v>-0.0032</v>
       </c>
       <c r="F183" s="11" t="n">
-        <v>503100</v>
+        <v>607100</v>
       </c>
       <c r="G183" s="12" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="H183" t="n">
-        <v>43.54</v>
+        <v>38.11</v>
       </c>
       <c r="I183" s="13" t="inlineStr">
         <is>
@@ -8703,16 +8703,466 @@
         </is>
       </c>
       <c r="J183" s="9" t="n">
-        <v>2.049</v>
+        <v>3.17</v>
       </c>
       <c r="K183" s="9" t="n">
-        <v>2.077</v>
+        <v>3.359</v>
       </c>
       <c r="L183" t="inlineStr"/>
       <c r="M183" s="14" t="inlineStr"/>
     </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>5916</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>MSC</t>
+        </is>
+      </c>
+      <c r="D184" s="9" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="E184" s="16" t="n">
+        <v>0.0245</v>
+      </c>
+      <c r="F184" s="11" t="n">
+        <v>605100</v>
+      </c>
+      <c r="G184" s="12" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="H184" t="n">
+        <v>47.49</v>
+      </c>
+      <c r="I184" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J184" s="9" t="n">
+        <v>1.672</v>
+      </c>
+      <c r="K184" s="9" t="n">
+        <v>1.798</v>
+      </c>
+      <c r="L184" t="inlineStr"/>
+      <c r="M184" s="14" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>3794</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>MCEMENT</t>
+        </is>
+      </c>
+      <c r="D185" s="9" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="E185" s="10" t="n">
+        <v>-0.005500000000000001</v>
+      </c>
+      <c r="F185" s="11" t="n">
+        <v>587900</v>
+      </c>
+      <c r="G185" s="12" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="H185" t="n">
+        <v>38.35</v>
+      </c>
+      <c r="I185" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J185" s="9" t="n">
+        <v>5.559</v>
+      </c>
+      <c r="K185" s="9" t="n">
+        <v>5.891</v>
+      </c>
+      <c r="L185" t="inlineStr"/>
+      <c r="M185" s="14" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>0112</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>MIKROMB</t>
+        </is>
+      </c>
+      <c r="D186" s="9" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="E186" s="10" t="n">
+        <v>-0.0234</v>
+      </c>
+      <c r="F186" s="11" t="n">
+        <v>575300</v>
+      </c>
+      <c r="G186" s="12" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H186" t="n">
+        <v>46.09</v>
+      </c>
+      <c r="I186" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J186" s="9" t="n">
+        <v>0.637</v>
+      </c>
+      <c r="K186" s="9" t="n">
+        <v>0.617</v>
+      </c>
+      <c r="L186" t="inlineStr"/>
+      <c r="M186" s="14" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>7293</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>YINSON</t>
+        </is>
+      </c>
+      <c r="D187" s="9" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="E187" s="16" t="n">
+        <v>0.004699999999999999</v>
+      </c>
+      <c r="F187" s="11" t="n">
+        <v>572900</v>
+      </c>
+      <c r="G187" s="12" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H187" t="n">
+        <v>58.6</v>
+      </c>
+      <c r="I187" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J187" s="9" t="n">
+        <v>2.104</v>
+      </c>
+      <c r="K187" s="9" t="n">
+        <v>2.051</v>
+      </c>
+      <c r="L187" t="inlineStr"/>
+      <c r="M187" s="14" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>0351</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>LSH</t>
+        </is>
+      </c>
+      <c r="D188" s="9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="E188" s="10" t="n">
+        <v>-0.0126</v>
+      </c>
+      <c r="F188" s="11" t="n">
+        <v>567500</v>
+      </c>
+      <c r="G188" s="12" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="H188" t="n">
+        <v>41.55</v>
+      </c>
+      <c r="I188" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J188" s="9" t="n">
+        <v>1.641</v>
+      </c>
+      <c r="K188" s="9" t="n">
+        <v>1.613</v>
+      </c>
+      <c r="L188" t="inlineStr"/>
+      <c r="M188" s="14" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>5306</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>FFB</t>
+        </is>
+      </c>
+      <c r="D189" s="9" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="E189" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F189" s="11" t="n">
+        <v>540900</v>
+      </c>
+      <c r="G189" s="12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H189" t="n">
+        <v>31.71</v>
+      </c>
+      <c r="I189" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J189" s="9" t="n">
+        <v>1.853</v>
+      </c>
+      <c r="K189" s="9" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="L189" t="inlineStr"/>
+      <c r="M189" s="14" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>0249</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>LGMS</t>
+        </is>
+      </c>
+      <c r="D190" s="9" t="n">
+        <v>0.535</v>
+      </c>
+      <c r="E190" s="10" t="n">
+        <v>-0.009300000000000001</v>
+      </c>
+      <c r="F190" s="11" t="n">
+        <v>536700</v>
+      </c>
+      <c r="G190" s="12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H190" t="n">
+        <v>55.22</v>
+      </c>
+      <c r="I190" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J190" s="9" t="n">
+        <v>0.528</v>
+      </c>
+      <c r="K190" s="9" t="n">
+        <v>0.506</v>
+      </c>
+      <c r="L190" t="inlineStr"/>
+      <c r="M190" s="14" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>5162</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>VSTECS</t>
+        </is>
+      </c>
+      <c r="D191" s="9" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="E191" s="10" t="n">
+        <v>-0.0125</v>
+      </c>
+      <c r="F191" s="11" t="n">
+        <v>529800</v>
+      </c>
+      <c r="G191" s="12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H191" t="n">
+        <v>42.48</v>
+      </c>
+      <c r="I191" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J191" s="9" t="n">
+        <v>1.651</v>
+      </c>
+      <c r="K191" s="9" t="n">
+        <v>1.673</v>
+      </c>
+      <c r="L191" t="inlineStr"/>
+      <c r="M191" s="14" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>7081</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>PHARMA</t>
+        </is>
+      </c>
+      <c r="D192" s="9" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="E192" s="10" t="n">
+        <v>-0.0289</v>
+      </c>
+      <c r="F192" s="11" t="n">
+        <v>518100</v>
+      </c>
+      <c r="G192" s="12" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H192" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="I192" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J192" s="9" t="n">
+        <v>0.987</v>
+      </c>
+      <c r="K192" s="9" t="n">
+        <v>1.099</v>
+      </c>
+      <c r="L192" t="inlineStr"/>
+      <c r="M192" s="14" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>2488</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>ABMB</t>
+        </is>
+      </c>
+      <c r="D193" s="9" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="E193" s="16" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="F193" s="11" t="n">
+        <v>500200</v>
+      </c>
+      <c r="G193" s="12" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="H193" t="n">
+        <v>39.48</v>
+      </c>
+      <c r="I193" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J193" s="9" t="n">
+        <v>4.676</v>
+      </c>
+      <c r="K193" s="9" t="n">
+        <v>4.796</v>
+      </c>
+      <c r="L193" t="inlineStr"/>
+      <c r="M193" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M183"/>
+  <autoFilter ref="A1:M193"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-14/bursa-report-2026-10-14.xlsx
+++ b/docs/downloads/2026-10-14/bursa-report-2026-10-14.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-14" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-14'!$A$1:$M$193</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-14'!$A$1:$M$197</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M193"/>
+  <dimension ref="A1:M197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -566,19 +566,19 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.027</v>
+        <v>0.0225</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>4002200</v>
+        <v>4023500</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>58.07</v>
+        <v>57.36</v>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>2.197</v>
+        <v>2.196</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>2.145</v>
+        <v>2.144</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
@@ -598,7 +598,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>SAR转多信号，RSI 58.07未超买，现价高于50日均线约6.3%，技术面信号偏可靠。</t>
+          <t>SAR转多，RSI 57.36处中性偏上，未超买；现价高于50日均线约5.9%，技术面信号偏正面。</t>
         </is>
       </c>
     </row>
@@ -625,10 +625,10 @@
         <v>-0.1538</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>208537800</v>
+        <v>218508900</v>
       </c>
       <c r="G3" s="12" t="n">
-        <v>0.47</v>
+        <v>0.49</v>
       </c>
       <c r="H3" t="n">
         <v>20.87</v>
@@ -670,7 +670,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>158942400</v>
+        <v>159561900</v>
       </c>
       <c r="G4" s="12" t="n"/>
       <c r="I4" s="13" t="inlineStr">
@@ -706,7 +706,7 @@
         <v>-0.0333</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>61449700</v>
+        <v>61705700</v>
       </c>
       <c r="G5" s="12" t="n">
         <v>0.88</v>
@@ -751,10 +751,10 @@
         <v>0.0409</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>50631900</v>
+        <v>51309500</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="H6" t="n">
         <v>66.39</v>
@@ -790,19 +790,19 @@
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.405</v>
+        <v>0.41</v>
       </c>
       <c r="E7" s="16" t="n">
-        <v>0.0385</v>
+        <v>0.0513</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>42730000</v>
+        <v>42780100</v>
       </c>
       <c r="G7" s="12" t="n">
         <v>1.15</v>
       </c>
       <c r="H7" t="n">
-        <v>73.73999999999999</v>
+        <v>74.70999999999999</v>
       </c>
       <c r="I7" s="17" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="J7" s="9" t="n">
-        <v>0.367</v>
+        <v>0.368</v>
       </c>
       <c r="K7" s="9" t="n">
         <v>0.256</v>
@@ -841,10 +841,10 @@
         <v>0</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>36069100</v>
+        <v>36462100</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="H8" t="n">
         <v>48.61</v>
@@ -880,19 +880,19 @@
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.335</v>
-      </c>
-      <c r="E9" s="10" t="n">
-        <v>-0.0147</v>
+        <v>0.34</v>
+      </c>
+      <c r="E9" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>30707700</v>
+        <v>30859600</v>
       </c>
       <c r="G9" s="12" t="n">
         <v>0.43</v>
       </c>
       <c r="H9" t="n">
-        <v>68.87</v>
+        <v>71.22</v>
       </c>
       <c r="I9" s="17" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         </is>
       </c>
       <c r="J9" s="9" t="n">
-        <v>0.293</v>
+        <v>0.294</v>
       </c>
       <c r="K9" s="9" t="n">
         <v>0.251</v>
@@ -931,10 +931,10 @@
         <v>-0.0208</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>22134100</v>
+        <v>22662000</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>2.43</v>
+        <v>2.49</v>
       </c>
       <c r="H10" t="n">
         <v>18.65</v>
@@ -961,39 +961,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>7020</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>ASTEEL</t>
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="E11" s="10" t="n">
-        <v>-0.0105</v>
+        <v>0.1</v>
+      </c>
+      <c r="E11" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>16294600</v>
+        <v>18220700</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>0.46</v>
+        <v>6.64</v>
       </c>
       <c r="H11" t="n">
-        <v>44.59</v>
-      </c>
-      <c r="I11" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.68</v>
+      </c>
+      <c r="I11" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J11" s="9" t="n">
-        <v>0.489</v>
+        <v>0.097</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>0.482</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="14" t="inlineStr"/>
@@ -1006,39 +1006,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>7020</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ASTEEL</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>0.105</v>
-      </c>
-      <c r="E12" s="16" t="n">
-        <v>0.05</v>
+        <v>0.47</v>
+      </c>
+      <c r="E12" s="10" t="n">
+        <v>-0.0105</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>16252600</v>
+        <v>16331400</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>5.93</v>
+        <v>0.46</v>
       </c>
       <c r="H12" t="n">
-        <v>57.96</v>
-      </c>
-      <c r="I12" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.59</v>
+      </c>
+      <c r="I12" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J12" s="9" t="n">
-        <v>0.097</v>
+        <v>0.489</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.482</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="14" t="inlineStr"/>
@@ -1051,28 +1051,28 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>7079</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>TWL</t>
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>3.89</v>
-      </c>
-      <c r="E13" s="10" t="n">
-        <v>-0.0512</v>
+        <v>0.025</v>
+      </c>
+      <c r="E13" s="16" t="n">
+        <v>0.25</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>14154700</v>
+        <v>14414600</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>1.6</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>49.97</v>
+        <v>51.85</v>
       </c>
       <c r="I13" s="13" t="inlineStr">
         <is>
@@ -1080,10 +1080,10 @@
         </is>
       </c>
       <c r="J13" s="9" t="n">
-        <v>3.99</v>
+        <v>0.024</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>3.507</v>
+        <v>0.025</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="14" t="inlineStr"/>
@@ -1096,39 +1096,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E14" s="15" t="n">
-        <v>0</v>
+        <v>3.91</v>
+      </c>
+      <c r="E14" s="10" t="n">
+        <v>-0.0463</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>12866600</v>
+        <v>14407900</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>0.51</v>
+        <v>1.63</v>
       </c>
       <c r="H14" t="n">
-        <v>68.89</v>
-      </c>
-      <c r="I14" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.64</v>
+      </c>
+      <c r="I14" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J14" s="9" t="n">
-        <v>0.593</v>
+        <v>3.992</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>0.516</v>
+        <v>3.507</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="14" t="inlineStr"/>
@@ -1141,39 +1141,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="E15" s="10" t="n">
-        <v>-0.09320000000000001</v>
+        <v>0.63</v>
+      </c>
+      <c r="E15" s="16" t="n">
+        <v>0.008</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>12692700</v>
+        <v>14046100</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>0.89</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>45.71</v>
-      </c>
-      <c r="I15" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>70.04000000000001</v>
+      </c>
+      <c r="I15" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J15" s="9" t="n">
-        <v>0.77</v>
+        <v>0.593</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>0.72</v>
+        <v>0.516</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="14" t="inlineStr"/>
@@ -1186,28 +1186,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>2.09</v>
+        <v>0.445</v>
       </c>
       <c r="E16" s="16" t="n">
-        <v>0.0146</v>
+        <v>0.023</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>12343200</v>
+        <v>12922400</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>0.4</v>
+        <v>0.63</v>
       </c>
       <c r="H16" t="n">
-        <v>64.08</v>
+        <v>61.25</v>
       </c>
       <c r="I16" s="17" t="inlineStr">
         <is>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="J16" s="9" t="n">
-        <v>1.902</v>
+        <v>0.416</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>1.698</v>
+        <v>0.357</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="14" t="inlineStr"/>
@@ -1231,39 +1231,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>0.445</v>
-      </c>
-      <c r="E17" s="16" t="n">
-        <v>0.023</v>
+        <v>0.73</v>
+      </c>
+      <c r="E17" s="10" t="n">
+        <v>-0.09320000000000001</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>12101500</v>
+        <v>12719700</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>0.59</v>
+        <v>0.89</v>
       </c>
       <c r="H17" t="n">
-        <v>61.25</v>
-      </c>
-      <c r="I17" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.71</v>
+      </c>
+      <c r="I17" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J17" s="9" t="n">
-        <v>0.416</v>
+        <v>0.77</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>0.357</v>
+        <v>0.72</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="14" t="inlineStr"/>
@@ -1276,28 +1276,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>0.315</v>
+        <v>2.06</v>
       </c>
       <c r="E18" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>11667300</v>
+        <v>12543400</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>0.6</v>
+        <v>0.41</v>
       </c>
       <c r="H18" t="n">
-        <v>61.97</v>
+        <v>62.88</v>
       </c>
       <c r="I18" s="17" t="inlineStr">
         <is>
@@ -1305,10 +1305,10 @@
         </is>
       </c>
       <c r="J18" s="9" t="n">
-        <v>0.308</v>
+        <v>1.899</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>0.298</v>
+        <v>1.697</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="14" t="inlineStr"/>
@@ -1321,28 +1321,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="E19" s="16" t="n">
-        <v>0.0133</v>
+        <v>0.315</v>
+      </c>
+      <c r="E19" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>10937600</v>
+        <v>11667300</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>0.74</v>
+        <v>0.6</v>
       </c>
       <c r="H19" t="n">
-        <v>48.88</v>
+        <v>61.97</v>
       </c>
       <c r="I19" s="17" t="inlineStr">
         <is>
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="J19" s="9" t="n">
-        <v>7.598</v>
+        <v>0.308</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>7.719</v>
+        <v>0.298</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="14" t="inlineStr"/>
@@ -1366,28 +1366,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E20" s="10" t="n">
-        <v>-0.005699999999999999</v>
+        <v>7.6</v>
+      </c>
+      <c r="E20" s="16" t="n">
+        <v>0.0133</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>10679500</v>
+        <v>10982300</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>0.54</v>
+        <v>0.74</v>
       </c>
       <c r="H20" t="n">
-        <v>46.29</v>
+        <v>48.88</v>
       </c>
       <c r="I20" s="17" t="inlineStr">
         <is>
@@ -1395,10 +1395,10 @@
         </is>
       </c>
       <c r="J20" s="9" t="n">
-        <v>0.868</v>
+        <v>7.598</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>0.869</v>
+        <v>7.719</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="14" t="inlineStr"/>
@@ -1411,39 +1411,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0051</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CUSCAPI</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="E21" s="16" t="n">
-        <v>0.125</v>
+        <v>0.865</v>
+      </c>
+      <c r="E21" s="10" t="n">
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>10178900</v>
+        <v>10809500</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>0.73</v>
+        <v>0.55</v>
       </c>
       <c r="H21" t="n">
-        <v>38.83</v>
-      </c>
-      <c r="I21" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.29</v>
+      </c>
+      <c r="I21" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J21" s="9" t="n">
-        <v>0.05</v>
+        <v>0.868</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>0.067</v>
+        <v>0.869</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="14" t="inlineStr"/>
@@ -1456,39 +1456,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>0051</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>CUSCAPI</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E22" s="15" t="n">
-        <v>0</v>
+        <v>0.045</v>
+      </c>
+      <c r="E22" s="16" t="n">
+        <v>0.125</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>9253500</v>
+        <v>10208900</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>0.61</v>
+        <v>0.74</v>
       </c>
       <c r="H22" t="n">
-        <v>50.46</v>
-      </c>
-      <c r="I22" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.83</v>
+      </c>
+      <c r="I22" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J22" s="9" t="n">
-        <v>0.774</v>
+        <v>0.05</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>0.775</v>
+        <v>0.067</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="14" t="inlineStr"/>
@@ -1501,28 +1501,28 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>0.62</v>
+        <v>0.775</v>
       </c>
       <c r="E23" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>8809400</v>
+        <v>9427700</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>0.82</v>
+        <v>0.62</v>
       </c>
       <c r="H23" t="n">
-        <v>54.39</v>
+        <v>50.46</v>
       </c>
       <c r="I23" s="17" t="inlineStr">
         <is>
@@ -1530,10 +1530,10 @@
         </is>
       </c>
       <c r="J23" s="9" t="n">
-        <v>0.614</v>
+        <v>0.774</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>0.613</v>
+        <v>0.775</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="14" t="inlineStr"/>
@@ -1546,28 +1546,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E24" s="10" t="n">
-        <v>-0.0123</v>
+        <v>0.62</v>
+      </c>
+      <c r="E24" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>8316700</v>
+        <v>8965400</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>0.66</v>
+        <v>0.84</v>
       </c>
       <c r="H24" t="n">
-        <v>54.4</v>
+        <v>54.39</v>
       </c>
       <c r="I24" s="17" t="inlineStr">
         <is>
@@ -1575,10 +1575,10 @@
         </is>
       </c>
       <c r="J24" s="9" t="n">
-        <v>0.389</v>
+        <v>0.614</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>0.377</v>
+        <v>0.613</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="14" t="inlineStr"/>
@@ -1591,28 +1591,28 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="E25" s="16" t="n">
-        <v>0.027</v>
+        <v>0.4</v>
+      </c>
+      <c r="E25" s="10" t="n">
+        <v>-0.0123</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>7652300</v>
+        <v>8316700</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>1.08</v>
+        <v>0.66</v>
       </c>
       <c r="H25" t="n">
-        <v>61.86</v>
+        <v>54.4</v>
       </c>
       <c r="I25" s="17" t="inlineStr">
         <is>
@@ -1620,10 +1620,10 @@
         </is>
       </c>
       <c r="J25" s="9" t="n">
-        <v>0.37</v>
+        <v>0.389</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>0.369</v>
+        <v>0.377</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="14" t="inlineStr"/>
@@ -1651,7 +1651,7 @@
         <v>-0.0074</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>7632800</v>
+        <v>7690400</v>
       </c>
       <c r="G26" s="12" t="n">
         <v>0.42</v>
@@ -1681,39 +1681,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>0.355</v>
-      </c>
-      <c r="E27" s="10" t="n">
-        <v>-0.0139</v>
+        <v>0.38</v>
+      </c>
+      <c r="E27" s="16" t="n">
+        <v>0.027</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>7550400</v>
+        <v>7652400</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>0.88</v>
+        <v>1.08</v>
       </c>
       <c r="H27" t="n">
-        <v>55.26</v>
-      </c>
-      <c r="I27" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.86</v>
+      </c>
+      <c r="I27" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J27" s="9" t="n">
-        <v>0.349</v>
+        <v>0.37</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>0.33</v>
+        <v>0.369</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="14" t="inlineStr"/>
@@ -1726,33 +1726,40 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0476</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>SLG</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E28" s="15" t="n">
-        <v>0</v>
+        <v>0.355</v>
+      </c>
+      <c r="E28" s="10" t="n">
+        <v>-0.0139</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>7532700</v>
+        <v>7560400</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="I28" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J28" s="9" t="n"/>
-      <c r="K28" s="9" t="n"/>
+        <v>0.89</v>
+      </c>
+      <c r="H28" t="n">
+        <v>55.26</v>
+      </c>
+      <c r="I28" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J28" s="9" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="K28" s="9" t="n">
+        <v>0.33</v>
+      </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="14" t="inlineStr"/>
     </row>
@@ -1764,40 +1771,33 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>7079</t>
+          <t>0476</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>TWL</t>
+          <t>SLG</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="E29" s="16" t="n">
         <v>0.25</v>
       </c>
+      <c r="E29" s="15" t="n">
+        <v>0</v>
+      </c>
       <c r="F29" s="11" t="n">
-        <v>7414600</v>
+        <v>7538500</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="H29" t="n">
-        <v>51.85</v>
-      </c>
-      <c r="I29" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J29" s="9" t="n">
-        <v>0.024</v>
-      </c>
-      <c r="K29" s="9" t="n">
-        <v>0.025</v>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="I29" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J29" s="9" t="n"/>
+      <c r="K29" s="9" t="n"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="14" t="inlineStr"/>
     </row>
@@ -1809,39 +1809,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>IOICORP</t>
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="E30" s="15" t="n">
-        <v>0</v>
+        <v>4.57</v>
+      </c>
+      <c r="E30" s="16" t="n">
+        <v>0.0022</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>7377000</v>
+        <v>7399900</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>0.45</v>
+        <v>0.78</v>
       </c>
       <c r="H30" t="n">
-        <v>58.27</v>
-      </c>
-      <c r="I30" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.31</v>
+      </c>
+      <c r="I30" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J30" s="9" t="n">
-        <v>0.8129999999999999</v>
+        <v>4.646</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>0.8080000000000001</v>
+        <v>4.63</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="14" t="inlineStr"/>
@@ -1854,39 +1854,39 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>IOICORP</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>4.57</v>
-      </c>
-      <c r="E31" s="16" t="n">
-        <v>0.0022</v>
+        <v>0.82</v>
+      </c>
+      <c r="E31" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>7175700</v>
+        <v>7377200</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>0.75</v>
+        <v>0.45</v>
       </c>
       <c r="H31" t="n">
-        <v>41.31</v>
-      </c>
-      <c r="I31" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.27</v>
+      </c>
+      <c r="I31" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J31" s="9" t="n">
-        <v>4.646</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>4.63</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="14" t="inlineStr"/>
@@ -1899,28 +1899,28 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>9377</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>FSBM</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>0.09</v>
+        <v>4.75</v>
       </c>
       <c r="E32" s="16" t="n">
-        <v>0.0588</v>
+        <v>0.0106</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>7051100</v>
+        <v>7093500</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>0.33</v>
+        <v>0.41</v>
       </c>
       <c r="H32" t="n">
-        <v>37.74</v>
+        <v>50.43</v>
       </c>
       <c r="I32" s="17" t="inlineStr">
         <is>
@@ -1928,10 +1928,10 @@
         </is>
       </c>
       <c r="J32" s="9" t="n">
-        <v>0.103</v>
+        <v>4.718</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>0.142</v>
+        <v>4.87</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="14" t="inlineStr"/>
@@ -1944,28 +1944,28 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>9377</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>FSBM</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="E33" s="16" t="n">
-        <v>0.0106</v>
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="E33" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>6975500</v>
+        <v>7081100</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>0.41</v>
+        <v>0.33</v>
       </c>
       <c r="H33" t="n">
-        <v>50.43</v>
+        <v>34.16</v>
       </c>
       <c r="I33" s="17" t="inlineStr">
         <is>
@@ -1973,10 +1973,10 @@
         </is>
       </c>
       <c r="J33" s="9" t="n">
-        <v>4.718</v>
+        <v>0.102</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>4.87</v>
+        <v>0.141</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="14" t="inlineStr"/>
@@ -1998,19 +1998,19 @@
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>0.175</v>
-      </c>
-      <c r="E34" s="10" t="n">
-        <v>-0.0278</v>
+        <v>0.18</v>
+      </c>
+      <c r="E34" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>6763600</v>
+        <v>6863800</v>
       </c>
       <c r="G34" s="12" t="n">
         <v>0.29</v>
       </c>
       <c r="H34" t="n">
-        <v>40.7</v>
+        <v>42.98</v>
       </c>
       <c r="I34" s="13" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         </is>
       </c>
       <c r="J34" s="9" t="n">
-        <v>0.192</v>
+        <v>0.193</v>
       </c>
       <c r="K34" s="9" t="n">
         <v>0.185</v>
@@ -2043,19 +2043,19 @@
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="E35" s="16" t="n">
-        <v>0.0052</v>
+        <v>1.92</v>
+      </c>
+      <c r="E35" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>6653800</v>
+        <v>6705800</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="H35" t="n">
-        <v>49.36</v>
+        <v>47.51</v>
       </c>
       <c r="I35" s="17" t="inlineStr">
         <is>
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="J35" s="9" t="n">
-        <v>1.926</v>
+        <v>1.925</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>1.954</v>
+        <v>1.953</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="14" t="inlineStr"/>
@@ -2133,19 +2133,19 @@
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="E37" s="10" t="n">
-        <v>-0.08470000000000001</v>
+        <v>-0.07820000000000001</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>6349200</v>
+        <v>6459500</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="H37" t="n">
-        <v>56.85</v>
+        <v>57.66</v>
       </c>
       <c r="I37" s="13" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         </is>
       </c>
       <c r="J37" s="9" t="n">
-        <v>2.764</v>
+        <v>2.766</v>
       </c>
       <c r="K37" s="9" t="n">
         <v>2.132</v>
@@ -2169,39 +2169,39 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0034</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>MMAG</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>0.02</v>
+        <v>4.86</v>
       </c>
       <c r="E38" s="10" t="n">
-        <v>-0.2</v>
+        <v>-0.0182</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>6236300</v>
+        <v>6261300</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>1.44</v>
+        <v>0.25</v>
       </c>
       <c r="H38" t="n">
-        <v>44.58</v>
-      </c>
-      <c r="I38" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.9</v>
+      </c>
+      <c r="I38" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J38" s="9" t="n">
-        <v>0.024</v>
+        <v>4.929</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>0.026</v>
+        <v>4.697</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="14" t="inlineStr"/>
@@ -2214,39 +2214,39 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>0034</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>MMAG</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="E39" s="16" t="n">
-        <v>0.0283</v>
+        <v>0.02</v>
+      </c>
+      <c r="E39" s="10" t="n">
+        <v>-0.2</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>6117400</v>
+        <v>6236300</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>0.62</v>
+        <v>1.44</v>
       </c>
       <c r="H39" t="n">
-        <v>53.79</v>
-      </c>
-      <c r="I39" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>44.58</v>
+      </c>
+      <c r="I39" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J39" s="9" t="n">
-        <v>1.07</v>
+        <v>0.024</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>1.04</v>
+        <v>0.026</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="14" t="inlineStr"/>
@@ -2259,28 +2259,28 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>4.87</v>
-      </c>
-      <c r="E40" s="10" t="n">
-        <v>-0.0162</v>
+        <v>1.08</v>
+      </c>
+      <c r="E40" s="16" t="n">
+        <v>0.0189</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>6061000</v>
+        <v>6152500</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>0.24</v>
+        <v>0.62</v>
       </c>
       <c r="H40" t="n">
-        <v>49.38</v>
+        <v>52.4</v>
       </c>
       <c r="I40" s="13" t="inlineStr">
         <is>
@@ -2288,10 +2288,10 @@
         </is>
       </c>
       <c r="J40" s="9" t="n">
-        <v>4.93</v>
+        <v>1.069</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>4.697</v>
+        <v>1.04</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="14" t="inlineStr"/>
@@ -2319,10 +2319,10 @@
         <v>0.0172</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>5833400</v>
+        <v>6121100</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>0.29</v>
+        <v>0.31</v>
       </c>
       <c r="H41" t="n">
         <v>53.84</v>
@@ -2349,28 +2349,28 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>AMBANK</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>6.39</v>
-      </c>
-      <c r="E42" s="16" t="n">
-        <v>0.0191</v>
+        <v>1.25</v>
+      </c>
+      <c r="E42" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>5819800</v>
+        <v>5902100</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>1.02</v>
+        <v>0.59</v>
       </c>
       <c r="H42" t="n">
-        <v>44.65</v>
+        <v>40.29</v>
       </c>
       <c r="I42" s="13" t="inlineStr">
         <is>
@@ -2378,10 +2378,10 @@
         </is>
       </c>
       <c r="J42" s="9" t="n">
-        <v>6.423</v>
+        <v>1.309</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>6.804</v>
+        <v>1.311</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="14" t="inlineStr"/>
@@ -2394,28 +2394,28 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>AMBANK</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>1.26</v>
+        <v>6.37</v>
       </c>
       <c r="E43" s="16" t="n">
-        <v>0.008</v>
+        <v>0.0159</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>5736900</v>
+        <v>5834400</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>0.58</v>
+        <v>1.03</v>
       </c>
       <c r="H43" t="n">
-        <v>41.98</v>
+        <v>43.5</v>
       </c>
       <c r="I43" s="13" t="inlineStr">
         <is>
@@ -2423,10 +2423,10 @@
         </is>
       </c>
       <c r="J43" s="9" t="n">
-        <v>1.31</v>
+        <v>6.421</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>1.311</v>
+        <v>6.803</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="14" t="inlineStr"/>
@@ -2448,19 +2448,19 @@
         </is>
       </c>
       <c r="D44" s="9" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="E44" s="16" t="n">
-        <v>0.1558</v>
+        <v>0.1658</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>5443900</v>
+        <v>5508600</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="H44" t="n">
-        <v>87.19</v>
+        <v>87.39</v>
       </c>
       <c r="I44" s="17" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="J44" s="9" t="n">
-        <v>0.76</v>
+        <v>0.761</v>
       </c>
       <c r="K44" s="9" t="n">
         <v>0.525</v>
@@ -2484,33 +2484,40 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0473</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>EVOCOM</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E45" s="15" t="n">
-        <v>0</v>
+        <v>9.98</v>
+      </c>
+      <c r="E45" s="16" t="n">
+        <v>0.002</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>5372100</v>
+        <v>5479600</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>0.38</v>
+        <v>0.41</v>
+      </c>
+      <c r="H45" t="n">
+        <v>45.15</v>
       </c>
       <c r="I45" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J45" s="9" t="n"/>
-      <c r="K45" s="9" t="n"/>
+      <c r="J45" s="9" t="n">
+        <v>10.007</v>
+      </c>
+      <c r="K45" s="9" t="n">
+        <v>10.178</v>
+      </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="14" t="inlineStr"/>
     </row>
@@ -2531,19 +2538,19 @@
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="E46" s="10" t="n">
-        <v>-0.0385</v>
+        <v>-0.0538</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>5347400</v>
+        <v>5457300</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="H46" t="n">
-        <v>54.24</v>
+        <v>52.29</v>
       </c>
       <c r="I46" s="13" t="inlineStr">
         <is>
@@ -2551,7 +2558,7 @@
         </is>
       </c>
       <c r="J46" s="9" t="n">
-        <v>1.256</v>
+        <v>1.254</v>
       </c>
       <c r="K46" s="9" t="n">
         <v>1.041</v>
@@ -2567,39 +2574,39 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>0096</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>NEXGRAM</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>0.475</v>
+        <v>0.045</v>
       </c>
       <c r="E47" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>5330300</v>
+        <v>5446300</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>0.77</v>
+        <v>2.74</v>
       </c>
       <c r="H47" t="n">
-        <v>22.56</v>
-      </c>
-      <c r="I47" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.31</v>
+      </c>
+      <c r="I47" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J47" s="9" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.042</v>
       </c>
       <c r="K47" s="9" t="n">
-        <v>0.629</v>
+        <v>0.047</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="14" t="inlineStr"/>
@@ -2612,40 +2619,33 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>0473</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>EVOCOM</t>
         </is>
       </c>
       <c r="D48" s="9" t="n">
-        <v>9.970000000000001</v>
-      </c>
-      <c r="E48" s="16" t="n">
-        <v>0.001</v>
+        <v>0.1</v>
+      </c>
+      <c r="E48" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>5326900</v>
+        <v>5404900</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H48" t="n">
-        <v>44.4</v>
+        <v>0.38</v>
       </c>
       <c r="I48" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J48" s="9" t="n">
-        <v>10.006</v>
-      </c>
-      <c r="K48" s="9" t="n">
-        <v>10.178</v>
-      </c>
+      <c r="J48" s="9" t="n"/>
+      <c r="K48" s="9" t="n"/>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="14" t="inlineStr"/>
     </row>
@@ -2657,39 +2657,39 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0096</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>NEXGRAM</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>0.045</v>
+        <v>0.475</v>
       </c>
       <c r="E49" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>5009600</v>
+        <v>5330800</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>2.52</v>
+        <v>0.77</v>
       </c>
       <c r="H49" t="n">
-        <v>55.31</v>
-      </c>
-      <c r="I49" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>22.56</v>
+      </c>
+      <c r="I49" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J49" s="9" t="n">
-        <v>0.042</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="K49" s="9" t="n">
-        <v>0.047</v>
+        <v>0.629</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="14" t="inlineStr"/>
@@ -2702,39 +2702,39 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D50" s="9" t="n">
-        <v>1.09</v>
+        <v>2.11</v>
       </c>
       <c r="E50" s="10" t="n">
-        <v>-0.07629999999999999</v>
+        <v>-0.014</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>4707600</v>
+        <v>5126200</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>0.6</v>
+        <v>0.26</v>
       </c>
       <c r="H50" t="n">
-        <v>52.9</v>
-      </c>
-      <c r="I50" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.82</v>
+      </c>
+      <c r="I50" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J50" s="9" t="n">
-        <v>1.103</v>
+        <v>2.109</v>
       </c>
       <c r="K50" s="9" t="n">
-        <v>0.86</v>
+        <v>2.094</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="14" t="inlineStr"/>
@@ -2747,39 +2747,39 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>7195</t>
+          <t>0340</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>BNASTRA</t>
+          <t>NORTHERN</t>
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="E51" s="15" t="n">
-        <v>0</v>
+        <v>1.1</v>
+      </c>
+      <c r="E51" s="10" t="n">
+        <v>-0.0678</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>4672300</v>
+        <v>4730900</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>4.3</v>
+        <v>0.6</v>
       </c>
       <c r="H51" t="n">
-        <v>82.43000000000001</v>
-      </c>
-      <c r="I51" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.65</v>
+      </c>
+      <c r="I51" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J51" s="9" t="n">
-        <v>2.539</v>
+        <v>1.103</v>
       </c>
       <c r="K51" s="9" t="n">
-        <v>2.386</v>
+        <v>0.86</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="14" t="inlineStr"/>
@@ -2792,28 +2792,28 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>7195</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>BNASTRA</t>
         </is>
       </c>
       <c r="D52" s="9" t="n">
-        <v>2.12</v>
+        <v>2.69</v>
       </c>
       <c r="E52" s="10" t="n">
-        <v>-0.009300000000000001</v>
+        <v>-0.0037</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>4672200</v>
+        <v>4678100</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>0.23</v>
+        <v>4.3</v>
       </c>
       <c r="H52" t="n">
-        <v>52.35</v>
+        <v>79.98999999999999</v>
       </c>
       <c r="I52" s="17" t="inlineStr">
         <is>
@@ -2821,10 +2821,10 @@
         </is>
       </c>
       <c r="J52" s="9" t="n">
-        <v>2.11</v>
+        <v>2.538</v>
       </c>
       <c r="K52" s="9" t="n">
-        <v>2.094</v>
+        <v>2.386</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="14" t="inlineStr"/>
@@ -2846,19 +2846,19 @@
         </is>
       </c>
       <c r="D53" s="9" t="n">
-        <v>3.73</v>
+        <v>3.74</v>
       </c>
       <c r="E53" s="16" t="n">
-        <v>0.0275</v>
+        <v>0.0303</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>4608300</v>
+        <v>4667500</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="H53" t="n">
-        <v>56.58</v>
+        <v>56.79</v>
       </c>
       <c r="I53" s="13" t="inlineStr">
         <is>
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="J53" s="9" t="n">
-        <v>3.608</v>
+        <v>3.609</v>
       </c>
       <c r="K53" s="9" t="n">
-        <v>2.871</v>
+        <v>2.872</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="14" t="inlineStr"/>
@@ -2891,19 +2891,19 @@
         </is>
       </c>
       <c r="D54" s="9" t="n">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="E54" s="10" t="n">
-        <v>-0.0142</v>
+        <v>-0.0177</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>4601700</v>
+        <v>4609700</v>
       </c>
       <c r="G54" s="12" t="n">
         <v>0.33</v>
       </c>
       <c r="H54" t="n">
-        <v>50.17</v>
+        <v>49.37</v>
       </c>
       <c r="I54" s="13" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         </is>
       </c>
       <c r="J54" s="9" t="n">
-        <v>2.796</v>
+        <v>2.795</v>
       </c>
       <c r="K54" s="9" t="n">
         <v>2.721</v>
@@ -2936,19 +2936,19 @@
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>0.4</v>
+        <v>0.405</v>
       </c>
       <c r="E55" s="10" t="n">
-        <v>-0.0244</v>
+        <v>-0.0122</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>4584400</v>
+        <v>4586000</v>
       </c>
       <c r="G55" s="12" t="n">
         <v>2.77</v>
       </c>
       <c r="H55" t="n">
-        <v>33.91</v>
+        <v>36.38</v>
       </c>
       <c r="I55" s="13" t="inlineStr">
         <is>
@@ -2981,19 +2981,19 @@
         </is>
       </c>
       <c r="D56" s="9" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="E56" s="10" t="n">
-        <v>-0.0048</v>
+        <v>2.08</v>
+      </c>
+      <c r="E56" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>4431900</v>
+        <v>4472700</v>
       </c>
       <c r="G56" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="H56" t="n">
-        <v>36.74</v>
+        <v>37.45</v>
       </c>
       <c r="I56" s="13" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         </is>
       </c>
       <c r="J56" s="9" t="n">
-        <v>2.189</v>
+        <v>2.19</v>
       </c>
       <c r="K56" s="9" t="n">
         <v>2.225</v>
@@ -3017,28 +3017,28 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>0.945</v>
-      </c>
-      <c r="E57" s="16" t="n">
-        <v>0.0161</v>
+        <v>1.25</v>
+      </c>
+      <c r="E57" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>4356300</v>
+        <v>4393600</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>0.79</v>
+        <v>1.14</v>
       </c>
       <c r="H57" t="n">
-        <v>63.48</v>
+        <v>21.97</v>
       </c>
       <c r="I57" s="13" t="inlineStr">
         <is>
@@ -3046,10 +3046,10 @@
         </is>
       </c>
       <c r="J57" s="9" t="n">
-        <v>0.912</v>
+        <v>1.44</v>
       </c>
       <c r="K57" s="9" t="n">
-        <v>0.869</v>
+        <v>1.589</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="14" t="inlineStr"/>
@@ -3062,28 +3062,28 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D58" s="9" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="E58" s="15" t="n">
-        <v>0</v>
+        <v>0.945</v>
+      </c>
+      <c r="E58" s="16" t="n">
+        <v>0.0161</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>4257800</v>
+        <v>4370400</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>0.39</v>
+        <v>0.79</v>
       </c>
       <c r="H58" t="n">
-        <v>33.84</v>
+        <v>63.48</v>
       </c>
       <c r="I58" s="13" t="inlineStr">
         <is>
@@ -3091,10 +3091,10 @@
         </is>
       </c>
       <c r="J58" s="9" t="n">
-        <v>0.399</v>
+        <v>0.912</v>
       </c>
       <c r="K58" s="9" t="n">
-        <v>0.408</v>
+        <v>0.869</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="14" t="inlineStr"/>
@@ -3107,28 +3107,28 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="E59" s="16" t="n">
-        <v>0.0233</v>
+        <v>0.39</v>
+      </c>
+      <c r="E59" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>4221000</v>
+        <v>4258800</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>0.16</v>
+        <v>0.39</v>
       </c>
       <c r="H59" t="n">
-        <v>33.45</v>
+        <v>33.84</v>
       </c>
       <c r="I59" s="13" t="inlineStr">
         <is>
@@ -3136,10 +3136,10 @@
         </is>
       </c>
       <c r="J59" s="9" t="n">
-        <v>0.241</v>
+        <v>0.399</v>
       </c>
       <c r="K59" s="9" t="n">
-        <v>0.295</v>
+        <v>0.408</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="14" t="inlineStr"/>
@@ -3152,28 +3152,28 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>VELESTO</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>0.225</v>
+        <v>0.22</v>
       </c>
       <c r="E60" s="16" t="n">
-        <v>0.04650000000000001</v>
+        <v>0.0233</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>4210900</v>
+        <v>4246200</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="H60" t="n">
-        <v>48.41</v>
+        <v>33.45</v>
       </c>
       <c r="I60" s="13" t="inlineStr">
         <is>
@@ -3181,10 +3181,10 @@
         </is>
       </c>
       <c r="J60" s="9" t="n">
-        <v>0.224</v>
+        <v>0.241</v>
       </c>
       <c r="K60" s="9" t="n">
-        <v>0.24</v>
+        <v>0.295</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="14" t="inlineStr"/>
@@ -3197,28 +3197,28 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>VELESTO</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>1.26</v>
+        <v>0.225</v>
       </c>
       <c r="E61" s="16" t="n">
-        <v>0.008</v>
+        <v>0.04650000000000001</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>4210400</v>
+        <v>4237500</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>1.1</v>
+        <v>0.2</v>
       </c>
       <c r="H61" t="n">
-        <v>23.74</v>
+        <v>48.41</v>
       </c>
       <c r="I61" s="13" t="inlineStr">
         <is>
@@ -3226,10 +3226,10 @@
         </is>
       </c>
       <c r="J61" s="9" t="n">
-        <v>1.441</v>
+        <v>0.224</v>
       </c>
       <c r="K61" s="9" t="n">
-        <v>1.59</v>
+        <v>0.24</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="14" t="inlineStr"/>
@@ -3251,19 +3251,19 @@
         </is>
       </c>
       <c r="D62" s="9" t="n">
-        <v>0.315</v>
+        <v>0.32</v>
       </c>
       <c r="E62" s="10" t="n">
-        <v>-0.0455</v>
+        <v>-0.0303</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>4040400</v>
+        <v>4076100</v>
       </c>
       <c r="G62" s="12" t="n">
         <v>0.5600000000000001</v>
       </c>
       <c r="H62" t="n">
-        <v>64.22</v>
+        <v>68.45</v>
       </c>
       <c r="I62" s="17" t="inlineStr">
         <is>
@@ -3302,7 +3302,7 @@
         <v>0</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>3985900</v>
+        <v>4003600</v>
       </c>
       <c r="G63" s="12" t="n">
         <v>0.1</v>
@@ -3347,7 +3347,7 @@
         <v>-0.0159</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>3799600</v>
+        <v>3813600</v>
       </c>
       <c r="G64" s="12" t="n">
         <v>0.76</v>
@@ -3392,7 +3392,7 @@
         <v>-0.01</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>3759900</v>
+        <v>3760100</v>
       </c>
       <c r="G65" s="12" t="n">
         <v>0.45</v>
@@ -3422,39 +3422,39 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0258</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>AGMO</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D66" s="9" t="n">
-        <v>0.29</v>
+        <v>7.34</v>
       </c>
       <c r="E66" s="16" t="n">
-        <v>0.0175</v>
+        <v>0.0124</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>3589500</v>
+        <v>3622700</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>4.78</v>
+        <v>0.47</v>
       </c>
       <c r="H66" t="n">
-        <v>53.95</v>
-      </c>
-      <c r="I66" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>44.29</v>
+      </c>
+      <c r="I66" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J66" s="9" t="n">
-        <v>0.28</v>
+        <v>7.376</v>
       </c>
       <c r="K66" s="9" t="n">
-        <v>0.301</v>
+        <v>7.687</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="14" t="inlineStr"/>
@@ -3467,39 +3467,39 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>0258</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>AGMO</t>
         </is>
       </c>
       <c r="D67" s="9" t="n">
-        <v>7.34</v>
+        <v>0.29</v>
       </c>
       <c r="E67" s="16" t="n">
-        <v>0.0124</v>
+        <v>0.0175</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>3511000</v>
+        <v>3589500</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>0.45</v>
+        <v>4.78</v>
       </c>
       <c r="H67" t="n">
-        <v>44.29</v>
-      </c>
-      <c r="I67" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.95</v>
+      </c>
+      <c r="I67" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J67" s="9" t="n">
-        <v>7.376</v>
+        <v>0.28</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>7.687</v>
+        <v>0.301</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="14" t="inlineStr"/>
@@ -3527,10 +3527,10 @@
         <v>-0.0083</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>3484200</v>
+        <v>3579700</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="H68" t="n">
         <v>37.03</v>
@@ -3572,7 +3572,7 @@
         <v>-0.0326</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>3460500</v>
+        <v>3531800</v>
       </c>
       <c r="G69" s="12" t="n">
         <v>0.42</v>
@@ -3602,28 +3602,28 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D70" s="9" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="E70" s="16" t="n">
-        <v>0.0259</v>
+        <v>1.04</v>
+      </c>
+      <c r="E70" s="10" t="n">
+        <v>-0.0095</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>3436000</v>
+        <v>3460200</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>0.45</v>
+        <v>0.41</v>
       </c>
       <c r="H70" t="n">
-        <v>54.4</v>
+        <v>49.14</v>
       </c>
       <c r="I70" s="13" t="inlineStr">
         <is>
@@ -3631,10 +3631,10 @@
         </is>
       </c>
       <c r="J70" s="9" t="n">
-        <v>1.163</v>
+        <v>1.069</v>
       </c>
       <c r="K70" s="9" t="n">
-        <v>1.127</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="14" t="inlineStr"/>
@@ -3647,28 +3647,28 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="E71" s="10" t="n">
-        <v>-0.0091</v>
+        <v>1.18</v>
+      </c>
+      <c r="E71" s="16" t="n">
+        <v>0.0172</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>3338400</v>
+        <v>3443400</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>0.24</v>
+        <v>0.45</v>
       </c>
       <c r="H71" t="n">
-        <v>44.82</v>
+        <v>53.23</v>
       </c>
       <c r="I71" s="13" t="inlineStr">
         <is>
@@ -3676,10 +3676,10 @@
         </is>
       </c>
       <c r="J71" s="9" t="n">
-        <v>5.603</v>
+        <v>1.162</v>
       </c>
       <c r="K71" s="9" t="n">
-        <v>5.387</v>
+        <v>1.127</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="14" t="inlineStr"/>
@@ -3692,28 +3692,28 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D72" s="9" t="n">
-        <v>1.04</v>
+        <v>5.46</v>
       </c>
       <c r="E72" s="10" t="n">
-        <v>-0.0095</v>
+        <v>-0.0073</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>3336700</v>
+        <v>3354500</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>0.39</v>
+        <v>0.24</v>
       </c>
       <c r="H72" t="n">
-        <v>49.14</v>
+        <v>45.19</v>
       </c>
       <c r="I72" s="13" t="inlineStr">
         <is>
@@ -3721,10 +3721,10 @@
         </is>
       </c>
       <c r="J72" s="9" t="n">
-        <v>1.069</v>
+        <v>5.604</v>
       </c>
       <c r="K72" s="9" t="n">
-        <v>0.9409999999999999</v>
+        <v>5.388</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="14" t="inlineStr"/>
@@ -3746,19 +3746,19 @@
         </is>
       </c>
       <c r="D73" s="9" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="E73" s="16" t="n">
-        <v>0.0062</v>
+        <v>0.805</v>
+      </c>
+      <c r="E73" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>3329900</v>
+        <v>3347900</v>
       </c>
       <c r="G73" s="12" t="n">
         <v>0.5600000000000001</v>
       </c>
       <c r="H73" t="n">
-        <v>69.31999999999999</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="I73" s="17" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         </is>
       </c>
       <c r="J73" s="9" t="n">
-        <v>0.792</v>
+        <v>0.791</v>
       </c>
       <c r="K73" s="9" t="n">
         <v>0.768</v>
@@ -3797,7 +3797,7 @@
         <v>0</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>3281500</v>
+        <v>3285000</v>
       </c>
       <c r="G74" s="12" t="n">
         <v>0.37</v>
@@ -3842,10 +3842,10 @@
         <v>-0.011</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>3059400</v>
+        <v>3085400</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="H75" t="n">
         <v>30.03</v>
@@ -3879,19 +3879,19 @@
         </is>
       </c>
       <c r="D76" s="9" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="E76" s="16" t="n">
-        <v>0.0137</v>
+        <v>0.36</v>
+      </c>
+      <c r="E76" s="10" t="n">
+        <v>-0.0137</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>2975000</v>
+        <v>3075000</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="H76" t="n">
-        <v>51.33</v>
+        <v>45.85</v>
       </c>
       <c r="I76" s="17" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="J76" s="9" t="n">
-        <v>0.364</v>
+        <v>0.363</v>
       </c>
       <c r="K76" s="9" t="n">
         <v>0.387</v>
@@ -3924,19 +3924,19 @@
         </is>
       </c>
       <c r="D77" s="9" t="n">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="E77" s="16" t="n">
-        <v>0.0067</v>
+        <v>0.0033</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>2945600</v>
+        <v>3026600</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>0.93</v>
+        <v>0.96</v>
       </c>
       <c r="H77" t="n">
-        <v>79.75</v>
+        <v>79.43000000000001</v>
       </c>
       <c r="I77" s="17" t="inlineStr">
         <is>
@@ -3944,10 +3944,10 @@
         </is>
       </c>
       <c r="J77" s="9" t="n">
-        <v>2.734</v>
+        <v>2.733</v>
       </c>
       <c r="K77" s="9" t="n">
-        <v>2.358</v>
+        <v>2.357</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="14" t="inlineStr"/>
@@ -3960,28 +3960,28 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>7243</t>
+          <t>0233</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>MAGMA</t>
+          <t>PEKAT</t>
         </is>
       </c>
       <c r="D78" s="9" t="n">
-        <v>0.285</v>
-      </c>
-      <c r="E78" s="16" t="n">
-        <v>0.0556</v>
+        <v>2.7</v>
+      </c>
+      <c r="E78" s="10" t="n">
+        <v>-0.0722</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>2891000</v>
+        <v>2932800</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>4.19</v>
+        <v>0.9</v>
       </c>
       <c r="H78" t="n">
-        <v>53.17</v>
+        <v>56.74</v>
       </c>
       <c r="I78" s="13" t="inlineStr">
         <is>
@@ -3989,10 +3989,10 @@
         </is>
       </c>
       <c r="J78" s="9" t="n">
-        <v>0.281</v>
+        <v>2.672</v>
       </c>
       <c r="K78" s="9" t="n">
-        <v>0.285</v>
+        <v>2.206</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="14" t="inlineStr"/>
@@ -4005,38 +4005,40 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0471</t>
+          <t>7243</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>PIONEER</t>
+          <t>MAGMA</t>
         </is>
       </c>
       <c r="D79" s="9" t="n">
-        <v>0.33</v>
+        <v>0.285</v>
       </c>
       <c r="E79" s="16" t="n">
-        <v>0.0476</v>
+        <v>0.0556</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>2816900</v>
+        <v>2891000</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>0.31</v>
+        <v>4.19</v>
       </c>
       <c r="H79" t="n">
-        <v>58.79</v>
-      </c>
-      <c r="I79" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.17</v>
+      </c>
+      <c r="I79" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J79" s="9" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="K79" s="9" t="n"/>
+        <v>0.281</v>
+      </c>
+      <c r="K79" s="9" t="n">
+        <v>0.285</v>
+      </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="14" t="inlineStr"/>
     </row>
@@ -4063,7 +4065,7 @@
         <v>0</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>2816700</v>
+        <v>2846700</v>
       </c>
       <c r="G80" s="12" t="n">
         <v>0.32</v>
@@ -4093,40 +4095,38 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>0471</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>PIONEER</t>
         </is>
       </c>
       <c r="D81" s="9" t="n">
-        <v>0.61</v>
+        <v>0.33</v>
       </c>
       <c r="E81" s="16" t="n">
-        <v>0.0167</v>
+        <v>0.0476</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>2739400</v>
+        <v>2826900</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>0.65</v>
+        <v>0.31</v>
       </c>
       <c r="H81" t="n">
-        <v>53.75</v>
-      </c>
-      <c r="I81" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.79</v>
+      </c>
+      <c r="I81" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J81" s="9" t="n">
-        <v>0.601</v>
-      </c>
-      <c r="K81" s="9" t="n">
-        <v>0.585</v>
-      </c>
+        <v>0.305</v>
+      </c>
+      <c r="K81" s="9" t="n"/>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="14" t="inlineStr"/>
     </row>
@@ -4138,39 +4138,39 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0100</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>ESCERAM</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D82" s="9" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="E82" s="15" t="n">
-        <v>0</v>
+        <v>0.615</v>
+      </c>
+      <c r="E82" s="16" t="n">
+        <v>0.025</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>2725400</v>
+        <v>2739700</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>1.58</v>
+        <v>0.65</v>
       </c>
       <c r="H82" t="n">
-        <v>74.25</v>
-      </c>
-      <c r="I82" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>54.8</v>
+      </c>
+      <c r="I82" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J82" s="9" t="n">
-        <v>0.193</v>
+        <v>0.601</v>
       </c>
       <c r="K82" s="9" t="n">
-        <v>0.186</v>
+        <v>0.585</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="14" t="inlineStr"/>
@@ -4183,28 +4183,28 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0233</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>PEKAT</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D83" s="9" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="E83" s="10" t="n">
-        <v>-0.0722</v>
+        <v>-0.0244</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>2637500</v>
+        <v>2738500</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.21</v>
       </c>
       <c r="H83" t="n">
-        <v>56.74</v>
+        <v>44.51</v>
       </c>
       <c r="I83" s="13" t="inlineStr">
         <is>
@@ -4212,10 +4212,10 @@
         </is>
       </c>
       <c r="J83" s="9" t="n">
-        <v>2.672</v>
+        <v>2.456</v>
       </c>
       <c r="K83" s="9" t="n">
-        <v>2.206</v>
+        <v>2.367</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="14" t="inlineStr"/>
@@ -4228,28 +4228,28 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>0100</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>ESCERAM</t>
         </is>
       </c>
       <c r="D84" s="9" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="E84" s="16" t="n">
-        <v>0.0126</v>
+        <v>0.225</v>
+      </c>
+      <c r="E84" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>2624500</v>
+        <v>2738400</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>0.39</v>
+        <v>1.59</v>
       </c>
       <c r="H84" t="n">
-        <v>46.72</v>
+        <v>74.25</v>
       </c>
       <c r="I84" s="17" t="inlineStr">
         <is>
@@ -4257,10 +4257,10 @@
         </is>
       </c>
       <c r="J84" s="9" t="n">
-        <v>1.613</v>
+        <v>0.193</v>
       </c>
       <c r="K84" s="9" t="n">
-        <v>1.709</v>
+        <v>0.186</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="14" t="inlineStr"/>
@@ -4273,28 +4273,28 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D85" s="9" t="n">
-        <v>7.32</v>
+        <v>0.645</v>
       </c>
       <c r="E85" s="16" t="n">
-        <v>0.0027</v>
+        <v>0.0238</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>2623300</v>
+        <v>2682200</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>0.26</v>
+        <v>0.51</v>
       </c>
       <c r="H85" t="n">
-        <v>33.52</v>
+        <v>66.98999999999999</v>
       </c>
       <c r="I85" s="13" t="inlineStr">
         <is>
@@ -4302,10 +4302,10 @@
         </is>
       </c>
       <c r="J85" s="9" t="n">
-        <v>7.52</v>
+        <v>0.554</v>
       </c>
       <c r="K85" s="9" t="n">
-        <v>8.026999999999999</v>
+        <v>0.458</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="14" t="inlineStr"/>
@@ -4318,28 +4318,28 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D86" s="9" t="n">
-        <v>0.64</v>
+        <v>7.34</v>
       </c>
       <c r="E86" s="16" t="n">
-        <v>0.0159</v>
+        <v>0.005500000000000001</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>2605300</v>
+        <v>2676300</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>0.5</v>
+        <v>0.26</v>
       </c>
       <c r="H86" t="n">
-        <v>66.54000000000001</v>
+        <v>34.85</v>
       </c>
       <c r="I86" s="13" t="inlineStr">
         <is>
@@ -4347,10 +4347,10 @@
         </is>
       </c>
       <c r="J86" s="9" t="n">
-        <v>0.554</v>
+        <v>7.521</v>
       </c>
       <c r="K86" s="9" t="n">
-        <v>0.458</v>
+        <v>8.026999999999999</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="14" t="inlineStr"/>
@@ -4363,39 +4363,39 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D87" s="9" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E87" s="10" t="n">
-        <v>-0.0064</v>
+        <v>1.61</v>
+      </c>
+      <c r="E87" s="16" t="n">
+        <v>0.0126</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>2578800</v>
+        <v>2648000</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>0.31</v>
+        <v>0.4</v>
       </c>
       <c r="H87" t="n">
-        <v>49.19</v>
-      </c>
-      <c r="I87" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.72</v>
+      </c>
+      <c r="I87" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J87" s="9" t="n">
-        <v>0.779</v>
+        <v>1.613</v>
       </c>
       <c r="K87" s="9" t="n">
-        <v>0.773</v>
+        <v>1.709</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="14" t="inlineStr"/>
@@ -4423,7 +4423,7 @@
         <v>-0.0326</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>2575500</v>
+        <v>2584600</v>
       </c>
       <c r="G88" s="12" t="n">
         <v>1.85</v>
@@ -4453,28 +4453,28 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>5323</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>JPG</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D89" s="9" t="n">
-        <v>1.7</v>
+        <v>0.775</v>
       </c>
       <c r="E89" s="10" t="n">
-        <v>-0.0116</v>
+        <v>-0.0064</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>2572600</v>
+        <v>2578800</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>0.4</v>
+        <v>0.31</v>
       </c>
       <c r="H89" t="n">
-        <v>34.64</v>
+        <v>49.19</v>
       </c>
       <c r="I89" s="13" t="inlineStr">
         <is>
@@ -4482,10 +4482,10 @@
         </is>
       </c>
       <c r="J89" s="9" t="n">
-        <v>1.794</v>
+        <v>0.779</v>
       </c>
       <c r="K89" s="9" t="n">
-        <v>1.909</v>
+        <v>0.773</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="14" t="inlineStr"/>
@@ -4498,28 +4498,28 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>5323</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>JPG</t>
         </is>
       </c>
       <c r="D90" s="9" t="n">
-        <v>2.41</v>
+        <v>1.7</v>
       </c>
       <c r="E90" s="10" t="n">
-        <v>-0.0203</v>
+        <v>-0.0116</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>2540700</v>
+        <v>2575200</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="H90" t="n">
-        <v>45.68</v>
+        <v>34.64</v>
       </c>
       <c r="I90" s="13" t="inlineStr">
         <is>
@@ -4527,10 +4527,10 @@
         </is>
       </c>
       <c r="J90" s="9" t="n">
-        <v>2.457</v>
+        <v>1.794</v>
       </c>
       <c r="K90" s="9" t="n">
-        <v>2.367</v>
+        <v>1.909</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="14" t="inlineStr"/>
@@ -4588,28 +4588,28 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>0372</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>KPJ</t>
+          <t>CHEEDING</t>
         </is>
       </c>
       <c r="D92" s="9" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="E92" s="16" t="n">
-        <v>0.0203</v>
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="E92" s="10" t="n">
+        <v>-0.0259</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>2439000</v>
+        <v>2530700</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>0.46</v>
+        <v>0.64</v>
       </c>
       <c r="H92" t="n">
-        <v>41.94</v>
+        <v>39.85</v>
       </c>
       <c r="I92" s="13" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="J92" s="9" t="n">
-        <v>2.571</v>
+        <v>0.605</v>
       </c>
       <c r="K92" s="9" t="n">
-        <v>2.75</v>
+        <v>0.606</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="14" t="inlineStr"/>
@@ -4633,39 +4633,39 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>KPJ</t>
         </is>
       </c>
       <c r="D93" s="9" t="n">
-        <v>4.34</v>
+        <v>2.51</v>
       </c>
       <c r="E93" s="16" t="n">
-        <v>0.0046</v>
+        <v>0.0203</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>2422800</v>
+        <v>2454000</v>
       </c>
       <c r="G93" s="12" t="n">
-        <v>0.37</v>
+        <v>0.46</v>
       </c>
       <c r="H93" t="n">
-        <v>48.01</v>
-      </c>
-      <c r="I93" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.94</v>
+      </c>
+      <c r="I93" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J93" s="9" t="n">
-        <v>4.356</v>
+        <v>2.571</v>
       </c>
       <c r="K93" s="9" t="n">
-        <v>4.441</v>
+        <v>2.75</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="14" t="inlineStr"/>
@@ -4678,28 +4678,28 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0056</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>NCT</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D94" s="9" t="n">
-        <v>0.5649999999999999</v>
+        <v>4.34</v>
       </c>
       <c r="E94" s="16" t="n">
-        <v>0.0089</v>
+        <v>0.0046</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>2409700</v>
+        <v>2435500</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>1.1</v>
+        <v>0.38</v>
       </c>
       <c r="H94" t="n">
-        <v>51.23</v>
+        <v>48.01</v>
       </c>
       <c r="I94" s="17" t="inlineStr">
         <is>
@@ -4707,10 +4707,10 @@
         </is>
       </c>
       <c r="J94" s="9" t="n">
-        <v>0.5629999999999999</v>
+        <v>4.356</v>
       </c>
       <c r="K94" s="9" t="n">
-        <v>0.5620000000000001</v>
+        <v>4.441</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="14" t="inlineStr"/>
@@ -4723,28 +4723,28 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>0056</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>TENAGA</t>
+          <t>NCT</t>
         </is>
       </c>
       <c r="D95" s="9" t="n">
-        <v>12.98</v>
-      </c>
-      <c r="E95" s="10" t="n">
-        <v>-0.0046</v>
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="E95" s="16" t="n">
+        <v>0.0089</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>2315500</v>
+        <v>2409700</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>0.25</v>
+        <v>1.1</v>
       </c>
       <c r="H95" t="n">
-        <v>44.04</v>
+        <v>51.23</v>
       </c>
       <c r="I95" s="17" t="inlineStr">
         <is>
@@ -4752,10 +4752,10 @@
         </is>
       </c>
       <c r="J95" s="9" t="n">
-        <v>13.025</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="K95" s="9" t="n">
-        <v>13.492</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="14" t="inlineStr"/>
@@ -4768,39 +4768,39 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>TENAGA</t>
         </is>
       </c>
       <c r="D96" s="9" t="n">
-        <v>1</v>
+        <v>12.98</v>
       </c>
       <c r="E96" s="10" t="n">
-        <v>-0.0566</v>
+        <v>-0.0046</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>2310300</v>
+        <v>2341000</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="H96" t="n">
-        <v>46.1</v>
-      </c>
-      <c r="I96" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>44.04</v>
+      </c>
+      <c r="I96" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J96" s="9" t="n">
-        <v>1.055</v>
+        <v>13.025</v>
       </c>
       <c r="K96" s="9" t="n">
-        <v>0.919</v>
+        <v>13.492</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="14" t="inlineStr"/>
@@ -4813,33 +4813,40 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0475</t>
+          <t>0296</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>GBBOND</t>
+          <t>HEGROUP</t>
         </is>
       </c>
       <c r="D97" s="9" t="n">
-        <v>0.205</v>
+        <v>1</v>
       </c>
       <c r="E97" s="10" t="n">
-        <v>-0.04650000000000001</v>
+        <v>-0.0566</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>2218000</v>
+        <v>2314800</v>
       </c>
       <c r="G97" s="12" t="n">
-        <v>0.16</v>
+        <v>0.5</v>
+      </c>
+      <c r="H97" t="n">
+        <v>46.1</v>
       </c>
       <c r="I97" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J97" s="9" t="n"/>
-      <c r="K97" s="9" t="n"/>
+      <c r="J97" s="9" t="n">
+        <v>1.055</v>
+      </c>
+      <c r="K97" s="9" t="n">
+        <v>0.919</v>
+      </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="14" t="inlineStr"/>
     </row>
@@ -4851,39 +4858,39 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>0272</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>TTVHB</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D98" s="9" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="E98" s="10" t="n">
-        <v>-0.0204</v>
+        <v>0.42</v>
+      </c>
+      <c r="E98" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>2173500</v>
+        <v>2272200</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>0.93</v>
+        <v>0.33</v>
       </c>
       <c r="H98" t="n">
-        <v>45.88</v>
-      </c>
-      <c r="I98" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.55</v>
+      </c>
+      <c r="I98" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J98" s="9" t="n">
-        <v>0.25</v>
+        <v>0.426</v>
       </c>
       <c r="K98" s="9" t="n">
-        <v>0.255</v>
+        <v>0.415</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="14" t="inlineStr"/>
@@ -4896,40 +4903,33 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>0475</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>GBBOND</t>
         </is>
       </c>
       <c r="D99" s="9" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="E99" s="15" t="n">
-        <v>0</v>
+        <v>0.205</v>
+      </c>
+      <c r="E99" s="10" t="n">
+        <v>-0.04650000000000001</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>2169400</v>
+        <v>2220100</v>
       </c>
       <c r="G99" s="12" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="H99" t="n">
-        <v>49.55</v>
-      </c>
-      <c r="I99" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J99" s="9" t="n">
-        <v>0.426</v>
-      </c>
-      <c r="K99" s="9" t="n">
-        <v>0.415</v>
-      </c>
+        <v>0.16</v>
+      </c>
+      <c r="I99" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J99" s="9" t="n"/>
+      <c r="K99" s="9" t="n"/>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="14" t="inlineStr"/>
     </row>
@@ -4941,28 +4941,28 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0278</t>
+          <t>0398</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>EDELTEQ</t>
+          <t>GDGROUP</t>
         </is>
       </c>
       <c r="D100" s="9" t="n">
-        <v>0.425</v>
-      </c>
-      <c r="E100" s="16" t="n">
-        <v>0.04940000000000001</v>
+        <v>0.385</v>
+      </c>
+      <c r="E100" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>2149900</v>
+        <v>2204500</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>0.46</v>
+        <v>2.47</v>
       </c>
       <c r="H100" t="n">
-        <v>62.89</v>
+        <v>57.12</v>
       </c>
       <c r="I100" s="17" t="inlineStr">
         <is>
@@ -4970,10 +4970,10 @@
         </is>
       </c>
       <c r="J100" s="9" t="n">
-        <v>0.375</v>
+        <v>0.381</v>
       </c>
       <c r="K100" s="9" t="n">
-        <v>0.354</v>
+        <v>0.379</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="14" t="inlineStr"/>
@@ -4986,39 +4986,39 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0398</t>
+          <t>0272</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>GDGROUP</t>
+          <t>TTVHB</t>
         </is>
       </c>
       <c r="D101" s="9" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="E101" s="15" t="n">
-        <v>0</v>
+        <v>0.24</v>
+      </c>
+      <c r="E101" s="10" t="n">
+        <v>-0.0204</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>2078500</v>
+        <v>2179100</v>
       </c>
       <c r="G101" s="12" t="n">
-        <v>2.33</v>
+        <v>0.93</v>
       </c>
       <c r="H101" t="n">
-        <v>57.12</v>
-      </c>
-      <c r="I101" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.88</v>
+      </c>
+      <c r="I101" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J101" s="9" t="n">
-        <v>0.381</v>
+        <v>0.25</v>
       </c>
       <c r="K101" s="9" t="n">
-        <v>0.379</v>
+        <v>0.255</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="14" t="inlineStr"/>
@@ -5031,28 +5031,28 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>0278</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>EDELTEQ</t>
         </is>
       </c>
       <c r="D102" s="9" t="n">
-        <v>1.23</v>
+        <v>0.43</v>
       </c>
       <c r="E102" s="16" t="n">
-        <v>0.025</v>
+        <v>0.0617</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>1980100</v>
+        <v>2150000</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>0.34</v>
+        <v>0.46</v>
       </c>
       <c r="H102" t="n">
-        <v>58.53</v>
+        <v>63.65</v>
       </c>
       <c r="I102" s="17" t="inlineStr">
         <is>
@@ -5060,10 +5060,10 @@
         </is>
       </c>
       <c r="J102" s="9" t="n">
-        <v>1.172</v>
+        <v>0.375</v>
       </c>
       <c r="K102" s="9" t="n">
-        <v>1.176</v>
+        <v>0.354</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="14" t="inlineStr"/>
@@ -5076,39 +5076,39 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0097</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>VITROX</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D103" s="9" t="n">
-        <v>10.68</v>
-      </c>
-      <c r="E103" s="10" t="n">
-        <v>-0.005600000000000001</v>
+        <v>6.7</v>
+      </c>
+      <c r="E103" s="16" t="n">
+        <v>0.0308</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>1903100</v>
+        <v>2064200</v>
       </c>
       <c r="G103" s="12" t="n">
-        <v>0.53</v>
+        <v>0.38</v>
       </c>
       <c r="H103" t="n">
-        <v>60.31</v>
-      </c>
-      <c r="I103" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.02</v>
+      </c>
+      <c r="I103" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J103" s="9" t="n">
-        <v>10.399</v>
+        <v>6.07</v>
       </c>
       <c r="K103" s="9" t="n">
-        <v>9.661</v>
+        <v>5.859</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="14" t="inlineStr"/>
@@ -5121,39 +5121,39 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D104" s="9" t="n">
-        <v>6.77</v>
-      </c>
-      <c r="E104" s="16" t="n">
-        <v>0.0415</v>
+        <v>0.885</v>
+      </c>
+      <c r="E104" s="10" t="n">
+        <v>-0.005600000000000001</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>1901800</v>
+        <v>1999900</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>0.35</v>
+        <v>0.8</v>
       </c>
       <c r="H104" t="n">
-        <v>61.79</v>
-      </c>
-      <c r="I104" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>22.89</v>
+      </c>
+      <c r="I104" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J104" s="9" t="n">
-        <v>6.077</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="K104" s="9" t="n">
-        <v>5.86</v>
+        <v>0.983</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="14" t="inlineStr"/>
@@ -5166,39 +5166,39 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D105" s="9" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="E105" s="10" t="n">
-        <v>-0.0112</v>
+        <v>1.23</v>
+      </c>
+      <c r="E105" s="16" t="n">
+        <v>0.025</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>1898000</v>
+        <v>1988600</v>
       </c>
       <c r="G105" s="12" t="n">
-        <v>0.76</v>
+        <v>0.34</v>
       </c>
       <c r="H105" t="n">
-        <v>22.06</v>
-      </c>
-      <c r="I105" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.53</v>
+      </c>
+      <c r="I105" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J105" s="9" t="n">
-        <v>0.9389999999999999</v>
+        <v>1.172</v>
       </c>
       <c r="K105" s="9" t="n">
-        <v>0.983</v>
+        <v>1.176</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="14" t="inlineStr"/>
@@ -5211,28 +5211,28 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>0372</t>
+          <t>0097</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>CHEEDING</t>
+          <t>VITROX</t>
         </is>
       </c>
       <c r="D106" s="9" t="n">
-        <v>0.57</v>
+        <v>10.7</v>
       </c>
       <c r="E106" s="10" t="n">
-        <v>-0.0172</v>
+        <v>-0.0037</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>1897600</v>
+        <v>1922800</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>0.48</v>
+        <v>0.53</v>
       </c>
       <c r="H106" t="n">
-        <v>40.78</v>
+        <v>60.79</v>
       </c>
       <c r="I106" s="13" t="inlineStr">
         <is>
@@ -5240,10 +5240,10 @@
         </is>
       </c>
       <c r="J106" s="9" t="n">
-        <v>0.606</v>
+        <v>10.4</v>
       </c>
       <c r="K106" s="9" t="n">
-        <v>0.606</v>
+        <v>9.661</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="14" t="inlineStr"/>
@@ -5256,28 +5256,28 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>0376</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>IAB</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D107" s="9" t="n">
-        <v>1.15</v>
+        <v>2.56</v>
       </c>
       <c r="E107" s="10" t="n">
-        <v>-0.0254</v>
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>1839600</v>
+        <v>1882000</v>
       </c>
       <c r="G107" s="12" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="H107" t="n">
-        <v>38.75</v>
+        <v>45.83</v>
       </c>
       <c r="I107" s="13" t="inlineStr">
         <is>
@@ -5285,10 +5285,10 @@
         </is>
       </c>
       <c r="J107" s="9" t="n">
-        <v>1.249</v>
+        <v>2.626</v>
       </c>
       <c r="K107" s="9" t="n">
-        <v>1.308</v>
+        <v>2.597</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="14" t="inlineStr"/>
@@ -5301,28 +5301,28 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>0376</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>IAB</t>
         </is>
       </c>
       <c r="D108" s="9" t="n">
-        <v>2.57</v>
+        <v>1.16</v>
       </c>
       <c r="E108" s="10" t="n">
-        <v>-0.0039</v>
+        <v>-0.0169</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>1834100</v>
+        <v>1858700</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>0.29</v>
+        <v>0.82</v>
       </c>
       <c r="H108" t="n">
-        <v>46.48</v>
+        <v>39.49</v>
       </c>
       <c r="I108" s="13" t="inlineStr">
         <is>
@@ -5330,10 +5330,10 @@
         </is>
       </c>
       <c r="J108" s="9" t="n">
-        <v>2.627</v>
+        <v>1.25</v>
       </c>
       <c r="K108" s="9" t="n">
-        <v>2.597</v>
+        <v>1.308</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="14" t="inlineStr"/>
@@ -5361,7 +5361,7 @@
         <v>-0.0105</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>1695900</v>
+        <v>1706000</v>
       </c>
       <c r="G109" s="12" t="n">
         <v>0.22</v>
@@ -5406,10 +5406,10 @@
         <v>-0.0179</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>1636500</v>
+        <v>1667800</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="H110" t="n">
         <v>51.04</v>
@@ -5436,28 +5436,28 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>5337</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>ECOSHOP</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D111" s="9" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="E111" s="10" t="n">
-        <v>-0.0069</v>
+        <v>0.535</v>
+      </c>
+      <c r="E111" s="16" t="n">
+        <v>0.009399999999999999</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>1603500</v>
+        <v>1636300</v>
       </c>
       <c r="G111" s="12" t="n">
-        <v>0.38</v>
+        <v>0.11</v>
       </c>
       <c r="H111" t="n">
-        <v>40.99</v>
+        <v>55.88</v>
       </c>
       <c r="I111" s="13" t="inlineStr">
         <is>
@@ -5465,10 +5465,10 @@
         </is>
       </c>
       <c r="J111" s="9" t="n">
-        <v>1.453</v>
+        <v>0.519</v>
       </c>
       <c r="K111" s="9" t="n">
-        <v>1.467</v>
+        <v>0.45</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="14" t="inlineStr"/>
@@ -5481,28 +5481,28 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D112" s="9" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="E112" s="15" t="n">
-        <v>0</v>
+        <v>0.595</v>
+      </c>
+      <c r="E112" s="16" t="n">
+        <v>0.0259</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>1603100</v>
+        <v>1606100</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>0.11</v>
+        <v>0.32</v>
       </c>
       <c r="H112" t="n">
-        <v>55.05</v>
+        <v>64.37</v>
       </c>
       <c r="I112" s="13" t="inlineStr">
         <is>
@@ -5510,10 +5510,10 @@
         </is>
       </c>
       <c r="J112" s="9" t="n">
-        <v>0.519</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="K112" s="9" t="n">
-        <v>0.449</v>
+        <v>0.506</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="14" t="inlineStr"/>
@@ -5526,28 +5526,28 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>5337</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>ECOSHOP</t>
         </is>
       </c>
       <c r="D113" s="9" t="n">
-        <v>0.595</v>
-      </c>
-      <c r="E113" s="16" t="n">
-        <v>0.0259</v>
+        <v>1.43</v>
+      </c>
+      <c r="E113" s="10" t="n">
+        <v>-0.0069</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>1599800</v>
+        <v>1604900</v>
       </c>
       <c r="G113" s="12" t="n">
-        <v>0.32</v>
+        <v>0.38</v>
       </c>
       <c r="H113" t="n">
-        <v>64.37</v>
+        <v>40.99</v>
       </c>
       <c r="I113" s="13" t="inlineStr">
         <is>
@@ -5555,10 +5555,10 @@
         </is>
       </c>
       <c r="J113" s="9" t="n">
-        <v>0.5590000000000001</v>
+        <v>1.453</v>
       </c>
       <c r="K113" s="9" t="n">
-        <v>0.506</v>
+        <v>1.467</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="14" t="inlineStr"/>
@@ -5571,28 +5571,28 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>0239</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>ECOMATE</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D114" s="9" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E114" s="15" t="n">
-        <v>0</v>
+        <v>0.75</v>
+      </c>
+      <c r="E114" s="10" t="n">
+        <v>-0.0066</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>1573000</v>
+        <v>1588500</v>
       </c>
       <c r="G114" s="12" t="n">
-        <v>0.49</v>
+        <v>0.23</v>
       </c>
       <c r="H114" t="n">
-        <v>51.92</v>
+        <v>54.72</v>
       </c>
       <c r="I114" s="13" t="inlineStr">
         <is>
@@ -5600,10 +5600,10 @@
         </is>
       </c>
       <c r="J114" s="9" t="n">
-        <v>0.865</v>
+        <v>0.743</v>
       </c>
       <c r="K114" s="9" t="n">
-        <v>0.859</v>
+        <v>0.665</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="14" t="inlineStr"/>
@@ -5616,28 +5616,28 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D115" s="9" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="E115" s="10" t="n">
-        <v>-0.0199</v>
+        <v>0.865</v>
+      </c>
+      <c r="E115" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>1541800</v>
+        <v>1573000</v>
       </c>
       <c r="G115" s="12" t="n">
-        <v>0.22</v>
+        <v>0.49</v>
       </c>
       <c r="H115" t="n">
-        <v>52.84</v>
+        <v>51.92</v>
       </c>
       <c r="I115" s="13" t="inlineStr">
         <is>
@@ -5645,10 +5645,10 @@
         </is>
       </c>
       <c r="J115" s="9" t="n">
-        <v>0.742</v>
+        <v>0.865</v>
       </c>
       <c r="K115" s="9" t="n">
-        <v>0.665</v>
+        <v>0.859</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="14" t="inlineStr"/>
@@ -5661,39 +5661,39 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>5329</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>AZAMJAYA</t>
+          <t>MALAKOF</t>
         </is>
       </c>
       <c r="D116" s="9" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="E116" s="16" t="n">
-        <v>0.0105</v>
+        <v>0.765</v>
+      </c>
+      <c r="E116" s="10" t="n">
+        <v>-0.0129</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>1474500</v>
+        <v>1494600</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v>16.26</v>
+        <v>0.34</v>
       </c>
       <c r="H116" t="n">
-        <v>47.94</v>
-      </c>
-      <c r="I116" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.45</v>
+      </c>
+      <c r="I116" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J116" s="9" t="n">
-        <v>0.966</v>
+        <v>0.787</v>
       </c>
       <c r="K116" s="9" t="n">
-        <v>0.977</v>
+        <v>0.804</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="14" t="inlineStr"/>
@@ -5706,39 +5706,39 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>5329</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>DATASONIC</t>
+          <t>AZAMJAYA</t>
         </is>
       </c>
       <c r="D117" s="9" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E117" s="10" t="n">
-        <v>-0.0167</v>
+        <v>0.99</v>
+      </c>
+      <c r="E117" s="16" t="n">
+        <v>0.0421</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>1440400</v>
+        <v>1475500</v>
       </c>
       <c r="G117" s="12" t="n">
-        <v>0.11</v>
+        <v>16.27</v>
       </c>
       <c r="H117" t="n">
-        <v>51.87</v>
-      </c>
-      <c r="I117" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.39</v>
+      </c>
+      <c r="I117" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J117" s="9" t="n">
-        <v>0.292</v>
+        <v>0.969</v>
       </c>
       <c r="K117" s="9" t="n">
-        <v>0.282</v>
+        <v>0.978</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="14" t="inlineStr"/>
@@ -5751,28 +5751,28 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>IOIPG</t>
         </is>
       </c>
       <c r="D118" s="9" t="n">
-        <v>0.745</v>
-      </c>
-      <c r="E118" s="16" t="n">
-        <v>0.0068</v>
+        <v>3.3</v>
+      </c>
+      <c r="E118" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>1420700</v>
+        <v>1440900</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v>0.65</v>
+        <v>0.22</v>
       </c>
       <c r="H118" t="n">
-        <v>55.71</v>
+        <v>33.44</v>
       </c>
       <c r="I118" s="13" t="inlineStr">
         <is>
@@ -5780,10 +5780,10 @@
         </is>
       </c>
       <c r="J118" s="9" t="n">
-        <v>0.724</v>
+        <v>3.425</v>
       </c>
       <c r="K118" s="9" t="n">
-        <v>0.699</v>
+        <v>3.632</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="14" t="inlineStr"/>
@@ -5796,28 +5796,28 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>IOIPG</t>
+          <t>DATASONIC</t>
         </is>
       </c>
       <c r="D119" s="9" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="E119" s="15" t="n">
-        <v>0</v>
+        <v>0.295</v>
+      </c>
+      <c r="E119" s="10" t="n">
+        <v>-0.0167</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>1401800</v>
+        <v>1440400</v>
       </c>
       <c r="G119" s="12" t="n">
-        <v>0.21</v>
+        <v>0.11</v>
       </c>
       <c r="H119" t="n">
-        <v>33.44</v>
+        <v>51.87</v>
       </c>
       <c r="I119" s="13" t="inlineStr">
         <is>
@@ -5825,10 +5825,10 @@
         </is>
       </c>
       <c r="J119" s="9" t="n">
-        <v>3.425</v>
+        <v>0.292</v>
       </c>
       <c r="K119" s="9" t="n">
-        <v>3.632</v>
+        <v>0.282</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="14" t="inlineStr"/>
@@ -5841,28 +5841,28 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>0291</t>
+          <t>0146</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>CHB</t>
+          <t>JFTECH</t>
         </is>
       </c>
       <c r="D120" s="9" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="E120" s="10" t="n">
-        <v>-0.0603</v>
+        <v>0.75</v>
+      </c>
+      <c r="E120" s="16" t="n">
+        <v>0.0135</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>1387800</v>
+        <v>1431400</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>0.9</v>
+        <v>0.65</v>
       </c>
       <c r="H120" t="n">
-        <v>61.35</v>
+        <v>56.46</v>
       </c>
       <c r="I120" s="13" t="inlineStr">
         <is>
@@ -5870,10 +5870,10 @@
         </is>
       </c>
       <c r="J120" s="9" t="n">
-        <v>2.534</v>
+        <v>0.724</v>
       </c>
       <c r="K120" s="9" t="n">
-        <v>2.212</v>
+        <v>0.699</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="14" t="inlineStr"/>
@@ -5886,28 +5886,28 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>0468</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>UNIPAC</t>
         </is>
       </c>
       <c r="D121" s="9" t="n">
-        <v>0.795</v>
-      </c>
-      <c r="E121" s="15" t="n">
-        <v>0</v>
+        <v>0.23</v>
+      </c>
+      <c r="E121" s="10" t="n">
+        <v>-0.0213</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>1371600</v>
+        <v>1405000</v>
       </c>
       <c r="G121" s="12" t="n">
-        <v>0.21</v>
+        <v>0.15</v>
       </c>
       <c r="H121" t="n">
-        <v>62.06</v>
+        <v>24.97</v>
       </c>
       <c r="I121" s="13" t="inlineStr">
         <is>
@@ -5915,11 +5915,9 @@
         </is>
       </c>
       <c r="J121" s="9" t="n">
-        <v>0.764</v>
-      </c>
-      <c r="K121" s="9" t="n">
-        <v>0.676</v>
-      </c>
+        <v>0.257</v>
+      </c>
+      <c r="K121" s="9" t="n"/>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="14" t="inlineStr"/>
     </row>
@@ -5931,28 +5929,28 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>0128</t>
+          <t>0291</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>FRONTKN</t>
+          <t>CHB</t>
         </is>
       </c>
       <c r="D122" s="9" t="n">
-        <v>5.14</v>
-      </c>
-      <c r="E122" s="16" t="n">
-        <v>0.0098</v>
+        <v>2.64</v>
+      </c>
+      <c r="E122" s="10" t="n">
+        <v>-0.0638</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>1356100</v>
+        <v>1393700</v>
       </c>
       <c r="G122" s="12" t="n">
-        <v>0.31</v>
+        <v>0.9</v>
       </c>
       <c r="H122" t="n">
-        <v>55.93</v>
+        <v>60.7</v>
       </c>
       <c r="I122" s="13" t="inlineStr">
         <is>
@@ -5960,10 +5958,10 @@
         </is>
       </c>
       <c r="J122" s="9" t="n">
-        <v>5.068</v>
+        <v>2.533</v>
       </c>
       <c r="K122" s="9" t="n">
-        <v>5.062</v>
+        <v>2.211</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="14" t="inlineStr"/>
@@ -5991,7 +5989,7 @@
         <v>0</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>1354000</v>
+        <v>1374000</v>
       </c>
       <c r="G123" s="12" t="n">
         <v>0.22</v>
@@ -6021,28 +6019,28 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>5246</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>MALAKOF</t>
+          <t>WPRTS</t>
         </is>
       </c>
       <c r="D124" s="9" t="n">
-        <v>0.765</v>
-      </c>
-      <c r="E124" s="10" t="n">
-        <v>-0.0129</v>
+        <v>6.76</v>
+      </c>
+      <c r="E124" s="16" t="n">
+        <v>0.004500000000000001</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>1352300</v>
+        <v>1373500</v>
       </c>
       <c r="G124" s="12" t="n">
         <v>0.31</v>
       </c>
       <c r="H124" t="n">
-        <v>42.45</v>
+        <v>49.84</v>
       </c>
       <c r="I124" s="13" t="inlineStr">
         <is>
@@ -6050,10 +6048,10 @@
         </is>
       </c>
       <c r="J124" s="9" t="n">
-        <v>0.787</v>
+        <v>6.761</v>
       </c>
       <c r="K124" s="9" t="n">
-        <v>0.804</v>
+        <v>6.839</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="14" t="inlineStr"/>
@@ -6066,28 +6064,28 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>SDG</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D125" s="9" t="n">
-        <v>5.98</v>
-      </c>
-      <c r="E125" s="16" t="n">
-        <v>0.0101</v>
+        <v>0.795</v>
+      </c>
+      <c r="E125" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>1338600</v>
+        <v>1372000</v>
       </c>
       <c r="G125" s="12" t="n">
-        <v>0.14</v>
+        <v>0.21</v>
       </c>
       <c r="H125" t="n">
-        <v>38.41</v>
+        <v>62.06</v>
       </c>
       <c r="I125" s="13" t="inlineStr">
         <is>
@@ -6095,10 +6093,10 @@
         </is>
       </c>
       <c r="J125" s="9" t="n">
-        <v>6.108</v>
+        <v>0.764</v>
       </c>
       <c r="K125" s="9" t="n">
-        <v>6.363</v>
+        <v>0.676</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="14" t="inlineStr"/>
@@ -6111,28 +6109,28 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>5195</t>
+          <t>0128</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>CENSOF</t>
+          <t>FRONTKN</t>
         </is>
       </c>
       <c r="D126" s="9" t="n">
-        <v>0.205</v>
-      </c>
-      <c r="E126" s="10" t="n">
-        <v>-0.0238</v>
+        <v>5.15</v>
+      </c>
+      <c r="E126" s="16" t="n">
+        <v>0.0118</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>1330600</v>
+        <v>1362000</v>
       </c>
       <c r="G126" s="12" t="n">
-        <v>0.6</v>
+        <v>0.31</v>
       </c>
       <c r="H126" t="n">
-        <v>43.5</v>
+        <v>56.5</v>
       </c>
       <c r="I126" s="13" t="inlineStr">
         <is>
@@ -6140,10 +6138,10 @@
         </is>
       </c>
       <c r="J126" s="9" t="n">
-        <v>0.218</v>
+        <v>5.069</v>
       </c>
       <c r="K126" s="9" t="n">
-        <v>0.208</v>
+        <v>5.062</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="14" t="inlineStr"/>
@@ -6156,39 +6154,39 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="D127" s="9" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="E127" s="10" t="n">
-        <v>-0.0061</v>
+        <v>5.99</v>
+      </c>
+      <c r="E127" s="16" t="n">
+        <v>0.0118</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>1319300</v>
+        <v>1355700</v>
       </c>
       <c r="G127" s="12" t="n">
-        <v>0.35</v>
+        <v>0.14</v>
       </c>
       <c r="H127" t="n">
-        <v>50.94</v>
-      </c>
-      <c r="I127" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.16</v>
+      </c>
+      <c r="I127" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J127" s="9" t="n">
-        <v>0.827</v>
+        <v>6.109</v>
       </c>
       <c r="K127" s="9" t="n">
-        <v>0.77</v>
+        <v>6.363</v>
       </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" s="14" t="inlineStr"/>
@@ -6201,39 +6199,39 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>7498</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>RALCO</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D128" s="9" t="n">
-        <v>1.01</v>
+        <v>0.275</v>
       </c>
       <c r="E128" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>1301700</v>
+        <v>1340400</v>
       </c>
       <c r="G128" s="12" t="n">
-        <v>1.99</v>
+        <v>0.15</v>
       </c>
       <c r="H128" t="n">
-        <v>55.9</v>
-      </c>
-      <c r="I128" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.42</v>
+      </c>
+      <c r="I128" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J128" s="9" t="n">
-        <v>0.999</v>
+        <v>0.278</v>
       </c>
       <c r="K128" s="9" t="n">
-        <v>0.982</v>
+        <v>0.3</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="14" t="inlineStr"/>
@@ -6246,39 +6244,39 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>0337</t>
+          <t>5195</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>SET</t>
+          <t>CENSOF</t>
         </is>
       </c>
       <c r="D129" s="9" t="n">
-        <v>0.255</v>
-      </c>
-      <c r="E129" s="15" t="n">
-        <v>0</v>
+        <v>0.205</v>
+      </c>
+      <c r="E129" s="10" t="n">
+        <v>-0.0238</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>1296800</v>
+        <v>1331000</v>
       </c>
       <c r="G129" s="12" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="H129" t="n">
-        <v>60.29</v>
-      </c>
-      <c r="I129" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.5</v>
+      </c>
+      <c r="I129" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J129" s="9" t="n">
-        <v>0.24</v>
+        <v>0.218</v>
       </c>
       <c r="K129" s="9" t="n">
-        <v>0.243</v>
+        <v>0.208</v>
       </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" s="14" t="inlineStr"/>
@@ -6291,38 +6289,40 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>0468</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>UNIPAC</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D130" s="9" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="E130" s="10" t="n">
-        <v>-0.0213</v>
+        <v>0.83</v>
+      </c>
+      <c r="E130" s="16" t="n">
+        <v>0.0061</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>1295000</v>
+        <v>1321300</v>
       </c>
       <c r="G130" s="12" t="n">
-        <v>0.14</v>
+        <v>0.35</v>
       </c>
       <c r="H130" t="n">
-        <v>24.97</v>
-      </c>
-      <c r="I130" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.72</v>
+      </c>
+      <c r="I130" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J130" s="9" t="n">
-        <v>0.257</v>
-      </c>
-      <c r="K130" s="9" t="n"/>
+        <v>0.828</v>
+      </c>
+      <c r="K130" s="9" t="n">
+        <v>0.77</v>
+      </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" s="14" t="inlineStr"/>
     </row>
@@ -6334,39 +6334,39 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>5246</t>
+          <t>7498</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>WPRTS</t>
+          <t>RALCO</t>
         </is>
       </c>
       <c r="D131" s="9" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="E131" s="16" t="n">
-        <v>0.003</v>
+        <v>1.01</v>
+      </c>
+      <c r="E131" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>1286100</v>
+        <v>1301700</v>
       </c>
       <c r="G131" s="12" t="n">
-        <v>0.29</v>
+        <v>1.99</v>
       </c>
       <c r="H131" t="n">
-        <v>49.22</v>
-      </c>
-      <c r="I131" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.9</v>
+      </c>
+      <c r="I131" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J131" s="9" t="n">
-        <v>6.76</v>
+        <v>0.999</v>
       </c>
       <c r="K131" s="9" t="n">
-        <v>6.839</v>
+        <v>0.982</v>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" s="14" t="inlineStr"/>
@@ -6379,28 +6379,28 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>0337</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>IHH</t>
+          <t>SET</t>
         </is>
       </c>
       <c r="D132" s="9" t="n">
-        <v>8.039999999999999</v>
-      </c>
-      <c r="E132" s="16" t="n">
-        <v>0.0075</v>
+        <v>0.255</v>
+      </c>
+      <c r="E132" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F132" s="11" t="n">
-        <v>1284000</v>
+        <v>1296800</v>
       </c>
       <c r="G132" s="12" t="n">
-        <v>0.33</v>
+        <v>0.7</v>
       </c>
       <c r="H132" t="n">
-        <v>57.92</v>
+        <v>60.29</v>
       </c>
       <c r="I132" s="17" t="inlineStr">
         <is>
@@ -6408,10 +6408,10 @@
         </is>
       </c>
       <c r="J132" s="9" t="n">
-        <v>7.896</v>
+        <v>0.24</v>
       </c>
       <c r="K132" s="9" t="n">
-        <v>7.989</v>
+        <v>0.243</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="14" t="inlineStr"/>
@@ -6424,39 +6424,39 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>0353</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>WESTRVR</t>
+          <t>IHH</t>
         </is>
       </c>
       <c r="D133" s="9" t="n">
-        <v>0.41</v>
+        <v>8.06</v>
       </c>
       <c r="E133" s="16" t="n">
-        <v>0.025</v>
+        <v>0.01</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>1275800</v>
+        <v>1284800</v>
       </c>
       <c r="G133" s="12" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="H133" t="n">
-        <v>50.62</v>
-      </c>
-      <c r="I133" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.84</v>
+      </c>
+      <c r="I133" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J133" s="9" t="n">
-        <v>0.418</v>
+        <v>7.898</v>
       </c>
       <c r="K133" s="9" t="n">
-        <v>0.376</v>
+        <v>7.989</v>
       </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" s="14" t="inlineStr"/>
@@ -6469,39 +6469,39 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>0353</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>ATECH</t>
+          <t>WESTRVR</t>
         </is>
       </c>
       <c r="D134" s="9" t="n">
-        <v>0.805</v>
+        <v>0.415</v>
       </c>
       <c r="E134" s="16" t="n">
-        <v>0.0321</v>
+        <v>0.0375</v>
       </c>
       <c r="F134" s="11" t="n">
-        <v>1270000</v>
+        <v>1277900</v>
       </c>
       <c r="G134" s="12" t="n">
-        <v>0.58</v>
+        <v>0.35</v>
       </c>
       <c r="H134" t="n">
-        <v>58</v>
-      </c>
-      <c r="I134" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.8</v>
+      </c>
+      <c r="I134" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J134" s="9" t="n">
-        <v>0.777</v>
+        <v>0.419</v>
       </c>
       <c r="K134" s="9" t="n">
-        <v>0.766</v>
+        <v>0.376</v>
       </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" s="14" t="inlineStr"/>
@@ -6514,39 +6514,39 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>5302</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>ATECH</t>
         </is>
       </c>
       <c r="D135" s="9" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="E135" s="10" t="n">
-        <v>-0.0182</v>
+        <v>0.8</v>
+      </c>
+      <c r="E135" s="16" t="n">
+        <v>0.0256</v>
       </c>
       <c r="F135" s="11" t="n">
-        <v>1255700</v>
+        <v>1275500</v>
       </c>
       <c r="G135" s="12" t="n">
-        <v>0.15</v>
+        <v>0.58</v>
       </c>
       <c r="H135" t="n">
-        <v>45.23</v>
-      </c>
-      <c r="I135" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.99</v>
+      </c>
+      <c r="I135" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J135" s="9" t="n">
-        <v>0.278</v>
+        <v>0.777</v>
       </c>
       <c r="K135" s="9" t="n">
-        <v>0.3</v>
+        <v>0.765</v>
       </c>
       <c r="L135" t="inlineStr"/>
       <c r="M135" s="14" t="inlineStr"/>
@@ -6568,19 +6568,19 @@
         </is>
       </c>
       <c r="D136" s="9" t="n">
-        <v>0.895</v>
+        <v>0.9</v>
       </c>
       <c r="E136" s="10" t="n">
-        <v>-0.011</v>
+        <v>-0.005500000000000001</v>
       </c>
       <c r="F136" s="11" t="n">
-        <v>1238100</v>
+        <v>1249900</v>
       </c>
       <c r="G136" s="12" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="H136" t="n">
-        <v>38.69</v>
+        <v>40.31</v>
       </c>
       <c r="I136" s="13" t="inlineStr">
         <is>
@@ -6591,7 +6591,7 @@
         <v>0.917</v>
       </c>
       <c r="K136" s="9" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" s="14" t="inlineStr"/>
@@ -6649,39 +6649,39 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>5932</t>
+          <t>0240</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>BPURI</t>
+          <t>CORAZA</t>
         </is>
       </c>
       <c r="D138" s="9" t="n">
-        <v>0.215</v>
-      </c>
-      <c r="E138" s="15" t="n">
-        <v>0</v>
+        <v>1.31</v>
+      </c>
+      <c r="E138" s="16" t="n">
+        <v>0.0077</v>
       </c>
       <c r="F138" s="11" t="n">
-        <v>1180700</v>
+        <v>1230500</v>
       </c>
       <c r="G138" s="12" t="n">
-        <v>2.62</v>
+        <v>0.52</v>
       </c>
       <c r="H138" t="n">
-        <v>38.87</v>
-      </c>
-      <c r="I138" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.5</v>
+      </c>
+      <c r="I138" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J138" s="9" t="n">
-        <v>0.225</v>
+        <v>1.245</v>
       </c>
       <c r="K138" s="9" t="n">
-        <v>0.233</v>
+        <v>1.164</v>
       </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" s="14" t="inlineStr"/>
@@ -6694,28 +6694,28 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>UWC</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D139" s="9" t="n">
-        <v>7.66</v>
-      </c>
-      <c r="E139" s="16" t="n">
-        <v>0.0013</v>
+        <v>1.7</v>
+      </c>
+      <c r="E139" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F139" s="11" t="n">
-        <v>1170800</v>
+        <v>1195900</v>
       </c>
       <c r="G139" s="12" t="n">
-        <v>0.28</v>
+        <v>0.24</v>
       </c>
       <c r="H139" t="n">
-        <v>61.77</v>
+        <v>42.09</v>
       </c>
       <c r="I139" s="13" t="inlineStr">
         <is>
@@ -6723,10 +6723,10 @@
         </is>
       </c>
       <c r="J139" s="9" t="n">
-        <v>7.375</v>
+        <v>1.746</v>
       </c>
       <c r="K139" s="9" t="n">
-        <v>6.846</v>
+        <v>1.774</v>
       </c>
       <c r="L139" t="inlineStr"/>
       <c r="M139" s="14" t="inlineStr"/>
@@ -6739,28 +6739,28 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>5932</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>BPURI</t>
         </is>
       </c>
       <c r="D140" s="9" t="n">
-        <v>1.7</v>
+        <v>0.215</v>
       </c>
       <c r="E140" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F140" s="11" t="n">
-        <v>1137500</v>
+        <v>1180700</v>
       </c>
       <c r="G140" s="12" t="n">
-        <v>0.23</v>
+        <v>2.62</v>
       </c>
       <c r="H140" t="n">
-        <v>42.09</v>
+        <v>38.87</v>
       </c>
       <c r="I140" s="13" t="inlineStr">
         <is>
@@ -6768,10 +6768,10 @@
         </is>
       </c>
       <c r="J140" s="9" t="n">
-        <v>1.746</v>
+        <v>0.225</v>
       </c>
       <c r="K140" s="9" t="n">
-        <v>1.774</v>
+        <v>0.233</v>
       </c>
       <c r="L140" t="inlineStr"/>
       <c r="M140" s="14" t="inlineStr"/>
@@ -6784,28 +6784,28 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>UWC</t>
         </is>
       </c>
       <c r="D141" s="9" t="n">
-        <v>0.365</v>
+        <v>7.65</v>
       </c>
       <c r="E141" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F141" s="11" t="n">
-        <v>1122200</v>
+        <v>1179200</v>
       </c>
       <c r="G141" s="12" t="n">
-        <v>0.12</v>
+        <v>0.28</v>
       </c>
       <c r="H141" t="n">
-        <v>57.29</v>
+        <v>61.58</v>
       </c>
       <c r="I141" s="13" t="inlineStr">
         <is>
@@ -6813,10 +6813,10 @@
         </is>
       </c>
       <c r="J141" s="9" t="n">
-        <v>0.357</v>
+        <v>7.374</v>
       </c>
       <c r="K141" s="9" t="n">
-        <v>0.325</v>
+        <v>6.846</v>
       </c>
       <c r="L141" t="inlineStr"/>
       <c r="M141" s="14" t="inlineStr"/>
@@ -6829,28 +6829,28 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D142" s="9" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="E142" s="15" t="n">
-        <v>0</v>
+        <v>0.27</v>
+      </c>
+      <c r="E142" s="16" t="n">
+        <v>0.0189</v>
       </c>
       <c r="F142" s="11" t="n">
-        <v>1120700</v>
+        <v>1178400</v>
       </c>
       <c r="G142" s="12" t="n">
-        <v>0.22</v>
+        <v>0.15</v>
       </c>
       <c r="H142" t="n">
-        <v>39.5</v>
+        <v>34.49</v>
       </c>
       <c r="I142" s="13" t="inlineStr">
         <is>
@@ -6858,10 +6858,10 @@
         </is>
       </c>
       <c r="J142" s="9" t="n">
-        <v>0.336</v>
+        <v>0.284</v>
       </c>
       <c r="K142" s="9" t="n">
-        <v>0.343</v>
+        <v>0.305</v>
       </c>
       <c r="L142" t="inlineStr"/>
       <c r="M142" s="14" t="inlineStr"/>
@@ -6874,39 +6874,39 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>SPSETIA</t>
         </is>
       </c>
       <c r="D143" s="9" t="n">
-        <v>1.33</v>
+        <v>0.695</v>
       </c>
       <c r="E143" s="16" t="n">
-        <v>0.0231</v>
+        <v>0.0146</v>
       </c>
       <c r="F143" s="11" t="n">
-        <v>1114800</v>
+        <v>1175200</v>
       </c>
       <c r="G143" s="12" t="n">
-        <v>0.47</v>
+        <v>0.17</v>
       </c>
       <c r="H143" t="n">
-        <v>62.13</v>
-      </c>
-      <c r="I143" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>31.47</v>
+      </c>
+      <c r="I143" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J143" s="9" t="n">
-        <v>1.247</v>
+        <v>0.74</v>
       </c>
       <c r="K143" s="9" t="n">
-        <v>1.165</v>
+        <v>0.806</v>
       </c>
       <c r="L143" t="inlineStr"/>
       <c r="M143" s="14" t="inlineStr"/>
@@ -6919,28 +6919,28 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>SPSETIA</t>
+          <t>MBSB</t>
         </is>
       </c>
       <c r="D144" s="9" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="E144" s="16" t="n">
-        <v>0.0073</v>
+        <v>0.54</v>
+      </c>
+      <c r="E144" s="10" t="n">
+        <v>-0.0182</v>
       </c>
       <c r="F144" s="11" t="n">
-        <v>1100000</v>
+        <v>1142200</v>
       </c>
       <c r="G144" s="12" t="n">
-        <v>0.16</v>
+        <v>0.34</v>
       </c>
       <c r="H144" t="n">
-        <v>29.43</v>
+        <v>41.5</v>
       </c>
       <c r="I144" s="13" t="inlineStr">
         <is>
@@ -6948,10 +6948,10 @@
         </is>
       </c>
       <c r="J144" s="9" t="n">
-        <v>0.739</v>
+        <v>0.549</v>
       </c>
       <c r="K144" s="9" t="n">
-        <v>0.806</v>
+        <v>0.577</v>
       </c>
       <c r="L144" t="inlineStr"/>
       <c r="M144" s="14" t="inlineStr"/>
@@ -6964,28 +6964,28 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>MRCB</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="D145" s="9" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="E145" s="16" t="n">
-        <v>0.0189</v>
+        <v>0.325</v>
+      </c>
+      <c r="E145" s="10" t="n">
+        <v>-0.0152</v>
       </c>
       <c r="F145" s="11" t="n">
-        <v>1088600</v>
+        <v>1134100</v>
       </c>
       <c r="G145" s="12" t="n">
-        <v>0.14</v>
+        <v>0.22</v>
       </c>
       <c r="H145" t="n">
-        <v>34.49</v>
+        <v>35.48</v>
       </c>
       <c r="I145" s="13" t="inlineStr">
         <is>
@@ -6993,10 +6993,10 @@
         </is>
       </c>
       <c r="J145" s="9" t="n">
-        <v>0.284</v>
+        <v>0.336</v>
       </c>
       <c r="K145" s="9" t="n">
-        <v>0.305</v>
+        <v>0.343</v>
       </c>
       <c r="L145" t="inlineStr"/>
       <c r="M145" s="14" t="inlineStr"/>
@@ -7009,28 +7009,28 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>0151</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>KGB</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D146" s="9" t="n">
-        <v>8.68</v>
-      </c>
-      <c r="E146" s="16" t="n">
-        <v>0.0212</v>
+        <v>0.365</v>
+      </c>
+      <c r="E146" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F146" s="11" t="n">
-        <v>1075100</v>
+        <v>1122200</v>
       </c>
       <c r="G146" s="12" t="n">
-        <v>0.47</v>
+        <v>0.12</v>
       </c>
       <c r="H146" t="n">
-        <v>49.72</v>
+        <v>57.29</v>
       </c>
       <c r="I146" s="13" t="inlineStr">
         <is>
@@ -7038,10 +7038,10 @@
         </is>
       </c>
       <c r="J146" s="9" t="n">
-        <v>8.709</v>
+        <v>0.357</v>
       </c>
       <c r="K146" s="9" t="n">
-        <v>8.702</v>
+        <v>0.325</v>
       </c>
       <c r="L146" t="inlineStr"/>
       <c r="M146" s="14" t="inlineStr"/>
@@ -7054,28 +7054,28 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>0298</t>
+          <t>0373</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>WENTEL</t>
+          <t>VERDANT</t>
         </is>
       </c>
       <c r="D147" s="9" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="E147" s="16" t="n">
-        <v>0.0213</v>
+        <v>0.235</v>
+      </c>
+      <c r="E147" s="10" t="n">
+        <v>-0.0408</v>
       </c>
       <c r="F147" s="11" t="n">
-        <v>1073400</v>
+        <v>1103200</v>
       </c>
       <c r="G147" s="12" t="n">
-        <v>0.64</v>
+        <v>0.23</v>
       </c>
       <c r="H147" t="n">
-        <v>35.75</v>
+        <v>45.82</v>
       </c>
       <c r="I147" s="13" t="inlineStr">
         <is>
@@ -7083,10 +7083,10 @@
         </is>
       </c>
       <c r="J147" s="9" t="n">
-        <v>0.258</v>
+        <v>0.249</v>
       </c>
       <c r="K147" s="9" t="n">
-        <v>0.276</v>
+        <v>0.222</v>
       </c>
       <c r="L147" t="inlineStr"/>
       <c r="M147" s="14" t="inlineStr"/>
@@ -7099,28 +7099,28 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>0373</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>VERDANT</t>
+          <t>MAHSING</t>
         </is>
       </c>
       <c r="D148" s="9" t="n">
-        <v>0.235</v>
-      </c>
-      <c r="E148" s="10" t="n">
-        <v>-0.0408</v>
+        <v>0.95</v>
+      </c>
+      <c r="E148" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F148" s="11" t="n">
-        <v>1066000</v>
+        <v>1101000</v>
       </c>
       <c r="G148" s="12" t="n">
-        <v>0.22</v>
+        <v>0.29</v>
       </c>
       <c r="H148" t="n">
-        <v>45.82</v>
+        <v>31.13</v>
       </c>
       <c r="I148" s="13" t="inlineStr">
         <is>
@@ -7128,10 +7128,10 @@
         </is>
       </c>
       <c r="J148" s="9" t="n">
-        <v>0.249</v>
+        <v>0.984</v>
       </c>
       <c r="K148" s="9" t="n">
-        <v>0.222</v>
+        <v>1.062</v>
       </c>
       <c r="L148" t="inlineStr"/>
       <c r="M148" s="14" t="inlineStr"/>
@@ -7144,39 +7144,39 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>0285</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>MERSEC</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D149" s="9" t="n">
-        <v>0.27</v>
+        <v>1.09</v>
       </c>
       <c r="E149" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F149" s="11" t="n">
-        <v>1054400</v>
+        <v>1081400</v>
       </c>
       <c r="G149" s="12" t="n">
-        <v>0.96</v>
+        <v>0.27</v>
       </c>
       <c r="H149" t="n">
-        <v>41.54</v>
-      </c>
-      <c r="I149" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.39</v>
+      </c>
+      <c r="I149" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J149" s="9" t="n">
-        <v>0.272</v>
+        <v>1.044</v>
       </c>
       <c r="K149" s="9" t="n">
-        <v>0.276</v>
+        <v>0.887</v>
       </c>
       <c r="L149" t="inlineStr"/>
       <c r="M149" s="14" t="inlineStr"/>
@@ -7189,39 +7189,39 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>0151</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>KGB</t>
         </is>
       </c>
       <c r="D150" s="9" t="n">
-        <v>1.1</v>
+        <v>8.67</v>
       </c>
       <c r="E150" s="16" t="n">
-        <v>0.0092</v>
+        <v>0.02</v>
       </c>
       <c r="F150" s="11" t="n">
-        <v>1051400</v>
+        <v>1075500</v>
       </c>
       <c r="G150" s="12" t="n">
-        <v>0.26</v>
+        <v>0.47</v>
       </c>
       <c r="H150" t="n">
-        <v>59.17</v>
-      </c>
-      <c r="I150" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.48</v>
+      </c>
+      <c r="I150" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J150" s="9" t="n">
-        <v>1.045</v>
+        <v>8.708</v>
       </c>
       <c r="K150" s="9" t="n">
-        <v>0.888</v>
+        <v>8.702</v>
       </c>
       <c r="L150" t="inlineStr"/>
       <c r="M150" s="14" t="inlineStr"/>
@@ -7234,39 +7234,39 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>7160</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>PENTA</t>
         </is>
       </c>
       <c r="D151" s="9" t="n">
-        <v>0.695</v>
-      </c>
-      <c r="E151" s="16" t="n">
-        <v>0.0072</v>
+        <v>5.49</v>
+      </c>
+      <c r="E151" s="10" t="n">
+        <v>-0.0036</v>
       </c>
       <c r="F151" s="11" t="n">
-        <v>1051300</v>
+        <v>1074000</v>
       </c>
       <c r="G151" s="12" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="H151" t="n">
-        <v>38.91</v>
-      </c>
-      <c r="I151" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.84</v>
+      </c>
+      <c r="I151" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J151" s="9" t="n">
-        <v>0.745</v>
+        <v>5.508</v>
       </c>
       <c r="K151" s="9" t="n">
-        <v>0.747</v>
+        <v>5.387</v>
       </c>
       <c r="L151" t="inlineStr"/>
       <c r="M151" s="14" t="inlineStr"/>
@@ -7279,28 +7279,28 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>0298</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>WENTEL</t>
         </is>
       </c>
       <c r="D152" s="9" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="E152" s="15" t="n">
-        <v>0</v>
+        <v>0.24</v>
+      </c>
+      <c r="E152" s="16" t="n">
+        <v>0.0213</v>
       </c>
       <c r="F152" s="11" t="n">
-        <v>1042600</v>
+        <v>1073400</v>
       </c>
       <c r="G152" s="12" t="n">
-        <v>0.32</v>
+        <v>0.64</v>
       </c>
       <c r="H152" t="n">
-        <v>33.88</v>
+        <v>35.75</v>
       </c>
       <c r="I152" s="13" t="inlineStr">
         <is>
@@ -7308,10 +7308,10 @@
         </is>
       </c>
       <c r="J152" s="9" t="n">
-        <v>2.931</v>
+        <v>0.258</v>
       </c>
       <c r="K152" s="9" t="n">
-        <v>3.026</v>
+        <v>0.276</v>
       </c>
       <c r="L152" t="inlineStr"/>
       <c r="M152" s="14" t="inlineStr"/>
@@ -7324,28 +7324,28 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D153" s="9" t="n">
-        <v>2.71</v>
+        <v>0.695</v>
       </c>
       <c r="E153" s="16" t="n">
-        <v>0.0037</v>
+        <v>0.0072</v>
       </c>
       <c r="F153" s="11" t="n">
-        <v>1008500</v>
+        <v>1068300</v>
       </c>
       <c r="G153" s="12" t="n">
-        <v>0.2</v>
+        <v>0.34</v>
       </c>
       <c r="H153" t="n">
-        <v>39.64</v>
+        <v>38.91</v>
       </c>
       <c r="I153" s="13" t="inlineStr">
         <is>
@@ -7353,10 +7353,10 @@
         </is>
       </c>
       <c r="J153" s="9" t="n">
-        <v>2.907</v>
+        <v>0.745</v>
       </c>
       <c r="K153" s="9" t="n">
-        <v>2.86</v>
+        <v>0.747</v>
       </c>
       <c r="L153" t="inlineStr"/>
       <c r="M153" s="14" t="inlineStr"/>
@@ -7369,39 +7369,39 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>7943</t>
+          <t>0285</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>GREENTEC</t>
+          <t>MERSEC</t>
         </is>
       </c>
       <c r="D154" s="9" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="E154" s="10" t="n">
-        <v>-0.0333</v>
+        <v>0.27</v>
+      </c>
+      <c r="E154" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F154" s="11" t="n">
-        <v>1007000</v>
+        <v>1054400</v>
       </c>
       <c r="G154" s="12" t="n">
-        <v>0.92</v>
+        <v>0.96</v>
       </c>
       <c r="H154" t="n">
-        <v>66.97</v>
-      </c>
-      <c r="I154" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.54</v>
+      </c>
+      <c r="I154" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J154" s="9" t="n">
-        <v>0.257</v>
+        <v>0.272</v>
       </c>
       <c r="K154" s="9" t="n">
-        <v>0.211</v>
+        <v>0.276</v>
       </c>
       <c r="L154" t="inlineStr"/>
       <c r="M154" s="14" t="inlineStr"/>
@@ -7414,39 +7414,39 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>7160</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>PENTA</t>
+          <t>SKYECHIP</t>
         </is>
       </c>
       <c r="D155" s="9" t="n">
-        <v>5.52</v>
+        <v>2.77</v>
       </c>
       <c r="E155" s="16" t="n">
-        <v>0.0018</v>
+        <v>0.0036</v>
       </c>
       <c r="F155" s="11" t="n">
-        <v>995200</v>
+        <v>1043200</v>
       </c>
       <c r="G155" s="12" t="n">
-        <v>0.27</v>
+        <v>0.32</v>
       </c>
       <c r="H155" t="n">
-        <v>51.62</v>
-      </c>
-      <c r="I155" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.92</v>
+      </c>
+      <c r="I155" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J155" s="9" t="n">
-        <v>5.511</v>
+        <v>2.932</v>
       </c>
       <c r="K155" s="9" t="n">
-        <v>5.387</v>
+        <v>3.026</v>
       </c>
       <c r="L155" t="inlineStr"/>
       <c r="M155" s="14" t="inlineStr"/>
@@ -7459,28 +7459,28 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>4383</t>
+          <t>0369</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>JTIASA</t>
+          <t>JSSOLAR</t>
         </is>
       </c>
       <c r="D156" s="9" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="E156" s="16" t="n">
-        <v>0.0162</v>
+        <v>0.235</v>
+      </c>
+      <c r="E156" s="10" t="n">
+        <v>-0.0408</v>
       </c>
       <c r="F156" s="11" t="n">
-        <v>974100</v>
+        <v>1028100</v>
       </c>
       <c r="G156" s="12" t="n">
-        <v>0.35</v>
+        <v>0.54</v>
       </c>
       <c r="H156" t="n">
-        <v>40.19</v>
+        <v>51.86</v>
       </c>
       <c r="I156" s="13" t="inlineStr">
         <is>
@@ -7488,10 +7488,10 @@
         </is>
       </c>
       <c r="J156" s="9" t="n">
-        <v>0.957</v>
+        <v>0.236</v>
       </c>
       <c r="K156" s="9" t="n">
-        <v>1.012</v>
+        <v>0.211</v>
       </c>
       <c r="L156" t="inlineStr"/>
       <c r="M156" s="14" t="inlineStr"/>
@@ -7504,28 +7504,28 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D157" s="9" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="E157" s="10" t="n">
-        <v>-0.0105</v>
+        <v>2.7</v>
+      </c>
+      <c r="E157" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F157" s="11" t="n">
-        <v>970900</v>
+        <v>1025600</v>
       </c>
       <c r="G157" s="12" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="H157" t="n">
-        <v>55.83</v>
+        <v>39.03</v>
       </c>
       <c r="I157" s="13" t="inlineStr">
         <is>
@@ -7533,10 +7533,10 @@
         </is>
       </c>
       <c r="J157" s="9" t="n">
-        <v>2.798</v>
+        <v>2.906</v>
       </c>
       <c r="K157" s="9" t="n">
-        <v>2.636</v>
+        <v>2.86</v>
       </c>
       <c r="L157" t="inlineStr"/>
       <c r="M157" s="14" t="inlineStr"/>
@@ -7549,39 +7549,39 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>9059</t>
+          <t>7943</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>TSH</t>
+          <t>GREENTEC</t>
         </is>
       </c>
       <c r="D158" s="9" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="E158" s="16" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.29</v>
+      </c>
+      <c r="E158" s="10" t="n">
+        <v>-0.0333</v>
       </c>
       <c r="F158" s="11" t="n">
-        <v>941600</v>
+        <v>1007000</v>
       </c>
       <c r="G158" s="12" t="n">
-        <v>0.41</v>
+        <v>0.92</v>
       </c>
       <c r="H158" t="n">
-        <v>33</v>
-      </c>
-      <c r="I158" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.97</v>
+      </c>
+      <c r="I158" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J158" s="9" t="n">
-        <v>1.262</v>
+        <v>0.257</v>
       </c>
       <c r="K158" s="9" t="n">
-        <v>1.309</v>
+        <v>0.211</v>
       </c>
       <c r="L158" t="inlineStr"/>
       <c r="M158" s="14" t="inlineStr"/>
@@ -7594,39 +7594,39 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>0045</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>DUFU</t>
+          <t>SSB8</t>
         </is>
       </c>
       <c r="D159" s="9" t="n">
-        <v>3.12</v>
+        <v>0.65</v>
       </c>
       <c r="E159" s="16" t="n">
-        <v>0.013</v>
+        <v>0.0156</v>
       </c>
       <c r="F159" s="11" t="n">
-        <v>916000</v>
+        <v>985900</v>
       </c>
       <c r="G159" s="12" t="n">
-        <v>0.29</v>
+        <v>0.26</v>
       </c>
       <c r="H159" t="n">
-        <v>57.02</v>
-      </c>
-      <c r="I159" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.56</v>
+      </c>
+      <c r="I159" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J159" s="9" t="n">
-        <v>3.033</v>
+        <v>0.64</v>
       </c>
       <c r="K159" s="9" t="n">
-        <v>2.839</v>
+        <v>0.609</v>
       </c>
       <c r="L159" t="inlineStr"/>
       <c r="M159" s="14" t="inlineStr"/>
@@ -7639,39 +7639,39 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>0045</t>
+          <t>4383</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>SSB8</t>
+          <t>JTIASA</t>
         </is>
       </c>
       <c r="D160" s="9" t="n">
-        <v>0.65</v>
+        <v>0.945</v>
       </c>
       <c r="E160" s="16" t="n">
-        <v>0.0156</v>
+        <v>0.0216</v>
       </c>
       <c r="F160" s="11" t="n">
-        <v>912400</v>
+        <v>984100</v>
       </c>
       <c r="G160" s="12" t="n">
-        <v>0.24</v>
+        <v>0.35</v>
       </c>
       <c r="H160" t="n">
-        <v>55.56</v>
-      </c>
-      <c r="I160" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.06</v>
+      </c>
+      <c r="I160" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J160" s="9" t="n">
-        <v>0.64</v>
+        <v>0.957</v>
       </c>
       <c r="K160" s="9" t="n">
-        <v>0.609</v>
+        <v>1.012</v>
       </c>
       <c r="L160" t="inlineStr"/>
       <c r="M160" s="14" t="inlineStr"/>
@@ -7684,28 +7684,28 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D161" s="9" t="n">
-        <v>1.24</v>
+        <v>2.84</v>
       </c>
       <c r="E161" s="10" t="n">
-        <v>-0.0159</v>
+        <v>-0.0105</v>
       </c>
       <c r="F161" s="11" t="n">
-        <v>905000</v>
+        <v>982400</v>
       </c>
       <c r="G161" s="12" t="n">
-        <v>0.27</v>
+        <v>0.11</v>
       </c>
       <c r="H161" t="n">
-        <v>46.99</v>
+        <v>55.83</v>
       </c>
       <c r="I161" s="13" t="inlineStr">
         <is>
@@ -7713,10 +7713,10 @@
         </is>
       </c>
       <c r="J161" s="9" t="n">
-        <v>1.29</v>
+        <v>2.798</v>
       </c>
       <c r="K161" s="9" t="n">
-        <v>1.213</v>
+        <v>2.636</v>
       </c>
       <c r="L161" t="inlineStr"/>
       <c r="M161" s="14" t="inlineStr"/>
@@ -7729,39 +7729,39 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>4863</t>
+          <t>9059</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>TM</t>
+          <t>TSH</t>
         </is>
       </c>
       <c r="D162" s="9" t="n">
-        <v>7.82</v>
-      </c>
-      <c r="E162" s="10" t="n">
-        <v>-0.0101</v>
+        <v>1.18</v>
+      </c>
+      <c r="E162" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F162" s="11" t="n">
-        <v>903700</v>
+        <v>974700</v>
       </c>
       <c r="G162" s="12" t="n">
-        <v>0.3</v>
+        <v>0.43</v>
       </c>
       <c r="H162" t="n">
-        <v>46.32</v>
-      </c>
-      <c r="I162" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>30.53</v>
+      </c>
+      <c r="I162" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J162" s="9" t="n">
-        <v>7.888</v>
+        <v>1.261</v>
       </c>
       <c r="K162" s="9" t="n">
-        <v>7.864</v>
+        <v>1.309</v>
       </c>
       <c r="L162" t="inlineStr"/>
       <c r="M162" s="14" t="inlineStr"/>
@@ -7774,28 +7774,28 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>DUFU</t>
         </is>
       </c>
       <c r="D163" s="9" t="n">
-        <v>0.895</v>
-      </c>
-      <c r="E163" s="10" t="n">
-        <v>-0.011</v>
+        <v>3.11</v>
+      </c>
+      <c r="E163" s="16" t="n">
+        <v>0.0097</v>
       </c>
       <c r="F163" s="11" t="n">
-        <v>883400</v>
+        <v>930500</v>
       </c>
       <c r="G163" s="12" t="n">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="H163" t="n">
-        <v>41.46</v>
+        <v>56.63</v>
       </c>
       <c r="I163" s="13" t="inlineStr">
         <is>
@@ -7803,10 +7803,10 @@
         </is>
       </c>
       <c r="J163" s="9" t="n">
-        <v>0.909</v>
+        <v>3.032</v>
       </c>
       <c r="K163" s="9" t="n">
-        <v>0.96</v>
+        <v>2.839</v>
       </c>
       <c r="L163" t="inlineStr"/>
       <c r="M163" s="14" t="inlineStr"/>
@@ -7819,39 +7819,39 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>CPETECH</t>
         </is>
       </c>
       <c r="D164" s="9" t="n">
-        <v>0.515</v>
+        <v>1.24</v>
       </c>
       <c r="E164" s="10" t="n">
-        <v>-0.009599999999999999</v>
+        <v>-0.0159</v>
       </c>
       <c r="F164" s="11" t="n">
-        <v>869400</v>
+        <v>906000</v>
       </c>
       <c r="G164" s="12" t="n">
-        <v>0.23</v>
+        <v>0.27</v>
       </c>
       <c r="H164" t="n">
-        <v>59.96</v>
-      </c>
-      <c r="I164" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.99</v>
+      </c>
+      <c r="I164" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J164" s="9" t="n">
-        <v>0.489</v>
+        <v>1.29</v>
       </c>
       <c r="K164" s="9" t="n">
-        <v>0.459</v>
+        <v>1.213</v>
       </c>
       <c r="L164" t="inlineStr"/>
       <c r="M164" s="14" t="inlineStr"/>
@@ -7864,28 +7864,28 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>5236</t>
+          <t>4863</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>MATRIX</t>
+          <t>TM</t>
         </is>
       </c>
       <c r="D165" s="9" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="E165" s="16" t="n">
-        <v>0.0187</v>
+        <v>7.83</v>
+      </c>
+      <c r="E165" s="10" t="n">
+        <v>-0.0089</v>
       </c>
       <c r="F165" s="11" t="n">
-        <v>856300</v>
+        <v>905100</v>
       </c>
       <c r="G165" s="12" t="n">
-        <v>0.68</v>
+        <v>0.3</v>
       </c>
       <c r="H165" t="n">
-        <v>45.75</v>
+        <v>46.87</v>
       </c>
       <c r="I165" s="17" t="inlineStr">
         <is>
@@ -7893,10 +7893,10 @@
         </is>
       </c>
       <c r="J165" s="9" t="n">
-        <v>1.097</v>
+        <v>7.889</v>
       </c>
       <c r="K165" s="9" t="n">
-        <v>1.14</v>
+        <v>7.864</v>
       </c>
       <c r="L165" t="inlineStr"/>
       <c r="M165" s="14" t="inlineStr"/>
@@ -7909,28 +7909,28 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>5258</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>BIMB</t>
         </is>
       </c>
       <c r="D166" s="9" t="n">
-        <v>0.945</v>
+        <v>2</v>
       </c>
       <c r="E166" s="10" t="n">
-        <v>-0.0053</v>
+        <v>-0.009899999999999999</v>
       </c>
       <c r="F166" s="11" t="n">
-        <v>856000</v>
+        <v>894500</v>
       </c>
       <c r="G166" s="12" t="n">
-        <v>0.22</v>
+        <v>1.15</v>
       </c>
       <c r="H166" t="n">
-        <v>30.03</v>
+        <v>33.38</v>
       </c>
       <c r="I166" s="13" t="inlineStr">
         <is>
@@ -7938,10 +7938,10 @@
         </is>
       </c>
       <c r="J166" s="9" t="n">
-        <v>0.984</v>
+        <v>2.048</v>
       </c>
       <c r="K166" s="9" t="n">
-        <v>1.062</v>
+        <v>2.089</v>
       </c>
       <c r="L166" t="inlineStr"/>
       <c r="M166" s="14" t="inlineStr"/>
@@ -7954,28 +7954,28 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>MBSB</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D167" s="9" t="n">
-        <v>0.535</v>
+        <v>0.895</v>
       </c>
       <c r="E167" s="10" t="n">
-        <v>-0.0273</v>
+        <v>-0.011</v>
       </c>
       <c r="F167" s="11" t="n">
-        <v>841900</v>
+        <v>892200</v>
       </c>
       <c r="G167" s="12" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="H167" t="n">
-        <v>39.4</v>
+        <v>41.46</v>
       </c>
       <c r="I167" s="13" t="inlineStr">
         <is>
@@ -7983,10 +7983,10 @@
         </is>
       </c>
       <c r="J167" s="9" t="n">
-        <v>0.549</v>
+        <v>0.909</v>
       </c>
       <c r="K167" s="9" t="n">
-        <v>0.577</v>
+        <v>0.96</v>
       </c>
       <c r="L167" t="inlineStr"/>
       <c r="M167" s="14" t="inlineStr"/>
@@ -7999,39 +7999,39 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>0375</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>THMY</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D168" s="9" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="E168" s="16" t="n">
-        <v>0.0144</v>
+        <v>0.515</v>
+      </c>
+      <c r="E168" s="10" t="n">
+        <v>-0.009599999999999999</v>
       </c>
       <c r="F168" s="11" t="n">
-        <v>831500</v>
+        <v>880400</v>
       </c>
       <c r="G168" s="12" t="n">
-        <v>0.35</v>
+        <v>0.23</v>
       </c>
       <c r="H168" t="n">
-        <v>52.42</v>
-      </c>
-      <c r="I168" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.96</v>
+      </c>
+      <c r="I168" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J168" s="9" t="n">
-        <v>2.118</v>
+        <v>0.489</v>
       </c>
       <c r="K168" s="9" t="n">
-        <v>1.98</v>
+        <v>0.459</v>
       </c>
       <c r="L168" t="inlineStr"/>
       <c r="M168" s="14" t="inlineStr"/>
@@ -8044,39 +8044,39 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>5258</t>
+          <t>5236</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>BIMB</t>
+          <t>MATRIX</t>
         </is>
       </c>
       <c r="D169" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="E169" s="10" t="n">
-        <v>-0.009899999999999999</v>
+        <v>1.09</v>
+      </c>
+      <c r="E169" s="16" t="n">
+        <v>0.0187</v>
       </c>
       <c r="F169" s="11" t="n">
-        <v>826200</v>
+        <v>867900</v>
       </c>
       <c r="G169" s="12" t="n">
-        <v>1.06</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H169" t="n">
-        <v>33.38</v>
-      </c>
-      <c r="I169" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>45.75</v>
+      </c>
+      <c r="I169" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J169" s="9" t="n">
-        <v>2.048</v>
+        <v>1.097</v>
       </c>
       <c r="K169" s="9" t="n">
-        <v>2.089</v>
+        <v>1.14</v>
       </c>
       <c r="L169" t="inlineStr"/>
       <c r="M169" s="14" t="inlineStr"/>
@@ -8089,39 +8089,39 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>5223</t>
+          <t>0375</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>MENTIGA</t>
+          <t>THMY</t>
         </is>
       </c>
       <c r="D170" s="9" t="n">
-        <v>0.79</v>
+        <v>2.11</v>
       </c>
       <c r="E170" s="16" t="n">
-        <v>0.3621</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="F170" s="11" t="n">
-        <v>802100</v>
+        <v>837500</v>
       </c>
       <c r="G170" s="12" t="n">
-        <v>36.29</v>
+        <v>0.35</v>
       </c>
       <c r="H170" t="n">
-        <v>73.45</v>
-      </c>
-      <c r="I170" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.87</v>
+      </c>
+      <c r="I170" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J170" s="9" t="n">
-        <v>0.609</v>
+        <v>2.117</v>
       </c>
       <c r="K170" s="9" t="n">
-        <v>0.642</v>
+        <v>1.979</v>
       </c>
       <c r="L170" t="inlineStr"/>
       <c r="M170" s="14" t="inlineStr"/>
@@ -8134,39 +8134,39 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>0265</t>
+          <t>5223</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>INFOM</t>
+          <t>MENTIGA</t>
         </is>
       </c>
       <c r="D171" s="9" t="n">
-        <v>1.87</v>
+        <v>0.79</v>
       </c>
       <c r="E171" s="16" t="n">
-        <v>0.0447</v>
+        <v>0.3621</v>
       </c>
       <c r="F171" s="11" t="n">
-        <v>782500</v>
+        <v>831800</v>
       </c>
       <c r="G171" s="12" t="n">
-        <v>1.1</v>
+        <v>37.64</v>
       </c>
       <c r="H171" t="n">
-        <v>71.20999999999999</v>
-      </c>
-      <c r="I171" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>73.45</v>
+      </c>
+      <c r="I171" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J171" s="9" t="n">
-        <v>1.753</v>
+        <v>0.609</v>
       </c>
       <c r="K171" s="9" t="n">
-        <v>1.627</v>
+        <v>0.642</v>
       </c>
       <c r="L171" t="inlineStr"/>
       <c r="M171" s="14" t="inlineStr"/>
@@ -8179,39 +8179,39 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>0336</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>WINSTAR</t>
+          <t>SUNWAY</t>
         </is>
       </c>
       <c r="D172" s="9" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E172" s="10" t="n">
-        <v>-0.0156</v>
+        <v>4.44</v>
+      </c>
+      <c r="E172" s="16" t="n">
+        <v>0.0091</v>
       </c>
       <c r="F172" s="11" t="n">
-        <v>769800</v>
+        <v>790100</v>
       </c>
       <c r="G172" s="12" t="n">
-        <v>1.27</v>
+        <v>0.14</v>
       </c>
       <c r="H172" t="n">
-        <v>35.73</v>
-      </c>
-      <c r="I172" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>43.65</v>
+      </c>
+      <c r="I172" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J172" s="9" t="n">
-        <v>0.643</v>
+        <v>4.474</v>
       </c>
       <c r="K172" s="9" t="n">
-        <v>0.63</v>
+        <v>4.774</v>
       </c>
       <c r="L172" t="inlineStr"/>
       <c r="M172" s="14" t="inlineStr"/>
@@ -8224,28 +8224,28 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>5053</t>
+          <t>0265</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>OSK</t>
+          <t>INFOM</t>
         </is>
       </c>
       <c r="D173" s="9" t="n">
-        <v>1.69</v>
+        <v>1.87</v>
       </c>
       <c r="E173" s="16" t="n">
-        <v>0.0181</v>
+        <v>0.0447</v>
       </c>
       <c r="F173" s="11" t="n">
-        <v>748400</v>
+        <v>786700</v>
       </c>
       <c r="G173" s="12" t="n">
-        <v>0.5</v>
+        <v>1.11</v>
       </c>
       <c r="H173" t="n">
-        <v>36.53</v>
+        <v>71.20999999999999</v>
       </c>
       <c r="I173" s="13" t="inlineStr">
         <is>
@@ -8253,10 +8253,10 @@
         </is>
       </c>
       <c r="J173" s="9" t="n">
-        <v>1.756</v>
+        <v>1.753</v>
       </c>
       <c r="K173" s="9" t="n">
-        <v>1.902</v>
+        <v>1.627</v>
       </c>
       <c r="L173" t="inlineStr"/>
       <c r="M173" s="14" t="inlineStr"/>
@@ -8269,28 +8269,28 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>0391</t>
+          <t>0336</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>AMBEST</t>
+          <t>WINSTAR</t>
         </is>
       </c>
       <c r="D174" s="9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="E174" s="16" t="n">
-        <v>0.0231</v>
+        <v>0.63</v>
+      </c>
+      <c r="E174" s="10" t="n">
+        <v>-0.0156</v>
       </c>
       <c r="F174" s="11" t="n">
-        <v>746800</v>
+        <v>769800</v>
       </c>
       <c r="G174" s="12" t="n">
-        <v>0.3</v>
+        <v>1.27</v>
       </c>
       <c r="H174" t="n">
-        <v>50.54</v>
+        <v>35.73</v>
       </c>
       <c r="I174" s="13" t="inlineStr">
         <is>
@@ -8298,10 +8298,10 @@
         </is>
       </c>
       <c r="J174" s="9" t="n">
-        <v>1.341</v>
+        <v>0.643</v>
       </c>
       <c r="K174" s="9" t="n">
-        <v>1.265</v>
+        <v>0.63</v>
       </c>
       <c r="L174" t="inlineStr"/>
       <c r="M174" s="14" t="inlineStr"/>
@@ -8314,39 +8314,39 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>5211</t>
+          <t>0391</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>SUNWAY</t>
+          <t>AMBEST</t>
         </is>
       </c>
       <c r="D175" s="9" t="n">
-        <v>4.45</v>
+        <v>1.34</v>
       </c>
       <c r="E175" s="16" t="n">
-        <v>0.0114</v>
+        <v>0.0308</v>
       </c>
       <c r="F175" s="11" t="n">
-        <v>745000</v>
+        <v>756600</v>
       </c>
       <c r="G175" s="12" t="n">
-        <v>0.13</v>
+        <v>0.3</v>
       </c>
       <c r="H175" t="n">
-        <v>44.36</v>
-      </c>
-      <c r="I175" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.86</v>
+      </c>
+      <c r="I175" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J175" s="9" t="n">
-        <v>4.475</v>
+        <v>1.341</v>
       </c>
       <c r="K175" s="9" t="n">
-        <v>4.774</v>
+        <v>1.265</v>
       </c>
       <c r="L175" t="inlineStr"/>
       <c r="M175" s="14" t="inlineStr"/>
@@ -8359,28 +8359,28 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>5053</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>DAYANG</t>
+          <t>OSK</t>
         </is>
       </c>
       <c r="D176" s="9" t="n">
-        <v>1.37</v>
+        <v>1.69</v>
       </c>
       <c r="E176" s="16" t="n">
-        <v>0.0074</v>
+        <v>0.0181</v>
       </c>
       <c r="F176" s="11" t="n">
-        <v>721600</v>
+        <v>749500</v>
       </c>
       <c r="G176" s="12" t="n">
-        <v>0.32</v>
+        <v>0.5</v>
       </c>
       <c r="H176" t="n">
-        <v>33.89</v>
+        <v>36.53</v>
       </c>
       <c r="I176" s="13" t="inlineStr">
         <is>
@@ -8388,10 +8388,10 @@
         </is>
       </c>
       <c r="J176" s="9" t="n">
-        <v>1.431</v>
+        <v>1.756</v>
       </c>
       <c r="K176" s="9" t="n">
-        <v>1.481</v>
+        <v>1.902</v>
       </c>
       <c r="L176" t="inlineStr"/>
       <c r="M176" s="14" t="inlineStr"/>
@@ -8404,39 +8404,39 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>6947</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>SEG</t>
+          <t>CDB</t>
         </is>
       </c>
       <c r="D177" s="9" t="n">
-        <v>0.625</v>
+        <v>2.52</v>
       </c>
       <c r="E177" s="10" t="n">
-        <v>-0.007900000000000001</v>
+        <v>-0.004</v>
       </c>
       <c r="F177" s="11" t="n">
-        <v>718500</v>
+        <v>743300</v>
       </c>
       <c r="G177" s="12" t="n">
-        <v>0.6</v>
+        <v>0.23</v>
       </c>
       <c r="H177" t="n">
-        <v>36.25</v>
-      </c>
-      <c r="I177" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>38.57</v>
+      </c>
+      <c r="I177" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J177" s="9" t="n">
-        <v>0.631</v>
+        <v>2.568</v>
       </c>
       <c r="K177" s="9" t="n">
-        <v>0.63</v>
+        <v>2.708</v>
       </c>
       <c r="L177" t="inlineStr"/>
       <c r="M177" s="14" t="inlineStr"/>
@@ -8449,39 +8449,39 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>6947</t>
+          <t>5141</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>CDB</t>
+          <t>DAYANG</t>
         </is>
       </c>
       <c r="D178" s="9" t="n">
-        <v>2.53</v>
+        <v>1.36</v>
       </c>
       <c r="E178" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F178" s="11" t="n">
-        <v>707000</v>
+        <v>726600</v>
       </c>
       <c r="G178" s="12" t="n">
-        <v>0.22</v>
+        <v>0.33</v>
       </c>
       <c r="H178" t="n">
-        <v>39.69</v>
-      </c>
-      <c r="I178" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>31.14</v>
+      </c>
+      <c r="I178" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J178" s="9" t="n">
-        <v>2.569</v>
+        <v>1.43</v>
       </c>
       <c r="K178" s="9" t="n">
-        <v>2.708</v>
+        <v>1.481</v>
       </c>
       <c r="L178" t="inlineStr"/>
       <c r="M178" s="14" t="inlineStr"/>
@@ -8494,39 +8494,39 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>5331</t>
+          <t>9792</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>PGLOBAL</t>
+          <t>SEG</t>
         </is>
       </c>
       <c r="D179" s="9" t="n">
-        <v>0.605</v>
+        <v>0.625</v>
       </c>
       <c r="E179" s="10" t="n">
-        <v>-0.032</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="F179" s="11" t="n">
-        <v>682700</v>
+        <v>718500</v>
       </c>
       <c r="G179" s="12" t="n">
-        <v>0.88</v>
+        <v>0.6</v>
       </c>
       <c r="H179" t="n">
-        <v>69.01000000000001</v>
-      </c>
-      <c r="I179" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.25</v>
+      </c>
+      <c r="I179" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J179" s="9" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.631</v>
       </c>
       <c r="K179" s="9" t="n">
-        <v>0.52</v>
+        <v>0.63</v>
       </c>
       <c r="L179" t="inlineStr"/>
       <c r="M179" s="14" t="inlineStr"/>
@@ -8539,39 +8539,39 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>5280</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>SUNREIT</t>
+          <t>KIPREIT</t>
         </is>
       </c>
       <c r="D180" s="9" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="E180" s="16" t="n">
-        <v>0.01</v>
+        <v>0.865</v>
+      </c>
+      <c r="E180" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F180" s="11" t="n">
-        <v>628500</v>
+        <v>685300</v>
       </c>
       <c r="G180" s="12" t="n">
-        <v>0.19</v>
+        <v>1</v>
       </c>
       <c r="H180" t="n">
-        <v>45.39</v>
-      </c>
-      <c r="I180" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.23</v>
+      </c>
+      <c r="I180" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J180" s="9" t="n">
-        <v>2.05</v>
+        <v>0.859</v>
       </c>
       <c r="K180" s="9" t="n">
-        <v>2.077</v>
+        <v>0.852</v>
       </c>
       <c r="L180" t="inlineStr"/>
       <c r="M180" s="14" t="inlineStr"/>
@@ -8584,39 +8584,39 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>7174</t>
+          <t>5331</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>CAB</t>
+          <t>PGLOBAL</t>
         </is>
       </c>
       <c r="D181" s="9" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="E181" s="15" t="n">
-        <v>0</v>
+        <v>0.61</v>
+      </c>
+      <c r="E181" s="10" t="n">
+        <v>-0.024</v>
       </c>
       <c r="F181" s="11" t="n">
-        <v>613400</v>
+        <v>682900</v>
       </c>
       <c r="G181" s="12" t="n">
-        <v>0.47</v>
+        <v>0.88</v>
       </c>
       <c r="H181" t="n">
-        <v>57.19</v>
-      </c>
-      <c r="I181" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>71.29000000000001</v>
+      </c>
+      <c r="I181" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J181" s="9" t="n">
-        <v>0.582</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="K181" s="9" t="n">
-        <v>0.545</v>
+        <v>0.52</v>
       </c>
       <c r="L181" t="inlineStr"/>
       <c r="M181" s="14" t="inlineStr"/>
@@ -8629,39 +8629,39 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>0271</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>WELLS</t>
+          <t>SUNREIT</t>
         </is>
       </c>
       <c r="D182" s="9" t="n">
-        <v>0.535</v>
-      </c>
-      <c r="E182" s="10" t="n">
-        <v>-0.0183</v>
+        <v>2.03</v>
+      </c>
+      <c r="E182" s="16" t="n">
+        <v>0.01</v>
       </c>
       <c r="F182" s="11" t="n">
-        <v>607700</v>
+        <v>630700</v>
       </c>
       <c r="G182" s="12" t="n">
-        <v>0.55</v>
+        <v>0.19</v>
       </c>
       <c r="H182" t="n">
-        <v>33.07</v>
-      </c>
-      <c r="I182" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.39</v>
+      </c>
+      <c r="I182" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J182" s="9" t="n">
-        <v>0.573</v>
+        <v>2.05</v>
       </c>
       <c r="K182" s="9" t="n">
-        <v>0.616</v>
+        <v>2.077</v>
       </c>
       <c r="L182" t="inlineStr"/>
       <c r="M182" s="14" t="inlineStr"/>
@@ -8683,19 +8683,19 @@
         </is>
       </c>
       <c r="D183" s="9" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="E183" s="10" t="n">
-        <v>-0.0032</v>
+        <v>3.08</v>
+      </c>
+      <c r="E183" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F183" s="11" t="n">
-        <v>607100</v>
+        <v>616400</v>
       </c>
       <c r="G183" s="12" t="n">
         <v>0.14</v>
       </c>
       <c r="H183" t="n">
-        <v>38.11</v>
+        <v>38.74</v>
       </c>
       <c r="I183" s="13" t="inlineStr">
         <is>
@@ -8703,7 +8703,7 @@
         </is>
       </c>
       <c r="J183" s="9" t="n">
-        <v>3.17</v>
+        <v>3.171</v>
       </c>
       <c r="K183" s="9" t="n">
         <v>3.359</v>
@@ -8719,39 +8719,39 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>5916</t>
+          <t>7174</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>MSC</t>
+          <t>CAB</t>
         </is>
       </c>
       <c r="D184" s="9" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="E184" s="16" t="n">
-        <v>0.0245</v>
+        <v>0.59</v>
+      </c>
+      <c r="E184" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F184" s="11" t="n">
-        <v>605100</v>
+        <v>613400</v>
       </c>
       <c r="G184" s="12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.47</v>
       </c>
       <c r="H184" t="n">
-        <v>47.49</v>
-      </c>
-      <c r="I184" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>57.19</v>
+      </c>
+      <c r="I184" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J184" s="9" t="n">
-        <v>1.672</v>
+        <v>0.582</v>
       </c>
       <c r="K184" s="9" t="n">
-        <v>1.798</v>
+        <v>0.545</v>
       </c>
       <c r="L184" t="inlineStr"/>
       <c r="M184" s="14" t="inlineStr"/>
@@ -8764,39 +8764,39 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>3794</t>
+          <t>0271</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>MCEMENT</t>
+          <t>WELLS</t>
         </is>
       </c>
       <c r="D185" s="9" t="n">
-        <v>5.4</v>
+        <v>0.535</v>
       </c>
       <c r="E185" s="10" t="n">
-        <v>-0.005500000000000001</v>
+        <v>-0.0183</v>
       </c>
       <c r="F185" s="11" t="n">
-        <v>587900</v>
+        <v>607700</v>
       </c>
       <c r="G185" s="12" t="n">
-        <v>0.43</v>
+        <v>0.55</v>
       </c>
       <c r="H185" t="n">
-        <v>38.35</v>
-      </c>
-      <c r="I185" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>33.07</v>
+      </c>
+      <c r="I185" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J185" s="9" t="n">
-        <v>5.559</v>
+        <v>0.573</v>
       </c>
       <c r="K185" s="9" t="n">
-        <v>5.891</v>
+        <v>0.616</v>
       </c>
       <c r="L185" t="inlineStr"/>
       <c r="M185" s="14" t="inlineStr"/>
@@ -8809,39 +8809,39 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>5916</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>MSC</t>
         </is>
       </c>
       <c r="D186" s="9" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E186" s="10" t="n">
-        <v>-0.0234</v>
+        <v>1.67</v>
+      </c>
+      <c r="E186" s="16" t="n">
+        <v>0.0245</v>
       </c>
       <c r="F186" s="11" t="n">
-        <v>575300</v>
+        <v>607300</v>
       </c>
       <c r="G186" s="12" t="n">
-        <v>0.22</v>
+        <v>0.57</v>
       </c>
       <c r="H186" t="n">
-        <v>46.09</v>
-      </c>
-      <c r="I186" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.49</v>
+      </c>
+      <c r="I186" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J186" s="9" t="n">
-        <v>0.637</v>
+        <v>1.672</v>
       </c>
       <c r="K186" s="9" t="n">
-        <v>0.617</v>
+        <v>1.798</v>
       </c>
       <c r="L186" t="inlineStr"/>
       <c r="M186" s="14" t="inlineStr"/>
@@ -8854,39 +8854,39 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>7293</t>
+          <t>0351</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>YINSON</t>
+          <t>LSH</t>
         </is>
       </c>
       <c r="D187" s="9" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="E187" s="16" t="n">
-        <v>0.004699999999999999</v>
+        <v>1.59</v>
+      </c>
+      <c r="E187" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F187" s="11" t="n">
-        <v>572900</v>
+        <v>597900</v>
       </c>
       <c r="G187" s="12" t="n">
-        <v>0.24</v>
+        <v>0.78</v>
       </c>
       <c r="H187" t="n">
-        <v>58.6</v>
-      </c>
-      <c r="I187" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.64</v>
+      </c>
+      <c r="I187" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J187" s="9" t="n">
-        <v>2.104</v>
+        <v>1.643</v>
       </c>
       <c r="K187" s="9" t="n">
-        <v>2.051</v>
+        <v>1.614</v>
       </c>
       <c r="L187" t="inlineStr"/>
       <c r="M187" s="14" t="inlineStr"/>
@@ -8899,28 +8899,28 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>0351</t>
+          <t>3794</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>LSH</t>
+          <t>MCEMENT</t>
         </is>
       </c>
       <c r="D188" s="9" t="n">
-        <v>1.57</v>
+        <v>5.38</v>
       </c>
       <c r="E188" s="10" t="n">
-        <v>-0.0126</v>
+        <v>-0.0092</v>
       </c>
       <c r="F188" s="11" t="n">
-        <v>567500</v>
+        <v>593000</v>
       </c>
       <c r="G188" s="12" t="n">
-        <v>0.74</v>
+        <v>0.43</v>
       </c>
       <c r="H188" t="n">
-        <v>41.55</v>
+        <v>37.59</v>
       </c>
       <c r="I188" s="13" t="inlineStr">
         <is>
@@ -8928,10 +8928,10 @@
         </is>
       </c>
       <c r="J188" s="9" t="n">
-        <v>1.641</v>
+        <v>5.557</v>
       </c>
       <c r="K188" s="9" t="n">
-        <v>1.613</v>
+        <v>5.891</v>
       </c>
       <c r="L188" t="inlineStr"/>
       <c r="M188" s="14" t="inlineStr"/>
@@ -8944,39 +8944,39 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>5306</t>
+          <t>7293</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>FFB</t>
+          <t>YINSON</t>
         </is>
       </c>
       <c r="D189" s="9" t="n">
-        <v>1.77</v>
+        <v>2.15</v>
       </c>
       <c r="E189" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F189" s="11" t="n">
-        <v>540900</v>
+        <v>588100</v>
       </c>
       <c r="G189" s="12" t="n">
-        <v>0.17</v>
+        <v>0.25</v>
       </c>
       <c r="H189" t="n">
-        <v>31.71</v>
-      </c>
-      <c r="I189" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.62</v>
+      </c>
+      <c r="I189" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J189" s="9" t="n">
-        <v>1.853</v>
+        <v>2.103</v>
       </c>
       <c r="K189" s="9" t="n">
-        <v>1.99</v>
+        <v>2.051</v>
       </c>
       <c r="L189" t="inlineStr"/>
       <c r="M189" s="14" t="inlineStr"/>
@@ -8989,39 +8989,39 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>0249</t>
+          <t>5162</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>LGMS</t>
+          <t>VSTECS</t>
         </is>
       </c>
       <c r="D190" s="9" t="n">
-        <v>0.535</v>
+        <v>1.58</v>
       </c>
       <c r="E190" s="10" t="n">
-        <v>-0.009300000000000001</v>
+        <v>-0.0125</v>
       </c>
       <c r="F190" s="11" t="n">
-        <v>536700</v>
+        <v>579600</v>
       </c>
       <c r="G190" s="12" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="H190" t="n">
-        <v>55.22</v>
-      </c>
-      <c r="I190" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.48</v>
+      </c>
+      <c r="I190" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J190" s="9" t="n">
-        <v>0.528</v>
+        <v>1.651</v>
       </c>
       <c r="K190" s="9" t="n">
-        <v>0.506</v>
+        <v>1.673</v>
       </c>
       <c r="L190" t="inlineStr"/>
       <c r="M190" s="14" t="inlineStr"/>
@@ -9034,28 +9034,28 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>5162</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>VSTECS</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D191" s="9" t="n">
-        <v>1.58</v>
+        <v>0.625</v>
       </c>
       <c r="E191" s="10" t="n">
-        <v>-0.0125</v>
+        <v>-0.0234</v>
       </c>
       <c r="F191" s="11" t="n">
-        <v>529800</v>
+        <v>575300</v>
       </c>
       <c r="G191" s="12" t="n">
-        <v>0.3</v>
+        <v>0.22</v>
       </c>
       <c r="H191" t="n">
-        <v>42.48</v>
+        <v>46.09</v>
       </c>
       <c r="I191" s="13" t="inlineStr">
         <is>
@@ -9063,10 +9063,10 @@
         </is>
       </c>
       <c r="J191" s="9" t="n">
-        <v>1.651</v>
+        <v>0.637</v>
       </c>
       <c r="K191" s="9" t="n">
-        <v>1.673</v>
+        <v>0.617</v>
       </c>
       <c r="L191" t="inlineStr"/>
       <c r="M191" s="14" t="inlineStr"/>
@@ -9079,28 +9079,28 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>5306</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>FFB</t>
         </is>
       </c>
       <c r="D192" s="9" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="E192" s="10" t="n">
-        <v>-0.0289</v>
+        <v>1.77</v>
+      </c>
+      <c r="E192" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F192" s="11" t="n">
-        <v>518100</v>
+        <v>543200</v>
       </c>
       <c r="G192" s="12" t="n">
-        <v>0.24</v>
+        <v>0.17</v>
       </c>
       <c r="H192" t="n">
-        <v>18.75</v>
+        <v>31.71</v>
       </c>
       <c r="I192" s="13" t="inlineStr">
         <is>
@@ -9108,10 +9108,10 @@
         </is>
       </c>
       <c r="J192" s="9" t="n">
-        <v>0.987</v>
+        <v>1.853</v>
       </c>
       <c r="K192" s="9" t="n">
-        <v>1.099</v>
+        <v>1.99</v>
       </c>
       <c r="L192" t="inlineStr"/>
       <c r="M192" s="14" t="inlineStr"/>
@@ -9124,28 +9124,28 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2488</t>
+          <t>9466</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>ABMB</t>
+          <t>KKB</t>
         </is>
       </c>
       <c r="D193" s="9" t="n">
-        <v>4.61</v>
+        <v>1.39</v>
       </c>
       <c r="E193" s="16" t="n">
-        <v>0.011</v>
+        <v>0.0692</v>
       </c>
       <c r="F193" s="11" t="n">
-        <v>500200</v>
+        <v>538600</v>
       </c>
       <c r="G193" s="12" t="n">
-        <v>0.46</v>
+        <v>3.05</v>
       </c>
       <c r="H193" t="n">
-        <v>39.48</v>
+        <v>78.02</v>
       </c>
       <c r="I193" s="17" t="inlineStr">
         <is>
@@ -9153,16 +9153,196 @@
         </is>
       </c>
       <c r="J193" s="9" t="n">
-        <v>4.676</v>
+        <v>1.217</v>
       </c>
       <c r="K193" s="9" t="n">
-        <v>4.796</v>
+        <v>1.121</v>
       </c>
       <c r="L193" t="inlineStr"/>
       <c r="M193" s="14" t="inlineStr"/>
     </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>0249</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>LGMS</t>
+        </is>
+      </c>
+      <c r="D194" s="9" t="n">
+        <v>0.535</v>
+      </c>
+      <c r="E194" s="10" t="n">
+        <v>-0.009300000000000001</v>
+      </c>
+      <c r="F194" s="11" t="n">
+        <v>538300</v>
+      </c>
+      <c r="G194" s="12" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="H194" t="n">
+        <v>55.22</v>
+      </c>
+      <c r="I194" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J194" s="9" t="n">
+        <v>0.528</v>
+      </c>
+      <c r="K194" s="9" t="n">
+        <v>0.506</v>
+      </c>
+      <c r="L194" t="inlineStr"/>
+      <c r="M194" s="14" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>7081</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>PHARMA</t>
+        </is>
+      </c>
+      <c r="D195" s="9" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="E195" s="10" t="n">
+        <v>-0.0289</v>
+      </c>
+      <c r="F195" s="11" t="n">
+        <v>530400</v>
+      </c>
+      <c r="G195" s="12" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H195" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="I195" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J195" s="9" t="n">
+        <v>0.987</v>
+      </c>
+      <c r="K195" s="9" t="n">
+        <v>1.099</v>
+      </c>
+      <c r="L195" t="inlineStr"/>
+      <c r="M195" s="14" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>4243</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>WTK</t>
+        </is>
+      </c>
+      <c r="D196" s="9" t="n">
+        <v>0.885</v>
+      </c>
+      <c r="E196" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F196" s="11" t="n">
+        <v>508400</v>
+      </c>
+      <c r="G196" s="12" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H196" t="n">
+        <v>34.24</v>
+      </c>
+      <c r="I196" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J196" s="9" t="n">
+        <v>0.946</v>
+      </c>
+      <c r="K196" s="9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="L196" t="inlineStr"/>
+      <c r="M196" s="14" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>2488</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>ABMB</t>
+        </is>
+      </c>
+      <c r="D197" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="E197" s="16" t="n">
+        <v>0.008800000000000001</v>
+      </c>
+      <c r="F197" s="11" t="n">
+        <v>500400</v>
+      </c>
+      <c r="G197" s="12" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="H197" t="n">
+        <v>38.23</v>
+      </c>
+      <c r="I197" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J197" s="9" t="n">
+        <v>4.675</v>
+      </c>
+      <c r="K197" s="9" t="n">
+        <v>4.796</v>
+      </c>
+      <c r="L197" t="inlineStr"/>
+      <c r="M197" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M193"/>
+  <autoFilter ref="A1:M197"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>